--- a/data/extracted/series/corpus_publication_cadence_and_audit.xlsx
+++ b/data/extracted/series/corpus_publication_cadence_and_audit.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Corpus Cadence &amp; Inventory" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Graphic &amp; Chart Extraction" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sub-Sector &amp; Fleet Breakdown" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Corpus Cadence &amp; Inventory" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Graphic &amp; Chart Extraction" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Sub-Sector &amp; Fleet Breakdown" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -967,7 +967,7 @@
       </c>
       <c r="S5" s="3" t="inlineStr">
         <is>
-          <t>bancosta_freight_rates_series.csv (20,587 rows), bancosta_ffa_series.csv (7,726 rows), bancosta_sales_series.csv (3,220 rows), bancosta_commodities_series.csv (8,555 rows), bancosta_newbuilding_series.csv (2,377 rows), bancosta_secondhand_matrix_series.csv (1,898 rows), bancosta_demolition_series.csv (959 rows)</t>
+          <t>bancosta_freight_rates_series.csv (20,587 rows), bancosta_ffa_series.csv (7,726 rows), bancosta_sales_series.csv (3,244 rows), bancosta_commodities_series.csv (8,555 rows), bancosta_newbuilding_series.csv (2,377 rows), bancosta_secondhand_matrix_series.csv (1,898 rows), bancosta_demolition_series.csv (959 rows)</t>
         </is>
       </c>
       <c r="T5" s="3" t="inlineStr">
@@ -1484,22 +1484,22 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="I11" s="2" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="J11" s="4" t="inlineStr">
         <is>
-          <t>CURRENT (11d ago)</t>
+          <t>CURRENT (4d ago)</t>
         </is>
       </c>
       <c r="K11" s="2" t="n">
         <v>109</v>
       </c>
       <c r="L11" s="2" t="n">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="M11" s="2" t="n">
         <v>0</v>
@@ -1508,10 +1508,10 @@
         <v>0</v>
       </c>
       <c r="O11" s="2" t="n">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="P11" s="3" t="n">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="Q11" s="3" t="inlineStr">
         <is>
@@ -1525,7 +1525,7 @@
       </c>
       <c r="S11" s="3" t="inlineStr">
         <is>
-          <t>gibson_tanker_spot_series.csv (3,583 rows), gibson_bunker_prices_series.csv (1,011 rows), gibson_master_tanker_series.xlsx</t>
+          <t>gibson_tanker_spot_series.csv (3,602 rows), gibson_bunker_prices_series.csv (1,015 rows), gibson_master_tanker_series.xlsx</t>
         </is>
       </c>
       <c r="T11" s="3" t="inlineStr">
@@ -2345,7 +2345,7 @@
         <v>0</v>
       </c>
       <c r="O20" s="2" t="n">
-        <v>1193</v>
+        <v>1192</v>
       </c>
       <c r="P20" s="3" t="n">
         <v>9057</v>
@@ -3344,15 +3344,15 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="I31" s="2" t="n">
-        <v>35</v>
+        <v>70</v>
       </c>
       <c r="J31" s="5" t="inlineStr">
         <is>
-          <t>NORMAL INTERVAL (35d ago)</t>
+          <t>NORMAL INTERVAL (70d ago)</t>
         </is>
       </c>
       <c r="K31" s="2" t="n">
@@ -5517,7 +5517,7 @@
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>3,220 rows</t>
+          <t>3,244 rows</t>
         </is>
       </c>
       <c r="H34" s="3" t="inlineStr">

--- a/data/extracted/series/corpus_publication_cadence_and_audit.xlsx
+++ b/data/extracted/series/corpus_publication_cadence_and_audit.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Corpus Cadence &amp; Inventory" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Graphic &amp; Chart Extraction" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Sub-Sector &amp; Fleet Breakdown" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Corpus Cadence &amp; Inventory" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Graphic &amp; Chart Extraction" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sub-Sector &amp; Fleet Breakdown" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -2159,7 +2159,7 @@
         <v>0</v>
       </c>
       <c r="O18" s="2" t="n">
-        <v>1638</v>
+        <v>1791</v>
       </c>
       <c r="P18" s="3" t="n">
         <v>4162</v>
@@ -2345,7 +2345,7 @@
         <v>0</v>
       </c>
       <c r="O20" s="2" t="n">
-        <v>1192</v>
+        <v>1193</v>
       </c>
       <c r="P20" s="3" t="n">
         <v>9057</v>
@@ -2641,7 +2641,7 @@
       </c>
       <c r="S23" s="3" t="inlineStr">
         <is>
-          <t>hellenic_vv_matrix_series.csv (12,350 rows), hellenic_vv_sales_series.csv (2,062 rows)</t>
+          <t>hellenic_vv_matrix_series.csv (12,350 rows), hellenic_vv_sales_series.csv (2,022 rows)</t>
         </is>
       </c>
       <c r="T23" s="3" t="inlineStr">
@@ -5094,7 +5094,7 @@
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>2,062 rows</t>
+          <t>2,022 rows</t>
         </is>
       </c>
       <c r="H25" s="3" t="inlineStr">

--- a/data/extracted/series/corpus_publication_cadence_and_audit.xlsx
+++ b/data/extracted/series/corpus_publication_cadence_and_audit.xlsx
@@ -2159,7 +2159,7 @@
         <v>0</v>
       </c>
       <c r="O18" s="2" t="n">
-        <v>1791</v>
+        <v>1641</v>
       </c>
       <c r="P18" s="3" t="n">
         <v>4162</v>
@@ -2641,7 +2641,7 @@
       </c>
       <c r="S23" s="3" t="inlineStr">
         <is>
-          <t>hellenic_vv_matrix_series.csv (12,350 rows), hellenic_vv_sales_series.csv (2,022 rows)</t>
+          <t>hellenic_vv_matrix_series.csv (12,350 rows), hellenic_vv_sales_series.csv (2,062 rows)</t>
         </is>
       </c>
       <c r="T23" s="3" t="inlineStr">
@@ -3344,15 +3344,15 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="I31" s="2" t="n">
-        <v>70</v>
+        <v>35</v>
       </c>
       <c r="J31" s="5" t="inlineStr">
         <is>
-          <t>NORMAL INTERVAL (70d ago)</t>
+          <t>NORMAL INTERVAL (35d ago)</t>
         </is>
       </c>
       <c r="K31" s="2" t="n">
@@ -5094,7 +5094,7 @@
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>2,022 rows</t>
+          <t>2,062 rows</t>
         </is>
       </c>
       <c r="H25" s="3" t="inlineStr">

--- a/data/extracted/series/corpus_publication_cadence_and_audit.xlsx
+++ b/data/extracted/series/corpus_publication_cadence_and_audit.xlsx
@@ -2159,7 +2159,7 @@
         <v>0</v>
       </c>
       <c r="O18" s="2" t="n">
-        <v>1641</v>
+        <v>1791</v>
       </c>
       <c r="P18" s="3" t="n">
         <v>4162</v>
@@ -2641,7 +2641,7 @@
       </c>
       <c r="S23" s="3" t="inlineStr">
         <is>
-          <t>hellenic_vv_matrix_series.csv (12,350 rows), hellenic_vv_sales_series.csv (2,062 rows)</t>
+          <t>hellenic_vv_matrix_series.csv (12,350 rows), hellenic_vv_sales_series.csv (2,022 rows)</t>
         </is>
       </c>
       <c r="T23" s="3" t="inlineStr">
@@ -3344,15 +3344,15 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="I31" s="2" t="n">
-        <v>35</v>
+        <v>70</v>
       </c>
       <c r="J31" s="5" t="inlineStr">
         <is>
-          <t>NORMAL INTERVAL (35d ago)</t>
+          <t>NORMAL INTERVAL (70d ago)</t>
         </is>
       </c>
       <c r="K31" s="2" t="n">
@@ -5094,7 +5094,7 @@
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>2,062 rows</t>
+          <t>2,022 rows</t>
         </is>
       </c>
       <c r="H25" s="3" t="inlineStr">

--- a/data/extracted/series/corpus_publication_cadence_and_audit.xlsx
+++ b/data/extracted/series/corpus_publication_cadence_and_audit.xlsx
@@ -2159,7 +2159,7 @@
         <v>0</v>
       </c>
       <c r="O18" s="2" t="n">
-        <v>1791</v>
+        <v>1641</v>
       </c>
       <c r="P18" s="3" t="n">
         <v>4162</v>
@@ -2641,7 +2641,7 @@
       </c>
       <c r="S23" s="3" t="inlineStr">
         <is>
-          <t>hellenic_vv_matrix_series.csv (12,350 rows), hellenic_vv_sales_series.csv (2,022 rows)</t>
+          <t>hellenic_vv_matrix_series.csv (12,350 rows), hellenic_vv_sales_series.csv (2,062 rows)</t>
         </is>
       </c>
       <c r="T23" s="3" t="inlineStr">
@@ -5094,7 +5094,7 @@
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>2,022 rows</t>
+          <t>2,062 rows</t>
         </is>
       </c>
       <c r="H25" s="3" t="inlineStr">

--- a/data/extracted/series/corpus_publication_cadence_and_audit.xlsx
+++ b/data/extracted/series/corpus_publication_cadence_and_audit.xlsx
@@ -2693,34 +2693,34 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="I24" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J24" s="4" t="inlineStr">
         <is>
-          <t>CURRENT (1d ago)</t>
+          <t>CURRENT (0d ago)</t>
         </is>
       </c>
       <c r="K24" s="2" t="n">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="L24" s="2" t="n">
-        <v>3242</v>
+        <v>3243</v>
       </c>
       <c r="M24" s="2" t="n">
-        <v>15092</v>
+        <v>15095</v>
       </c>
       <c r="N24" s="2" t="n">
-        <v>3213</v>
+        <v>3214</v>
       </c>
       <c r="O24" s="2" t="n">
-        <v>3504</v>
+        <v>3506</v>
       </c>
       <c r="P24" s="3" t="n">
-        <v>21851</v>
+        <v>21857</v>
       </c>
       <c r="Q24" s="3" t="inlineStr">
         <is>
@@ -2734,7 +2734,7 @@
       </c>
       <c r="S24" s="3" t="inlineStr">
         <is>
-          <t>breakwave_fundamentals_series.csv (2,745 rows), breakwave_insights_metadata.csv (3,213 rows)</t>
+          <t>breakwave_fundamentals_series.csv (2,755 rows), breakwave_insights_metadata.csv (3,214 rows)</t>
         </is>
       </c>
       <c r="T24" s="3" t="inlineStr">
@@ -3292,7 +3292,7 @@
       </c>
       <c r="S30" s="3" t="inlineStr">
         <is>
-          <t>baltic_reports_metadata.csv (2,228 rows), baltic_ncfi_series.csv (2,036 rows)</t>
+          <t>baltic_reports_metadata.csv (2,228 rows), baltic_ncfi_series.csv (2,041 rows)</t>
         </is>
       </c>
       <c r="T30" s="3" t="inlineStr">

--- a/data/extracted/series/corpus_publication_cadence_and_audit.xlsx
+++ b/data/extracted/series/corpus_publication_cadence_and_audit.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Corpus Cadence &amp; Inventory" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Graphic &amp; Chart Extraction" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sub-Sector &amp; Fleet Breakdown" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Corpus Cadence &amp; Inventory" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Graphic &amp; Chart Extraction" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Sub-Sector &amp; Fleet Breakdown" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -926,19 +926,19 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="I5" s="2" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="J5" s="4" t="inlineStr">
         <is>
-          <t>CURRENT (6d ago)</t>
+          <t>CURRENT (0d ago)</t>
         </is>
       </c>
       <c r="K5" s="2" t="n">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="L5" s="2" t="n">
         <v>0</v>
@@ -950,11 +950,11 @@
         <v>0</v>
       </c>
       <c r="O5" s="2" t="n">
+        <v>251</v>
+      </c>
+      <c r="P5" s="3" t="n">
         <v>249</v>
       </c>
-      <c r="P5" s="3" t="n">
-        <v>248</v>
-      </c>
       <c r="Q5" s="3" t="inlineStr">
         <is>
           <t>Yes (Freight rates, FFA forward curves, ConTex index)</t>
@@ -967,7 +967,7 @@
       </c>
       <c r="S5" s="3" t="inlineStr">
         <is>
-          <t>bancosta_freight_rates_series.csv (20,587 rows), bancosta_ffa_series.csv (7,726 rows), bancosta_sales_series.csv (3,244 rows), bancosta_commodities_series.csv (8,555 rows), bancosta_newbuilding_series.csv (2,377 rows), bancosta_secondhand_matrix_series.csv (1,898 rows), bancosta_demolition_series.csv (959 rows)</t>
+          <t>bancosta_freight_rates_series.csv (20,677 rows), bancosta_ffa_series.csv (7,762 rows), bancosta_sales_series.csv (3,264 rows), bancosta_commodities_series.csv (8,582 rows), bancosta_newbuilding_series.csv (2,377 rows), bancosta_secondhand_matrix_series.csv (1,898 rows), bancosta_demolition_series.csv (959 rows)</t>
         </is>
       </c>
       <c r="T5" s="3" t="inlineStr">
@@ -1577,19 +1577,19 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="I12" s="2" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="J12" s="4" t="inlineStr">
         <is>
-          <t>CURRENT (6d ago)</t>
+          <t>CURRENT (0d ago)</t>
         </is>
       </c>
       <c r="K12" s="2" t="n">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="L12" s="2" t="n">
         <v>0</v>
@@ -1601,10 +1601,10 @@
         <v>0</v>
       </c>
       <c r="O12" s="2" t="n">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="P12" s="3" t="n">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="Q12" s="3" t="inlineStr">
         <is>
@@ -1856,19 +1856,19 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="I15" s="2" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="J15" s="4" t="inlineStr">
         <is>
-          <t>CURRENT (8d ago)</t>
+          <t>CURRENT (1d ago)</t>
         </is>
       </c>
       <c r="K15" s="2" t="n">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="L15" s="2" t="n">
         <v>0</v>
@@ -1883,7 +1883,7 @@
         <v>531</v>
       </c>
       <c r="P15" s="3" t="n">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="Q15" s="3" t="inlineStr">
         <is>
@@ -1897,7 +1897,7 @@
       </c>
       <c r="S15" s="3" t="inlineStr">
         <is>
-          <t>ssy_capesize_index_series.csv (8,729 rows), ssy_capesize_series.csv (8,881 rows), ssy_route_rates_series.csv (5,160 rows), ssy_capesize_index_time_series.csv (516 rows)</t>
+          <t>ssy_capesize_index_series.csv (8,729 rows), ssy_capesize_series.csv (8,881 rows), ssy_route_rates_series.csv (5,170 rows), ssy_capesize_index_time_series.csv (517 rows)</t>
         </is>
       </c>
       <c r="T15" s="3" t="inlineStr">
@@ -2042,19 +2042,19 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="I17" s="2" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="J17" s="4" t="inlineStr">
         <is>
-          <t>CURRENT (7d ago)</t>
+          <t>CURRENT (0d ago)</t>
         </is>
       </c>
       <c r="K17" s="2" t="n">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="L17" s="2" t="n">
         <v>0</v>
@@ -2066,10 +2066,10 @@
         <v>0</v>
       </c>
       <c r="O17" s="2" t="n">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="P17" s="3" t="n">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="Q17" s="3" t="inlineStr">
         <is>
@@ -2083,7 +2083,7 @@
       </c>
       <c r="S17" s="3" t="inlineStr">
         <is>
-          <t>xclusiv_secondhand_series.csv (8,529 rows), xclusiv_sales_series.csv (5,542 rows), xclusiv_demolition_series.csv (2,082 rows), xclusiv_newbuilding_prices_series.csv (1,379 rows), xclusiv_newbuilding_orders_series.csv (1,313 rows)</t>
+          <t>xclusiv_secondhand_series.csv (8,561 rows), xclusiv_sales_series.csv (5,565 rows), xclusiv_demolition_series.csv (2,090 rows), xclusiv_newbuilding_prices_series.csv (1,379 rows), xclusiv_newbuilding_orders_series.csv (1,313 rows)</t>
         </is>
       </c>
       <c r="T17" s="3" t="inlineStr">
@@ -5423,7 +5423,7 @@
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>5,542 rows</t>
+          <t>5,565 rows</t>
         </is>
       </c>
       <c r="H32" s="3" t="inlineStr">
@@ -5517,7 +5517,7 @@
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>3,244 rows</t>
+          <t>3,264 rows</t>
         </is>
       </c>
       <c r="H34" s="3" t="inlineStr">

--- a/data/extracted/series/corpus_publication_cadence_and_audit.xlsx
+++ b/data/extracted/series/corpus_publication_cadence_and_audit.xlsx
@@ -550,7 +550,7 @@
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>Status (2026-10-06)</t>
+          <t>Status (2026-10-07)</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
@@ -651,11 +651,11 @@
         </is>
       </c>
       <c r="I2" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J2" s="4" t="inlineStr">
         <is>
-          <t>CURRENT (3d ago)</t>
+          <t>CURRENT (4d ago)</t>
         </is>
       </c>
       <c r="K2" s="2" t="n">
@@ -744,11 +744,11 @@
         </is>
       </c>
       <c r="I3" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J3" s="4" t="inlineStr">
         <is>
-          <t>CURRENT (3d ago)</t>
+          <t>CURRENT (4d ago)</t>
         </is>
       </c>
       <c r="K3" s="2" t="n">
@@ -837,11 +837,11 @@
         </is>
       </c>
       <c r="I4" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J4" s="4" t="inlineStr">
         <is>
-          <t>CURRENT (4d ago)</t>
+          <t>CURRENT (5d ago)</t>
         </is>
       </c>
       <c r="K4" s="2" t="n">
@@ -1023,11 +1023,11 @@
         </is>
       </c>
       <c r="I6" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J6" s="4" t="inlineStr">
         <is>
-          <t>CURRENT (8d ago)</t>
+          <t>CURRENT (9d ago)</t>
         </is>
       </c>
       <c r="K6" s="2" t="n">
@@ -1205,15 +1205,15 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="I8" s="2" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="J8" s="4" t="inlineStr">
         <is>
-          <t>CURRENT (4d ago)</t>
+          <t>CURRENT (0d ago)</t>
         </is>
       </c>
       <c r="K8" s="2" t="n">
@@ -1229,7 +1229,7 @@
         <v>4742</v>
       </c>
       <c r="O8" s="2" t="n">
-        <v>12000</v>
+        <v>12005</v>
       </c>
       <c r="P8" s="3" t="n">
         <v>5005</v>
@@ -1298,15 +1298,15 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="I9" s="2" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="J9" s="4" t="inlineStr">
         <is>
-          <t>CURRENT (4d ago)</t>
+          <t>CURRENT (0d ago)</t>
         </is>
       </c>
       <c r="K9" s="2" t="n">
@@ -1395,11 +1395,11 @@
         </is>
       </c>
       <c r="I10" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J10" s="4" t="inlineStr">
         <is>
-          <t>CURRENT (4d ago)</t>
+          <t>CURRENT (5d ago)</t>
         </is>
       </c>
       <c r="K10" s="2" t="n">
@@ -1488,11 +1488,11 @@
         </is>
       </c>
       <c r="I11" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J11" s="4" t="inlineStr">
         <is>
-          <t>CURRENT (4d ago)</t>
+          <t>CURRENT (5d ago)</t>
         </is>
       </c>
       <c r="K11" s="2" t="n">
@@ -1674,11 +1674,11 @@
         </is>
       </c>
       <c r="I13" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J13" s="4" t="inlineStr">
         <is>
-          <t>CURRENT (8d ago)</t>
+          <t>CURRENT (9d ago)</t>
         </is>
       </c>
       <c r="K13" s="2" t="n">
@@ -1860,11 +1860,11 @@
         </is>
       </c>
       <c r="I15" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J15" s="4" t="inlineStr">
         <is>
-          <t>CURRENT (1d ago)</t>
+          <t>CURRENT (2d ago)</t>
         </is>
       </c>
       <c r="K15" s="2" t="n">
@@ -1953,11 +1953,11 @@
         </is>
       </c>
       <c r="I16" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J16" s="4" t="inlineStr">
         <is>
-          <t>CURRENT (1d ago)</t>
+          <t>CURRENT (2d ago)</t>
         </is>
       </c>
       <c r="K16" s="2" t="n">
@@ -2046,11 +2046,11 @@
         </is>
       </c>
       <c r="I17" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J17" s="4" t="inlineStr">
         <is>
-          <t>CURRENT (0d ago)</t>
+          <t>CURRENT (1d ago)</t>
         </is>
       </c>
       <c r="K17" s="2" t="n">
@@ -2139,11 +2139,11 @@
         </is>
       </c>
       <c r="I18" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J18" s="4" t="inlineStr">
         <is>
-          <t>CURRENT (3d ago)</t>
+          <t>CURRENT (4d ago)</t>
         </is>
       </c>
       <c r="K18" s="2" t="n">
@@ -2232,11 +2232,11 @@
         </is>
       </c>
       <c r="I19" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J19" s="4" t="inlineStr">
         <is>
-          <t>CURRENT (6d ago)</t>
+          <t>CURRENT (7d ago)</t>
         </is>
       </c>
       <c r="K19" s="2" t="n">
@@ -2325,11 +2325,11 @@
         </is>
       </c>
       <c r="I20" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J20" s="4" t="inlineStr">
         <is>
-          <t>CURRENT (1d ago)</t>
+          <t>CURRENT (2d ago)</t>
         </is>
       </c>
       <c r="K20" s="2" t="n">
@@ -2418,11 +2418,11 @@
         </is>
       </c>
       <c r="I21" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="J21" s="4" t="inlineStr">
         <is>
-          <t>CURRENT (7d ago)</t>
+          <t>CURRENT (8d ago)</t>
         </is>
       </c>
       <c r="K21" s="2" t="n">
@@ -2511,11 +2511,11 @@
         </is>
       </c>
       <c r="I22" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J22" s="4" t="inlineStr">
         <is>
-          <t>CURRENT (6d ago)</t>
+          <t>CURRENT (7d ago)</t>
         </is>
       </c>
       <c r="K22" s="2" t="n">
@@ -2604,11 +2604,11 @@
         </is>
       </c>
       <c r="I23" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="J23" s="4" t="inlineStr">
         <is>
-          <t>CURRENT (7d ago)</t>
+          <t>CURRENT (8d ago)</t>
         </is>
       </c>
       <c r="K23" s="2" t="n">
@@ -2697,11 +2697,11 @@
         </is>
       </c>
       <c r="I24" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J24" s="4" t="inlineStr">
         <is>
-          <t>CURRENT (0d ago)</t>
+          <t>CURRENT (1d ago)</t>
         </is>
       </c>
       <c r="K24" s="2" t="n">
@@ -2790,11 +2790,11 @@
         </is>
       </c>
       <c r="I25" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J25" s="4" t="inlineStr">
         <is>
-          <t>CURRENT (8d ago)</t>
+          <t>CURRENT (9d ago)</t>
         </is>
       </c>
       <c r="K25" s="2" t="n">
@@ -2883,11 +2883,11 @@
         </is>
       </c>
       <c r="I26" s="2" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="J26" s="5" t="inlineStr">
         <is>
-          <t>NORMAL INTERVAL (35d ago)</t>
+          <t>NORMAL INTERVAL (36d ago)</t>
         </is>
       </c>
       <c r="K26" s="2" t="n">
@@ -2976,11 +2976,11 @@
         </is>
       </c>
       <c r="I27" s="2" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="J27" s="4" t="inlineStr">
         <is>
-          <t>CURRENT (12d ago)</t>
+          <t>CURRENT (13d ago)</t>
         </is>
       </c>
       <c r="K27" s="2" t="n">
@@ -3069,11 +3069,11 @@
         </is>
       </c>
       <c r="I28" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J28" s="4" t="inlineStr">
         <is>
-          <t>CURRENT (5d ago)</t>
+          <t>CURRENT (6d ago)</t>
         </is>
       </c>
       <c r="K28" s="2" t="n">
@@ -3162,11 +3162,11 @@
         </is>
       </c>
       <c r="I29" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="J29" s="4" t="inlineStr">
         <is>
-          <t>CURRENT (7d ago)</t>
+          <t>CURRENT (8d ago)</t>
         </is>
       </c>
       <c r="K29" s="2" t="n">
@@ -3255,11 +3255,11 @@
         </is>
       </c>
       <c r="I30" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J30" s="4" t="inlineStr">
         <is>
-          <t>CURRENT (4d ago)</t>
+          <t>CURRENT (5d ago)</t>
         </is>
       </c>
       <c r="K30" s="2" t="n">
@@ -3348,11 +3348,11 @@
         </is>
       </c>
       <c r="I31" s="2" t="n">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="J31" s="5" t="inlineStr">
         <is>
-          <t>NORMAL INTERVAL (70d ago)</t>
+          <t>NORMAL INTERVAL (71d ago)</t>
         </is>
       </c>
       <c r="K31" s="2" t="n">
@@ -3441,11 +3441,11 @@
         </is>
       </c>
       <c r="I32" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J32" s="4" t="inlineStr">
         <is>
-          <t>CURRENT (4d ago)</t>
+          <t>CURRENT (5d ago)</t>
         </is>
       </c>
       <c r="K32" s="2" t="n">
@@ -3534,11 +3534,11 @@
         </is>
       </c>
       <c r="I33" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J33" s="4" t="inlineStr">
         <is>
-          <t>CURRENT (2d ago)</t>
+          <t>CURRENT (3d ago)</t>
         </is>
       </c>
       <c r="K33" s="2" t="n">

--- a/data/extracted/series/corpus_publication_cadence_and_audit.xlsx
+++ b/data/extracted/series/corpus_publication_cadence_and_audit.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Corpus Cadence &amp; Inventory" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Graphic &amp; Chart Extraction" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Sub-Sector &amp; Fleet Breakdown" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Corpus Cadence &amp; Inventory" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Graphic &amp; Chart Extraction" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sub-Sector &amp; Fleet Breakdown" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1391,15 +1391,15 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="I10" s="2" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="J10" s="4" t="inlineStr">
         <is>
-          <t>CURRENT (5d ago)</t>
+          <t>CURRENT (0d ago)</t>
         </is>
       </c>
       <c r="K10" s="2" t="n">
@@ -1412,13 +1412,13 @@
         <v>2827</v>
       </c>
       <c r="N10" s="2" t="n">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="O10" s="2" t="n">
         <v>183</v>
       </c>
       <c r="P10" s="3" t="n">
-        <v>3191</v>
+        <v>3193</v>
       </c>
       <c r="Q10" s="3" t="inlineStr">
         <is>

--- a/data/extracted/series/corpus_publication_cadence_and_audit.xlsx
+++ b/data/extracted/series/corpus_publication_cadence_and_audit.xlsx
@@ -938,7 +938,7 @@
         </is>
       </c>
       <c r="K5" s="2" t="n">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="L5" s="2" t="n">
         <v>0</v>
@@ -953,7 +953,7 @@
         <v>251</v>
       </c>
       <c r="P5" s="3" t="n">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="Q5" s="3" t="inlineStr">
         <is>
@@ -1589,7 +1589,7 @@
         </is>
       </c>
       <c r="K12" s="2" t="n">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="L12" s="2" t="n">
         <v>0</v>
@@ -1604,7 +1604,7 @@
         <v>258</v>
       </c>
       <c r="P12" s="3" t="n">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="Q12" s="3" t="inlineStr">
         <is>
@@ -1868,7 +1868,7 @@
         </is>
       </c>
       <c r="K15" s="2" t="n">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="L15" s="2" t="n">
         <v>0</v>
@@ -1883,7 +1883,7 @@
         <v>531</v>
       </c>
       <c r="P15" s="3" t="n">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="Q15" s="3" t="inlineStr">
         <is>
@@ -2054,7 +2054,7 @@
         </is>
       </c>
       <c r="K17" s="2" t="n">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="L17" s="2" t="n">
         <v>0</v>
@@ -2069,7 +2069,7 @@
         <v>273</v>
       </c>
       <c r="P17" s="3" t="n">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="Q17" s="3" t="inlineStr">
         <is>
@@ -2135,22 +2135,22 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="I18" s="2" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="J18" s="4" t="inlineStr">
         <is>
-          <t>CURRENT (4d ago)</t>
+          <t>CURRENT (1d ago)</t>
         </is>
       </c>
       <c r="K18" s="2" t="n">
-        <v>2141</v>
+        <v>2143</v>
       </c>
       <c r="L18" s="2" t="n">
-        <v>810</v>
+        <v>811</v>
       </c>
       <c r="M18" s="2" t="n">
         <v>1211</v>
@@ -2159,10 +2159,10 @@
         <v>0</v>
       </c>
       <c r="O18" s="2" t="n">
-        <v>1641</v>
+        <v>1642</v>
       </c>
       <c r="P18" s="3" t="n">
-        <v>4162</v>
+        <v>4165</v>
       </c>
       <c r="Q18" s="3" t="inlineStr">
         <is>
@@ -2321,19 +2321,19 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="I20" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J20" s="4" t="inlineStr">
         <is>
-          <t>CURRENT (2d ago)</t>
+          <t>CURRENT (0d ago)</t>
         </is>
       </c>
       <c r="K20" s="2" t="n">
-        <v>4524</v>
+        <v>4528</v>
       </c>
       <c r="L20" s="2" t="n">
         <v>1202</v>
@@ -2345,7 +2345,7 @@
         <v>0</v>
       </c>
       <c r="O20" s="2" t="n">
-        <v>1193</v>
+        <v>1197</v>
       </c>
       <c r="P20" s="3" t="n">
         <v>9057</v>
@@ -2414,22 +2414,22 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="I21" s="2" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="J21" s="4" t="inlineStr">
         <is>
-          <t>CURRENT (8d ago)</t>
+          <t>CURRENT (1d ago)</t>
         </is>
       </c>
       <c r="K21" s="2" t="n">
-        <v>1362</v>
+        <v>1363</v>
       </c>
       <c r="L21" s="2" t="n">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="M21" s="2" t="n">
         <v>180</v>
@@ -2441,7 +2441,7 @@
         <v>165</v>
       </c>
       <c r="P21" s="3" t="n">
-        <v>1921</v>
+        <v>1923</v>
       </c>
       <c r="Q21" s="3" t="inlineStr">
         <is>
@@ -2600,22 +2600,22 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="I23" s="2" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="J23" s="4" t="inlineStr">
         <is>
-          <t>CURRENT (8d ago)</t>
+          <t>CURRENT (1d ago)</t>
         </is>
       </c>
       <c r="K23" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L23" s="2" t="n">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="M23" s="2" t="n">
         <v>733</v>
@@ -2627,7 +2627,7 @@
         <v>261</v>
       </c>
       <c r="P23" s="3" t="n">
-        <v>1007</v>
+        <v>1008</v>
       </c>
       <c r="Q23" s="3" t="inlineStr">
         <is>
@@ -2641,7 +2641,7 @@
       </c>
       <c r="S23" s="3" t="inlineStr">
         <is>
-          <t>hellenic_vv_matrix_series.csv (12,350 rows), hellenic_vv_sales_series.csv (2,062 rows)</t>
+          <t>hellenic_vv_matrix_series.csv (12,350 rows), hellenic_vv_sales_series.csv (2,030 rows)</t>
         </is>
       </c>
       <c r="T23" s="3" t="inlineStr">
@@ -5094,7 +5094,7 @@
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>2,062 rows</t>
+          <t>2,030 rows</t>
         </is>
       </c>
       <c r="H25" s="3" t="inlineStr">

--- a/data/extracted/series/corpus_publication_cadence_and_audit.xlsx
+++ b/data/extracted/series/corpus_publication_cadence_and_audit.xlsx
@@ -1226,13 +1226,13 @@
         <v>0</v>
       </c>
       <c r="N8" s="2" t="n">
-        <v>4742</v>
+        <v>4750</v>
       </c>
       <c r="O8" s="2" t="n">
-        <v>12005</v>
+        <v>12008</v>
       </c>
       <c r="P8" s="3" t="n">
-        <v>5005</v>
+        <v>5013</v>
       </c>
       <c r="Q8" s="3" t="inlineStr">
         <is>
@@ -1319,7 +1319,7 @@
         <v>0</v>
       </c>
       <c r="N9" s="2" t="n">
-        <v>4742</v>
+        <v>4750</v>
       </c>
       <c r="O9" s="2" t="n">
         <v>11750</v>
@@ -1403,22 +1403,22 @@
         </is>
       </c>
       <c r="K10" s="2" t="n">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="L10" s="2" t="n">
         <v>0</v>
       </c>
       <c r="M10" s="2" t="n">
-        <v>2827</v>
+        <v>2847</v>
       </c>
       <c r="N10" s="2" t="n">
         <v>186</v>
       </c>
       <c r="O10" s="2" t="n">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="P10" s="3" t="n">
-        <v>3193</v>
+        <v>3216</v>
       </c>
       <c r="Q10" s="3" t="inlineStr">
         <is>
@@ -1432,7 +1432,7 @@
       </c>
       <c r="S10" s="3" t="inlineStr">
         <is>
-          <t>fearnleys_md_master_econometric_series.xlsx (6 sheets, 26 lead models), fearnleys_md_vessel_tightness_series.csv (112 rows), fearnleys_md_macro_correlations_series.csv (78 rows), fearnleys_md_coal_futures_spread_series.csv (47 rows), fearnleys_md_shipment_volumes_series.csv (40 rows)</t>
+          <t>fearnleys_md_master_econometric_series.xlsx (6 sheets, 26 lead models), fearnleys_md_vessel_tightness_series.csv (115 rows), fearnleys_md_macro_correlations_series.csv (78 rows), fearnleys_md_coal_futures_spread_series.csv (48 rows), fearnleys_md_shipment_volumes_series.csv (43 rows)</t>
         </is>
       </c>
       <c r="T10" s="3" t="inlineStr">
@@ -5235,7 +5235,7 @@
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>223 rows</t>
+          <t>232 rows</t>
         </is>
       </c>
       <c r="H28" s="3" t="inlineStr">

--- a/data/extracted/series/corpus_publication_cadence_and_audit.xlsx
+++ b/data/extracted/series/corpus_publication_cadence_and_audit.xlsx
@@ -1019,19 +1019,19 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="I6" s="2" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="J6" s="4" t="inlineStr">
         <is>
-          <t>CURRENT (9d ago)</t>
+          <t>CURRENT (2d ago)</t>
         </is>
       </c>
       <c r="K6" s="2" t="n">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="L6" s="2" t="n">
         <v>0</v>
@@ -1043,11 +1043,11 @@
         <v>0</v>
       </c>
       <c r="O6" s="2" t="n">
+        <v>138</v>
+      </c>
+      <c r="P6" s="3" t="n">
         <v>137</v>
       </c>
-      <c r="P6" s="3" t="n">
-        <v>136</v>
-      </c>
       <c r="Q6" s="3" t="inlineStr">
         <is>
           <t>No (Tabular S&amp;P and Baltic BSPA/BDA indices)</t>
@@ -1060,7 +1060,7 @@
       </c>
       <c r="S6" s="3" t="inlineStr">
         <is>
-          <t>carriers_sales_series.csv (3,130 rows), carriers_dry_tc_period_series.csv (3,216 rows), carriers_indices_series.csv (1,876 rows), carriers_tanker_tce_series.csv (804 rows), carriers_bspa_series.csv (749 rows), carriers_newbuilding_series.csv (312 rows), carriers_demolition_series.csv (178 rows)</t>
+          <t>carriers_sales_series.csv (3,165 rows), carriers_dry_tc_period_series.csv (3,216 rows), carriers_indices_series.csv (1,876 rows), carriers_tanker_tce_series.csv (804 rows), carriers_bspa_series.csv (755 rows), carriers_newbuilding_series.csv (312 rows), carriers_demolition_series.csv (178 rows)</t>
         </is>
       </c>
       <c r="T6" s="3" t="inlineStr">
@@ -1217,7 +1217,7 @@
         </is>
       </c>
       <c r="K8" s="2" t="n">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="L8" s="2" t="n">
         <v>0</v>
@@ -1229,10 +1229,10 @@
         <v>4750</v>
       </c>
       <c r="O8" s="2" t="n">
-        <v>12008</v>
+        <v>12006</v>
       </c>
       <c r="P8" s="3" t="n">
-        <v>5013</v>
+        <v>5014</v>
       </c>
       <c r="Q8" s="3" t="inlineStr">
         <is>
@@ -1246,7 +1246,7 @@
       </c>
       <c r="S8" s="3" t="inlineStr">
         <is>
-          <t>fearnleys_rates_series.csv (17,076 rows)</t>
+          <t>fearnleys_rates_series.csv (17,112 rows)</t>
         </is>
       </c>
       <c r="T8" s="3" t="inlineStr">
@@ -2228,25 +2228,25 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="I19" s="2" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="J19" s="4" t="inlineStr">
         <is>
-          <t>CURRENT (7d ago)</t>
+          <t>CURRENT (0d ago)</t>
         </is>
       </c>
       <c r="K19" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L19" s="2" t="n">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="M19" s="2" t="n">
-        <v>761</v>
+        <v>762</v>
       </c>
       <c r="N19" s="2" t="n">
         <v>0</v>
@@ -2255,7 +2255,7 @@
         <v>266</v>
       </c>
       <c r="P19" s="3" t="n">
-        <v>1040</v>
+        <v>1042</v>
       </c>
       <c r="Q19" s="3" t="inlineStr">
         <is>
@@ -2507,34 +2507,34 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="I22" s="2" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="J22" s="4" t="inlineStr">
         <is>
-          <t>CURRENT (7d ago)</t>
+          <t>CURRENT (0d ago)</t>
         </is>
       </c>
       <c r="K22" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L22" s="2" t="n">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="M22" s="2" t="n">
-        <v>758</v>
+        <v>759</v>
       </c>
       <c r="N22" s="2" t="n">
         <v>0</v>
       </c>
       <c r="O22" s="2" t="n">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="P22" s="3" t="n">
-        <v>1036</v>
+        <v>1038</v>
       </c>
       <c r="Q22" s="3" t="inlineStr">
         <is>

--- a/data/extracted/series/corpus_publication_cadence_and_audit.xlsx
+++ b/data/extracted/series/corpus_publication_cadence_and_audit.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Corpus Cadence &amp; Inventory" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Graphic &amp; Chart Extraction" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sub-Sector &amp; Fleet Breakdown" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Corpus Cadence &amp; Inventory" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Graphic &amp; Chart Extraction" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Sub-Sector &amp; Fleet Breakdown" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1019,19 +1019,19 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="I6" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J6" s="4" t="inlineStr">
         <is>
-          <t>CURRENT (2d ago)</t>
+          <t>CURRENT (0d ago)</t>
         </is>
       </c>
       <c r="K6" s="2" t="n">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="L6" s="2" t="n">
         <v>0</v>
@@ -1046,7 +1046,7 @@
         <v>138</v>
       </c>
       <c r="P6" s="3" t="n">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="Q6" s="3" t="inlineStr">
         <is>
@@ -1205,7 +1205,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="I8" s="2" t="n">
@@ -1217,7 +1217,7 @@
         </is>
       </c>
       <c r="K8" s="2" t="n">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="L8" s="2" t="n">
         <v>0</v>
@@ -1232,7 +1232,7 @@
         <v>12006</v>
       </c>
       <c r="P8" s="3" t="n">
-        <v>5014</v>
+        <v>5015</v>
       </c>
       <c r="Q8" s="3" t="inlineStr">
         <is>

--- a/data/extracted/series/corpus_publication_cadence_and_audit.xlsx
+++ b/data/extracted/series/corpus_publication_cadence_and_audit.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Corpus Cadence &amp; Inventory" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Graphic &amp; Chart Extraction" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Sub-Sector &amp; Fleet Breakdown" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Corpus Cadence &amp; Inventory" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Graphic &amp; Chart Extraction" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sub-Sector &amp; Fleet Breakdown" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -550,7 +550,7 @@
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>Status (2026-10-07)</t>
+          <t>Status (2026-10-08)</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
@@ -651,11 +651,11 @@
         </is>
       </c>
       <c r="I2" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J2" s="4" t="inlineStr">
         <is>
-          <t>CURRENT (4d ago)</t>
+          <t>CURRENT (5d ago)</t>
         </is>
       </c>
       <c r="K2" s="2" t="n">
@@ -744,11 +744,11 @@
         </is>
       </c>
       <c r="I3" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J3" s="4" t="inlineStr">
         <is>
-          <t>CURRENT (4d ago)</t>
+          <t>CURRENT (5d ago)</t>
         </is>
       </c>
       <c r="K3" s="2" t="n">
@@ -837,11 +837,11 @@
         </is>
       </c>
       <c r="I4" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J4" s="4" t="inlineStr">
         <is>
-          <t>CURRENT (5d ago)</t>
+          <t>CURRENT (6d ago)</t>
         </is>
       </c>
       <c r="K4" s="2" t="n">
@@ -930,11 +930,11 @@
         </is>
       </c>
       <c r="I5" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J5" s="4" t="inlineStr">
         <is>
-          <t>CURRENT (0d ago)</t>
+          <t>CURRENT (1d ago)</t>
         </is>
       </c>
       <c r="K5" s="2" t="n">
@@ -1023,11 +1023,11 @@
         </is>
       </c>
       <c r="I6" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J6" s="4" t="inlineStr">
         <is>
-          <t>CURRENT (0d ago)</t>
+          <t>CURRENT (1d ago)</t>
         </is>
       </c>
       <c r="K6" s="2" t="n">
@@ -1136,7 +1136,7 @@
         <v>0</v>
       </c>
       <c r="O7" s="2" t="n">
-        <v>188</v>
+        <v>181</v>
       </c>
       <c r="P7" s="3" t="n">
         <v>181</v>
@@ -1153,7 +1153,7 @@
       </c>
       <c r="S7" s="3" t="inlineStr">
         <is>
-          <t>clarksons_sales_series.csv (1,343 rows)</t>
+          <t>clarksons_sales_series.csv (1,365 rows)</t>
         </is>
       </c>
       <c r="T7" s="3" t="inlineStr">
@@ -1229,7 +1229,7 @@
         <v>4750</v>
       </c>
       <c r="O8" s="2" t="n">
-        <v>12006</v>
+        <v>12009</v>
       </c>
       <c r="P8" s="3" t="n">
         <v>5015</v>
@@ -1302,11 +1302,11 @@
         </is>
       </c>
       <c r="I9" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J9" s="4" t="inlineStr">
         <is>
-          <t>CURRENT (0d ago)</t>
+          <t>CURRENT (1d ago)</t>
         </is>
       </c>
       <c r="K9" s="2" t="n">
@@ -1395,11 +1395,11 @@
         </is>
       </c>
       <c r="I10" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J10" s="4" t="inlineStr">
         <is>
-          <t>CURRENT (0d ago)</t>
+          <t>CURRENT (1d ago)</t>
         </is>
       </c>
       <c r="K10" s="2" t="n">
@@ -1488,11 +1488,11 @@
         </is>
       </c>
       <c r="I11" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J11" s="4" t="inlineStr">
         <is>
-          <t>CURRENT (5d ago)</t>
+          <t>CURRENT (6d ago)</t>
         </is>
       </c>
       <c r="K11" s="2" t="n">
@@ -1581,11 +1581,11 @@
         </is>
       </c>
       <c r="I12" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J12" s="4" t="inlineStr">
         <is>
-          <t>CURRENT (0d ago)</t>
+          <t>CURRENT (1d ago)</t>
         </is>
       </c>
       <c r="K12" s="2" t="n">
@@ -1674,11 +1674,11 @@
         </is>
       </c>
       <c r="I13" s="2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J13" s="4" t="inlineStr">
         <is>
-          <t>CURRENT (9d ago)</t>
+          <t>CURRENT (10d ago)</t>
         </is>
       </c>
       <c r="K13" s="2" t="n">
@@ -1860,11 +1860,11 @@
         </is>
       </c>
       <c r="I15" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J15" s="4" t="inlineStr">
         <is>
-          <t>CURRENT (2d ago)</t>
+          <t>CURRENT (3d ago)</t>
         </is>
       </c>
       <c r="K15" s="2" t="n">
@@ -1953,11 +1953,11 @@
         </is>
       </c>
       <c r="I16" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J16" s="4" t="inlineStr">
         <is>
-          <t>CURRENT (2d ago)</t>
+          <t>CURRENT (3d ago)</t>
         </is>
       </c>
       <c r="K16" s="2" t="n">
@@ -2046,11 +2046,11 @@
         </is>
       </c>
       <c r="I17" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J17" s="4" t="inlineStr">
         <is>
-          <t>CURRENT (1d ago)</t>
+          <t>CURRENT (2d ago)</t>
         </is>
       </c>
       <c r="K17" s="2" t="n">
@@ -2139,11 +2139,11 @@
         </is>
       </c>
       <c r="I18" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J18" s="4" t="inlineStr">
         <is>
-          <t>CURRENT (1d ago)</t>
+          <t>CURRENT (2d ago)</t>
         </is>
       </c>
       <c r="K18" s="2" t="n">
@@ -2232,11 +2232,11 @@
         </is>
       </c>
       <c r="I19" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J19" s="4" t="inlineStr">
         <is>
-          <t>CURRENT (0d ago)</t>
+          <t>CURRENT (1d ago)</t>
         </is>
       </c>
       <c r="K19" s="2" t="n">
@@ -2325,11 +2325,11 @@
         </is>
       </c>
       <c r="I20" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J20" s="4" t="inlineStr">
         <is>
-          <t>CURRENT (0d ago)</t>
+          <t>CURRENT (1d ago)</t>
         </is>
       </c>
       <c r="K20" s="2" t="n">
@@ -2418,11 +2418,11 @@
         </is>
       </c>
       <c r="I21" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J21" s="4" t="inlineStr">
         <is>
-          <t>CURRENT (1d ago)</t>
+          <t>CURRENT (2d ago)</t>
         </is>
       </c>
       <c r="K21" s="2" t="n">
@@ -2511,11 +2511,11 @@
         </is>
       </c>
       <c r="I22" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J22" s="4" t="inlineStr">
         <is>
-          <t>CURRENT (0d ago)</t>
+          <t>CURRENT (1d ago)</t>
         </is>
       </c>
       <c r="K22" s="2" t="n">
@@ -2604,11 +2604,11 @@
         </is>
       </c>
       <c r="I23" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J23" s="4" t="inlineStr">
         <is>
-          <t>CURRENT (1d ago)</t>
+          <t>CURRENT (2d ago)</t>
         </is>
       </c>
       <c r="K23" s="2" t="n">
@@ -2697,11 +2697,11 @@
         </is>
       </c>
       <c r="I24" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J24" s="4" t="inlineStr">
         <is>
-          <t>CURRENT (1d ago)</t>
+          <t>CURRENT (2d ago)</t>
         </is>
       </c>
       <c r="K24" s="2" t="n">
@@ -2790,11 +2790,11 @@
         </is>
       </c>
       <c r="I25" s="2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J25" s="4" t="inlineStr">
         <is>
-          <t>CURRENT (9d ago)</t>
+          <t>CURRENT (10d ago)</t>
         </is>
       </c>
       <c r="K25" s="2" t="n">
@@ -2883,11 +2883,11 @@
         </is>
       </c>
       <c r="I26" s="2" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="J26" s="5" t="inlineStr">
         <is>
-          <t>NORMAL INTERVAL (36d ago)</t>
+          <t>NORMAL INTERVAL (37d ago)</t>
         </is>
       </c>
       <c r="K26" s="2" t="n">
@@ -2976,11 +2976,11 @@
         </is>
       </c>
       <c r="I27" s="2" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="J27" s="4" t="inlineStr">
         <is>
-          <t>CURRENT (13d ago)</t>
+          <t>CURRENT (14d ago)</t>
         </is>
       </c>
       <c r="K27" s="2" t="n">
@@ -3069,11 +3069,11 @@
         </is>
       </c>
       <c r="I28" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J28" s="4" t="inlineStr">
         <is>
-          <t>CURRENT (6d ago)</t>
+          <t>CURRENT (7d ago)</t>
         </is>
       </c>
       <c r="K28" s="2" t="n">
@@ -3162,11 +3162,11 @@
         </is>
       </c>
       <c r="I29" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J29" s="4" t="inlineStr">
         <is>
-          <t>CURRENT (8d ago)</t>
+          <t>CURRENT (9d ago)</t>
         </is>
       </c>
       <c r="K29" s="2" t="n">
@@ -3255,11 +3255,11 @@
         </is>
       </c>
       <c r="I30" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J30" s="4" t="inlineStr">
         <is>
-          <t>CURRENT (5d ago)</t>
+          <t>CURRENT (6d ago)</t>
         </is>
       </c>
       <c r="K30" s="2" t="n">
@@ -3348,11 +3348,11 @@
         </is>
       </c>
       <c r="I31" s="2" t="n">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="J31" s="5" t="inlineStr">
         <is>
-          <t>NORMAL INTERVAL (71d ago)</t>
+          <t>NORMAL INTERVAL (72d ago)</t>
         </is>
       </c>
       <c r="K31" s="2" t="n">
@@ -3441,11 +3441,11 @@
         </is>
       </c>
       <c r="I32" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J32" s="4" t="inlineStr">
         <is>
-          <t>CURRENT (5d ago)</t>
+          <t>CURRENT (6d ago)</t>
         </is>
       </c>
       <c r="K32" s="2" t="n">
@@ -3534,11 +3534,11 @@
         </is>
       </c>
       <c r="I33" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J33" s="4" t="inlineStr">
         <is>
-          <t>CURRENT (3d ago)</t>
+          <t>CURRENT (4d ago)</t>
         </is>
       </c>
       <c r="K33" s="2" t="n">

--- a/data/extracted/series/corpus_publication_cadence_and_audit.xlsx
+++ b/data/extracted/series/corpus_publication_cadence_and_audit.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Corpus Cadence &amp; Inventory" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Graphic &amp; Chart Extraction" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sub-Sector &amp; Fleet Breakdown" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Corpus Cadence &amp; Inventory" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Graphic &amp; Chart Extraction" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Sub-Sector &amp; Fleet Breakdown" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1499,7 +1499,7 @@
         <v>109</v>
       </c>
       <c r="L11" s="2" t="n">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="M11" s="2" t="n">
         <v>0</v>
@@ -1508,10 +1508,10 @@
         <v>0</v>
       </c>
       <c r="O11" s="2" t="n">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="P11" s="3" t="n">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="Q11" s="3" t="inlineStr">
         <is>
@@ -1525,7 +1525,7 @@
       </c>
       <c r="S11" s="3" t="inlineStr">
         <is>
-          <t>gibson_tanker_spot_series.csv (3,602 rows), gibson_bunker_prices_series.csv (1,015 rows), gibson_master_tanker_series.xlsx</t>
+          <t>gibson_tanker_spot_series.csv (3,616 rows), gibson_bunker_prices_series.csv (1,019 rows), gibson_master_tanker_series.xlsx</t>
         </is>
       </c>
       <c r="T11" s="3" t="inlineStr">

--- a/data/extracted/series/corpus_publication_cadence_and_audit.xlsx
+++ b/data/extracted/series/corpus_publication_cadence_and_audit.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Corpus Cadence &amp; Inventory" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Graphic &amp; Chart Extraction" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Sub-Sector &amp; Fleet Breakdown" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Corpus Cadence &amp; Inventory" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Graphic &amp; Chart Extraction" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sub-Sector &amp; Fleet Breakdown" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -5235,7 +5235,7 @@
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>232 rows</t>
+          <t>233 rows</t>
         </is>
       </c>
       <c r="H28" s="3" t="inlineStr">

--- a/data/extracted/series/corpus_publication_cadence_and_audit.xlsx
+++ b/data/extracted/series/corpus_publication_cadence_and_audit.xlsx
@@ -2321,19 +2321,19 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="I20" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J20" s="4" t="inlineStr">
         <is>
-          <t>CURRENT (1d ago)</t>
+          <t>CURRENT (0d ago)</t>
         </is>
       </c>
       <c r="K20" s="2" t="n">
-        <v>4528</v>
+        <v>4530</v>
       </c>
       <c r="L20" s="2" t="n">
         <v>1202</v>
@@ -2345,7 +2345,7 @@
         <v>0</v>
       </c>
       <c r="O20" s="2" t="n">
-        <v>1197</v>
+        <v>1199</v>
       </c>
       <c r="P20" s="3" t="n">
         <v>9057</v>
@@ -2693,34 +2693,34 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="I24" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J24" s="4" t="inlineStr">
         <is>
-          <t>CURRENT (2d ago)</t>
+          <t>CURRENT (0d ago)</t>
         </is>
       </c>
       <c r="K24" s="2" t="n">
         <v>305</v>
       </c>
       <c r="L24" s="2" t="n">
-        <v>3243</v>
+        <v>3245</v>
       </c>
       <c r="M24" s="2" t="n">
-        <v>15095</v>
+        <v>15102</v>
       </c>
       <c r="N24" s="2" t="n">
-        <v>3214</v>
+        <v>3216</v>
       </c>
       <c r="O24" s="2" t="n">
-        <v>3506</v>
+        <v>3508</v>
       </c>
       <c r="P24" s="3" t="n">
-        <v>21857</v>
+        <v>21868</v>
       </c>
       <c r="Q24" s="3" t="inlineStr">
         <is>
@@ -2734,7 +2734,7 @@
       </c>
       <c r="S24" s="3" t="inlineStr">
         <is>
-          <t>breakwave_fundamentals_series.csv (2,755 rows), breakwave_insights_metadata.csv (3,214 rows)</t>
+          <t>breakwave_fundamentals_series.csv (2,755 rows), breakwave_insights_metadata.csv (3,216 rows)</t>
         </is>
       </c>
       <c r="T24" s="3" t="inlineStr">
@@ -3266,19 +3266,19 @@
         <v>0</v>
       </c>
       <c r="L30" s="2" t="n">
-        <v>3048</v>
+        <v>3049</v>
       </c>
       <c r="M30" s="2" t="n">
         <v>0</v>
       </c>
       <c r="N30" s="2" t="n">
-        <v>2228</v>
+        <v>2229</v>
       </c>
       <c r="O30" s="2" t="n">
-        <v>2228</v>
+        <v>2229</v>
       </c>
       <c r="P30" s="3" t="n">
-        <v>5276</v>
+        <v>5278</v>
       </c>
       <c r="Q30" s="3" t="inlineStr">
         <is>
@@ -3292,7 +3292,7 @@
       </c>
       <c r="S30" s="3" t="inlineStr">
         <is>
-          <t>baltic_reports_metadata.csv (2,228 rows), baltic_ncfi_series.csv (2,041 rows)</t>
+          <t>baltic_reports_metadata.csv (2,229 rows), baltic_ncfi_series.csv (2,045 rows)</t>
         </is>
       </c>
       <c r="T30" s="3" t="inlineStr">

--- a/data/extracted/series/corpus_publication_cadence_and_audit.xlsx
+++ b/data/extracted/series/corpus_publication_cadence_and_audit.xlsx
@@ -2159,7 +2159,7 @@
         <v>0</v>
       </c>
       <c r="O18" s="2" t="n">
-        <v>1642</v>
+        <v>1797</v>
       </c>
       <c r="P18" s="3" t="n">
         <v>4165</v>

--- a/data/extracted/series/corpus_publication_cadence_and_audit.xlsx
+++ b/data/extracted/series/corpus_publication_cadence_and_audit.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Corpus Cadence &amp; Inventory" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Graphic &amp; Chart Extraction" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sub-Sector &amp; Fleet Breakdown" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Corpus Cadence &amp; Inventory" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Graphic &amp; Chart Extraction" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Sub-Sector &amp; Fleet Breakdown" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>

--- a/data/extracted/series/corpus_publication_cadence_and_audit.xlsx
+++ b/data/extracted/series/corpus_publication_cadence_and_audit.xlsx
@@ -550,7 +550,7 @@
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>Status (2026-10-08)</t>
+          <t>Status (2026-10-09)</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
@@ -651,11 +651,11 @@
         </is>
       </c>
       <c r="I2" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J2" s="4" t="inlineStr">
         <is>
-          <t>CURRENT (5d ago)</t>
+          <t>CURRENT (6d ago)</t>
         </is>
       </c>
       <c r="K2" s="2" t="n">
@@ -744,11 +744,11 @@
         </is>
       </c>
       <c r="I3" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J3" s="4" t="inlineStr">
         <is>
-          <t>CURRENT (5d ago)</t>
+          <t>CURRENT (6d ago)</t>
         </is>
       </c>
       <c r="K3" s="2" t="n">
@@ -837,11 +837,11 @@
         </is>
       </c>
       <c r="I4" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J4" s="4" t="inlineStr">
         <is>
-          <t>CURRENT (6d ago)</t>
+          <t>CURRENT (7d ago)</t>
         </is>
       </c>
       <c r="K4" s="2" t="n">
@@ -930,11 +930,11 @@
         </is>
       </c>
       <c r="I5" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J5" s="4" t="inlineStr">
         <is>
-          <t>CURRENT (1d ago)</t>
+          <t>CURRENT (2d ago)</t>
         </is>
       </c>
       <c r="K5" s="2" t="n">
@@ -1023,11 +1023,11 @@
         </is>
       </c>
       <c r="I6" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J6" s="4" t="inlineStr">
         <is>
-          <t>CURRENT (1d ago)</t>
+          <t>CURRENT (2d ago)</t>
         </is>
       </c>
       <c r="K6" s="2" t="n">
@@ -1209,11 +1209,11 @@
         </is>
       </c>
       <c r="I8" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J8" s="4" t="inlineStr">
         <is>
-          <t>CURRENT (0d ago)</t>
+          <t>CURRENT (1d ago)</t>
         </is>
       </c>
       <c r="K8" s="2" t="n">
@@ -1302,11 +1302,11 @@
         </is>
       </c>
       <c r="I9" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J9" s="4" t="inlineStr">
         <is>
-          <t>CURRENT (1d ago)</t>
+          <t>CURRENT (2d ago)</t>
         </is>
       </c>
       <c r="K9" s="2" t="n">
@@ -1395,11 +1395,11 @@
         </is>
       </c>
       <c r="I10" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J10" s="4" t="inlineStr">
         <is>
-          <t>CURRENT (1d ago)</t>
+          <t>CURRENT (2d ago)</t>
         </is>
       </c>
       <c r="K10" s="2" t="n">
@@ -1488,11 +1488,11 @@
         </is>
       </c>
       <c r="I11" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J11" s="4" t="inlineStr">
         <is>
-          <t>CURRENT (6d ago)</t>
+          <t>CURRENT (7d ago)</t>
         </is>
       </c>
       <c r="K11" s="2" t="n">
@@ -1581,11 +1581,11 @@
         </is>
       </c>
       <c r="I12" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J12" s="4" t="inlineStr">
         <is>
-          <t>CURRENT (1d ago)</t>
+          <t>CURRENT (2d ago)</t>
         </is>
       </c>
       <c r="K12" s="2" t="n">
@@ -1674,11 +1674,11 @@
         </is>
       </c>
       <c r="I13" s="2" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="J13" s="4" t="inlineStr">
         <is>
-          <t>CURRENT (10d ago)</t>
+          <t>CURRENT (11d ago)</t>
         </is>
       </c>
       <c r="K13" s="2" t="n">
@@ -1860,11 +1860,11 @@
         </is>
       </c>
       <c r="I15" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J15" s="4" t="inlineStr">
         <is>
-          <t>CURRENT (3d ago)</t>
+          <t>CURRENT (4d ago)</t>
         </is>
       </c>
       <c r="K15" s="2" t="n">
@@ -1953,11 +1953,11 @@
         </is>
       </c>
       <c r="I16" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J16" s="4" t="inlineStr">
         <is>
-          <t>CURRENT (3d ago)</t>
+          <t>CURRENT (4d ago)</t>
         </is>
       </c>
       <c r="K16" s="2" t="n">
@@ -2046,11 +2046,11 @@
         </is>
       </c>
       <c r="I17" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J17" s="4" t="inlineStr">
         <is>
-          <t>CURRENT (2d ago)</t>
+          <t>CURRENT (3d ago)</t>
         </is>
       </c>
       <c r="K17" s="2" t="n">
@@ -2139,11 +2139,11 @@
         </is>
       </c>
       <c r="I18" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J18" s="4" t="inlineStr">
         <is>
-          <t>CURRENT (2d ago)</t>
+          <t>CURRENT (3d ago)</t>
         </is>
       </c>
       <c r="K18" s="2" t="n">
@@ -2232,11 +2232,11 @@
         </is>
       </c>
       <c r="I19" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J19" s="4" t="inlineStr">
         <is>
-          <t>CURRENT (1d ago)</t>
+          <t>CURRENT (2d ago)</t>
         </is>
       </c>
       <c r="K19" s="2" t="n">
@@ -2325,11 +2325,11 @@
         </is>
       </c>
       <c r="I20" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J20" s="4" t="inlineStr">
         <is>
-          <t>CURRENT (0d ago)</t>
+          <t>CURRENT (1d ago)</t>
         </is>
       </c>
       <c r="K20" s="2" t="n">
@@ -2418,11 +2418,11 @@
         </is>
       </c>
       <c r="I21" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J21" s="4" t="inlineStr">
         <is>
-          <t>CURRENT (2d ago)</t>
+          <t>CURRENT (3d ago)</t>
         </is>
       </c>
       <c r="K21" s="2" t="n">
@@ -2511,11 +2511,11 @@
         </is>
       </c>
       <c r="I22" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J22" s="4" t="inlineStr">
         <is>
-          <t>CURRENT (1d ago)</t>
+          <t>CURRENT (2d ago)</t>
         </is>
       </c>
       <c r="K22" s="2" t="n">
@@ -2604,11 +2604,11 @@
         </is>
       </c>
       <c r="I23" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J23" s="4" t="inlineStr">
         <is>
-          <t>CURRENT (2d ago)</t>
+          <t>CURRENT (3d ago)</t>
         </is>
       </c>
       <c r="K23" s="2" t="n">
@@ -2697,11 +2697,11 @@
         </is>
       </c>
       <c r="I24" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J24" s="4" t="inlineStr">
         <is>
-          <t>CURRENT (0d ago)</t>
+          <t>CURRENT (1d ago)</t>
         </is>
       </c>
       <c r="K24" s="2" t="n">
@@ -2790,11 +2790,11 @@
         </is>
       </c>
       <c r="I25" s="2" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="J25" s="4" t="inlineStr">
         <is>
-          <t>CURRENT (10d ago)</t>
+          <t>CURRENT (11d ago)</t>
         </is>
       </c>
       <c r="K25" s="2" t="n">
@@ -2883,11 +2883,11 @@
         </is>
       </c>
       <c r="I26" s="2" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="J26" s="5" t="inlineStr">
         <is>
-          <t>NORMAL INTERVAL (37d ago)</t>
+          <t>NORMAL INTERVAL (38d ago)</t>
         </is>
       </c>
       <c r="K26" s="2" t="n">
@@ -2976,11 +2976,11 @@
         </is>
       </c>
       <c r="I27" s="2" t="n">
-        <v>14</v>
-      </c>
-      <c r="J27" s="4" t="inlineStr">
-        <is>
-          <t>CURRENT (14d ago)</t>
+        <v>15</v>
+      </c>
+      <c r="J27" s="5" t="inlineStr">
+        <is>
+          <t>NORMAL INTERVAL (15d ago)</t>
         </is>
       </c>
       <c r="K27" s="2" t="n">
@@ -3069,11 +3069,11 @@
         </is>
       </c>
       <c r="I28" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="J28" s="4" t="inlineStr">
         <is>
-          <t>CURRENT (7d ago)</t>
+          <t>CURRENT (8d ago)</t>
         </is>
       </c>
       <c r="K28" s="2" t="n">
@@ -3162,11 +3162,11 @@
         </is>
       </c>
       <c r="I29" s="2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J29" s="4" t="inlineStr">
         <is>
-          <t>CURRENT (9d ago)</t>
+          <t>CURRENT (10d ago)</t>
         </is>
       </c>
       <c r="K29" s="2" t="n">
@@ -3255,11 +3255,11 @@
         </is>
       </c>
       <c r="I30" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J30" s="4" t="inlineStr">
         <is>
-          <t>CURRENT (6d ago)</t>
+          <t>CURRENT (7d ago)</t>
         </is>
       </c>
       <c r="K30" s="2" t="n">
@@ -3348,11 +3348,11 @@
         </is>
       </c>
       <c r="I31" s="2" t="n">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="J31" s="5" t="inlineStr">
         <is>
-          <t>NORMAL INTERVAL (72d ago)</t>
+          <t>NORMAL INTERVAL (73d ago)</t>
         </is>
       </c>
       <c r="K31" s="2" t="n">
@@ -3441,11 +3441,11 @@
         </is>
       </c>
       <c r="I32" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J32" s="4" t="inlineStr">
         <is>
-          <t>CURRENT (6d ago)</t>
+          <t>CURRENT (7d ago)</t>
         </is>
       </c>
       <c r="K32" s="2" t="n">
@@ -3534,11 +3534,11 @@
         </is>
       </c>
       <c r="I33" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J33" s="4" t="inlineStr">
         <is>
-          <t>CURRENT (4d ago)</t>
+          <t>CURRENT (5d ago)</t>
         </is>
       </c>
       <c r="K33" s="2" t="n">

--- a/data/extracted/series/corpus_publication_cadence_and_audit.xlsx
+++ b/data/extracted/series/corpus_publication_cadence_and_audit.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Corpus Cadence &amp; Inventory" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Graphic &amp; Chart Extraction" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Sub-Sector &amp; Fleet Breakdown" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Corpus Cadence &amp; Inventory" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Graphic &amp; Chart Extraction" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sub-Sector &amp; Fleet Breakdown" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -2321,19 +2321,19 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="I20" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J20" s="4" t="inlineStr">
         <is>
-          <t>CURRENT (1d ago)</t>
+          <t>CURRENT (0d ago)</t>
         </is>
       </c>
       <c r="K20" s="2" t="n">
-        <v>4530</v>
+        <v>4532</v>
       </c>
       <c r="L20" s="2" t="n">
         <v>1202</v>
@@ -2345,7 +2345,7 @@
         <v>0</v>
       </c>
       <c r="O20" s="2" t="n">
-        <v>1199</v>
+        <v>1201</v>
       </c>
       <c r="P20" s="3" t="n">
         <v>9057</v>
@@ -3251,34 +3251,34 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="I30" s="2" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="J30" s="4" t="inlineStr">
         <is>
-          <t>CURRENT (7d ago)</t>
+          <t>CURRENT (0d ago)</t>
         </is>
       </c>
       <c r="K30" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L30" s="2" t="n">
-        <v>3049</v>
+        <v>3054</v>
       </c>
       <c r="M30" s="2" t="n">
         <v>0</v>
       </c>
       <c r="N30" s="2" t="n">
-        <v>2229</v>
+        <v>2234</v>
       </c>
       <c r="O30" s="2" t="n">
-        <v>2229</v>
+        <v>2234</v>
       </c>
       <c r="P30" s="3" t="n">
-        <v>5278</v>
+        <v>5288</v>
       </c>
       <c r="Q30" s="3" t="inlineStr">
         <is>
@@ -3292,7 +3292,7 @@
       </c>
       <c r="S30" s="3" t="inlineStr">
         <is>
-          <t>baltic_reports_metadata.csv (2,229 rows), baltic_ncfi_series.csv (2,045 rows)</t>
+          <t>baltic_reports_metadata.csv (2,234 rows), baltic_ncfi_series.csv (2,049 rows)</t>
         </is>
       </c>
       <c r="T30" s="3" t="inlineStr">

--- a/data/extracted/series/corpus_publication_cadence_and_audit.xlsx
+++ b/data/extracted/series/corpus_publication_cadence_and_audit.xlsx
@@ -647,19 +647,19 @@
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="I2" s="2" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="J2" s="4" t="inlineStr">
         <is>
-          <t>CURRENT (6d ago)</t>
+          <t>CURRENT (0d ago)</t>
         </is>
       </c>
       <c r="K2" s="2" t="n">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="L2" s="2" t="n">
         <v>0</v>
@@ -671,10 +671,10 @@
         <v>0</v>
       </c>
       <c r="O2" s="2" t="n">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="P2" s="3" t="n">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="Q2" s="3" t="inlineStr">
         <is>
@@ -688,7 +688,7 @@
       </c>
       <c r="S2" s="3" t="inlineStr">
         <is>
-          <t>advanced_shipping_sales_series.csv (6,097 rows), advanced_shipping_demolition_series.csv (2,016 rows), advanced_shipping_secondhand_matrix_series.csv (8,078 rows), advanced_shipping_newbuilding_series.csv (1,895 rows), advanced_shipping_demo_sales_series.csv (601 rows)</t>
+          <t>advanced_shipping_sales_series.csv (6,114 rows), advanced_shipping_demolition_series.csv (2,016 rows), advanced_shipping_secondhand_matrix_series.csv (8,110 rows), advanced_shipping_newbuilding_series.csv (1,911 rows), advanced_shipping_demo_sales_series.csv (601 rows)</t>
         </is>
       </c>
       <c r="T2" s="3" t="inlineStr">
@@ -740,19 +740,19 @@
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="I3" s="2" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="J3" s="4" t="inlineStr">
         <is>
-          <t>CURRENT (6d ago)</t>
+          <t>CURRENT (0d ago)</t>
         </is>
       </c>
       <c r="K3" s="2" t="n">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="L3" s="2" t="n">
         <v>0</v>
@@ -767,7 +767,7 @@
         <v>255</v>
       </c>
       <c r="P3" s="3" t="n">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="Q3" s="3" t="inlineStr">
         <is>
@@ -781,7 +781,7 @@
       </c>
       <c r="S3" s="3" t="inlineStr">
         <is>
-          <t>affinity_tce_series.csv (4,039 rows), affinity_bda_series.csv (744 rows), affinity_indices_series.csv (496 rows)</t>
+          <t>affinity_tce_series.csv (4,058 rows), affinity_bda_series.csv (747 rows), affinity_indices_series.csv (496 rows)</t>
         </is>
       </c>
       <c r="T3" s="3" t="inlineStr">
@@ -833,19 +833,19 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="I4" s="2" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="J4" s="4" t="inlineStr">
         <is>
-          <t>CURRENT (7d ago)</t>
+          <t>CURRENT (1d ago)</t>
         </is>
       </c>
       <c r="K4" s="2" t="n">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="L4" s="2" t="n">
         <v>0</v>
@@ -857,10 +857,10 @@
         <v>0</v>
       </c>
       <c r="O4" s="2" t="n">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="P4" s="3" t="n">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="Q4" s="3" t="inlineStr">
         <is>
@@ -1153,7 +1153,7 @@
       </c>
       <c r="S7" s="3" t="inlineStr">
         <is>
-          <t>clarksons_sales_series.csv (1,365 rows)</t>
+          <t>clarksons_sales_series.csv (1,375 rows)</t>
         </is>
       </c>
       <c r="T7" s="3" t="inlineStr">
@@ -1775,7 +1775,7 @@
         </is>
       </c>
       <c r="K14" s="2" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="L14" s="2" t="n">
         <v>0</v>
@@ -1787,10 +1787,10 @@
         <v>0</v>
       </c>
       <c r="O14" s="2" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="P14" s="3" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="Q14" s="3" t="inlineStr">
         <is>
@@ -1804,7 +1804,7 @@
       </c>
       <c r="S14" s="3" t="inlineStr">
         <is>
-          <t>lion_deals_series.csv (1,269 rows), lion_sales_series.csv (1,164 rows), lion_demometer_series.csv (564 rows), lion_demolition_series.csv (516 rows), lion_demo_sales_series.csv (105 rows)</t>
+          <t>lion_deals_series.csv (1,303 rows), lion_sales_series.csv (1,194 rows), lion_demometer_series.csv (576 rows), lion_demolition_series.csv (516 rows), lion_demo_sales_series.csv (109 rows)</t>
         </is>
       </c>
       <c r="T14" s="3" t="inlineStr">
@@ -2135,34 +2135,34 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="I18" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J18" s="4" t="inlineStr">
         <is>
-          <t>CURRENT (3d ago)</t>
+          <t>CURRENT (0d ago)</t>
         </is>
       </c>
       <c r="K18" s="2" t="n">
-        <v>2143</v>
+        <v>2147</v>
       </c>
       <c r="L18" s="2" t="n">
-        <v>811</v>
+        <v>813</v>
       </c>
       <c r="M18" s="2" t="n">
-        <v>1211</v>
+        <v>1212</v>
       </c>
       <c r="N18" s="2" t="n">
         <v>0</v>
       </c>
       <c r="O18" s="2" t="n">
-        <v>1797</v>
+        <v>1800</v>
       </c>
       <c r="P18" s="3" t="n">
-        <v>4165</v>
+        <v>4172</v>
       </c>
       <c r="Q18" s="3" t="inlineStr">
         <is>
@@ -5470,7 +5470,7 @@
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>6,097 rows</t>
+          <t>6,114 rows</t>
         </is>
       </c>
       <c r="H33" s="3" t="inlineStr">

--- a/data/extracted/series/corpus_publication_cadence_and_audit.xlsx
+++ b/data/extracted/series/corpus_publication_cadence_and_audit.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Corpus Cadence &amp; Inventory" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Graphic &amp; Chart Extraction" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sub-Sector &amp; Fleet Breakdown" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Corpus Cadence &amp; Inventory" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Graphic &amp; Chart Extraction" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Sub-Sector &amp; Fleet Breakdown" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -647,7 +647,7 @@
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="I2" s="2" t="n">
@@ -659,7 +659,7 @@
         </is>
       </c>
       <c r="K2" s="2" t="n">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="L2" s="2" t="n">
         <v>0</v>
@@ -674,7 +674,7 @@
         <v>256</v>
       </c>
       <c r="P2" s="3" t="n">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="Q2" s="3" t="inlineStr">
         <is>
@@ -740,7 +740,7 @@
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="I3" s="2" t="n">
@@ -752,7 +752,7 @@
         </is>
       </c>
       <c r="K3" s="2" t="n">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="L3" s="2" t="n">
         <v>0</v>
@@ -767,7 +767,7 @@
         <v>255</v>
       </c>
       <c r="P3" s="3" t="n">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="Q3" s="3" t="inlineStr">
         <is>
@@ -833,19 +833,19 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="I4" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J4" s="4" t="inlineStr">
         <is>
-          <t>CURRENT (1d ago)</t>
+          <t>CURRENT (0d ago)</t>
         </is>
       </c>
       <c r="K4" s="2" t="n">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="L4" s="2" t="n">
         <v>0</v>
@@ -857,10 +857,10 @@
         <v>0</v>
       </c>
       <c r="O4" s="2" t="n">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="P4" s="3" t="n">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="Q4" s="3" t="inlineStr">
         <is>
@@ -1484,22 +1484,22 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="I11" s="2" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="J11" s="4" t="inlineStr">
         <is>
-          <t>CURRENT (7d ago)</t>
+          <t>CURRENT (0d ago)</t>
         </is>
       </c>
       <c r="K11" s="2" t="n">
         <v>109</v>
       </c>
       <c r="L11" s="2" t="n">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="M11" s="2" t="n">
         <v>0</v>
@@ -1508,10 +1508,10 @@
         <v>0</v>
       </c>
       <c r="O11" s="2" t="n">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="P11" s="3" t="n">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="Q11" s="3" t="inlineStr">
         <is>
@@ -1525,7 +1525,7 @@
       </c>
       <c r="S11" s="3" t="inlineStr">
         <is>
-          <t>gibson_tanker_spot_series.csv (3,616 rows), gibson_bunker_prices_series.csv (1,019 rows), gibson_master_tanker_series.xlsx</t>
+          <t>gibson_tanker_spot_series.csv (3,630 rows), gibson_bunker_prices_series.csv (1,023 rows), gibson_master_tanker_series.xlsx</t>
         </is>
       </c>
       <c r="T11" s="3" t="inlineStr">
@@ -1775,7 +1775,7 @@
         </is>
       </c>
       <c r="K14" s="2" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="L14" s="2" t="n">
         <v>0</v>
@@ -1790,7 +1790,7 @@
         <v>49</v>
       </c>
       <c r="P14" s="3" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="Q14" s="3" t="inlineStr">
         <is>

--- a/data/extracted/series/corpus_publication_cadence_and_audit.xlsx
+++ b/data/extracted/series/corpus_publication_cadence_and_audit.xlsx
@@ -3158,34 +3158,34 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="I29" s="2" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="J29" s="4" t="inlineStr">
         <is>
-          <t>CURRENT (10d ago)</t>
+          <t>CURRENT (0d ago)</t>
         </is>
       </c>
       <c r="K29" s="2" t="n">
         <v>10</v>
       </c>
       <c r="L29" s="2" t="n">
-        <v>515</v>
+        <v>518</v>
       </c>
       <c r="M29" s="2" t="n">
-        <v>1494</v>
+        <v>1528</v>
       </c>
       <c r="N29" s="2" t="n">
-        <v>450</v>
+        <v>453</v>
       </c>
       <c r="O29" s="2" t="n">
-        <v>446</v>
+        <v>449</v>
       </c>
       <c r="P29" s="3" t="n">
-        <v>2895</v>
+        <v>2935</v>
       </c>
       <c r="Q29" s="3" t="inlineStr">
         <is>
@@ -3199,7 +3199,7 @@
       </c>
       <c r="S29" s="3" t="inlineStr">
         <is>
-          <t>signal_reports_metadata.csv (446 rows), signal_vessel_counts_series.csv (106 rows), data/views/signal/live_fleet_positions.json (9,082 tracked hulls), data/views/signal/port_queues_active.json (1,932 ports)</t>
+          <t>signal_reports_metadata.csv (449 rows), signal_vessel_counts_series.csv (120 rows), data/views/signal/live_fleet_positions.json (9,082 tracked hulls), data/views/signal/port_queues_active.json (1,932 ports)</t>
         </is>
       </c>
       <c r="T29" s="3" t="inlineStr">
@@ -5376,7 +5376,7 @@
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>446 rows</t>
+          <t>449 rows</t>
         </is>
       </c>
       <c r="H31" s="3" t="inlineStr">

--- a/data/extracted/series/corpus_publication_cadence_and_audit.xlsx
+++ b/data/extracted/series/corpus_publication_cadence_and_audit.xlsx
@@ -550,7 +550,7 @@
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>Status (2026-10-09)</t>
+          <t>Status (2026-10-10)</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
@@ -837,11 +837,11 @@
         </is>
       </c>
       <c r="I4" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J4" s="4" t="inlineStr">
         <is>
-          <t>CURRENT (0d ago)</t>
+          <t>CURRENT (1d ago)</t>
         </is>
       </c>
       <c r="K4" s="2" t="n">
@@ -930,11 +930,11 @@
         </is>
       </c>
       <c r="I5" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J5" s="4" t="inlineStr">
         <is>
-          <t>CURRENT (2d ago)</t>
+          <t>CURRENT (3d ago)</t>
         </is>
       </c>
       <c r="K5" s="2" t="n">
@@ -1023,11 +1023,11 @@
         </is>
       </c>
       <c r="I6" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J6" s="4" t="inlineStr">
         <is>
-          <t>CURRENT (2d ago)</t>
+          <t>CURRENT (3d ago)</t>
         </is>
       </c>
       <c r="K6" s="2" t="n">
@@ -1209,11 +1209,11 @@
         </is>
       </c>
       <c r="I8" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J8" s="4" t="inlineStr">
         <is>
-          <t>CURRENT (1d ago)</t>
+          <t>CURRENT (2d ago)</t>
         </is>
       </c>
       <c r="K8" s="2" t="n">
@@ -1302,11 +1302,11 @@
         </is>
       </c>
       <c r="I9" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J9" s="4" t="inlineStr">
         <is>
-          <t>CURRENT (2d ago)</t>
+          <t>CURRENT (3d ago)</t>
         </is>
       </c>
       <c r="K9" s="2" t="n">
@@ -1395,11 +1395,11 @@
         </is>
       </c>
       <c r="I10" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J10" s="4" t="inlineStr">
         <is>
-          <t>CURRENT (2d ago)</t>
+          <t>CURRENT (3d ago)</t>
         </is>
       </c>
       <c r="K10" s="2" t="n">
@@ -1488,11 +1488,11 @@
         </is>
       </c>
       <c r="I11" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J11" s="4" t="inlineStr">
         <is>
-          <t>CURRENT (0d ago)</t>
+          <t>CURRENT (1d ago)</t>
         </is>
       </c>
       <c r="K11" s="2" t="n">
@@ -1581,11 +1581,11 @@
         </is>
       </c>
       <c r="I12" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J12" s="4" t="inlineStr">
         <is>
-          <t>CURRENT (2d ago)</t>
+          <t>CURRENT (3d ago)</t>
         </is>
       </c>
       <c r="K12" s="2" t="n">
@@ -1674,11 +1674,11 @@
         </is>
       </c>
       <c r="I13" s="2" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="J13" s="4" t="inlineStr">
         <is>
-          <t>CURRENT (11d ago)</t>
+          <t>CURRENT (12d ago)</t>
         </is>
       </c>
       <c r="K13" s="2" t="n">
@@ -1860,11 +1860,11 @@
         </is>
       </c>
       <c r="I15" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J15" s="4" t="inlineStr">
         <is>
-          <t>CURRENT (4d ago)</t>
+          <t>CURRENT (5d ago)</t>
         </is>
       </c>
       <c r="K15" s="2" t="n">
@@ -1953,11 +1953,11 @@
         </is>
       </c>
       <c r="I16" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J16" s="4" t="inlineStr">
         <is>
-          <t>CURRENT (4d ago)</t>
+          <t>CURRENT (5d ago)</t>
         </is>
       </c>
       <c r="K16" s="2" t="n">
@@ -2046,11 +2046,11 @@
         </is>
       </c>
       <c r="I17" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J17" s="4" t="inlineStr">
         <is>
-          <t>CURRENT (3d ago)</t>
+          <t>CURRENT (4d ago)</t>
         </is>
       </c>
       <c r="K17" s="2" t="n">
@@ -2232,11 +2232,11 @@
         </is>
       </c>
       <c r="I19" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J19" s="4" t="inlineStr">
         <is>
-          <t>CURRENT (2d ago)</t>
+          <t>CURRENT (3d ago)</t>
         </is>
       </c>
       <c r="K19" s="2" t="n">
@@ -2325,11 +2325,11 @@
         </is>
       </c>
       <c r="I20" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J20" s="4" t="inlineStr">
         <is>
-          <t>CURRENT (0d ago)</t>
+          <t>CURRENT (1d ago)</t>
         </is>
       </c>
       <c r="K20" s="2" t="n">
@@ -2418,11 +2418,11 @@
         </is>
       </c>
       <c r="I21" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J21" s="4" t="inlineStr">
         <is>
-          <t>CURRENT (3d ago)</t>
+          <t>CURRENT (4d ago)</t>
         </is>
       </c>
       <c r="K21" s="2" t="n">
@@ -2511,11 +2511,11 @@
         </is>
       </c>
       <c r="I22" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J22" s="4" t="inlineStr">
         <is>
-          <t>CURRENT (2d ago)</t>
+          <t>CURRENT (3d ago)</t>
         </is>
       </c>
       <c r="K22" s="2" t="n">
@@ -2604,11 +2604,11 @@
         </is>
       </c>
       <c r="I23" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J23" s="4" t="inlineStr">
         <is>
-          <t>CURRENT (3d ago)</t>
+          <t>CURRENT (4d ago)</t>
         </is>
       </c>
       <c r="K23" s="2" t="n">
@@ -2697,11 +2697,11 @@
         </is>
       </c>
       <c r="I24" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J24" s="4" t="inlineStr">
         <is>
-          <t>CURRENT (1d ago)</t>
+          <t>CURRENT (2d ago)</t>
         </is>
       </c>
       <c r="K24" s="2" t="n">
@@ -2790,11 +2790,11 @@
         </is>
       </c>
       <c r="I25" s="2" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="J25" s="4" t="inlineStr">
         <is>
-          <t>CURRENT (11d ago)</t>
+          <t>CURRENT (12d ago)</t>
         </is>
       </c>
       <c r="K25" s="2" t="n">
@@ -2883,11 +2883,11 @@
         </is>
       </c>
       <c r="I26" s="2" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="J26" s="5" t="inlineStr">
         <is>
-          <t>NORMAL INTERVAL (38d ago)</t>
+          <t>NORMAL INTERVAL (39d ago)</t>
         </is>
       </c>
       <c r="K26" s="2" t="n">
@@ -2976,11 +2976,11 @@
         </is>
       </c>
       <c r="I27" s="2" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="J27" s="5" t="inlineStr">
         <is>
-          <t>NORMAL INTERVAL (15d ago)</t>
+          <t>NORMAL INTERVAL (16d ago)</t>
         </is>
       </c>
       <c r="K27" s="2" t="n">
@@ -3069,11 +3069,11 @@
         </is>
       </c>
       <c r="I28" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J28" s="4" t="inlineStr">
         <is>
-          <t>CURRENT (8d ago)</t>
+          <t>CURRENT (9d ago)</t>
         </is>
       </c>
       <c r="K28" s="2" t="n">
@@ -3162,11 +3162,11 @@
         </is>
       </c>
       <c r="I29" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J29" s="4" t="inlineStr">
         <is>
-          <t>CURRENT (0d ago)</t>
+          <t>CURRENT (1d ago)</t>
         </is>
       </c>
       <c r="K29" s="2" t="n">
@@ -3255,11 +3255,11 @@
         </is>
       </c>
       <c r="I30" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J30" s="4" t="inlineStr">
         <is>
-          <t>CURRENT (0d ago)</t>
+          <t>CURRENT (1d ago)</t>
         </is>
       </c>
       <c r="K30" s="2" t="n">
@@ -3348,11 +3348,11 @@
         </is>
       </c>
       <c r="I31" s="2" t="n">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="J31" s="5" t="inlineStr">
         <is>
-          <t>NORMAL INTERVAL (73d ago)</t>
+          <t>NORMAL INTERVAL (74d ago)</t>
         </is>
       </c>
       <c r="K31" s="2" t="n">
@@ -3441,11 +3441,11 @@
         </is>
       </c>
       <c r="I32" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="J32" s="4" t="inlineStr">
         <is>
-          <t>CURRENT (7d ago)</t>
+          <t>CURRENT (8d ago)</t>
         </is>
       </c>
       <c r="K32" s="2" t="n">
@@ -3534,11 +3534,11 @@
         </is>
       </c>
       <c r="I33" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J33" s="4" t="inlineStr">
         <is>
-          <t>CURRENT (5d ago)</t>
+          <t>CURRENT (6d ago)</t>
         </is>
       </c>
       <c r="K33" s="2" t="n">

--- a/data/extracted/series/corpus_publication_cadence_and_audit.xlsx
+++ b/data/extracted/series/corpus_publication_cadence_and_audit.xlsx
@@ -550,7 +550,7 @@
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>Status (2026-10-10)</t>
+          <t>Status (2026-10-11)</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
@@ -651,11 +651,11 @@
         </is>
       </c>
       <c r="I2" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J2" s="4" t="inlineStr">
         <is>
-          <t>CURRENT (0d ago)</t>
+          <t>CURRENT (1d ago)</t>
         </is>
       </c>
       <c r="K2" s="2" t="n">
@@ -688,7 +688,7 @@
       </c>
       <c r="S2" s="3" t="inlineStr">
         <is>
-          <t>advanced_shipping_sales_series.csv (6,114 rows), advanced_shipping_demolition_series.csv (2,016 rows), advanced_shipping_secondhand_matrix_series.csv (8,110 rows), advanced_shipping_newbuilding_series.csv (1,911 rows), advanced_shipping_demo_sales_series.csv (601 rows)</t>
+          <t>advanced_shipping_sales_series.csv (6,114 rows), advanced_shipping_demolition_series.csv (2,016 rows), advanced_shipping_secondhand_matrix_series.csv (8,125 rows), advanced_shipping_newbuilding_series.csv (1,911 rows), advanced_shipping_demo_sales_series.csv (601 rows)</t>
         </is>
       </c>
       <c r="T2" s="3" t="inlineStr">
@@ -744,11 +744,11 @@
         </is>
       </c>
       <c r="I3" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J3" s="4" t="inlineStr">
         <is>
-          <t>CURRENT (0d ago)</t>
+          <t>CURRENT (1d ago)</t>
         </is>
       </c>
       <c r="K3" s="2" t="n">
@@ -837,11 +837,11 @@
         </is>
       </c>
       <c r="I4" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J4" s="4" t="inlineStr">
         <is>
-          <t>CURRENT (1d ago)</t>
+          <t>CURRENT (2d ago)</t>
         </is>
       </c>
       <c r="K4" s="2" t="n">
@@ -930,11 +930,11 @@
         </is>
       </c>
       <c r="I5" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J5" s="4" t="inlineStr">
         <is>
-          <t>CURRENT (3d ago)</t>
+          <t>CURRENT (4d ago)</t>
         </is>
       </c>
       <c r="K5" s="2" t="n">
@@ -1023,11 +1023,11 @@
         </is>
       </c>
       <c r="I6" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J6" s="4" t="inlineStr">
         <is>
-          <t>CURRENT (3d ago)</t>
+          <t>CURRENT (4d ago)</t>
         </is>
       </c>
       <c r="K6" s="2" t="n">
@@ -1060,7 +1060,7 @@
       </c>
       <c r="S6" s="3" t="inlineStr">
         <is>
-          <t>carriers_sales_series.csv (3,165 rows), carriers_dry_tc_period_series.csv (3,216 rows), carriers_indices_series.csv (1,876 rows), carriers_tanker_tce_series.csv (804 rows), carriers_bspa_series.csv (755 rows), carriers_newbuilding_series.csv (312 rows), carriers_demolition_series.csv (178 rows)</t>
+          <t>carriers_sales_series.csv (3,165 rows), carriers_dry_tc_period_series.csv (3,216 rows), carriers_indices_series.csv (1,876 rows), carriers_tanker_tce_series.csv (804 rows), carriers_bspa_series.csv (809 rows), carriers_newbuilding_series.csv (312 rows), carriers_demolition_series.csv (178 rows)</t>
         </is>
       </c>
       <c r="T6" s="3" t="inlineStr">
@@ -1209,11 +1209,11 @@
         </is>
       </c>
       <c r="I8" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J8" s="4" t="inlineStr">
         <is>
-          <t>CURRENT (2d ago)</t>
+          <t>CURRENT (3d ago)</t>
         </is>
       </c>
       <c r="K8" s="2" t="n">
@@ -1302,11 +1302,11 @@
         </is>
       </c>
       <c r="I9" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J9" s="4" t="inlineStr">
         <is>
-          <t>CURRENT (3d ago)</t>
+          <t>CURRENT (4d ago)</t>
         </is>
       </c>
       <c r="K9" s="2" t="n">
@@ -1395,11 +1395,11 @@
         </is>
       </c>
       <c r="I10" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J10" s="4" t="inlineStr">
         <is>
-          <t>CURRENT (3d ago)</t>
+          <t>CURRENT (4d ago)</t>
         </is>
       </c>
       <c r="K10" s="2" t="n">
@@ -1488,11 +1488,11 @@
         </is>
       </c>
       <c r="I11" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J11" s="4" t="inlineStr">
         <is>
-          <t>CURRENT (1d ago)</t>
+          <t>CURRENT (2d ago)</t>
         </is>
       </c>
       <c r="K11" s="2" t="n">
@@ -1581,11 +1581,11 @@
         </is>
       </c>
       <c r="I12" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J12" s="4" t="inlineStr">
         <is>
-          <t>CURRENT (3d ago)</t>
+          <t>CURRENT (4d ago)</t>
         </is>
       </c>
       <c r="K12" s="2" t="n">
@@ -1674,11 +1674,11 @@
         </is>
       </c>
       <c r="I13" s="2" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="J13" s="4" t="inlineStr">
         <is>
-          <t>CURRENT (12d ago)</t>
+          <t>CURRENT (13d ago)</t>
         </is>
       </c>
       <c r="K13" s="2" t="n">
@@ -1860,11 +1860,11 @@
         </is>
       </c>
       <c r="I15" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J15" s="4" t="inlineStr">
         <is>
-          <t>CURRENT (5d ago)</t>
+          <t>CURRENT (6d ago)</t>
         </is>
       </c>
       <c r="K15" s="2" t="n">
@@ -1897,7 +1897,7 @@
       </c>
       <c r="S15" s="3" t="inlineStr">
         <is>
-          <t>ssy_capesize_index_series.csv (8,729 rows), ssy_capesize_series.csv (8,881 rows), ssy_route_rates_series.csv (5,170 rows), ssy_capesize_index_time_series.csv (517 rows)</t>
+          <t>ssy_capesize_index_series.csv (8,731 rows), ssy_capesize_series.csv (8,881 rows), ssy_route_rates_series.csv (5,170 rows), ssy_capesize_index_time_series.csv (517 rows)</t>
         </is>
       </c>
       <c r="T15" s="3" t="inlineStr">
@@ -1953,11 +1953,11 @@
         </is>
       </c>
       <c r="I16" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J16" s="4" t="inlineStr">
         <is>
-          <t>CURRENT (5d ago)</t>
+          <t>CURRENT (6d ago)</t>
         </is>
       </c>
       <c r="K16" s="2" t="n">
@@ -2046,11 +2046,11 @@
         </is>
       </c>
       <c r="I17" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J17" s="4" t="inlineStr">
         <is>
-          <t>CURRENT (4d ago)</t>
+          <t>CURRENT (5d ago)</t>
         </is>
       </c>
       <c r="K17" s="2" t="n">
@@ -2139,11 +2139,11 @@
         </is>
       </c>
       <c r="I18" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J18" s="4" t="inlineStr">
         <is>
-          <t>CURRENT (0d ago)</t>
+          <t>CURRENT (1d ago)</t>
         </is>
       </c>
       <c r="K18" s="2" t="n">
@@ -2159,7 +2159,7 @@
         <v>0</v>
       </c>
       <c r="O18" s="2" t="n">
-        <v>1800</v>
+        <v>1275</v>
       </c>
       <c r="P18" s="3" t="n">
         <v>4172</v>
@@ -2176,7 +2176,7 @@
       </c>
       <c r="S18" s="3" t="inlineStr">
         <is>
-          <t>hellenic_athenian_demolition_series.csv (2,916 rows), hellenic_gms_port_positions_series.csv (2,921 rows), hellenic_gms_demolition_series.csv (1,096 rows), hellenic_best_oasis_deals_series.csv (892 rows), hellenic_best_oasis_demolition_series.csv (867 rows)</t>
+          <t>athenian_indicative_demolition_series.csv (3,064 rows), hellenic_gms_port_positions_series.csv (3,014 rows), hellenic_gms_demolition_series.csv (1,104 rows), hellenic_best_oasis_deals_series.csv (905 rows), hellenic_best_oasis_demolition_series.csv (866 rows)</t>
         </is>
       </c>
       <c r="T18" s="3" t="inlineStr">
@@ -2232,11 +2232,11 @@
         </is>
       </c>
       <c r="I19" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J19" s="4" t="inlineStr">
         <is>
-          <t>CURRENT (3d ago)</t>
+          <t>CURRENT (4d ago)</t>
         </is>
       </c>
       <c r="K19" s="2" t="n">
@@ -2325,11 +2325,11 @@
         </is>
       </c>
       <c r="I20" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J20" s="4" t="inlineStr">
         <is>
-          <t>CURRENT (1d ago)</t>
+          <t>CURRENT (2d ago)</t>
         </is>
       </c>
       <c r="K20" s="2" t="n">
@@ -2418,11 +2418,11 @@
         </is>
       </c>
       <c r="I21" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J21" s="4" t="inlineStr">
         <is>
-          <t>CURRENT (4d ago)</t>
+          <t>CURRENT (5d ago)</t>
         </is>
       </c>
       <c r="K21" s="2" t="n">
@@ -2511,11 +2511,11 @@
         </is>
       </c>
       <c r="I22" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J22" s="4" t="inlineStr">
         <is>
-          <t>CURRENT (3d ago)</t>
+          <t>CURRENT (4d ago)</t>
         </is>
       </c>
       <c r="K22" s="2" t="n">
@@ -2604,11 +2604,11 @@
         </is>
       </c>
       <c r="I23" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J23" s="4" t="inlineStr">
         <is>
-          <t>CURRENT (4d ago)</t>
+          <t>CURRENT (5d ago)</t>
         </is>
       </c>
       <c r="K23" s="2" t="n">
@@ -2641,7 +2641,7 @@
       </c>
       <c r="S23" s="3" t="inlineStr">
         <is>
-          <t>hellenic_vv_matrix_series.csv (12,350 rows), hellenic_vv_sales_series.csv (2,030 rows)</t>
+          <t>hellenic_vv_matrix_series.csv (12,373 rows), hellenic_vv_sales_series.csv (2,067 rows)</t>
         </is>
       </c>
       <c r="T23" s="3" t="inlineStr">
@@ -2697,11 +2697,11 @@
         </is>
       </c>
       <c r="I24" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J24" s="4" t="inlineStr">
         <is>
-          <t>CURRENT (2d ago)</t>
+          <t>CURRENT (3d ago)</t>
         </is>
       </c>
       <c r="K24" s="2" t="n">
@@ -2790,11 +2790,11 @@
         </is>
       </c>
       <c r="I25" s="2" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="J25" s="4" t="inlineStr">
         <is>
-          <t>CURRENT (12d ago)</t>
+          <t>CURRENT (13d ago)</t>
         </is>
       </c>
       <c r="K25" s="2" t="n">
@@ -2883,11 +2883,11 @@
         </is>
       </c>
       <c r="I26" s="2" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="J26" s="5" t="inlineStr">
         <is>
-          <t>NORMAL INTERVAL (39d ago)</t>
+          <t>NORMAL INTERVAL (40d ago)</t>
         </is>
       </c>
       <c r="K26" s="2" t="n">
@@ -2976,15 +2976,15 @@
         </is>
       </c>
       <c r="I27" s="2" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="J27" s="5" t="inlineStr">
         <is>
-          <t>NORMAL INTERVAL (16d ago)</t>
+          <t>NORMAL INTERVAL (17d ago)</t>
         </is>
       </c>
       <c r="K27" s="2" t="n">
-        <v>288</v>
+        <v>291</v>
       </c>
       <c r="L27" s="2" t="n">
         <v>0</v>
@@ -2996,10 +2996,10 @@
         <v>0</v>
       </c>
       <c r="O27" s="2" t="n">
-        <v>288</v>
+        <v>291</v>
       </c>
       <c r="P27" s="3" t="n">
-        <v>289</v>
+        <v>292</v>
       </c>
       <c r="Q27" s="3" t="inlineStr">
         <is>
@@ -3013,7 +3013,7 @@
       </c>
       <c r="S27" s="3" t="inlineStr">
         <is>
-          <t>drewry_ais_fleet_performance_series.csv (14,768 rows), drewry_ais_regional_congestion_series.csv (6,792 rows), drewry_ais_deployment_speed_series.csv (2,427 rows), drewry_ais_utilisation_curves_series.csv (1,007 rows)</t>
+          <t>drewry_ais_fleet_performance_series.csv (14,828 rows), drewry_ais_regional_congestion_series.csv (6,840 rows), drewry_ais_deployment_speed_series.csv (2,634 rows), drewry_ais_utilisation_curves_series.csv (809 rows)</t>
         </is>
       </c>
       <c r="T27" s="3" t="inlineStr">
@@ -3065,15 +3065,15 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="I28" s="2" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="J28" s="4" t="inlineStr">
         <is>
-          <t>CURRENT (9d ago)</t>
+          <t>CURRENT (3d ago)</t>
         </is>
       </c>
       <c r="K28" s="2" t="n">
@@ -3086,10 +3086,10 @@
         <v>0</v>
       </c>
       <c r="N28" s="2" t="n">
-        <v>1092</v>
+        <v>1093</v>
       </c>
       <c r="O28" s="2" t="n">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="P28" s="3" t="n">
         <v>1108</v>
@@ -3106,7 +3106,7 @@
       </c>
       <c r="S28" s="3" t="inlineStr">
         <is>
-          <t>drewry_wci_historical.csv (136 rows), drewry_opinions_metadata.csv (551 rows), drewry_wci_series.csv (6 rows)</t>
+          <t>drewry_wci_historical.csv (137 rows), drewry_opinions_metadata.csv (552 rows), drewry_wci_series.csv (7 rows)</t>
         </is>
       </c>
       <c r="T28" s="3" t="inlineStr">
@@ -3162,11 +3162,11 @@
         </is>
       </c>
       <c r="I29" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J29" s="4" t="inlineStr">
         <is>
-          <t>CURRENT (1d ago)</t>
+          <t>CURRENT (2d ago)</t>
         </is>
       </c>
       <c r="K29" s="2" t="n">
@@ -3255,11 +3255,11 @@
         </is>
       </c>
       <c r="I30" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J30" s="4" t="inlineStr">
         <is>
-          <t>CURRENT (1d ago)</t>
+          <t>CURRENT (2d ago)</t>
         </is>
       </c>
       <c r="K30" s="2" t="n">
@@ -3348,11 +3348,11 @@
         </is>
       </c>
       <c r="I31" s="2" t="n">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="J31" s="5" t="inlineStr">
         <is>
-          <t>NORMAL INTERVAL (74d ago)</t>
+          <t>NORMAL INTERVAL (75d ago)</t>
         </is>
       </c>
       <c r="K31" s="2" t="n">
@@ -3437,15 +3437,15 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="I32" s="2" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="J32" s="4" t="inlineStr">
         <is>
-          <t>CURRENT (8d ago)</t>
+          <t>CURRENT (2d ago)</t>
         </is>
       </c>
       <c r="K32" s="2" t="n">
@@ -3458,13 +3458,13 @@
         <v>0</v>
       </c>
       <c r="N32" s="2" t="n">
-        <v>1310</v>
+        <v>1311</v>
       </c>
       <c r="O32" s="2" t="n">
         <v>1310</v>
       </c>
       <c r="P32" s="3" t="n">
-        <v>1310</v>
+        <v>1311</v>
       </c>
       <c r="Q32" s="3" t="inlineStr">
         <is>
@@ -3534,11 +3534,11 @@
         </is>
       </c>
       <c r="I33" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J33" s="4" t="inlineStr">
         <is>
-          <t>CURRENT (6d ago)</t>
+          <t>CURRENT (7d ago)</t>
         </is>
       </c>
       <c r="K33" s="2" t="n">
@@ -4013,7 +4013,7 @@
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>14,768 rows</t>
+          <t>14,828 rows</t>
         </is>
       </c>
       <c r="H2" s="3" t="inlineStr">
@@ -4060,7 +4060,7 @@
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>14,768 rows</t>
+          <t>14,828 rows</t>
         </is>
       </c>
       <c r="H3" s="3" t="inlineStr">
@@ -4107,7 +4107,7 @@
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>14,768 rows</t>
+          <t>14,828 rows</t>
         </is>
       </c>
       <c r="H4" s="3" t="inlineStr">
@@ -4154,7 +4154,7 @@
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>14,768 rows</t>
+          <t>14,828 rows</t>
         </is>
       </c>
       <c r="H5" s="3" t="inlineStr">
@@ -4201,7 +4201,7 @@
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>14,768 rows</t>
+          <t>14,828 rows</t>
         </is>
       </c>
       <c r="H6" s="3" t="inlineStr">
@@ -4248,7 +4248,7 @@
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>14,768 rows</t>
+          <t>14,828 rows</t>
         </is>
       </c>
       <c r="H7" s="3" t="inlineStr">
@@ -4295,7 +4295,7 @@
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>14,768 rows</t>
+          <t>14,828 rows</t>
         </is>
       </c>
       <c r="H8" s="3" t="inlineStr">
@@ -4342,7 +4342,7 @@
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>14,768 rows</t>
+          <t>14,828 rows</t>
         </is>
       </c>
       <c r="H9" s="3" t="inlineStr">
@@ -4389,7 +4389,7 @@
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>14,768 rows</t>
+          <t>14,828 rows</t>
         </is>
       </c>
       <c r="H10" s="3" t="inlineStr">
@@ -4436,7 +4436,7 @@
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>14,768 rows</t>
+          <t>14,828 rows</t>
         </is>
       </c>
       <c r="H11" s="3" t="inlineStr">
@@ -4483,7 +4483,7 @@
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>6,792 rows</t>
+          <t>6,840 rows</t>
         </is>
       </c>
       <c r="H12" s="3" t="inlineStr">
@@ -4530,7 +4530,7 @@
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>2,427 rows</t>
+          <t>2,634 rows</t>
         </is>
       </c>
       <c r="H13" s="3" t="inlineStr">
@@ -4577,7 +4577,7 @@
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>1,007 rows</t>
+          <t>809 rows</t>
         </is>
       </c>
       <c r="H14" s="3" t="inlineStr">
@@ -4619,12 +4619,12 @@
       </c>
       <c r="F15" s="3" t="inlineStr">
         <is>
-          <t>hellenic_athenian_demolition_series.csv</t>
+          <t>athenian_indicative_demolition_series.csv</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>2,916 rows</t>
+          <t>3,064 rows</t>
         </is>
       </c>
       <c r="H15" s="3" t="inlineStr">
@@ -4671,7 +4671,7 @@
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>1,096 rows</t>
+          <t>1,104 rows</t>
         </is>
       </c>
       <c r="H16" s="3" t="inlineStr">
@@ -4718,7 +4718,7 @@
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>2,921 rows</t>
+          <t>3,014 rows</t>
         </is>
       </c>
       <c r="H17" s="3" t="inlineStr">
@@ -4765,7 +4765,7 @@
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>892 rows</t>
+          <t>905 rows</t>
         </is>
       </c>
       <c r="H18" s="3" t="inlineStr">
@@ -5047,7 +5047,7 @@
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>12,350 rows</t>
+          <t>12,373 rows</t>
         </is>
       </c>
       <c r="H24" s="3" t="inlineStr">
@@ -5094,7 +5094,7 @@
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>2,030 rows</t>
+          <t>2,067 rows</t>
         </is>
       </c>
       <c r="H25" s="3" t="inlineStr">
@@ -5611,7 +5611,7 @@
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>136 rows</t>
+          <t>137 rows</t>
         </is>
       </c>
       <c r="H36" s="3" t="inlineStr">

--- a/data/extracted/series/corpus_publication_cadence_and_audit.xlsx
+++ b/data/extracted/series/corpus_publication_cadence_and_audit.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Corpus Cadence &amp; Inventory" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Graphic &amp; Chart Extraction" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Sub-Sector &amp; Fleet Breakdown" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Corpus Cadence &amp; Inventory" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Graphic &amp; Chart Extraction" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sub-Sector &amp; Fleet Breakdown" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -550,7 +550,7 @@
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>Status (2026-10-11)</t>
+          <t>Status (2026-10-12)</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
@@ -651,11 +651,11 @@
         </is>
       </c>
       <c r="I2" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J2" s="4" t="inlineStr">
         <is>
-          <t>CURRENT (1d ago)</t>
+          <t>CURRENT (2d ago)</t>
         </is>
       </c>
       <c r="K2" s="2" t="n">
@@ -671,7 +671,7 @@
         <v>0</v>
       </c>
       <c r="O2" s="2" t="n">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="P2" s="3" t="n">
         <v>257</v>
@@ -688,7 +688,7 @@
       </c>
       <c r="S2" s="3" t="inlineStr">
         <is>
-          <t>advanced_shipping_sales_series.csv (6,114 rows), advanced_shipping_demolition_series.csv (2,016 rows), advanced_shipping_secondhand_matrix_series.csv (8,125 rows), advanced_shipping_newbuilding_series.csv (1,911 rows), advanced_shipping_demo_sales_series.csv (601 rows)</t>
+          <t>advanced_shipping_sales_series.csv (6,097 rows), advanced_shipping_demolition_series.csv (2,000 rows), advanced_shipping_secondhand_matrix_series.csv (8,093 rows), advanced_shipping_newbuilding_series.csv (1,898 rows), advanced_shipping_demo_sales_series.csv (599 rows)</t>
         </is>
       </c>
       <c r="T2" s="3" t="inlineStr">
@@ -744,11 +744,11 @@
         </is>
       </c>
       <c r="I3" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J3" s="4" t="inlineStr">
         <is>
-          <t>CURRENT (1d ago)</t>
+          <t>CURRENT (2d ago)</t>
         </is>
       </c>
       <c r="K3" s="2" t="n">
@@ -837,11 +837,11 @@
         </is>
       </c>
       <c r="I4" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J4" s="4" t="inlineStr">
         <is>
-          <t>CURRENT (2d ago)</t>
+          <t>CURRENT (3d ago)</t>
         </is>
       </c>
       <c r="K4" s="2" t="n">
@@ -857,7 +857,7 @@
         <v>0</v>
       </c>
       <c r="O4" s="2" t="n">
-        <v>221</v>
+        <v>216</v>
       </c>
       <c r="P4" s="3" t="n">
         <v>221</v>
@@ -930,11 +930,11 @@
         </is>
       </c>
       <c r="I5" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J5" s="4" t="inlineStr">
         <is>
-          <t>CURRENT (4d ago)</t>
+          <t>CURRENT (5d ago)</t>
         </is>
       </c>
       <c r="K5" s="2" t="n">
@@ -950,7 +950,7 @@
         <v>0</v>
       </c>
       <c r="O5" s="2" t="n">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="P5" s="3" t="n">
         <v>250</v>
@@ -967,7 +967,7 @@
       </c>
       <c r="S5" s="3" t="inlineStr">
         <is>
-          <t>bancosta_freight_rates_series.csv (20,677 rows), bancosta_ffa_series.csv (7,762 rows), bancosta_sales_series.csv (3,264 rows), bancosta_commodities_series.csv (8,582 rows), bancosta_newbuilding_series.csv (2,377 rows), bancosta_secondhand_matrix_series.csv (1,898 rows), bancosta_demolition_series.csv (959 rows)</t>
+          <t>bancosta_freight_rates_series.csv (20,587 rows), bancosta_ffa_series.csv (7,726 rows), bancosta_sales_series.csv (3,240 rows), bancosta_commodities_series.csv (8,546 rows), bancosta_newbuilding_series.csv (2,377 rows), bancosta_secondhand_matrix_series.csv (1,898 rows), bancosta_demolition_series.csv (959 rows)</t>
         </is>
       </c>
       <c r="T5" s="3" t="inlineStr">
@@ -1023,11 +1023,11 @@
         </is>
       </c>
       <c r="I6" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J6" s="4" t="inlineStr">
         <is>
-          <t>CURRENT (4d ago)</t>
+          <t>CURRENT (5d ago)</t>
         </is>
       </c>
       <c r="K6" s="2" t="n">
@@ -1043,7 +1043,7 @@
         <v>0</v>
       </c>
       <c r="O6" s="2" t="n">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="P6" s="3" t="n">
         <v>138</v>
@@ -1060,7 +1060,7 @@
       </c>
       <c r="S6" s="3" t="inlineStr">
         <is>
-          <t>carriers_sales_series.csv (3,165 rows), carriers_dry_tc_period_series.csv (3,216 rows), carriers_indices_series.csv (1,876 rows), carriers_tanker_tce_series.csv (804 rows), carriers_bspa_series.csv (809 rows), carriers_newbuilding_series.csv (312 rows), carriers_demolition_series.csv (178 rows)</t>
+          <t>carriers_sales_series.csv (3,060 rows), carriers_dry_tc_period_series.csv (3,096 rows), carriers_indices_series.csv (1,806 rows), carriers_tanker_tce_series.csv (774 rows), carriers_bspa_series.csv (779 rows), carriers_newbuilding_series.csv (302 rows), carriers_demolition_series.csv (170 rows)</t>
         </is>
       </c>
       <c r="T6" s="3" t="inlineStr">
@@ -1205,7 +1205,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="I8" s="2" t="n">
@@ -1226,13 +1226,13 @@
         <v>0</v>
       </c>
       <c r="N8" s="2" t="n">
-        <v>4750</v>
+        <v>4763</v>
       </c>
       <c r="O8" s="2" t="n">
-        <v>12009</v>
+        <v>12021</v>
       </c>
       <c r="P8" s="3" t="n">
-        <v>5015</v>
+        <v>5028</v>
       </c>
       <c r="Q8" s="3" t="inlineStr">
         <is>
@@ -1298,15 +1298,15 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="I9" s="2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J9" s="4" t="inlineStr">
         <is>
-          <t>CURRENT (4d ago)</t>
+          <t>CURRENT (3d ago)</t>
         </is>
       </c>
       <c r="K9" s="2" t="n">
@@ -1319,10 +1319,10 @@
         <v>0</v>
       </c>
       <c r="N9" s="2" t="n">
-        <v>4750</v>
+        <v>4763</v>
       </c>
       <c r="O9" s="2" t="n">
-        <v>11750</v>
+        <v>11760</v>
       </c>
       <c r="P9" s="3" t="n">
         <v>11750</v>
@@ -1395,11 +1395,11 @@
         </is>
       </c>
       <c r="I10" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J10" s="4" t="inlineStr">
         <is>
-          <t>CURRENT (4d ago)</t>
+          <t>CURRENT (5d ago)</t>
         </is>
       </c>
       <c r="K10" s="2" t="n">
@@ -1412,27 +1412,27 @@
         <v>2847</v>
       </c>
       <c r="N10" s="2" t="n">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="O10" s="2" t="n">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="P10" s="3" t="n">
-        <v>3216</v>
+        <v>3215</v>
       </c>
       <c r="Q10" s="3" t="inlineStr">
         <is>
-          <t>Yes (Top 52 econometric recurring lead-indicator models)</t>
+          <t>No (raster PNG charts carry no data; chart titles and printed tables only)</t>
         </is>
       </c>
       <c r="R10" s="3" t="inlineStr">
         <is>
-          <t>Proprietary Dynamic Affine Calibration Engine (R^2 &gt;= 0.999)</t>
+          <t>API content-block renderer (fearnleys_md_rebuild.py); chart values are not read</t>
         </is>
       </c>
       <c r="S10" s="3" t="inlineStr">
         <is>
-          <t>fearnleys_md_master_econometric_series.xlsx (6 sheets, 26 lead models), fearnleys_md_vessel_tightness_series.csv (115 rows), fearnleys_md_macro_correlations_series.csv (78 rows), fearnleys_md_coal_futures_spread_series.csv (48 rows), fearnleys_md_shipment_volumes_series.csv (43 rows)</t>
+          <t>fearnleys-md .tables.json sidecars (56 exact API tables, 14 printed Cape composite-model tables, chart titles); earlier chart series quarantined in data/_quarantine/fearnleys_md/</t>
         </is>
       </c>
       <c r="T10" s="3" t="inlineStr">
@@ -1442,7 +1442,7 @@
       </c>
       <c r="U10" s="3" t="inlineStr">
         <is>
-          <t>2,827 high-res vector charts extracted and calibrated. First/last pages discarded per rule.</t>
+          <t>Charts are raster PNGs kept as images with their titles; the earlier calibrated chart series were wrong and are quarantined.</t>
         </is>
       </c>
     </row>
@@ -1488,18 +1488,18 @@
         </is>
       </c>
       <c r="I11" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J11" s="4" t="inlineStr">
         <is>
-          <t>CURRENT (2d ago)</t>
+          <t>CURRENT (3d ago)</t>
         </is>
       </c>
       <c r="K11" s="2" t="n">
         <v>109</v>
       </c>
       <c r="L11" s="2" t="n">
-        <v>170</v>
+        <v>165</v>
       </c>
       <c r="M11" s="2" t="n">
         <v>0</v>
@@ -1508,10 +1508,10 @@
         <v>0</v>
       </c>
       <c r="O11" s="2" t="n">
-        <v>267</v>
+        <v>264</v>
       </c>
       <c r="P11" s="3" t="n">
-        <v>279</v>
+        <v>274</v>
       </c>
       <c r="Q11" s="3" t="inlineStr">
         <is>
@@ -1525,7 +1525,7 @@
       </c>
       <c r="S11" s="3" t="inlineStr">
         <is>
-          <t>gibson_tanker_spot_series.csv (3,630 rows), gibson_bunker_prices_series.csv (1,023 rows), gibson_master_tanker_series.xlsx</t>
+          <t>gibson_tanker_spot_series.csv (3,598 rows), gibson_bunker_prices_series.csv (1,028 rows), gibson_master_tanker_series.xlsx</t>
         </is>
       </c>
       <c r="T11" s="3" t="inlineStr">
@@ -1581,11 +1581,11 @@
         </is>
       </c>
       <c r="I12" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J12" s="4" t="inlineStr">
         <is>
-          <t>CURRENT (4d ago)</t>
+          <t>CURRENT (5d ago)</t>
         </is>
       </c>
       <c r="K12" s="2" t="n">
@@ -1601,7 +1601,7 @@
         <v>0</v>
       </c>
       <c r="O12" s="2" t="n">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="P12" s="3" t="n">
         <v>259</v>
@@ -1674,11 +1674,11 @@
         </is>
       </c>
       <c r="I13" s="2" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="J13" s="4" t="inlineStr">
         <is>
-          <t>CURRENT (13d ago)</t>
+          <t>CURRENT (14d ago)</t>
         </is>
       </c>
       <c r="K13" s="2" t="n">
@@ -1787,7 +1787,7 @@
         <v>0</v>
       </c>
       <c r="O14" s="2" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="P14" s="3" t="n">
         <v>50</v>
@@ -1860,11 +1860,11 @@
         </is>
       </c>
       <c r="I15" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J15" s="4" t="inlineStr">
         <is>
-          <t>CURRENT (6d ago)</t>
+          <t>CURRENT (7d ago)</t>
         </is>
       </c>
       <c r="K15" s="2" t="n">
@@ -1953,11 +1953,11 @@
         </is>
       </c>
       <c r="I16" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J16" s="4" t="inlineStr">
         <is>
-          <t>CURRENT (6d ago)</t>
+          <t>CURRENT (7d ago)</t>
         </is>
       </c>
       <c r="K16" s="2" t="n">
@@ -2046,11 +2046,11 @@
         </is>
       </c>
       <c r="I17" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J17" s="4" t="inlineStr">
         <is>
-          <t>CURRENT (5d ago)</t>
+          <t>CURRENT (6d ago)</t>
         </is>
       </c>
       <c r="K17" s="2" t="n">
@@ -2066,7 +2066,7 @@
         <v>0</v>
       </c>
       <c r="O17" s="2" t="n">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="P17" s="3" t="n">
         <v>273</v>
@@ -2139,11 +2139,11 @@
         </is>
       </c>
       <c r="I18" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J18" s="4" t="inlineStr">
         <is>
-          <t>CURRENT (1d ago)</t>
+          <t>CURRENT (2d ago)</t>
         </is>
       </c>
       <c r="K18" s="2" t="n">
@@ -2232,11 +2232,11 @@
         </is>
       </c>
       <c r="I19" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J19" s="4" t="inlineStr">
         <is>
-          <t>CURRENT (4d ago)</t>
+          <t>CURRENT (5d ago)</t>
         </is>
       </c>
       <c r="K19" s="2" t="n">
@@ -2325,11 +2325,11 @@
         </is>
       </c>
       <c r="I20" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J20" s="4" t="inlineStr">
         <is>
-          <t>CURRENT (2d ago)</t>
+          <t>CURRENT (3d ago)</t>
         </is>
       </c>
       <c r="K20" s="2" t="n">
@@ -2345,7 +2345,7 @@
         <v>0</v>
       </c>
       <c r="O20" s="2" t="n">
-        <v>1201</v>
+        <v>1189</v>
       </c>
       <c r="P20" s="3" t="n">
         <v>9057</v>
@@ -2418,11 +2418,11 @@
         </is>
       </c>
       <c r="I21" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J21" s="4" t="inlineStr">
         <is>
-          <t>CURRENT (5d ago)</t>
+          <t>CURRENT (6d ago)</t>
         </is>
       </c>
       <c r="K21" s="2" t="n">
@@ -2511,11 +2511,11 @@
         </is>
       </c>
       <c r="I22" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J22" s="4" t="inlineStr">
         <is>
-          <t>CURRENT (4d ago)</t>
+          <t>CURRENT (5d ago)</t>
         </is>
       </c>
       <c r="K22" s="2" t="n">
@@ -2604,11 +2604,11 @@
         </is>
       </c>
       <c r="I23" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J23" s="4" t="inlineStr">
         <is>
-          <t>CURRENT (5d ago)</t>
+          <t>CURRENT (6d ago)</t>
         </is>
       </c>
       <c r="K23" s="2" t="n">
@@ -2697,11 +2697,11 @@
         </is>
       </c>
       <c r="I24" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J24" s="4" t="inlineStr">
         <is>
-          <t>CURRENT (3d ago)</t>
+          <t>CURRENT (4d ago)</t>
         </is>
       </c>
       <c r="K24" s="2" t="n">
@@ -2717,7 +2717,7 @@
         <v>3216</v>
       </c>
       <c r="O24" s="2" t="n">
-        <v>3508</v>
+        <v>3507</v>
       </c>
       <c r="P24" s="3" t="n">
         <v>21868</v>
@@ -2786,19 +2786,19 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="I25" s="2" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="J25" s="4" t="inlineStr">
         <is>
-          <t>CURRENT (13d ago)</t>
+          <t>CURRENT (0d ago)</t>
         </is>
       </c>
       <c r="K25" s="2" t="n">
-        <v>1087</v>
+        <v>1094</v>
       </c>
       <c r="L25" s="2" t="n">
         <v>0</v>
@@ -2807,10 +2807,10 @@
         <v>0</v>
       </c>
       <c r="N25" s="2" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="O25" s="2" t="n">
-        <v>1087</v>
+        <v>1090</v>
       </c>
       <c r="P25" s="3" t="n">
         <v>3270</v>
@@ -2827,7 +2827,7 @@
       </c>
       <c r="S25" s="3" t="inlineStr">
         <is>
-          <t>poten_opinions_metadata.csv (1,087 rows), poten_top_charterers_series.csv (756 rows), poten_fixtures_series.csv (100 rows)</t>
+          <t>poten_opinions_metadata.csv (1,094 rows), poten_top_charterers_series.csv (776 rows), poten_fixtures_series.csv (100 rows)</t>
         </is>
       </c>
       <c r="T25" s="3" t="inlineStr">
@@ -2883,15 +2883,15 @@
         </is>
       </c>
       <c r="I26" s="2" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="J26" s="5" t="inlineStr">
         <is>
-          <t>NORMAL INTERVAL (40d ago)</t>
+          <t>NORMAL INTERVAL (41d ago)</t>
         </is>
       </c>
       <c r="K26" s="2" t="n">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="L26" s="2" t="n">
         <v>0</v>
@@ -2906,7 +2906,7 @@
         <v>98</v>
       </c>
       <c r="P26" s="3" t="n">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="Q26" s="3" t="inlineStr">
         <is>
@@ -2920,7 +2920,7 @@
       </c>
       <c r="S26" s="3" t="inlineStr">
         <is>
-          <t>seabrokers_osv_monthly_history_series.csv (6,280 rows), seabrokers_rigs_market_series.csv (4,467 rows), seabrokers_osv_utilisation_series.csv (2,304 rows), seabrokers_osv_spot_rates_series.csv (1,855 rows)</t>
+          <t>seabrokers_osv_monthly_history_series.csv (6,376 rows), seabrokers_rigs_market_series.csv (4,482 rows), seabrokers_osv_utilisation_series.csv (2,328 rows), seabrokers_osv_spot_rates_series.csv (1,875 rows)</t>
         </is>
       </c>
       <c r="T26" s="3" t="inlineStr">
@@ -2976,11 +2976,11 @@
         </is>
       </c>
       <c r="I27" s="2" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="J27" s="5" t="inlineStr">
         <is>
-          <t>NORMAL INTERVAL (17d ago)</t>
+          <t>NORMAL INTERVAL (18d ago)</t>
         </is>
       </c>
       <c r="K27" s="2" t="n">
@@ -3069,11 +3069,11 @@
         </is>
       </c>
       <c r="I28" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J28" s="4" t="inlineStr">
         <is>
-          <t>CURRENT (3d ago)</t>
+          <t>CURRENT (4d ago)</t>
         </is>
       </c>
       <c r="K28" s="2" t="n">
@@ -3162,11 +3162,11 @@
         </is>
       </c>
       <c r="I29" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J29" s="4" t="inlineStr">
         <is>
-          <t>CURRENT (2d ago)</t>
+          <t>CURRENT (3d ago)</t>
         </is>
       </c>
       <c r="K29" s="2" t="n">
@@ -3176,7 +3176,7 @@
         <v>518</v>
       </c>
       <c r="M29" s="2" t="n">
-        <v>1528</v>
+        <v>1531</v>
       </c>
       <c r="N29" s="2" t="n">
         <v>453</v>
@@ -3185,7 +3185,7 @@
         <v>449</v>
       </c>
       <c r="P29" s="3" t="n">
-        <v>2935</v>
+        <v>2938</v>
       </c>
       <c r="Q29" s="3" t="inlineStr">
         <is>
@@ -3255,11 +3255,11 @@
         </is>
       </c>
       <c r="I30" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J30" s="4" t="inlineStr">
         <is>
-          <t>CURRENT (2d ago)</t>
+          <t>CURRENT (3d ago)</t>
         </is>
       </c>
       <c r="K30" s="2" t="n">
@@ -3348,11 +3348,11 @@
         </is>
       </c>
       <c r="I31" s="2" t="n">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="J31" s="5" t="inlineStr">
         <is>
-          <t>NORMAL INTERVAL (75d ago)</t>
+          <t>NORMAL INTERVAL (76d ago)</t>
         </is>
       </c>
       <c r="K31" s="2" t="n">
@@ -3441,11 +3441,11 @@
         </is>
       </c>
       <c r="I32" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J32" s="4" t="inlineStr">
         <is>
-          <t>CURRENT (2d ago)</t>
+          <t>CURRENT (3d ago)</t>
         </is>
       </c>
       <c r="K32" s="2" t="n">
@@ -3534,11 +3534,11 @@
         </is>
       </c>
       <c r="I33" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="J33" s="4" t="inlineStr">
         <is>
-          <t>CURRENT (7d ago)</t>
+          <t>CURRENT (8d ago)</t>
         </is>
       </c>
       <c r="K33" s="2" t="n">
@@ -3601,7 +3601,7 @@
   <cols>
     <col width="32" customWidth="1" min="1" max="1"/>
     <col width="19" customWidth="1" min="2" max="2"/>
-    <col width="42" customWidth="1" min="3" max="3"/>
+    <col width="44" customWidth="1" min="3" max="3"/>
     <col width="48" customWidth="1" min="4" max="4"/>
     <col width="48" customWidth="1" min="5" max="5"/>
   </cols>
@@ -3644,17 +3644,17 @@
       </c>
       <c r="C2" s="7" t="inlineStr">
         <is>
-          <t>PNG (200 DPI vector clips), JPG</t>
+          <t>Raster PNG charts (no embedded data), JPG</t>
         </is>
       </c>
       <c r="D2" s="7" t="inlineStr">
         <is>
-          <t>Dynamic affine scale regression (R^2 &gt;= 0.999)</t>
+          <t>Not read; titles kept, printed tables transcribed and verified</t>
         </is>
       </c>
       <c r="E2" s="7" t="inlineStr">
         <is>
-          <t>fearnleys_md_master_econometric_series.xlsx (26 lead models)</t>
+          <t>Chart titles in MDs and .tables.json sidecars; calibrated series quarantined</t>
         </is>
       </c>
     </row>
@@ -3925,10 +3925,10 @@
     <col width="40" customWidth="1" min="1" max="1"/>
     <col width="48" customWidth="1" min="2" max="2"/>
     <col width="21" customWidth="1" min="3" max="3"/>
-    <col width="26" customWidth="1" min="4" max="4"/>
+    <col width="27" customWidth="1" min="4" max="4"/>
     <col width="48" customWidth="1" min="5" max="5"/>
     <col width="48" customWidth="1" min="6" max="6"/>
-    <col width="28" customWidth="1" min="7" max="7"/>
+    <col width="36" customWidth="1" min="7" max="7"/>
     <col width="36" customWidth="1" min="8" max="8"/>
     <col width="48" customWidth="1" min="9" max="9"/>
   </cols>
@@ -5205,47 +5205,47 @@
     <row r="28">
       <c r="A28" s="3" t="inlineStr">
         <is>
-          <t>Fearnleys Econometric</t>
+          <t>Fearnleys Research Tables</t>
         </is>
       </c>
       <c r="B28" s="3" t="inlineStr">
         <is>
-          <t>26 Lead-Indicator Econometric Models</t>
+          <t>API data tables + printed Cape composite-model tables</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>26 models</t>
+          <t>70 tables</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>Vector charts / Excel</t>
+          <t>Markdown / JSON sidecars</t>
         </is>
       </c>
       <c r="E28" s="3" t="inlineStr">
         <is>
-          <t>Copper vs Supramax, Coal curve vs P5, Iron Ore vs 5TC, S&amp;P vs 1Y TC</t>
+          <t>Fleet deliveries/scrapping, Cape composite model buckets</t>
         </is>
       </c>
       <c r="F28" s="3" t="inlineStr">
         <is>
-          <t>fearnleys_md_master_econometric_series.xlsx</t>
+          <t>data/extracted/md/fearnleys-md/*.tables.json</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>233 rows</t>
+          <t>56 API tables + 14 printed tables</t>
         </is>
       </c>
       <c r="H28" s="3" t="inlineStr">
         <is>
-          <t>export_fearnleys_md_excel.py</t>
+          <t>run_fearnleys_md_full_power.py</t>
         </is>
       </c>
       <c r="I28" s="3" t="inlineStr">
         <is>
-          <t>data/extracted/series/</t>
+          <t>data/extracted/md/fearnleys-md/</t>
         </is>
       </c>
     </row>
@@ -5282,7 +5282,7 @@
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>756 rows</t>
+          <t>776 rows</t>
         </is>
       </c>
       <c r="H29" s="3" t="inlineStr">
@@ -5329,7 +5329,7 @@
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>6,280 rows</t>
+          <t>6,376 rows</t>
         </is>
       </c>
       <c r="H30" s="3" t="inlineStr">
@@ -5470,7 +5470,7 @@
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>6,114 rows</t>
+          <t>6,097 rows</t>
         </is>
       </c>
       <c r="H33" s="3" t="inlineStr">
@@ -5517,7 +5517,7 @@
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>3,264 rows</t>
+          <t>3,240 rows</t>
         </is>
       </c>
       <c r="H34" s="3" t="inlineStr">

--- a/data/extracted/series/corpus_publication_cadence_and_audit.xlsx
+++ b/data/extracted/series/corpus_publication_cadence_and_audit.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Corpus Cadence &amp; Inventory" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Graphic &amp; Chart Extraction" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sub-Sector &amp; Fleet Breakdown" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Corpus Cadence &amp; Inventory" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Graphic &amp; Chart Extraction" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Sub-Sector &amp; Fleet Breakdown" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1856,19 +1856,19 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="I15" s="2" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="J15" s="4" t="inlineStr">
         <is>
-          <t>CURRENT (7d ago)</t>
+          <t>CURRENT (0d ago)</t>
         </is>
       </c>
       <c r="K15" s="2" t="n">
-        <v>532</v>
+        <v>534</v>
       </c>
       <c r="L15" s="2" t="n">
         <v>0</v>
@@ -1883,7 +1883,7 @@
         <v>531</v>
       </c>
       <c r="P15" s="3" t="n">
-        <v>532</v>
+        <v>534</v>
       </c>
       <c r="Q15" s="3" t="inlineStr">
         <is>
@@ -1897,7 +1897,7 @@
       </c>
       <c r="S15" s="3" t="inlineStr">
         <is>
-          <t>ssy_capesize_index_series.csv (8,731 rows), ssy_capesize_series.csv (8,881 rows), ssy_route_rates_series.csv (5,170 rows), ssy_capesize_index_time_series.csv (517 rows)</t>
+          <t>ssy_capesize_index_series.csv (8,874 rows), ssy_capesize_series.csv (8,881 rows), ssy_route_rates_series.csv (5,190 rows), ssy_capesize_index_time_series.csv (519 rows)</t>
         </is>
       </c>
       <c r="T15" s="3" t="inlineStr">
@@ -1949,19 +1949,19 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="I16" s="2" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="J16" s="4" t="inlineStr">
         <is>
-          <t>CURRENT (7d ago)</t>
+          <t>CURRENT (0d ago)</t>
         </is>
       </c>
       <c r="K16" s="2" t="n">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="L16" s="2" t="n">
         <v>0</v>
@@ -1976,7 +1976,7 @@
         <v>200</v>
       </c>
       <c r="P16" s="3" t="n">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="Q16" s="3" t="inlineStr">
         <is>
@@ -1990,7 +1990,7 @@
       </c>
       <c r="S16" s="3" t="inlineStr">
         <is>
-          <t>star_asia_snp_sales_series.csv (3,575 rows), star_asia_deals_series.csv (3,354 rows), star_asia_valuation_matrix_series.csv (3,232 rows), star_asia_demolition_series.csv (3,136 rows), star_asia_metals_energy_series.csv (1,327 rows)</t>
+          <t>star_asia_snp_sales_series.csv (3,575 rows), star_asia_deals_series.csv (3,362 rows), star_asia_valuation_matrix_series.csv (3,232 rows), star_asia_demolition_series.csv (3,152 rows), star_asia_metals_energy_series.csv (1,327 rows)</t>
         </is>
       </c>
       <c r="T16" s="3" t="inlineStr">

--- a/data/extracted/series/corpus_publication_cadence_and_audit.xlsx
+++ b/data/extracted/series/corpus_publication_cadence_and_audit.xlsx
@@ -2693,34 +2693,34 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="I24" s="2" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="J24" s="4" t="inlineStr">
         <is>
-          <t>CURRENT (4d ago)</t>
+          <t>CURRENT (0d ago)</t>
         </is>
       </c>
       <c r="K24" s="2" t="n">
         <v>305</v>
       </c>
       <c r="L24" s="2" t="n">
-        <v>3245</v>
+        <v>3247</v>
       </c>
       <c r="M24" s="2" t="n">
-        <v>15102</v>
+        <v>15107</v>
       </c>
       <c r="N24" s="2" t="n">
-        <v>3216</v>
+        <v>3218</v>
       </c>
       <c r="O24" s="2" t="n">
-        <v>3507</v>
+        <v>3510</v>
       </c>
       <c r="P24" s="3" t="n">
-        <v>21868</v>
+        <v>21877</v>
       </c>
       <c r="Q24" s="3" t="inlineStr">
         <is>
@@ -2734,7 +2734,7 @@
       </c>
       <c r="S24" s="3" t="inlineStr">
         <is>
-          <t>breakwave_fundamentals_series.csv (2,755 rows), breakwave_insights_metadata.csv (3,216 rows)</t>
+          <t>breakwave_fundamentals_series.csv (2,755 rows), breakwave_insights_metadata.csv (3,218 rows)</t>
         </is>
       </c>
       <c r="T24" s="3" t="inlineStr">

--- a/data/extracted/series/corpus_publication_cadence_and_audit.xlsx
+++ b/data/extracted/series/corpus_publication_cadence_and_audit.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Corpus Cadence &amp; Inventory" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Graphic &amp; Chart Extraction" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Sub-Sector &amp; Fleet Breakdown" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Corpus Cadence &amp; Inventory" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Graphic &amp; Chart Extraction" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sub-Sector &amp; Fleet Breakdown" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>

--- a/data/extracted/series/corpus_publication_cadence_and_audit.xlsx
+++ b/data/extracted/series/corpus_publication_cadence_and_audit.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Corpus Cadence &amp; Inventory" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Graphic &amp; Chart Extraction" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sub-Sector &amp; Fleet Breakdown" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Corpus Cadence &amp; Inventory" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Graphic &amp; Chart Extraction" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Sub-Sector &amp; Fleet Breakdown" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -550,7 +550,7 @@
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>Status (2026-10-12)</t>
+          <t>Status (2026-10-13)</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
@@ -651,11 +651,11 @@
         </is>
       </c>
       <c r="I2" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J2" s="4" t="inlineStr">
         <is>
-          <t>CURRENT (2d ago)</t>
+          <t>CURRENT (3d ago)</t>
         </is>
       </c>
       <c r="K2" s="2" t="n">
@@ -744,11 +744,11 @@
         </is>
       </c>
       <c r="I3" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J3" s="4" t="inlineStr">
         <is>
-          <t>CURRENT (2d ago)</t>
+          <t>CURRENT (3d ago)</t>
         </is>
       </c>
       <c r="K3" s="2" t="n">
@@ -837,11 +837,11 @@
         </is>
       </c>
       <c r="I4" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J4" s="4" t="inlineStr">
         <is>
-          <t>CURRENT (3d ago)</t>
+          <t>CURRENT (4d ago)</t>
         </is>
       </c>
       <c r="K4" s="2" t="n">
@@ -930,11 +930,11 @@
         </is>
       </c>
       <c r="I5" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J5" s="4" t="inlineStr">
         <is>
-          <t>CURRENT (5d ago)</t>
+          <t>CURRENT (6d ago)</t>
         </is>
       </c>
       <c r="K5" s="2" t="n">
@@ -1023,11 +1023,11 @@
         </is>
       </c>
       <c r="I6" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J6" s="4" t="inlineStr">
         <is>
-          <t>CURRENT (5d ago)</t>
+          <t>CURRENT (6d ago)</t>
         </is>
       </c>
       <c r="K6" s="2" t="n">
@@ -1209,11 +1209,11 @@
         </is>
       </c>
       <c r="I8" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J8" s="4" t="inlineStr">
         <is>
-          <t>CURRENT (3d ago)</t>
+          <t>CURRENT (4d ago)</t>
         </is>
       </c>
       <c r="K8" s="2" t="n">
@@ -1302,11 +1302,11 @@
         </is>
       </c>
       <c r="I9" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J9" s="4" t="inlineStr">
         <is>
-          <t>CURRENT (3d ago)</t>
+          <t>CURRENT (4d ago)</t>
         </is>
       </c>
       <c r="K9" s="2" t="n">
@@ -1395,11 +1395,11 @@
         </is>
       </c>
       <c r="I10" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J10" s="4" t="inlineStr">
         <is>
-          <t>CURRENT (5d ago)</t>
+          <t>CURRENT (6d ago)</t>
         </is>
       </c>
       <c r="K10" s="2" t="n">
@@ -1488,11 +1488,11 @@
         </is>
       </c>
       <c r="I11" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J11" s="4" t="inlineStr">
         <is>
-          <t>CURRENT (3d ago)</t>
+          <t>CURRENT (4d ago)</t>
         </is>
       </c>
       <c r="K11" s="2" t="n">
@@ -1581,11 +1581,11 @@
         </is>
       </c>
       <c r="I12" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J12" s="4" t="inlineStr">
         <is>
-          <t>CURRENT (5d ago)</t>
+          <t>CURRENT (6d ago)</t>
         </is>
       </c>
       <c r="K12" s="2" t="n">
@@ -1670,19 +1670,19 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="I13" s="2" t="n">
-        <v>14</v>
+        <v>1</v>
       </c>
       <c r="J13" s="4" t="inlineStr">
         <is>
-          <t>CURRENT (14d ago)</t>
+          <t>CURRENT (1d ago)</t>
         </is>
       </c>
       <c r="K13" s="2" t="n">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="L13" s="2" t="n">
         <v>0</v>
@@ -1697,7 +1697,7 @@
         <v>230</v>
       </c>
       <c r="P13" s="3" t="n">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="Q13" s="3" t="inlineStr">
         <is>
@@ -1711,7 +1711,7 @@
       </c>
       <c r="S13" s="3" t="inlineStr">
         <is>
-          <t>ism_handy_freight_series.csv (17,968 rows), ism_coaster_freight_series.csv (12,462 rows)</t>
+          <t>ism_handy_freight_series.csv (17,968 rows), ism_coaster_freight_series.csv (12,599 rows)</t>
         </is>
       </c>
       <c r="T13" s="3" t="inlineStr">
@@ -1860,11 +1860,11 @@
         </is>
       </c>
       <c r="I15" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J15" s="4" t="inlineStr">
         <is>
-          <t>CURRENT (0d ago)</t>
+          <t>CURRENT (1d ago)</t>
         </is>
       </c>
       <c r="K15" s="2" t="n">
@@ -1897,7 +1897,7 @@
       </c>
       <c r="S15" s="3" t="inlineStr">
         <is>
-          <t>ssy_capesize_index_series.csv (8,874 rows), ssy_capesize_series.csv (8,881 rows), ssy_route_rates_series.csv (5,190 rows), ssy_capesize_index_time_series.csv (519 rows)</t>
+          <t>ssy_capesize_index_series.csv (9,016 rows), ssy_capesize_series.csv (8,881 rows), ssy_route_rates_series.csv (5,190 rows), ssy_capesize_index_time_series.csv (519 rows)</t>
         </is>
       </c>
       <c r="T15" s="3" t="inlineStr">
@@ -1953,11 +1953,11 @@
         </is>
       </c>
       <c r="I16" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J16" s="4" t="inlineStr">
         <is>
-          <t>CURRENT (0d ago)</t>
+          <t>CURRENT (1d ago)</t>
         </is>
       </c>
       <c r="K16" s="2" t="n">
@@ -2042,19 +2042,19 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="I17" s="2" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="J17" s="4" t="inlineStr">
         <is>
-          <t>CURRENT (6d ago)</t>
+          <t>CURRENT (0d ago)</t>
         </is>
       </c>
       <c r="K17" s="2" t="n">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="L17" s="2" t="n">
         <v>0</v>
@@ -2069,7 +2069,7 @@
         <v>271</v>
       </c>
       <c r="P17" s="3" t="n">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="Q17" s="3" t="inlineStr">
         <is>
@@ -2083,7 +2083,7 @@
       </c>
       <c r="S17" s="3" t="inlineStr">
         <is>
-          <t>xclusiv_secondhand_series.csv (8,561 rows), xclusiv_sales_series.csv (5,565 rows), xclusiv_demolition_series.csv (2,090 rows), xclusiv_newbuilding_prices_series.csv (1,379 rows), xclusiv_newbuilding_orders_series.csv (1,313 rows)</t>
+          <t>xclusiv_secondhand_series.csv (8,593 rows), xclusiv_sales_series.csv (5,584 rows), xclusiv_demolition_series.csv (2,098 rows), xclusiv_newbuilding_prices_series.csv (1,379 rows), xclusiv_newbuilding_orders_series.csv (1,313 rows)</t>
         </is>
       </c>
       <c r="T17" s="3" t="inlineStr">
@@ -2139,11 +2139,11 @@
         </is>
       </c>
       <c r="I18" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J18" s="4" t="inlineStr">
         <is>
-          <t>CURRENT (2d ago)</t>
+          <t>CURRENT (3d ago)</t>
         </is>
       </c>
       <c r="K18" s="2" t="n">
@@ -2232,11 +2232,11 @@
         </is>
       </c>
       <c r="I19" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J19" s="4" t="inlineStr">
         <is>
-          <t>CURRENT (5d ago)</t>
+          <t>CURRENT (6d ago)</t>
         </is>
       </c>
       <c r="K19" s="2" t="n">
@@ -2325,11 +2325,11 @@
         </is>
       </c>
       <c r="I20" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J20" s="4" t="inlineStr">
         <is>
-          <t>CURRENT (3d ago)</t>
+          <t>CURRENT (4d ago)</t>
         </is>
       </c>
       <c r="K20" s="2" t="n">
@@ -2418,11 +2418,11 @@
         </is>
       </c>
       <c r="I21" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J21" s="4" t="inlineStr">
         <is>
-          <t>CURRENT (6d ago)</t>
+          <t>CURRENT (7d ago)</t>
         </is>
       </c>
       <c r="K21" s="2" t="n">
@@ -2511,11 +2511,11 @@
         </is>
       </c>
       <c r="I22" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J22" s="4" t="inlineStr">
         <is>
-          <t>CURRENT (5d ago)</t>
+          <t>CURRENT (6d ago)</t>
         </is>
       </c>
       <c r="K22" s="2" t="n">
@@ -2604,11 +2604,11 @@
         </is>
       </c>
       <c r="I23" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J23" s="4" t="inlineStr">
         <is>
-          <t>CURRENT (6d ago)</t>
+          <t>CURRENT (7d ago)</t>
         </is>
       </c>
       <c r="K23" s="2" t="n">
@@ -2697,11 +2697,11 @@
         </is>
       </c>
       <c r="I24" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J24" s="4" t="inlineStr">
         <is>
-          <t>CURRENT (0d ago)</t>
+          <t>CURRENT (1d ago)</t>
         </is>
       </c>
       <c r="K24" s="2" t="n">
@@ -2883,11 +2883,11 @@
         </is>
       </c>
       <c r="I26" s="2" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="J26" s="5" t="inlineStr">
         <is>
-          <t>NORMAL INTERVAL (41d ago)</t>
+          <t>NORMAL INTERVAL (42d ago)</t>
         </is>
       </c>
       <c r="K26" s="2" t="n">
@@ -2976,11 +2976,11 @@
         </is>
       </c>
       <c r="I27" s="2" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J27" s="5" t="inlineStr">
         <is>
-          <t>NORMAL INTERVAL (18d ago)</t>
+          <t>NORMAL INTERVAL (19d ago)</t>
         </is>
       </c>
       <c r="K27" s="2" t="n">
@@ -3069,11 +3069,11 @@
         </is>
       </c>
       <c r="I28" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J28" s="4" t="inlineStr">
         <is>
-          <t>CURRENT (4d ago)</t>
+          <t>CURRENT (5d ago)</t>
         </is>
       </c>
       <c r="K28" s="2" t="n">
@@ -3162,11 +3162,11 @@
         </is>
       </c>
       <c r="I29" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J29" s="4" t="inlineStr">
         <is>
-          <t>CURRENT (3d ago)</t>
+          <t>CURRENT (4d ago)</t>
         </is>
       </c>
       <c r="K29" s="2" t="n">
@@ -3255,11 +3255,11 @@
         </is>
       </c>
       <c r="I30" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J30" s="4" t="inlineStr">
         <is>
-          <t>CURRENT (3d ago)</t>
+          <t>CURRENT (4d ago)</t>
         </is>
       </c>
       <c r="K30" s="2" t="n">
@@ -3348,11 +3348,11 @@
         </is>
       </c>
       <c r="I31" s="2" t="n">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="J31" s="5" t="inlineStr">
         <is>
-          <t>NORMAL INTERVAL (76d ago)</t>
+          <t>NORMAL INTERVAL (77d ago)</t>
         </is>
       </c>
       <c r="K31" s="2" t="n">
@@ -3441,11 +3441,11 @@
         </is>
       </c>
       <c r="I32" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J32" s="4" t="inlineStr">
         <is>
-          <t>CURRENT (3d ago)</t>
+          <t>CURRENT (4d ago)</t>
         </is>
       </c>
       <c r="K32" s="2" t="n">
@@ -3534,11 +3534,11 @@
         </is>
       </c>
       <c r="I33" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J33" s="4" t="inlineStr">
         <is>
-          <t>CURRENT (8d ago)</t>
+          <t>CURRENT (9d ago)</t>
         </is>
       </c>
       <c r="K33" s="2" t="n">
@@ -5423,7 +5423,7 @@
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>5,565 rows</t>
+          <t>5,584 rows</t>
         </is>
       </c>
       <c r="H32" s="3" t="inlineStr">

--- a/data/extracted/series/corpus_publication_cadence_and_audit.xlsx
+++ b/data/extracted/series/corpus_publication_cadence_and_audit.xlsx
@@ -550,7 +550,7 @@
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>Status (2026-10-12)</t>
+          <t>Status (2026-10-13)</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
@@ -651,11 +651,11 @@
         </is>
       </c>
       <c r="I2" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J2" s="4" t="inlineStr">
         <is>
-          <t>CURRENT (2d ago)</t>
+          <t>CURRENT (3d ago)</t>
         </is>
       </c>
       <c r="K2" s="2" t="n">
@@ -744,11 +744,11 @@
         </is>
       </c>
       <c r="I3" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J3" s="4" t="inlineStr">
         <is>
-          <t>CURRENT (2d ago)</t>
+          <t>CURRENT (3d ago)</t>
         </is>
       </c>
       <c r="K3" s="2" t="n">
@@ -837,11 +837,11 @@
         </is>
       </c>
       <c r="I4" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J4" s="4" t="inlineStr">
         <is>
-          <t>CURRENT (3d ago)</t>
+          <t>CURRENT (4d ago)</t>
         </is>
       </c>
       <c r="K4" s="2" t="n">
@@ -930,11 +930,11 @@
         </is>
       </c>
       <c r="I5" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J5" s="4" t="inlineStr">
         <is>
-          <t>CURRENT (5d ago)</t>
+          <t>CURRENT (6d ago)</t>
         </is>
       </c>
       <c r="K5" s="2" t="n">
@@ -1023,11 +1023,11 @@
         </is>
       </c>
       <c r="I6" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J6" s="4" t="inlineStr">
         <is>
-          <t>CURRENT (5d ago)</t>
+          <t>CURRENT (6d ago)</t>
         </is>
       </c>
       <c r="K6" s="2" t="n">
@@ -1112,15 +1112,15 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="I7" s="2" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="J7" s="4" t="inlineStr">
         <is>
-          <t>CURRENT (0d ago)</t>
+          <t>CURRENT (4d ago)</t>
         </is>
       </c>
       <c r="K7" s="2" t="n">
@@ -1209,11 +1209,11 @@
         </is>
       </c>
       <c r="I8" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J8" s="4" t="inlineStr">
         <is>
-          <t>CURRENT (3d ago)</t>
+          <t>CURRENT (4d ago)</t>
         </is>
       </c>
       <c r="K8" s="2" t="n">
@@ -1302,11 +1302,11 @@
         </is>
       </c>
       <c r="I9" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J9" s="4" t="inlineStr">
         <is>
-          <t>CURRENT (3d ago)</t>
+          <t>CURRENT (4d ago)</t>
         </is>
       </c>
       <c r="K9" s="2" t="n">
@@ -1395,11 +1395,11 @@
         </is>
       </c>
       <c r="I10" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J10" s="4" t="inlineStr">
         <is>
-          <t>CURRENT (5d ago)</t>
+          <t>CURRENT (6d ago)</t>
         </is>
       </c>
       <c r="K10" s="2" t="n">
@@ -1488,11 +1488,11 @@
         </is>
       </c>
       <c r="I11" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J11" s="4" t="inlineStr">
         <is>
-          <t>CURRENT (3d ago)</t>
+          <t>CURRENT (4d ago)</t>
         </is>
       </c>
       <c r="K11" s="2" t="n">
@@ -1581,11 +1581,11 @@
         </is>
       </c>
       <c r="I12" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J12" s="4" t="inlineStr">
         <is>
-          <t>CURRENT (5d ago)</t>
+          <t>CURRENT (6d ago)</t>
         </is>
       </c>
       <c r="K12" s="2" t="n">
@@ -1674,11 +1674,11 @@
         </is>
       </c>
       <c r="I13" s="2" t="n">
-        <v>14</v>
-      </c>
-      <c r="J13" s="4" t="inlineStr">
-        <is>
-          <t>CURRENT (14d ago)</t>
+        <v>15</v>
+      </c>
+      <c r="J13" s="5" t="inlineStr">
+        <is>
+          <t>NORMAL INTERVAL (15d ago)</t>
         </is>
       </c>
       <c r="K13" s="2" t="n">
@@ -1763,15 +1763,15 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="I14" s="2" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="J14" s="4" t="inlineStr">
         <is>
-          <t>CURRENT (0d ago)</t>
+          <t>CURRENT (4d ago)</t>
         </is>
       </c>
       <c r="K14" s="2" t="n">
@@ -1804,7 +1804,7 @@
       </c>
       <c r="S14" s="3" t="inlineStr">
         <is>
-          <t>lion_deals_series.csv (1,303 rows), lion_sales_series.csv (1,194 rows), lion_demometer_series.csv (576 rows), lion_demolition_series.csv (516 rows), lion_demo_sales_series.csv (109 rows)</t>
+          <t>lion_deals_series.csv (1,312 rows), lion_sales_series.csv (1,203 rows), lion_demometer_series.csv (576 rows), lion_demolition_series.csv (516 rows), lion_demo_sales_series.csv (109 rows)</t>
         </is>
       </c>
       <c r="T14" s="3" t="inlineStr">
@@ -1860,11 +1860,11 @@
         </is>
       </c>
       <c r="I15" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J15" s="4" t="inlineStr">
         <is>
-          <t>CURRENT (0d ago)</t>
+          <t>CURRENT (1d ago)</t>
         </is>
       </c>
       <c r="K15" s="2" t="n">
@@ -1953,11 +1953,11 @@
         </is>
       </c>
       <c r="I16" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J16" s="4" t="inlineStr">
         <is>
-          <t>CURRENT (0d ago)</t>
+          <t>CURRENT (1d ago)</t>
         </is>
       </c>
       <c r="K16" s="2" t="n">
@@ -2046,11 +2046,11 @@
         </is>
       </c>
       <c r="I17" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J17" s="4" t="inlineStr">
         <is>
-          <t>CURRENT (6d ago)</t>
+          <t>CURRENT (7d ago)</t>
         </is>
       </c>
       <c r="K17" s="2" t="n">
@@ -2139,11 +2139,11 @@
         </is>
       </c>
       <c r="I18" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J18" s="4" t="inlineStr">
         <is>
-          <t>CURRENT (2d ago)</t>
+          <t>CURRENT (3d ago)</t>
         </is>
       </c>
       <c r="K18" s="2" t="n">
@@ -2232,11 +2232,11 @@
         </is>
       </c>
       <c r="I19" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J19" s="4" t="inlineStr">
         <is>
-          <t>CURRENT (5d ago)</t>
+          <t>CURRENT (6d ago)</t>
         </is>
       </c>
       <c r="K19" s="2" t="n">
@@ -2325,11 +2325,11 @@
         </is>
       </c>
       <c r="I20" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J20" s="4" t="inlineStr">
         <is>
-          <t>CURRENT (3d ago)</t>
+          <t>CURRENT (4d ago)</t>
         </is>
       </c>
       <c r="K20" s="2" t="n">
@@ -2418,11 +2418,11 @@
         </is>
       </c>
       <c r="I21" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J21" s="4" t="inlineStr">
         <is>
-          <t>CURRENT (6d ago)</t>
+          <t>CURRENT (7d ago)</t>
         </is>
       </c>
       <c r="K21" s="2" t="n">
@@ -2511,11 +2511,11 @@
         </is>
       </c>
       <c r="I22" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J22" s="4" t="inlineStr">
         <is>
-          <t>CURRENT (5d ago)</t>
+          <t>CURRENT (6d ago)</t>
         </is>
       </c>
       <c r="K22" s="2" t="n">
@@ -2604,11 +2604,11 @@
         </is>
       </c>
       <c r="I23" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J23" s="4" t="inlineStr">
         <is>
-          <t>CURRENT (6d ago)</t>
+          <t>CURRENT (7d ago)</t>
         </is>
       </c>
       <c r="K23" s="2" t="n">
@@ -2697,11 +2697,11 @@
         </is>
       </c>
       <c r="I24" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J24" s="4" t="inlineStr">
         <is>
-          <t>CURRENT (4d ago)</t>
+          <t>CURRENT (5d ago)</t>
         </is>
       </c>
       <c r="K24" s="2" t="n">
@@ -2786,15 +2786,15 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="I25" s="2" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="J25" s="4" t="inlineStr">
         <is>
-          <t>CURRENT (0d ago)</t>
+          <t>CURRENT (11d ago)</t>
         </is>
       </c>
       <c r="K25" s="2" t="n">
@@ -2883,11 +2883,11 @@
         </is>
       </c>
       <c r="I26" s="2" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="J26" s="5" t="inlineStr">
         <is>
-          <t>NORMAL INTERVAL (41d ago)</t>
+          <t>NORMAL INTERVAL (42d ago)</t>
         </is>
       </c>
       <c r="K26" s="2" t="n">
@@ -2976,11 +2976,11 @@
         </is>
       </c>
       <c r="I27" s="2" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J27" s="5" t="inlineStr">
         <is>
-          <t>NORMAL INTERVAL (18d ago)</t>
+          <t>NORMAL INTERVAL (19d ago)</t>
         </is>
       </c>
       <c r="K27" s="2" t="n">
@@ -3069,11 +3069,11 @@
         </is>
       </c>
       <c r="I28" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J28" s="4" t="inlineStr">
         <is>
-          <t>CURRENT (4d ago)</t>
+          <t>CURRENT (5d ago)</t>
         </is>
       </c>
       <c r="K28" s="2" t="n">
@@ -3162,11 +3162,11 @@
         </is>
       </c>
       <c r="I29" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J29" s="4" t="inlineStr">
         <is>
-          <t>CURRENT (3d ago)</t>
+          <t>CURRENT (4d ago)</t>
         </is>
       </c>
       <c r="K29" s="2" t="n">
@@ -3255,11 +3255,11 @@
         </is>
       </c>
       <c r="I30" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J30" s="4" t="inlineStr">
         <is>
-          <t>CURRENT (3d ago)</t>
+          <t>CURRENT (4d ago)</t>
         </is>
       </c>
       <c r="K30" s="2" t="n">
@@ -3348,11 +3348,11 @@
         </is>
       </c>
       <c r="I31" s="2" t="n">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="J31" s="5" t="inlineStr">
         <is>
-          <t>NORMAL INTERVAL (76d ago)</t>
+          <t>NORMAL INTERVAL (77d ago)</t>
         </is>
       </c>
       <c r="K31" s="2" t="n">
@@ -3441,11 +3441,11 @@
         </is>
       </c>
       <c r="I32" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J32" s="4" t="inlineStr">
         <is>
-          <t>CURRENT (3d ago)</t>
+          <t>CURRENT (4d ago)</t>
         </is>
       </c>
       <c r="K32" s="2" t="n">
@@ -3534,11 +3534,11 @@
         </is>
       </c>
       <c r="I33" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J33" s="4" t="inlineStr">
         <is>
-          <t>CURRENT (8d ago)</t>
+          <t>CURRENT (9d ago)</t>
         </is>
       </c>
       <c r="K33" s="2" t="n">

--- a/data/extracted/series/corpus_publication_cadence_and_audit.xlsx
+++ b/data/extracted/series/corpus_publication_cadence_and_audit.xlsx
@@ -950,7 +950,7 @@
         <v>0</v>
       </c>
       <c r="O5" s="2" t="n">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="P5" s="3" t="n">
         <v>250</v>
@@ -1019,19 +1019,19 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="I6" s="2" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="J6" s="4" t="inlineStr">
         <is>
-          <t>CURRENT (6d ago)</t>
+          <t>CURRENT (1d ago)</t>
         </is>
       </c>
       <c r="K6" s="2" t="n">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="L6" s="2" t="n">
         <v>0</v>
@@ -1046,7 +1046,7 @@
         <v>137</v>
       </c>
       <c r="P6" s="3" t="n">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="Q6" s="3" t="inlineStr">
         <is>
@@ -1060,7 +1060,7 @@
       </c>
       <c r="S6" s="3" t="inlineStr">
         <is>
-          <t>carriers_sales_series.csv (3,060 rows), carriers_dry_tc_period_series.csv (3,096 rows), carriers_indices_series.csv (1,806 rows), carriers_tanker_tce_series.csv (774 rows), carriers_bspa_series.csv (779 rows), carriers_newbuilding_series.csv (302 rows), carriers_demolition_series.csv (170 rows)</t>
+          <t>carriers_sales_series.csv (3,081 rows), carriers_dry_tc_period_series.csv (3,096 rows), carriers_indices_series.csv (1,806 rows), carriers_tanker_tce_series.csv (774 rows), carriers_bspa_series.csv (785 rows), carriers_newbuilding_series.csv (302 rows), carriers_demolition_series.csv (170 rows)</t>
         </is>
       </c>
       <c r="T6" s="3" t="inlineStr">
@@ -1112,15 +1112,15 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="I7" s="2" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="J7" s="4" t="inlineStr">
         <is>
-          <t>CURRENT (0d ago)</t>
+          <t>CURRENT (4d ago)</t>
         </is>
       </c>
       <c r="K7" s="2" t="n">
@@ -1763,15 +1763,15 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="I14" s="2" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="J14" s="4" t="inlineStr">
         <is>
-          <t>CURRENT (0d ago)</t>
+          <t>CURRENT (4d ago)</t>
         </is>
       </c>
       <c r="K14" s="2" t="n">
@@ -1804,7 +1804,7 @@
       </c>
       <c r="S14" s="3" t="inlineStr">
         <is>
-          <t>lion_deals_series.csv (1,303 rows), lion_sales_series.csv (1,194 rows), lion_demometer_series.csv (576 rows), lion_demolition_series.csv (516 rows), lion_demo_sales_series.csv (109 rows)</t>
+          <t>lion_deals_series.csv (1,312 rows), lion_sales_series.csv (1,203 rows), lion_demometer_series.csv (576 rows), lion_demolition_series.csv (516 rows), lion_demo_sales_series.csv (109 rows)</t>
         </is>
       </c>
       <c r="T14" s="3" t="inlineStr">
@@ -1897,7 +1897,7 @@
       </c>
       <c r="S15" s="3" t="inlineStr">
         <is>
-          <t>ssy_capesize_index_series.csv (9,016 rows), ssy_capesize_series.csv (8,881 rows), ssy_route_rates_series.csv (5,190 rows), ssy_capesize_index_time_series.csv (519 rows)</t>
+          <t>ssy_capesize_index_series.csv (9,158 rows), ssy_capesize_series.csv (8,881 rows), ssy_route_rates_series.csv (5,190 rows), ssy_capesize_index_time_series.csv (519 rows)</t>
         </is>
       </c>
       <c r="T15" s="3" t="inlineStr">
@@ -2269,7 +2269,7 @@
       </c>
       <c r="S19" s="3" t="inlineStr">
         <is>
-          <t>hellenic_alibra_dry_tc_series.csv (6,467 rows)</t>
+          <t>hellenic_alibra_dry_tc_series.csv (6,539 rows)</t>
         </is>
       </c>
       <c r="T19" s="3" t="inlineStr">
@@ -2548,7 +2548,7 @@
       </c>
       <c r="S22" s="3" t="inlineStr">
         <is>
-          <t>hellenic_alibra_tanker_tc_series.csv (7,205 rows)</t>
+          <t>hellenic_alibra_tanker_tc_series.csv (7,448 rows)</t>
         </is>
       </c>
       <c r="T22" s="3" t="inlineStr">
@@ -2717,7 +2717,7 @@
         <v>3218</v>
       </c>
       <c r="O24" s="2" t="n">
-        <v>3510</v>
+        <v>3509</v>
       </c>
       <c r="P24" s="3" t="n">
         <v>21877</v>
@@ -2734,7 +2734,7 @@
       </c>
       <c r="S24" s="3" t="inlineStr">
         <is>
-          <t>breakwave_fundamentals_series.csv (2,755 rows), breakwave_insights_metadata.csv (3,218 rows)</t>
+          <t>breakwave_fundamentals_series.csv (2,747 rows), breakwave_insights_metadata.csv (3,218 rows)</t>
         </is>
       </c>
       <c r="T24" s="3" t="inlineStr">
@@ -2786,15 +2786,15 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="I25" s="2" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="J25" s="4" t="inlineStr">
         <is>
-          <t>CURRENT (0d ago)</t>
+          <t>CURRENT (11d ago)</t>
         </is>
       </c>
       <c r="K25" s="2" t="n">
@@ -4812,7 +4812,7 @@
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>6,467 rows</t>
+          <t>6,539 rows</t>
         </is>
       </c>
       <c r="H19" s="3" t="inlineStr">
@@ -4859,7 +4859,7 @@
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>7,205 rows</t>
+          <t>7,448 rows</t>
         </is>
       </c>
       <c r="H20" s="3" t="inlineStr">

--- a/data/extracted/series/corpus_publication_cadence_and_audit.xlsx
+++ b/data/extracted/series/corpus_publication_cadence_and_audit.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Corpus Cadence &amp; Inventory" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Graphic &amp; Chart Extraction" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Sub-Sector &amp; Fleet Breakdown" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Corpus Cadence &amp; Inventory" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Graphic &amp; Chart Extraction" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sub-Sector &amp; Fleet Breakdown" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -688,7 +688,7 @@
       </c>
       <c r="S2" s="3" t="inlineStr">
         <is>
-          <t>advanced_shipping_sales_series.csv (6,097 rows), advanced_shipping_demolition_series.csv (2,000 rows), advanced_shipping_secondhand_matrix_series.csv (8,093 rows), advanced_shipping_newbuilding_series.csv (1,898 rows), advanced_shipping_demo_sales_series.csv (599 rows)</t>
+          <t>advanced_shipping_sales_series.csv (6,106 rows), advanced_shipping_demolition_series.csv (2,000 rows), advanced_shipping_secondhand_matrix_series.csv (8,093 rows), advanced_shipping_newbuilding_series.csv (1,898 rows), advanced_shipping_demo_sales_series.csv (599 rows)</t>
         </is>
       </c>
       <c r="T2" s="3" t="inlineStr">
@@ -1031,7 +1031,7 @@
         </is>
       </c>
       <c r="K6" s="2" t="n">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="L6" s="2" t="n">
         <v>0</v>
@@ -1046,7 +1046,7 @@
         <v>137</v>
       </c>
       <c r="P6" s="3" t="n">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="Q6" s="3" t="inlineStr">
         <is>
@@ -1682,7 +1682,7 @@
         </is>
       </c>
       <c r="K13" s="2" t="n">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="L13" s="2" t="n">
         <v>0</v>
@@ -1697,7 +1697,7 @@
         <v>230</v>
       </c>
       <c r="P13" s="3" t="n">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="Q13" s="3" t="inlineStr">
         <is>
@@ -1868,7 +1868,7 @@
         </is>
       </c>
       <c r="K15" s="2" t="n">
-        <v>534</v>
+        <v>536</v>
       </c>
       <c r="L15" s="2" t="n">
         <v>0</v>
@@ -1883,7 +1883,7 @@
         <v>531</v>
       </c>
       <c r="P15" s="3" t="n">
-        <v>534</v>
+        <v>536</v>
       </c>
       <c r="Q15" s="3" t="inlineStr">
         <is>
@@ -1961,7 +1961,7 @@
         </is>
       </c>
       <c r="K16" s="2" t="n">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="L16" s="2" t="n">
         <v>0</v>
@@ -1976,7 +1976,7 @@
         <v>200</v>
       </c>
       <c r="P16" s="3" t="n">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="Q16" s="3" t="inlineStr">
         <is>
@@ -2054,7 +2054,7 @@
         </is>
       </c>
       <c r="K17" s="2" t="n">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="L17" s="2" t="n">
         <v>0</v>
@@ -2069,7 +2069,7 @@
         <v>271</v>
       </c>
       <c r="P17" s="3" t="n">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="Q17" s="3" t="inlineStr">
         <is>
@@ -2321,19 +2321,19 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="I20" s="2" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="J20" s="4" t="inlineStr">
         <is>
-          <t>CURRENT (4d ago)</t>
+          <t>CURRENT (0d ago)</t>
         </is>
       </c>
       <c r="K20" s="2" t="n">
-        <v>4532</v>
+        <v>4536</v>
       </c>
       <c r="L20" s="2" t="n">
         <v>1202</v>
@@ -2345,7 +2345,7 @@
         <v>0</v>
       </c>
       <c r="O20" s="2" t="n">
-        <v>1189</v>
+        <v>1193</v>
       </c>
       <c r="P20" s="3" t="n">
         <v>9057</v>
@@ -2693,34 +2693,34 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="I24" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J24" s="4" t="inlineStr">
         <is>
-          <t>CURRENT (1d ago)</t>
+          <t>CURRENT (0d ago)</t>
         </is>
       </c>
       <c r="K24" s="2" t="n">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="L24" s="2" t="n">
-        <v>3247</v>
+        <v>3249</v>
       </c>
       <c r="M24" s="2" t="n">
-        <v>15107</v>
+        <v>15111</v>
       </c>
       <c r="N24" s="2" t="n">
-        <v>3218</v>
+        <v>3220</v>
       </c>
       <c r="O24" s="2" t="n">
-        <v>3509</v>
+        <v>3512</v>
       </c>
       <c r="P24" s="3" t="n">
-        <v>21877</v>
+        <v>21886</v>
       </c>
       <c r="Q24" s="3" t="inlineStr">
         <is>
@@ -2734,7 +2734,7 @@
       </c>
       <c r="S24" s="3" t="inlineStr">
         <is>
-          <t>breakwave_fundamentals_series.csv (2,747 rows), breakwave_insights_metadata.csv (3,218 rows)</t>
+          <t>breakwave_fundamentals_series.csv (2,759 rows), breakwave_insights_metadata.csv (3,220 rows)</t>
         </is>
       </c>
       <c r="T24" s="3" t="inlineStr">
@@ -5470,7 +5470,7 @@
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>6,097 rows</t>
+          <t>6,106 rows</t>
         </is>
       </c>
       <c r="H33" s="3" t="inlineStr">

--- a/data/extracted/series/corpus_publication_cadence_and_audit.xlsx
+++ b/data/extracted/series/corpus_publication_cadence_and_audit.xlsx
@@ -2522,7 +2522,7 @@
         <v>0</v>
       </c>
       <c r="L22" s="2" t="n">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="M22" s="2" t="n">
         <v>759</v>
@@ -2531,10 +2531,10 @@
         <v>0</v>
       </c>
       <c r="O22" s="2" t="n">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="P22" s="3" t="n">
-        <v>1038</v>
+        <v>1039</v>
       </c>
       <c r="Q22" s="3" t="inlineStr">
         <is>

--- a/data/extracted/series/corpus_publication_cadence_and_audit.xlsx
+++ b/data/extracted/series/corpus_publication_cadence_and_audit.xlsx
@@ -2531,7 +2531,7 @@
         <v>0</v>
       </c>
       <c r="O22" s="2" t="n">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="P22" s="3" t="n">
         <v>1039</v>

--- a/data/extracted/series/corpus_publication_cadence_and_audit.xlsx
+++ b/data/extracted/series/corpus_publication_cadence_and_audit.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Corpus Cadence &amp; Inventory" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Graphic &amp; Chart Extraction" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sub-Sector &amp; Fleet Breakdown" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Corpus Cadence &amp; Inventory" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Graphic &amp; Chart Extraction" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Sub-Sector &amp; Fleet Breakdown" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -926,34 +926,34 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="I5" s="2" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="J5" s="4" t="inlineStr">
         <is>
-          <t>CURRENT (6d ago)</t>
+          <t>CURRENT (0d ago)</t>
         </is>
       </c>
       <c r="K5" s="2" t="n">
+        <v>251</v>
+      </c>
+      <c r="L5" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M5" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N5" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O5" s="2" t="n">
         <v>250</v>
       </c>
-      <c r="L5" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M5" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="N5" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="O5" s="2" t="n">
-        <v>249</v>
-      </c>
       <c r="P5" s="3" t="n">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="Q5" s="3" t="inlineStr">
         <is>
@@ -1577,19 +1577,19 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="I12" s="2" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="J12" s="4" t="inlineStr">
         <is>
-          <t>CURRENT (6d ago)</t>
+          <t>CURRENT (0d ago)</t>
         </is>
       </c>
       <c r="K12" s="2" t="n">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="L12" s="2" t="n">
         <v>0</v>
@@ -1601,10 +1601,10 @@
         <v>0</v>
       </c>
       <c r="O12" s="2" t="n">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="P12" s="3" t="n">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="Q12" s="3" t="inlineStr">
         <is>
@@ -1897,7 +1897,7 @@
       </c>
       <c r="S15" s="3" t="inlineStr">
         <is>
-          <t>ssy_capesize_index_series.csv (9,158 rows), ssy_capesize_series.csv (8,881 rows), ssy_route_rates_series.csv (5,190 rows), ssy_capesize_index_time_series.csv (519 rows)</t>
+          <t>ssy_capesize_index_series.csv (9,300 rows), ssy_capesize_series.csv (8,881 rows), ssy_route_rates_series.csv (5,190 rows), ssy_capesize_index_time_series.csv (519 rows)</t>
         </is>
       </c>
       <c r="T15" s="3" t="inlineStr">

--- a/data/extracted/series/corpus_publication_cadence_and_audit.xlsx
+++ b/data/extracted/series/corpus_publication_cadence_and_audit.xlsx
@@ -550,7 +550,7 @@
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>Status (2026-10-13)</t>
+          <t>Status (2026-10-14)</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
@@ -651,11 +651,11 @@
         </is>
       </c>
       <c r="I2" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J2" s="4" t="inlineStr">
         <is>
-          <t>CURRENT (3d ago)</t>
+          <t>CURRENT (4d ago)</t>
         </is>
       </c>
       <c r="K2" s="2" t="n">
@@ -744,11 +744,11 @@
         </is>
       </c>
       <c r="I3" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J3" s="4" t="inlineStr">
         <is>
-          <t>CURRENT (3d ago)</t>
+          <t>CURRENT (4d ago)</t>
         </is>
       </c>
       <c r="K3" s="2" t="n">
@@ -837,11 +837,11 @@
         </is>
       </c>
       <c r="I4" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J4" s="4" t="inlineStr">
         <is>
-          <t>CURRENT (4d ago)</t>
+          <t>CURRENT (5d ago)</t>
         </is>
       </c>
       <c r="K4" s="2" t="n">
@@ -1023,11 +1023,11 @@
         </is>
       </c>
       <c r="I6" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J6" s="4" t="inlineStr">
         <is>
-          <t>CURRENT (1d ago)</t>
+          <t>CURRENT (2d ago)</t>
         </is>
       </c>
       <c r="K6" s="2" t="n">
@@ -1116,11 +1116,11 @@
         </is>
       </c>
       <c r="I7" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J7" s="4" t="inlineStr">
         <is>
-          <t>CURRENT (4d ago)</t>
+          <t>CURRENT (5d ago)</t>
         </is>
       </c>
       <c r="K7" s="2" t="n">
@@ -1205,15 +1205,15 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="I8" s="2" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="J8" s="4" t="inlineStr">
         <is>
-          <t>CURRENT (4d ago)</t>
+          <t>CURRENT (0d ago)</t>
         </is>
       </c>
       <c r="K8" s="2" t="n">
@@ -1229,7 +1229,7 @@
         <v>4756</v>
       </c>
       <c r="O8" s="2" t="n">
-        <v>5027</v>
+        <v>5030</v>
       </c>
       <c r="P8" s="3" t="n">
         <v>5021</v>
@@ -1298,15 +1298,15 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="I9" s="2" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="J9" s="4" t="inlineStr">
         <is>
-          <t>CURRENT (4d ago)</t>
+          <t>CURRENT (0d ago)</t>
         </is>
       </c>
       <c r="K9" s="2" t="n">
@@ -1322,7 +1322,7 @@
         <v>4756</v>
       </c>
       <c r="O9" s="2" t="n">
-        <v>4766</v>
+        <v>4769</v>
       </c>
       <c r="P9" s="3" t="n">
         <v>4765</v>
@@ -1395,11 +1395,11 @@
         </is>
       </c>
       <c r="I10" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J10" s="4" t="inlineStr">
         <is>
-          <t>CURRENT (6d ago)</t>
+          <t>CURRENT (7d ago)</t>
         </is>
       </c>
       <c r="K10" s="2" t="n">
@@ -1488,11 +1488,11 @@
         </is>
       </c>
       <c r="I11" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J11" s="4" t="inlineStr">
         <is>
-          <t>CURRENT (4d ago)</t>
+          <t>CURRENT (5d ago)</t>
         </is>
       </c>
       <c r="K11" s="2" t="n">
@@ -1674,11 +1674,11 @@
         </is>
       </c>
       <c r="I13" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J13" s="4" t="inlineStr">
         <is>
-          <t>CURRENT (1d ago)</t>
+          <t>CURRENT (2d ago)</t>
         </is>
       </c>
       <c r="K13" s="2" t="n">
@@ -1767,11 +1767,11 @@
         </is>
       </c>
       <c r="I14" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J14" s="4" t="inlineStr">
         <is>
-          <t>CURRENT (4d ago)</t>
+          <t>CURRENT (5d ago)</t>
         </is>
       </c>
       <c r="K14" s="2" t="n">
@@ -1860,11 +1860,11 @@
         </is>
       </c>
       <c r="I15" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J15" s="4" t="inlineStr">
         <is>
-          <t>CURRENT (1d ago)</t>
+          <t>CURRENT (2d ago)</t>
         </is>
       </c>
       <c r="K15" s="2" t="n">
@@ -1897,7 +1897,7 @@
       </c>
       <c r="S15" s="3" t="inlineStr">
         <is>
-          <t>ssy_capesize_index_series.csv (9,300 rows), ssy_capesize_series.csv (8,881 rows), ssy_route_rates_series.csv (5,190 rows), ssy_capesize_index_time_series.csv (519 rows)</t>
+          <t>ssy_capesize_index_series.csv (9,442 rows), ssy_capesize_series.csv (8,881 rows), ssy_route_rates_series.csv (5,190 rows), ssy_capesize_index_time_series.csv (519 rows)</t>
         </is>
       </c>
       <c r="T15" s="3" t="inlineStr">
@@ -1953,11 +1953,11 @@
         </is>
       </c>
       <c r="I16" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J16" s="4" t="inlineStr">
         <is>
-          <t>CURRENT (1d ago)</t>
+          <t>CURRENT (2d ago)</t>
         </is>
       </c>
       <c r="K16" s="2" t="n">
@@ -2046,11 +2046,11 @@
         </is>
       </c>
       <c r="I17" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J17" s="4" t="inlineStr">
         <is>
-          <t>CURRENT (0d ago)</t>
+          <t>CURRENT (1d ago)</t>
         </is>
       </c>
       <c r="K17" s="2" t="n">
@@ -2139,11 +2139,11 @@
         </is>
       </c>
       <c r="I18" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J18" s="4" t="inlineStr">
         <is>
-          <t>CURRENT (3d ago)</t>
+          <t>CURRENT (4d ago)</t>
         </is>
       </c>
       <c r="K18" s="2" t="n">
@@ -2232,11 +2232,11 @@
         </is>
       </c>
       <c r="I19" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J19" s="4" t="inlineStr">
         <is>
-          <t>CURRENT (6d ago)</t>
+          <t>CURRENT (7d ago)</t>
         </is>
       </c>
       <c r="K19" s="2" t="n">
@@ -2325,11 +2325,11 @@
         </is>
       </c>
       <c r="I20" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J20" s="4" t="inlineStr">
         <is>
-          <t>CURRENT (0d ago)</t>
+          <t>CURRENT (1d ago)</t>
         </is>
       </c>
       <c r="K20" s="2" t="n">
@@ -2418,11 +2418,11 @@
         </is>
       </c>
       <c r="I21" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="J21" s="4" t="inlineStr">
         <is>
-          <t>CURRENT (7d ago)</t>
+          <t>CURRENT (8d ago)</t>
         </is>
       </c>
       <c r="K21" s="2" t="n">
@@ -2511,11 +2511,11 @@
         </is>
       </c>
       <c r="I22" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J22" s="4" t="inlineStr">
         <is>
-          <t>CURRENT (6d ago)</t>
+          <t>CURRENT (7d ago)</t>
         </is>
       </c>
       <c r="K22" s="2" t="n">
@@ -2604,11 +2604,11 @@
         </is>
       </c>
       <c r="I23" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="J23" s="4" t="inlineStr">
         <is>
-          <t>CURRENT (7d ago)</t>
+          <t>CURRENT (8d ago)</t>
         </is>
       </c>
       <c r="K23" s="2" t="n">
@@ -2697,11 +2697,11 @@
         </is>
       </c>
       <c r="I24" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J24" s="4" t="inlineStr">
         <is>
-          <t>CURRENT (0d ago)</t>
+          <t>CURRENT (1d ago)</t>
         </is>
       </c>
       <c r="K24" s="2" t="n">
@@ -2790,11 +2790,11 @@
         </is>
       </c>
       <c r="I25" s="2" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="J25" s="4" t="inlineStr">
         <is>
-          <t>CURRENT (11d ago)</t>
+          <t>CURRENT (12d ago)</t>
         </is>
       </c>
       <c r="K25" s="2" t="n">
@@ -2883,11 +2883,11 @@
         </is>
       </c>
       <c r="I26" s="2" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="J26" s="5" t="inlineStr">
         <is>
-          <t>NORMAL INTERVAL (42d ago)</t>
+          <t>NORMAL INTERVAL (43d ago)</t>
         </is>
       </c>
       <c r="K26" s="2" t="n">
@@ -2976,11 +2976,11 @@
         </is>
       </c>
       <c r="I27" s="2" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="J27" s="5" t="inlineStr">
         <is>
-          <t>NORMAL INTERVAL (19d ago)</t>
+          <t>NORMAL INTERVAL (20d ago)</t>
         </is>
       </c>
       <c r="K27" s="2" t="n">
@@ -3069,11 +3069,11 @@
         </is>
       </c>
       <c r="I28" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J28" s="4" t="inlineStr">
         <is>
-          <t>CURRENT (5d ago)</t>
+          <t>CURRENT (6d ago)</t>
         </is>
       </c>
       <c r="K28" s="2" t="n">
@@ -3162,11 +3162,11 @@
         </is>
       </c>
       <c r="I29" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J29" s="4" t="inlineStr">
         <is>
-          <t>CURRENT (4d ago)</t>
+          <t>CURRENT (5d ago)</t>
         </is>
       </c>
       <c r="K29" s="2" t="n">
@@ -3255,11 +3255,11 @@
         </is>
       </c>
       <c r="I30" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J30" s="4" t="inlineStr">
         <is>
-          <t>CURRENT (4d ago)</t>
+          <t>CURRENT (5d ago)</t>
         </is>
       </c>
       <c r="K30" s="2" t="n">
@@ -3348,11 +3348,11 @@
         </is>
       </c>
       <c r="I31" s="2" t="n">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="J31" s="5" t="inlineStr">
         <is>
-          <t>NORMAL INTERVAL (77d ago)</t>
+          <t>NORMAL INTERVAL (78d ago)</t>
         </is>
       </c>
       <c r="K31" s="2" t="n">
@@ -3441,11 +3441,11 @@
         </is>
       </c>
       <c r="I32" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J32" s="4" t="inlineStr">
         <is>
-          <t>CURRENT (4d ago)</t>
+          <t>CURRENT (5d ago)</t>
         </is>
       </c>
       <c r="K32" s="2" t="n">
@@ -3534,11 +3534,11 @@
         </is>
       </c>
       <c r="I33" s="2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J33" s="4" t="inlineStr">
         <is>
-          <t>CURRENT (9d ago)</t>
+          <t>CURRENT (10d ago)</t>
         </is>
       </c>
       <c r="K33" s="2" t="n">

--- a/data/extracted/series/corpus_publication_cadence_and_audit.xlsx
+++ b/data/extracted/series/corpus_publication_cadence_and_audit.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Corpus Cadence &amp; Inventory" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Graphic &amp; Chart Extraction" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Sub-Sector &amp; Fleet Breakdown" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Corpus Cadence &amp; Inventory" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Graphic &amp; Chart Extraction" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sub-Sector &amp; Fleet Breakdown" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -938,7 +938,7 @@
         </is>
       </c>
       <c r="K5" s="2" t="n">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="L5" s="2" t="n">
         <v>0</v>
@@ -953,7 +953,7 @@
         <v>250</v>
       </c>
       <c r="P5" s="3" t="n">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="Q5" s="3" t="inlineStr">
         <is>
@@ -1391,15 +1391,15 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="I10" s="2" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="J10" s="4" t="inlineStr">
         <is>
-          <t>CURRENT (7d ago)</t>
+          <t>CURRENT (0d ago)</t>
         </is>
       </c>
       <c r="K10" s="2" t="n">
@@ -1412,13 +1412,13 @@
         <v>2847</v>
       </c>
       <c r="N10" s="2" t="n">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="O10" s="2" t="n">
         <v>184</v>
       </c>
       <c r="P10" s="3" t="n">
-        <v>3215</v>
+        <v>3216</v>
       </c>
       <c r="Q10" s="3" t="inlineStr">
         <is>
@@ -1589,7 +1589,7 @@
         </is>
       </c>
       <c r="K12" s="2" t="n">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="L12" s="2" t="n">
         <v>0</v>
@@ -1604,7 +1604,7 @@
         <v>257</v>
       </c>
       <c r="P12" s="3" t="n">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="Q12" s="3" t="inlineStr">
         <is>
@@ -2321,19 +2321,19 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="I20" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J20" s="4" t="inlineStr">
         <is>
-          <t>CURRENT (1d ago)</t>
+          <t>CURRENT (0d ago)</t>
         </is>
       </c>
       <c r="K20" s="2" t="n">
-        <v>4536</v>
+        <v>4538</v>
       </c>
       <c r="L20" s="2" t="n">
         <v>1202</v>
@@ -2345,7 +2345,7 @@
         <v>0</v>
       </c>
       <c r="O20" s="2" t="n">
-        <v>1193</v>
+        <v>1195</v>
       </c>
       <c r="P20" s="3" t="n">
         <v>9057</v>
@@ -2693,34 +2693,34 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="I24" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J24" s="4" t="inlineStr">
         <is>
-          <t>CURRENT (1d ago)</t>
+          <t>CURRENT (0d ago)</t>
         </is>
       </c>
       <c r="K24" s="2" t="n">
         <v>306</v>
       </c>
       <c r="L24" s="2" t="n">
-        <v>3249</v>
+        <v>3251</v>
       </c>
       <c r="M24" s="2" t="n">
         <v>15111</v>
       </c>
       <c r="N24" s="2" t="n">
-        <v>3220</v>
+        <v>3222</v>
       </c>
       <c r="O24" s="2" t="n">
-        <v>3512</v>
+        <v>3514</v>
       </c>
       <c r="P24" s="3" t="n">
-        <v>21886</v>
+        <v>21890</v>
       </c>
       <c r="Q24" s="3" t="inlineStr">
         <is>
@@ -2734,7 +2734,7 @@
       </c>
       <c r="S24" s="3" t="inlineStr">
         <is>
-          <t>breakwave_fundamentals_series.csv (2,759 rows), breakwave_insights_metadata.csv (3,220 rows)</t>
+          <t>breakwave_fundamentals_series.csv (2,759 rows), breakwave_insights_metadata.csv (3,222 rows)</t>
         </is>
       </c>
       <c r="T24" s="3" t="inlineStr">

--- a/data/extracted/series/corpus_publication_cadence_and_audit.xlsx
+++ b/data/extracted/series/corpus_publication_cadence_and_audit.xlsx
@@ -1226,13 +1226,13 @@
         <v>0</v>
       </c>
       <c r="N8" s="2" t="n">
-        <v>4756</v>
+        <v>4764</v>
       </c>
       <c r="O8" s="2" t="n">
-        <v>5030</v>
+        <v>5035</v>
       </c>
       <c r="P8" s="3" t="n">
-        <v>5021</v>
+        <v>5029</v>
       </c>
       <c r="Q8" s="3" t="inlineStr">
         <is>
@@ -1319,10 +1319,10 @@
         <v>0</v>
       </c>
       <c r="N9" s="2" t="n">
-        <v>4756</v>
+        <v>4764</v>
       </c>
       <c r="O9" s="2" t="n">
-        <v>4769</v>
+        <v>4774</v>
       </c>
       <c r="P9" s="3" t="n">
         <v>4765</v>
@@ -1403,22 +1403,22 @@
         </is>
       </c>
       <c r="K10" s="2" t="n">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="L10" s="2" t="n">
         <v>0</v>
       </c>
       <c r="M10" s="2" t="n">
-        <v>2847</v>
+        <v>2858</v>
       </c>
       <c r="N10" s="2" t="n">
         <v>186</v>
       </c>
       <c r="O10" s="2" t="n">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="P10" s="3" t="n">
-        <v>3216</v>
+        <v>3228</v>
       </c>
       <c r="Q10" s="3" t="inlineStr">
         <is>

--- a/data/extracted/series/corpus_publication_cadence_and_audit.xlsx
+++ b/data/extracted/series/corpus_publication_cadence_and_audit.xlsx
@@ -1229,7 +1229,7 @@
         <v>4764</v>
       </c>
       <c r="O8" s="2" t="n">
-        <v>5035</v>
+        <v>5030</v>
       </c>
       <c r="P8" s="3" t="n">
         <v>5029</v>
@@ -1322,7 +1322,7 @@
         <v>4764</v>
       </c>
       <c r="O9" s="2" t="n">
-        <v>4774</v>
+        <v>4769</v>
       </c>
       <c r="P9" s="3" t="n">
         <v>4765</v>

--- a/data/extracted/series/corpus_publication_cadence_and_audit.xlsx
+++ b/data/extracted/series/corpus_publication_cadence_and_audit.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Corpus Cadence &amp; Inventory" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Graphic &amp; Chart Extraction" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sub-Sector &amp; Fleet Breakdown" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Corpus Cadence &amp; Inventory" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Graphic &amp; Chart Extraction" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Sub-Sector &amp; Fleet Breakdown" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1897,7 +1897,7 @@
       </c>
       <c r="S15" s="3" t="inlineStr">
         <is>
-          <t>ssy_capesize_index_series.csv (9,442 rows), ssy_capesize_series.csv (8,881 rows), ssy_route_rates_series.csv (5,190 rows), ssy_capesize_index_time_series.csv (519 rows)</t>
+          <t>ssy_capesize_index_series.csv (9,584 rows), ssy_capesize_series.csv (8,881 rows), ssy_route_rates_series.csv (5,190 rows), ssy_capesize_index_time_series.csv (519 rows)</t>
         </is>
       </c>
       <c r="T15" s="3" t="inlineStr">

--- a/data/extracted/series/corpus_publication_cadence_and_audit.xlsx
+++ b/data/extracted/series/corpus_publication_cadence_and_audit.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Corpus Cadence &amp; Inventory" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Graphic &amp; Chart Extraction" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Sub-Sector &amp; Fleet Breakdown" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Corpus Cadence &amp; Inventory" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Graphic &amp; Chart Extraction" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sub-Sector &amp; Fleet Breakdown" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -550,7 +550,7 @@
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>Status (2026-10-14)</t>
+          <t>Status (2026-10-15)</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
@@ -651,11 +651,11 @@
         </is>
       </c>
       <c r="I2" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J2" s="4" t="inlineStr">
         <is>
-          <t>CURRENT (4d ago)</t>
+          <t>CURRENT (5d ago)</t>
         </is>
       </c>
       <c r="K2" s="2" t="n">
@@ -744,11 +744,11 @@
         </is>
       </c>
       <c r="I3" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J3" s="4" t="inlineStr">
         <is>
-          <t>CURRENT (4d ago)</t>
+          <t>CURRENT (5d ago)</t>
         </is>
       </c>
       <c r="K3" s="2" t="n">
@@ -837,11 +837,11 @@
         </is>
       </c>
       <c r="I4" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J4" s="4" t="inlineStr">
         <is>
-          <t>CURRENT (5d ago)</t>
+          <t>CURRENT (6d ago)</t>
         </is>
       </c>
       <c r="K4" s="2" t="n">
@@ -930,11 +930,11 @@
         </is>
       </c>
       <c r="I5" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J5" s="4" t="inlineStr">
         <is>
-          <t>CURRENT (0d ago)</t>
+          <t>CURRENT (1d ago)</t>
         </is>
       </c>
       <c r="K5" s="2" t="n">
@@ -1023,11 +1023,11 @@
         </is>
       </c>
       <c r="I6" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J6" s="4" t="inlineStr">
         <is>
-          <t>CURRENT (2d ago)</t>
+          <t>CURRENT (3d ago)</t>
         </is>
       </c>
       <c r="K6" s="2" t="n">
@@ -1116,11 +1116,11 @@
         </is>
       </c>
       <c r="I7" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J7" s="4" t="inlineStr">
         <is>
-          <t>CURRENT (5d ago)</t>
+          <t>CURRENT (6d ago)</t>
         </is>
       </c>
       <c r="K7" s="2" t="n">
@@ -1209,11 +1209,11 @@
         </is>
       </c>
       <c r="I8" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J8" s="4" t="inlineStr">
         <is>
-          <t>CURRENT (0d ago)</t>
+          <t>CURRENT (1d ago)</t>
         </is>
       </c>
       <c r="K8" s="2" t="n">
@@ -1229,7 +1229,7 @@
         <v>4764</v>
       </c>
       <c r="O8" s="2" t="n">
-        <v>5030</v>
+        <v>5035</v>
       </c>
       <c r="P8" s="3" t="n">
         <v>5029</v>
@@ -1302,11 +1302,11 @@
         </is>
       </c>
       <c r="I9" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J9" s="4" t="inlineStr">
         <is>
-          <t>CURRENT (0d ago)</t>
+          <t>CURRENT (1d ago)</t>
         </is>
       </c>
       <c r="K9" s="2" t="n">
@@ -1322,7 +1322,7 @@
         <v>4764</v>
       </c>
       <c r="O9" s="2" t="n">
-        <v>4769</v>
+        <v>4774</v>
       </c>
       <c r="P9" s="3" t="n">
         <v>4765</v>
@@ -1395,11 +1395,11 @@
         </is>
       </c>
       <c r="I10" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J10" s="4" t="inlineStr">
         <is>
-          <t>CURRENT (0d ago)</t>
+          <t>CURRENT (1d ago)</t>
         </is>
       </c>
       <c r="K10" s="2" t="n">
@@ -1488,11 +1488,11 @@
         </is>
       </c>
       <c r="I11" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J11" s="4" t="inlineStr">
         <is>
-          <t>CURRENT (5d ago)</t>
+          <t>CURRENT (6d ago)</t>
         </is>
       </c>
       <c r="K11" s="2" t="n">
@@ -1581,11 +1581,11 @@
         </is>
       </c>
       <c r="I12" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J12" s="4" t="inlineStr">
         <is>
-          <t>CURRENT (0d ago)</t>
+          <t>CURRENT (1d ago)</t>
         </is>
       </c>
       <c r="K12" s="2" t="n">
@@ -1674,11 +1674,11 @@
         </is>
       </c>
       <c r="I13" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J13" s="4" t="inlineStr">
         <is>
-          <t>CURRENT (2d ago)</t>
+          <t>CURRENT (3d ago)</t>
         </is>
       </c>
       <c r="K13" s="2" t="n">
@@ -1767,11 +1767,11 @@
         </is>
       </c>
       <c r="I14" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J14" s="4" t="inlineStr">
         <is>
-          <t>CURRENT (5d ago)</t>
+          <t>CURRENT (6d ago)</t>
         </is>
       </c>
       <c r="K14" s="2" t="n">
@@ -1860,11 +1860,11 @@
         </is>
       </c>
       <c r="I15" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J15" s="4" t="inlineStr">
         <is>
-          <t>CURRENT (2d ago)</t>
+          <t>CURRENT (3d ago)</t>
         </is>
       </c>
       <c r="K15" s="2" t="n">
@@ -1953,11 +1953,11 @@
         </is>
       </c>
       <c r="I16" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J16" s="4" t="inlineStr">
         <is>
-          <t>CURRENT (2d ago)</t>
+          <t>CURRENT (3d ago)</t>
         </is>
       </c>
       <c r="K16" s="2" t="n">
@@ -2046,11 +2046,11 @@
         </is>
       </c>
       <c r="I17" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J17" s="4" t="inlineStr">
         <is>
-          <t>CURRENT (1d ago)</t>
+          <t>CURRENT (2d ago)</t>
         </is>
       </c>
       <c r="K17" s="2" t="n">
@@ -2139,11 +2139,11 @@
         </is>
       </c>
       <c r="I18" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J18" s="4" t="inlineStr">
         <is>
-          <t>CURRENT (4d ago)</t>
+          <t>CURRENT (5d ago)</t>
         </is>
       </c>
       <c r="K18" s="2" t="n">
@@ -2232,11 +2232,11 @@
         </is>
       </c>
       <c r="I19" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="J19" s="4" t="inlineStr">
         <is>
-          <t>CURRENT (7d ago)</t>
+          <t>CURRENT (8d ago)</t>
         </is>
       </c>
       <c r="K19" s="2" t="n">
@@ -2325,11 +2325,11 @@
         </is>
       </c>
       <c r="I20" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J20" s="4" t="inlineStr">
         <is>
-          <t>CURRENT (0d ago)</t>
+          <t>CURRENT (1d ago)</t>
         </is>
       </c>
       <c r="K20" s="2" t="n">
@@ -2418,11 +2418,11 @@
         </is>
       </c>
       <c r="I21" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J21" s="4" t="inlineStr">
         <is>
-          <t>CURRENT (8d ago)</t>
+          <t>CURRENT (9d ago)</t>
         </is>
       </c>
       <c r="K21" s="2" t="n">
@@ -2511,11 +2511,11 @@
         </is>
       </c>
       <c r="I22" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="J22" s="4" t="inlineStr">
         <is>
-          <t>CURRENT (7d ago)</t>
+          <t>CURRENT (8d ago)</t>
         </is>
       </c>
       <c r="K22" s="2" t="n">
@@ -2604,11 +2604,11 @@
         </is>
       </c>
       <c r="I23" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J23" s="4" t="inlineStr">
         <is>
-          <t>CURRENT (8d ago)</t>
+          <t>CURRENT (9d ago)</t>
         </is>
       </c>
       <c r="K23" s="2" t="n">
@@ -2697,11 +2697,11 @@
         </is>
       </c>
       <c r="I24" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J24" s="4" t="inlineStr">
         <is>
-          <t>CURRENT (0d ago)</t>
+          <t>CURRENT (1d ago)</t>
         </is>
       </c>
       <c r="K24" s="2" t="n">
@@ -2790,11 +2790,11 @@
         </is>
       </c>
       <c r="I25" s="2" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="J25" s="4" t="inlineStr">
         <is>
-          <t>CURRENT (12d ago)</t>
+          <t>CURRENT (13d ago)</t>
         </is>
       </c>
       <c r="K25" s="2" t="n">
@@ -2883,11 +2883,11 @@
         </is>
       </c>
       <c r="I26" s="2" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="J26" s="5" t="inlineStr">
         <is>
-          <t>NORMAL INTERVAL (43d ago)</t>
+          <t>NORMAL INTERVAL (44d ago)</t>
         </is>
       </c>
       <c r="K26" s="2" t="n">
@@ -2976,11 +2976,11 @@
         </is>
       </c>
       <c r="I27" s="2" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="J27" s="5" t="inlineStr">
         <is>
-          <t>NORMAL INTERVAL (20d ago)</t>
+          <t>NORMAL INTERVAL (21d ago)</t>
         </is>
       </c>
       <c r="K27" s="2" t="n">
@@ -3069,11 +3069,11 @@
         </is>
       </c>
       <c r="I28" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J28" s="4" t="inlineStr">
         <is>
-          <t>CURRENT (6d ago)</t>
+          <t>CURRENT (7d ago)</t>
         </is>
       </c>
       <c r="K28" s="2" t="n">
@@ -3162,11 +3162,11 @@
         </is>
       </c>
       <c r="I29" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J29" s="4" t="inlineStr">
         <is>
-          <t>CURRENT (5d ago)</t>
+          <t>CURRENT (6d ago)</t>
         </is>
       </c>
       <c r="K29" s="2" t="n">
@@ -3255,11 +3255,11 @@
         </is>
       </c>
       <c r="I30" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J30" s="4" t="inlineStr">
         <is>
-          <t>CURRENT (5d ago)</t>
+          <t>CURRENT (6d ago)</t>
         </is>
       </c>
       <c r="K30" s="2" t="n">
@@ -3348,11 +3348,11 @@
         </is>
       </c>
       <c r="I31" s="2" t="n">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="J31" s="5" t="inlineStr">
         <is>
-          <t>NORMAL INTERVAL (78d ago)</t>
+          <t>NORMAL INTERVAL (79d ago)</t>
         </is>
       </c>
       <c r="K31" s="2" t="n">
@@ -3441,11 +3441,11 @@
         </is>
       </c>
       <c r="I32" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J32" s="4" t="inlineStr">
         <is>
-          <t>CURRENT (5d ago)</t>
+          <t>CURRENT (6d ago)</t>
         </is>
       </c>
       <c r="K32" s="2" t="n">
@@ -3534,11 +3534,11 @@
         </is>
       </c>
       <c r="I33" s="2" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="J33" s="4" t="inlineStr">
         <is>
-          <t>CURRENT (10d ago)</t>
+          <t>CURRENT (11d ago)</t>
         </is>
       </c>
       <c r="K33" s="2" t="n">

--- a/data/extracted/series/corpus_publication_cadence_and_audit.xlsx
+++ b/data/extracted/series/corpus_publication_cadence_and_audit.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Corpus Cadence &amp; Inventory" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Graphic &amp; Chart Extraction" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sub-Sector &amp; Fleet Breakdown" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Corpus Cadence &amp; Inventory" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Graphic &amp; Chart Extraction" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Sub-Sector &amp; Fleet Breakdown" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1205,19 +1205,19 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="I8" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J8" s="4" t="inlineStr">
         <is>
-          <t>CURRENT (1d ago)</t>
+          <t>CURRENT (0d ago)</t>
         </is>
       </c>
       <c r="K8" s="2" t="n">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="L8" s="2" t="n">
         <v>0</v>
@@ -1229,10 +1229,10 @@
         <v>4764</v>
       </c>
       <c r="O8" s="2" t="n">
-        <v>5035</v>
+        <v>5036</v>
       </c>
       <c r="P8" s="3" t="n">
-        <v>5029</v>
+        <v>5030</v>
       </c>
       <c r="Q8" s="3" t="inlineStr">
         <is>
@@ -1246,7 +1246,7 @@
       </c>
       <c r="S8" s="3" t="inlineStr">
         <is>
-          <t>fearnleys_rates_series.csv (17,112 rows)</t>
+          <t>fearnleys_rates_series.csv (17,153 rows)</t>
         </is>
       </c>
       <c r="T8" s="3" t="inlineStr">
@@ -1897,7 +1897,7 @@
       </c>
       <c r="S15" s="3" t="inlineStr">
         <is>
-          <t>ssy_capesize_index_series.csv (9,584 rows), ssy_capesize_series.csv (8,881 rows), ssy_route_rates_series.csv (5,190 rows), ssy_capesize_index_time_series.csv (519 rows)</t>
+          <t>ssy_capesize_index_series.csv (9,726 rows), ssy_capesize_series.csv (8,881 rows), ssy_route_rates_series.csv (5,190 rows), ssy_capesize_index_time_series.csv (519 rows)</t>
         </is>
       </c>
       <c r="T15" s="3" t="inlineStr">

--- a/data/extracted/series/corpus_publication_cadence_and_audit.xlsx
+++ b/data/extracted/series/corpus_publication_cadence_and_audit.xlsx
@@ -1217,7 +1217,7 @@
         </is>
       </c>
       <c r="K8" s="2" t="n">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="L8" s="2" t="n">
         <v>0</v>
@@ -1232,7 +1232,7 @@
         <v>5036</v>
       </c>
       <c r="P8" s="3" t="n">
-        <v>5030</v>
+        <v>5031</v>
       </c>
       <c r="Q8" s="3" t="inlineStr">
         <is>
@@ -2228,34 +2228,34 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="I19" s="2" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="J19" s="4" t="inlineStr">
         <is>
-          <t>CURRENT (8d ago)</t>
+          <t>CURRENT (1d ago)</t>
         </is>
       </c>
       <c r="K19" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L19" s="2" t="n">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="M19" s="2" t="n">
-        <v>762</v>
+        <v>763</v>
       </c>
       <c r="N19" s="2" t="n">
         <v>0</v>
       </c>
       <c r="O19" s="2" t="n">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="P19" s="3" t="n">
-        <v>1042</v>
+        <v>1044</v>
       </c>
       <c r="Q19" s="3" t="inlineStr">
         <is>
@@ -2321,19 +2321,19 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="I20" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J20" s="4" t="inlineStr">
         <is>
-          <t>CURRENT (1d ago)</t>
+          <t>CURRENT (0d ago)</t>
         </is>
       </c>
       <c r="K20" s="2" t="n">
-        <v>4538</v>
+        <v>4540</v>
       </c>
       <c r="L20" s="2" t="n">
         <v>1202</v>
@@ -2345,7 +2345,7 @@
         <v>0</v>
       </c>
       <c r="O20" s="2" t="n">
-        <v>1195</v>
+        <v>1197</v>
       </c>
       <c r="P20" s="3" t="n">
         <v>9057</v>
@@ -2507,34 +2507,34 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="I22" s="2" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="J22" s="4" t="inlineStr">
         <is>
-          <t>CURRENT (8d ago)</t>
+          <t>CURRENT (1d ago)</t>
         </is>
       </c>
       <c r="K22" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L22" s="2" t="n">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="M22" s="2" t="n">
-        <v>759</v>
+        <v>760</v>
       </c>
       <c r="N22" s="2" t="n">
         <v>0</v>
       </c>
       <c r="O22" s="2" t="n">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="P22" s="3" t="n">
-        <v>1039</v>
+        <v>1041</v>
       </c>
       <c r="Q22" s="3" t="inlineStr">
         <is>
@@ -2600,22 +2600,22 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="I23" s="2" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="J23" s="4" t="inlineStr">
         <is>
-          <t>CURRENT (9d ago)</t>
+          <t>CURRENT (1d ago)</t>
         </is>
       </c>
       <c r="K23" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L23" s="2" t="n">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="M23" s="2" t="n">
         <v>733</v>
@@ -2627,7 +2627,7 @@
         <v>261</v>
       </c>
       <c r="P23" s="3" t="n">
-        <v>1008</v>
+        <v>1009</v>
       </c>
       <c r="Q23" s="3" t="inlineStr">
         <is>
@@ -2641,7 +2641,7 @@
       </c>
       <c r="S23" s="3" t="inlineStr">
         <is>
-          <t>hellenic_vv_matrix_series.csv (12,373 rows), hellenic_vv_sales_series.csv (2,067 rows)</t>
+          <t>hellenic_vv_matrix_series.csv (12,373 rows), hellenic_vv_sales_series.csv (2,077 rows)</t>
         </is>
       </c>
       <c r="T23" s="3" t="inlineStr">
@@ -2693,34 +2693,34 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="I24" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J24" s="4" t="inlineStr">
         <is>
-          <t>CURRENT (1d ago)</t>
+          <t>CURRENT (0d ago)</t>
         </is>
       </c>
       <c r="K24" s="2" t="n">
         <v>306</v>
       </c>
       <c r="L24" s="2" t="n">
-        <v>3251</v>
+        <v>3252</v>
       </c>
       <c r="M24" s="2" t="n">
-        <v>15111</v>
+        <v>15113</v>
       </c>
       <c r="N24" s="2" t="n">
-        <v>3222</v>
+        <v>3223</v>
       </c>
       <c r="O24" s="2" t="n">
-        <v>3514</v>
+        <v>3515</v>
       </c>
       <c r="P24" s="3" t="n">
-        <v>21890</v>
+        <v>21894</v>
       </c>
       <c r="Q24" s="3" t="inlineStr">
         <is>
@@ -2734,7 +2734,7 @@
       </c>
       <c r="S24" s="3" t="inlineStr">
         <is>
-          <t>breakwave_fundamentals_series.csv (2,759 rows), breakwave_insights_metadata.csv (3,222 rows)</t>
+          <t>breakwave_fundamentals_series.csv (2,759 rows), breakwave_insights_metadata.csv (3,223 rows)</t>
         </is>
       </c>
       <c r="T24" s="3" t="inlineStr">
@@ -5094,7 +5094,7 @@
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>2,067 rows</t>
+          <t>2,077 rows</t>
         </is>
       </c>
       <c r="H25" s="3" t="inlineStr">

--- a/data/extracted/series/corpus_publication_cadence_and_audit.xlsx
+++ b/data/extracted/series/corpus_publication_cadence_and_audit.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Corpus Cadence &amp; Inventory" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Graphic &amp; Chart Extraction" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sub-Sector &amp; Fleet Breakdown" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Corpus Cadence &amp; Inventory" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Graphic &amp; Chart Extraction" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Sub-Sector &amp; Fleet Breakdown" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1897,7 +1897,7 @@
       </c>
       <c r="S15" s="3" t="inlineStr">
         <is>
-          <t>ssy_capesize_index_series.csv (9,726 rows), ssy_capesize_series.csv (8,881 rows), ssy_route_rates_series.csv (5,190 rows), ssy_capesize_index_time_series.csv (519 rows)</t>
+          <t>ssy_capesize_index_series.csv (9,868 rows), ssy_capesize_series.csv (8,881 rows), ssy_route_rates_series.csv (5,190 rows), ssy_capesize_index_time_series.csv (519 rows)</t>
         </is>
       </c>
       <c r="T15" s="3" t="inlineStr">

--- a/data/extracted/series/corpus_publication_cadence_and_audit.xlsx
+++ b/data/extracted/series/corpus_publication_cadence_and_audit.xlsx
@@ -550,7 +550,7 @@
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>Status (2026-10-15)</t>
+          <t>Status (2026-10-16)</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
@@ -651,11 +651,11 @@
         </is>
       </c>
       <c r="I2" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J2" s="4" t="inlineStr">
         <is>
-          <t>CURRENT (5d ago)</t>
+          <t>CURRENT (6d ago)</t>
         </is>
       </c>
       <c r="K2" s="2" t="n">
@@ -744,11 +744,11 @@
         </is>
       </c>
       <c r="I3" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J3" s="4" t="inlineStr">
         <is>
-          <t>CURRENT (5d ago)</t>
+          <t>CURRENT (6d ago)</t>
         </is>
       </c>
       <c r="K3" s="2" t="n">
@@ -837,11 +837,11 @@
         </is>
       </c>
       <c r="I4" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J4" s="4" t="inlineStr">
         <is>
-          <t>CURRENT (6d ago)</t>
+          <t>CURRENT (7d ago)</t>
         </is>
       </c>
       <c r="K4" s="2" t="n">
@@ -930,11 +930,11 @@
         </is>
       </c>
       <c r="I5" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J5" s="4" t="inlineStr">
         <is>
-          <t>CURRENT (1d ago)</t>
+          <t>CURRENT (2d ago)</t>
         </is>
       </c>
       <c r="K5" s="2" t="n">
@@ -1023,11 +1023,11 @@
         </is>
       </c>
       <c r="I6" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J6" s="4" t="inlineStr">
         <is>
-          <t>CURRENT (3d ago)</t>
+          <t>CURRENT (4d ago)</t>
         </is>
       </c>
       <c r="K6" s="2" t="n">
@@ -1116,11 +1116,11 @@
         </is>
       </c>
       <c r="I7" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J7" s="4" t="inlineStr">
         <is>
-          <t>CURRENT (6d ago)</t>
+          <t>CURRENT (7d ago)</t>
         </is>
       </c>
       <c r="K7" s="2" t="n">
@@ -1209,11 +1209,11 @@
         </is>
       </c>
       <c r="I8" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J8" s="4" t="inlineStr">
         <is>
-          <t>CURRENT (0d ago)</t>
+          <t>CURRENT (1d ago)</t>
         </is>
       </c>
       <c r="K8" s="2" t="n">
@@ -1302,11 +1302,11 @@
         </is>
       </c>
       <c r="I9" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J9" s="4" t="inlineStr">
         <is>
-          <t>CURRENT (1d ago)</t>
+          <t>CURRENT (2d ago)</t>
         </is>
       </c>
       <c r="K9" s="2" t="n">
@@ -1395,11 +1395,11 @@
         </is>
       </c>
       <c r="I10" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J10" s="4" t="inlineStr">
         <is>
-          <t>CURRENT (1d ago)</t>
+          <t>CURRENT (2d ago)</t>
         </is>
       </c>
       <c r="K10" s="2" t="n">
@@ -1488,11 +1488,11 @@
         </is>
       </c>
       <c r="I11" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J11" s="4" t="inlineStr">
         <is>
-          <t>CURRENT (6d ago)</t>
+          <t>CURRENT (7d ago)</t>
         </is>
       </c>
       <c r="K11" s="2" t="n">
@@ -1581,11 +1581,11 @@
         </is>
       </c>
       <c r="I12" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J12" s="4" t="inlineStr">
         <is>
-          <t>CURRENT (1d ago)</t>
+          <t>CURRENT (2d ago)</t>
         </is>
       </c>
       <c r="K12" s="2" t="n">
@@ -1674,11 +1674,11 @@
         </is>
       </c>
       <c r="I13" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J13" s="4" t="inlineStr">
         <is>
-          <t>CURRENT (3d ago)</t>
+          <t>CURRENT (4d ago)</t>
         </is>
       </c>
       <c r="K13" s="2" t="n">
@@ -1767,11 +1767,11 @@
         </is>
       </c>
       <c r="I14" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J14" s="4" t="inlineStr">
         <is>
-          <t>CURRENT (6d ago)</t>
+          <t>CURRENT (7d ago)</t>
         </is>
       </c>
       <c r="K14" s="2" t="n">
@@ -1860,11 +1860,11 @@
         </is>
       </c>
       <c r="I15" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J15" s="4" t="inlineStr">
         <is>
-          <t>CURRENT (3d ago)</t>
+          <t>CURRENT (4d ago)</t>
         </is>
       </c>
       <c r="K15" s="2" t="n">
@@ -1897,7 +1897,7 @@
       </c>
       <c r="S15" s="3" t="inlineStr">
         <is>
-          <t>ssy_capesize_index_series.csv (9,868 rows), ssy_capesize_series.csv (8,881 rows), ssy_route_rates_series.csv (5,190 rows), ssy_capesize_index_time_series.csv (519 rows)</t>
+          <t>ssy_capesize_index_series.csv (10,010 rows), ssy_capesize_series.csv (8,881 rows), ssy_route_rates_series.csv (5,190 rows), ssy_capesize_index_time_series.csv (519 rows)</t>
         </is>
       </c>
       <c r="T15" s="3" t="inlineStr">
@@ -1953,11 +1953,11 @@
         </is>
       </c>
       <c r="I16" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J16" s="4" t="inlineStr">
         <is>
-          <t>CURRENT (3d ago)</t>
+          <t>CURRENT (4d ago)</t>
         </is>
       </c>
       <c r="K16" s="2" t="n">
@@ -2046,11 +2046,11 @@
         </is>
       </c>
       <c r="I17" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J17" s="4" t="inlineStr">
         <is>
-          <t>CURRENT (2d ago)</t>
+          <t>CURRENT (3d ago)</t>
         </is>
       </c>
       <c r="K17" s="2" t="n">
@@ -2139,11 +2139,11 @@
         </is>
       </c>
       <c r="I18" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J18" s="4" t="inlineStr">
         <is>
-          <t>CURRENT (5d ago)</t>
+          <t>CURRENT (6d ago)</t>
         </is>
       </c>
       <c r="K18" s="2" t="n">
@@ -2232,11 +2232,11 @@
         </is>
       </c>
       <c r="I19" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J19" s="4" t="inlineStr">
         <is>
-          <t>CURRENT (1d ago)</t>
+          <t>CURRENT (2d ago)</t>
         </is>
       </c>
       <c r="K19" s="2" t="n">
@@ -2325,11 +2325,11 @@
         </is>
       </c>
       <c r="I20" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J20" s="4" t="inlineStr">
         <is>
-          <t>CURRENT (0d ago)</t>
+          <t>CURRENT (1d ago)</t>
         </is>
       </c>
       <c r="K20" s="2" t="n">
@@ -2418,11 +2418,11 @@
         </is>
       </c>
       <c r="I21" s="2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J21" s="4" t="inlineStr">
         <is>
-          <t>CURRENT (9d ago)</t>
+          <t>CURRENT (10d ago)</t>
         </is>
       </c>
       <c r="K21" s="2" t="n">
@@ -2511,11 +2511,11 @@
         </is>
       </c>
       <c r="I22" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J22" s="4" t="inlineStr">
         <is>
-          <t>CURRENT (1d ago)</t>
+          <t>CURRENT (2d ago)</t>
         </is>
       </c>
       <c r="K22" s="2" t="n">
@@ -2604,11 +2604,11 @@
         </is>
       </c>
       <c r="I23" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J23" s="4" t="inlineStr">
         <is>
-          <t>CURRENT (1d ago)</t>
+          <t>CURRENT (2d ago)</t>
         </is>
       </c>
       <c r="K23" s="2" t="n">
@@ -2697,11 +2697,11 @@
         </is>
       </c>
       <c r="I24" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J24" s="4" t="inlineStr">
         <is>
-          <t>CURRENT (0d ago)</t>
+          <t>CURRENT (1d ago)</t>
         </is>
       </c>
       <c r="K24" s="2" t="n">
@@ -2790,11 +2790,11 @@
         </is>
       </c>
       <c r="I25" s="2" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="J25" s="4" t="inlineStr">
         <is>
-          <t>CURRENT (13d ago)</t>
+          <t>CURRENT (14d ago)</t>
         </is>
       </c>
       <c r="K25" s="2" t="n">
@@ -2883,11 +2883,11 @@
         </is>
       </c>
       <c r="I26" s="2" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="J26" s="5" t="inlineStr">
         <is>
-          <t>NORMAL INTERVAL (44d ago)</t>
+          <t>NORMAL INTERVAL (45d ago)</t>
         </is>
       </c>
       <c r="K26" s="2" t="n">
@@ -2976,11 +2976,11 @@
         </is>
       </c>
       <c r="I27" s="2" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="J27" s="5" t="inlineStr">
         <is>
-          <t>NORMAL INTERVAL (21d ago)</t>
+          <t>NORMAL INTERVAL (22d ago)</t>
         </is>
       </c>
       <c r="K27" s="2" t="n">
@@ -3069,11 +3069,11 @@
         </is>
       </c>
       <c r="I28" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="J28" s="4" t="inlineStr">
         <is>
-          <t>CURRENT (7d ago)</t>
+          <t>CURRENT (8d ago)</t>
         </is>
       </c>
       <c r="K28" s="2" t="n">
@@ -3162,11 +3162,11 @@
         </is>
       </c>
       <c r="I29" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J29" s="4" t="inlineStr">
         <is>
-          <t>CURRENT (6d ago)</t>
+          <t>CURRENT (7d ago)</t>
         </is>
       </c>
       <c r="K29" s="2" t="n">
@@ -3255,11 +3255,11 @@
         </is>
       </c>
       <c r="I30" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J30" s="4" t="inlineStr">
         <is>
-          <t>CURRENT (6d ago)</t>
+          <t>CURRENT (7d ago)</t>
         </is>
       </c>
       <c r="K30" s="2" t="n">
@@ -3348,11 +3348,11 @@
         </is>
       </c>
       <c r="I31" s="2" t="n">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="J31" s="5" t="inlineStr">
         <is>
-          <t>NORMAL INTERVAL (79d ago)</t>
+          <t>NORMAL INTERVAL (80d ago)</t>
         </is>
       </c>
       <c r="K31" s="2" t="n">
@@ -3441,11 +3441,11 @@
         </is>
       </c>
       <c r="I32" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J32" s="4" t="inlineStr">
         <is>
-          <t>CURRENT (6d ago)</t>
+          <t>CURRENT (7d ago)</t>
         </is>
       </c>
       <c r="K32" s="2" t="n">
@@ -3534,11 +3534,11 @@
         </is>
       </c>
       <c r="I33" s="2" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="J33" s="4" t="inlineStr">
         <is>
-          <t>CURRENT (11d ago)</t>
+          <t>CURRENT (12d ago)</t>
         </is>
       </c>
       <c r="K33" s="2" t="n">

--- a/data/extracted/series/corpus_publication_cadence_and_audit.xlsx
+++ b/data/extracted/series/corpus_publication_cadence_and_audit.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Corpus Cadence &amp; Inventory" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Graphic &amp; Chart Extraction" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Sub-Sector &amp; Fleet Breakdown" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Corpus Cadence &amp; Inventory" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Graphic &amp; Chart Extraction" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sub-Sector &amp; Fleet Breakdown" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -2321,19 +2321,19 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="I20" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J20" s="4" t="inlineStr">
         <is>
-          <t>CURRENT (1d ago)</t>
+          <t>CURRENT (0d ago)</t>
         </is>
       </c>
       <c r="K20" s="2" t="n">
-        <v>4540</v>
+        <v>4542</v>
       </c>
       <c r="L20" s="2" t="n">
         <v>1202</v>
@@ -2345,7 +2345,7 @@
         <v>0</v>
       </c>
       <c r="O20" s="2" t="n">
-        <v>1197</v>
+        <v>1199</v>
       </c>
       <c r="P20" s="3" t="n">
         <v>9057</v>
@@ -2693,34 +2693,34 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="I24" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J24" s="4" t="inlineStr">
         <is>
-          <t>CURRENT (1d ago)</t>
+          <t>CURRENT (0d ago)</t>
         </is>
       </c>
       <c r="K24" s="2" t="n">
         <v>306</v>
       </c>
       <c r="L24" s="2" t="n">
-        <v>3252</v>
+        <v>3254</v>
       </c>
       <c r="M24" s="2" t="n">
-        <v>15113</v>
+        <v>15120</v>
       </c>
       <c r="N24" s="2" t="n">
-        <v>3223</v>
+        <v>3225</v>
       </c>
       <c r="O24" s="2" t="n">
-        <v>3515</v>
+        <v>3517</v>
       </c>
       <c r="P24" s="3" t="n">
-        <v>21894</v>
+        <v>21905</v>
       </c>
       <c r="Q24" s="3" t="inlineStr">
         <is>
@@ -2734,7 +2734,7 @@
       </c>
       <c r="S24" s="3" t="inlineStr">
         <is>
-          <t>breakwave_fundamentals_series.csv (2,759 rows), breakwave_insights_metadata.csv (3,223 rows)</t>
+          <t>breakwave_fundamentals_series.csv (2,759 rows), breakwave_insights_metadata.csv (3,225 rows)</t>
         </is>
       </c>
       <c r="T24" s="3" t="inlineStr">
@@ -3251,34 +3251,34 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="I30" s="2" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="J30" s="4" t="inlineStr">
         <is>
-          <t>CURRENT (7d ago)</t>
+          <t>CURRENT (0d ago)</t>
         </is>
       </c>
       <c r="K30" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L30" s="2" t="n">
-        <v>3054</v>
+        <v>3059</v>
       </c>
       <c r="M30" s="2" t="n">
         <v>0</v>
       </c>
       <c r="N30" s="2" t="n">
-        <v>2234</v>
+        <v>2239</v>
       </c>
       <c r="O30" s="2" t="n">
-        <v>2234</v>
+        <v>2239</v>
       </c>
       <c r="P30" s="3" t="n">
-        <v>5288</v>
+        <v>5298</v>
       </c>
       <c r="Q30" s="3" t="inlineStr">
         <is>
@@ -3292,7 +3292,7 @@
       </c>
       <c r="S30" s="3" t="inlineStr">
         <is>
-          <t>baltic_reports_metadata.csv (2,234 rows), baltic_ncfi_series.csv (2,049 rows)</t>
+          <t>baltic_reports_metadata.csv (2,239 rows), baltic_ncfi_series.csv (2,053 rows)</t>
         </is>
       </c>
       <c r="T30" s="3" t="inlineStr">

--- a/data/extracted/series/corpus_publication_cadence_and_audit.xlsx
+++ b/data/extracted/series/corpus_publication_cadence_and_audit.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Corpus Cadence &amp; Inventory" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Graphic &amp; Chart Extraction" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sub-Sector &amp; Fleet Breakdown" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Corpus Cadence &amp; Inventory" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Graphic &amp; Chart Extraction" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Sub-Sector &amp; Fleet Breakdown" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -2786,19 +2786,19 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="I25" s="2" t="n">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="J25" s="4" t="inlineStr">
         <is>
-          <t>CURRENT (14d ago)</t>
+          <t>CURRENT (5d ago)</t>
         </is>
       </c>
       <c r="K25" s="2" t="n">
-        <v>1094</v>
+        <v>1095</v>
       </c>
       <c r="L25" s="2" t="n">
         <v>0</v>
@@ -2807,10 +2807,10 @@
         <v>0</v>
       </c>
       <c r="N25" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O25" s="2" t="n">
-        <v>1090</v>
+        <v>1091</v>
       </c>
       <c r="P25" s="3" t="n">
         <v>3270</v>
@@ -2827,7 +2827,7 @@
       </c>
       <c r="S25" s="3" t="inlineStr">
         <is>
-          <t>poten_opinions_metadata.csv (1,094 rows), poten_top_charterers_series.csv (776 rows), poten_fixtures_series.csv (100 rows)</t>
+          <t>poten_opinions_metadata.csv (1,095 rows), poten_top_charterers_series.csv (776 rows), poten_fixtures_series.csv (100 rows)</t>
         </is>
       </c>
       <c r="T25" s="3" t="inlineStr">
@@ -2984,7 +2984,7 @@
         </is>
       </c>
       <c r="K27" s="2" t="n">
-        <v>291</v>
+        <v>294</v>
       </c>
       <c r="L27" s="2" t="n">
         <v>0</v>
@@ -2996,10 +2996,10 @@
         <v>0</v>
       </c>
       <c r="O27" s="2" t="n">
-        <v>291</v>
+        <v>294</v>
       </c>
       <c r="P27" s="3" t="n">
-        <v>292</v>
+        <v>295</v>
       </c>
       <c r="Q27" s="3" t="inlineStr">
         <is>
@@ -3013,7 +3013,7 @@
       </c>
       <c r="S27" s="3" t="inlineStr">
         <is>
-          <t>drewry_ais_chart_series.csv (82,793 rows)</t>
+          <t>drewry_ais_chart_series.csv (83,090 rows)</t>
         </is>
       </c>
       <c r="T27" s="3" t="inlineStr">
@@ -3065,15 +3065,15 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="I28" s="2" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="J28" s="4" t="inlineStr">
         <is>
-          <t>CURRENT (8d ago)</t>
+          <t>CURRENT (1d ago)</t>
         </is>
       </c>
       <c r="K28" s="2" t="n">
@@ -3086,10 +3086,10 @@
         <v>0</v>
       </c>
       <c r="N28" s="2" t="n">
-        <v>1093</v>
+        <v>1096</v>
       </c>
       <c r="O28" s="2" t="n">
-        <v>552</v>
+        <v>555</v>
       </c>
       <c r="P28" s="3" t="n">
         <v>1108</v>
@@ -3106,7 +3106,7 @@
       </c>
       <c r="S28" s="3" t="inlineStr">
         <is>
-          <t>drewry_wci_historical.csv (137 rows), drewry_opinions_metadata.csv (552 rows), drewry_wci_series.csv (7 rows)</t>
+          <t>drewry_wci_historical.csv (138 rows), drewry_opinions_metadata.csv (555 rows), drewry_wci_series.csv (8 rows)</t>
         </is>
       </c>
       <c r="T28" s="3" t="inlineStr">
@@ -4013,7 +4013,7 @@
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>82,793 rows</t>
+          <t>83,090 rows</t>
         </is>
       </c>
       <c r="H2" s="3" t="inlineStr">
@@ -4060,7 +4060,7 @@
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>82,793 rows</t>
+          <t>83,090 rows</t>
         </is>
       </c>
       <c r="H3" s="3" t="inlineStr">
@@ -4107,7 +4107,7 @@
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>82,793 rows</t>
+          <t>83,090 rows</t>
         </is>
       </c>
       <c r="H4" s="3" t="inlineStr">
@@ -4154,7 +4154,7 @@
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>82,793 rows</t>
+          <t>83,090 rows</t>
         </is>
       </c>
       <c r="H5" s="3" t="inlineStr">
@@ -4201,7 +4201,7 @@
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>82,793 rows</t>
+          <t>83,090 rows</t>
         </is>
       </c>
       <c r="H6" s="3" t="inlineStr">
@@ -4248,7 +4248,7 @@
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>82,793 rows</t>
+          <t>83,090 rows</t>
         </is>
       </c>
       <c r="H7" s="3" t="inlineStr">
@@ -4295,7 +4295,7 @@
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>82,793 rows</t>
+          <t>83,090 rows</t>
         </is>
       </c>
       <c r="H8" s="3" t="inlineStr">
@@ -4342,7 +4342,7 @@
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>82,793 rows</t>
+          <t>83,090 rows</t>
         </is>
       </c>
       <c r="H9" s="3" t="inlineStr">
@@ -4389,7 +4389,7 @@
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>82,793 rows</t>
+          <t>83,090 rows</t>
         </is>
       </c>
       <c r="H10" s="3" t="inlineStr">
@@ -4436,7 +4436,7 @@
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>82,793 rows</t>
+          <t>83,090 rows</t>
         </is>
       </c>
       <c r="H11" s="3" t="inlineStr">
@@ -4483,7 +4483,7 @@
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>82,793 rows</t>
+          <t>83,090 rows</t>
         </is>
       </c>
       <c r="H12" s="3" t="inlineStr">
@@ -4530,7 +4530,7 @@
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>82,793 rows</t>
+          <t>83,090 rows</t>
         </is>
       </c>
       <c r="H13" s="3" t="inlineStr">
@@ -4577,7 +4577,7 @@
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>82,793 rows</t>
+          <t>83,090 rows</t>
         </is>
       </c>
       <c r="H14" s="3" t="inlineStr">
@@ -5611,7 +5611,7 @@
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>137 rows</t>
+          <t>138 rows</t>
         </is>
       </c>
       <c r="H36" s="3" t="inlineStr">

--- a/data/extracted/series/corpus_publication_cadence_and_audit.xlsx
+++ b/data/extracted/series/corpus_publication_cadence_and_audit.xlsx
@@ -1484,22 +1484,22 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="I11" s="2" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="J11" s="4" t="inlineStr">
         <is>
-          <t>CURRENT (7d ago)</t>
+          <t>CURRENT (0d ago)</t>
         </is>
       </c>
       <c r="K11" s="2" t="n">
         <v>109</v>
       </c>
       <c r="L11" s="2" t="n">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="M11" s="2" t="n">
         <v>0</v>
@@ -1511,7 +1511,7 @@
         <v>264</v>
       </c>
       <c r="P11" s="3" t="n">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="Q11" s="3" t="inlineStr">
         <is>
@@ -1525,7 +1525,7 @@
       </c>
       <c r="S11" s="3" t="inlineStr">
         <is>
-          <t>gibson_tanker_spot_series.csv (3,598 rows), gibson_bunker_prices_series.csv (1,028 rows), gibson_master_tanker_series.xlsx</t>
+          <t>gibson_tanker_spot_series.csv (3,612 rows), gibson_bunker_prices_series.csv (1,032 rows), gibson_master_tanker_series.xlsx</t>
         </is>
       </c>
       <c r="T11" s="3" t="inlineStr">
@@ -1897,7 +1897,7 @@
       </c>
       <c r="S15" s="3" t="inlineStr">
         <is>
-          <t>ssy_capesize_index_series.csv (10,010 rows), ssy_capesize_series.csv (8,881 rows), ssy_route_rates_series.csv (5,190 rows), ssy_capesize_index_time_series.csv (519 rows)</t>
+          <t>ssy_capesize_index_series.csv (10,152 rows), ssy_capesize_series.csv (8,881 rows), ssy_route_rates_series.csv (5,190 rows), ssy_capesize_index_time_series.csv (519 rows)</t>
         </is>
       </c>
       <c r="T15" s="3" t="inlineStr">

--- a/data/extracted/series/corpus_publication_cadence_and_audit.xlsx
+++ b/data/extracted/series/corpus_publication_cadence_and_audit.xlsx
@@ -3158,34 +3158,34 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="I29" s="2" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="J29" s="4" t="inlineStr">
         <is>
-          <t>CURRENT (7d ago)</t>
+          <t>CURRENT (0d ago)</t>
         </is>
       </c>
       <c r="K29" s="2" t="n">
         <v>10</v>
       </c>
       <c r="L29" s="2" t="n">
-        <v>518</v>
+        <v>521</v>
       </c>
       <c r="M29" s="2" t="n">
-        <v>1531</v>
+        <v>1564</v>
       </c>
       <c r="N29" s="2" t="n">
-        <v>453</v>
+        <v>456</v>
       </c>
       <c r="O29" s="2" t="n">
-        <v>449</v>
+        <v>452</v>
       </c>
       <c r="P29" s="3" t="n">
-        <v>2938</v>
+        <v>2977</v>
       </c>
       <c r="Q29" s="3" t="inlineStr">
         <is>
@@ -3199,7 +3199,7 @@
       </c>
       <c r="S29" s="3" t="inlineStr">
         <is>
-          <t>signal_reports_metadata.csv (449 rows), signal_vessel_counts_series.csv (120 rows), data/views/signal/live_fleet_positions.json (9,082 tracked hulls), data/views/signal/port_queues_active.json (1,932 ports)</t>
+          <t>signal_reports_metadata.csv (452 rows), signal_vessel_counts_series.csv (120 rows), data/views/signal/live_fleet_positions.json (9,082 tracked hulls), data/views/signal/port_queues_active.json (1,932 ports)</t>
         </is>
       </c>
       <c r="T29" s="3" t="inlineStr">
@@ -5376,7 +5376,7 @@
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>449 rows</t>
+          <t>452 rows</t>
         </is>
       </c>
       <c r="H31" s="3" t="inlineStr">

--- a/data/extracted/series/corpus_publication_cadence_and_audit.xlsx
+++ b/data/extracted/series/corpus_publication_cadence_and_audit.xlsx
@@ -550,7 +550,7 @@
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>Status (2026-10-16)</t>
+          <t>Status (2026-10-17)</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
@@ -647,19 +647,19 @@
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="I2" s="2" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="J2" s="4" t="inlineStr">
         <is>
-          <t>CURRENT (6d ago)</t>
+          <t>CURRENT (0d ago)</t>
         </is>
       </c>
       <c r="K2" s="2" t="n">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="L2" s="2" t="n">
         <v>0</v>
@@ -674,7 +674,7 @@
         <v>254</v>
       </c>
       <c r="P2" s="3" t="n">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="Q2" s="3" t="inlineStr">
         <is>
@@ -688,7 +688,7 @@
       </c>
       <c r="S2" s="3" t="inlineStr">
         <is>
-          <t>advanced_shipping_sales_series.csv (6,106 rows), advanced_shipping_demolition_series.csv (2,000 rows), advanced_shipping_secondhand_matrix_series.csv (8,093 rows), advanced_shipping_newbuilding_series.csv (1,898 rows), advanced_shipping_demo_sales_series.csv (599 rows)</t>
+          <t>advanced_shipping_sales_series.csv (6,133 rows), advanced_shipping_demolition_series.csv (2,000 rows), advanced_shipping_secondhand_matrix_series.csv (8,125 rows), advanced_shipping_newbuilding_series.csv (1,907 rows), advanced_shipping_demo_sales_series.csv (600 rows)</t>
         </is>
       </c>
       <c r="T2" s="3" t="inlineStr">
@@ -740,19 +740,19 @@
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="I3" s="2" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="J3" s="4" t="inlineStr">
         <is>
-          <t>CURRENT (6d ago)</t>
+          <t>CURRENT (0d ago)</t>
         </is>
       </c>
       <c r="K3" s="2" t="n">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="L3" s="2" t="n">
         <v>0</v>
@@ -767,7 +767,7 @@
         <v>255</v>
       </c>
       <c r="P3" s="3" t="n">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="Q3" s="3" t="inlineStr">
         <is>
@@ -781,7 +781,7 @@
       </c>
       <c r="S3" s="3" t="inlineStr">
         <is>
-          <t>affinity_tce_series.csv (4,058 rows), affinity_bda_series.csv (747 rows), affinity_indices_series.csv (496 rows)</t>
+          <t>affinity_tce_series.csv (4,077 rows), affinity_bda_series.csv (750 rows), affinity_indices_series.csv (496 rows)</t>
         </is>
       </c>
       <c r="T3" s="3" t="inlineStr">
@@ -837,11 +837,11 @@
         </is>
       </c>
       <c r="I4" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="J4" s="4" t="inlineStr">
         <is>
-          <t>CURRENT (7d ago)</t>
+          <t>CURRENT (8d ago)</t>
         </is>
       </c>
       <c r="K4" s="2" t="n">
@@ -930,11 +930,11 @@
         </is>
       </c>
       <c r="I5" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J5" s="4" t="inlineStr">
         <is>
-          <t>CURRENT (2d ago)</t>
+          <t>CURRENT (3d ago)</t>
         </is>
       </c>
       <c r="K5" s="2" t="n">
@@ -1023,11 +1023,11 @@
         </is>
       </c>
       <c r="I6" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J6" s="4" t="inlineStr">
         <is>
-          <t>CURRENT (4d ago)</t>
+          <t>CURRENT (5d ago)</t>
         </is>
       </c>
       <c r="K6" s="2" t="n">
@@ -1116,11 +1116,11 @@
         </is>
       </c>
       <c r="I7" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="J7" s="4" t="inlineStr">
         <is>
-          <t>CURRENT (7d ago)</t>
+          <t>CURRENT (8d ago)</t>
         </is>
       </c>
       <c r="K7" s="2" t="n">
@@ -1209,11 +1209,11 @@
         </is>
       </c>
       <c r="I8" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J8" s="4" t="inlineStr">
         <is>
-          <t>CURRENT (1d ago)</t>
+          <t>CURRENT (2d ago)</t>
         </is>
       </c>
       <c r="K8" s="2" t="n">
@@ -1302,11 +1302,11 @@
         </is>
       </c>
       <c r="I9" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J9" s="4" t="inlineStr">
         <is>
-          <t>CURRENT (2d ago)</t>
+          <t>CURRENT (3d ago)</t>
         </is>
       </c>
       <c r="K9" s="2" t="n">
@@ -1395,11 +1395,11 @@
         </is>
       </c>
       <c r="I10" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J10" s="4" t="inlineStr">
         <is>
-          <t>CURRENT (2d ago)</t>
+          <t>CURRENT (3d ago)</t>
         </is>
       </c>
       <c r="K10" s="2" t="n">
@@ -1488,11 +1488,11 @@
         </is>
       </c>
       <c r="I11" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J11" s="4" t="inlineStr">
         <is>
-          <t>CURRENT (0d ago)</t>
+          <t>CURRENT (1d ago)</t>
         </is>
       </c>
       <c r="K11" s="2" t="n">
@@ -1581,11 +1581,11 @@
         </is>
       </c>
       <c r="I12" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J12" s="4" t="inlineStr">
         <is>
-          <t>CURRENT (2d ago)</t>
+          <t>CURRENT (3d ago)</t>
         </is>
       </c>
       <c r="K12" s="2" t="n">
@@ -1674,11 +1674,11 @@
         </is>
       </c>
       <c r="I13" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J13" s="4" t="inlineStr">
         <is>
-          <t>CURRENT (4d ago)</t>
+          <t>CURRENT (5d ago)</t>
         </is>
       </c>
       <c r="K13" s="2" t="n">
@@ -1767,11 +1767,11 @@
         </is>
       </c>
       <c r="I14" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="J14" s="4" t="inlineStr">
         <is>
-          <t>CURRENT (7d ago)</t>
+          <t>CURRENT (8d ago)</t>
         </is>
       </c>
       <c r="K14" s="2" t="n">
@@ -1860,11 +1860,11 @@
         </is>
       </c>
       <c r="I15" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J15" s="4" t="inlineStr">
         <is>
-          <t>CURRENT (4d ago)</t>
+          <t>CURRENT (5d ago)</t>
         </is>
       </c>
       <c r="K15" s="2" t="n">
@@ -1897,7 +1897,7 @@
       </c>
       <c r="S15" s="3" t="inlineStr">
         <is>
-          <t>ssy_capesize_index_series.csv (10,152 rows), ssy_capesize_series.csv (8,881 rows), ssy_route_rates_series.csv (5,190 rows), ssy_capesize_index_time_series.csv (519 rows)</t>
+          <t>ssy_capesize_index_series.csv (10,294 rows), ssy_capesize_series.csv (8,881 rows), ssy_route_rates_series.csv (5,190 rows), ssy_capesize_index_time_series.csv (519 rows)</t>
         </is>
       </c>
       <c r="T15" s="3" t="inlineStr">
@@ -1953,11 +1953,11 @@
         </is>
       </c>
       <c r="I16" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J16" s="4" t="inlineStr">
         <is>
-          <t>CURRENT (4d ago)</t>
+          <t>CURRENT (5d ago)</t>
         </is>
       </c>
       <c r="K16" s="2" t="n">
@@ -2046,11 +2046,11 @@
         </is>
       </c>
       <c r="I17" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J17" s="4" t="inlineStr">
         <is>
-          <t>CURRENT (3d ago)</t>
+          <t>CURRENT (4d ago)</t>
         </is>
       </c>
       <c r="K17" s="2" t="n">
@@ -2139,11 +2139,11 @@
         </is>
       </c>
       <c r="I18" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J18" s="4" t="inlineStr">
         <is>
-          <t>CURRENT (6d ago)</t>
+          <t>CURRENT (7d ago)</t>
         </is>
       </c>
       <c r="K18" s="2" t="n">
@@ -2232,11 +2232,11 @@
         </is>
       </c>
       <c r="I19" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J19" s="4" t="inlineStr">
         <is>
-          <t>CURRENT (2d ago)</t>
+          <t>CURRENT (3d ago)</t>
         </is>
       </c>
       <c r="K19" s="2" t="n">
@@ -2325,11 +2325,11 @@
         </is>
       </c>
       <c r="I20" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J20" s="4" t="inlineStr">
         <is>
-          <t>CURRENT (0d ago)</t>
+          <t>CURRENT (1d ago)</t>
         </is>
       </c>
       <c r="K20" s="2" t="n">
@@ -2418,11 +2418,11 @@
         </is>
       </c>
       <c r="I21" s="2" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="J21" s="4" t="inlineStr">
         <is>
-          <t>CURRENT (10d ago)</t>
+          <t>CURRENT (11d ago)</t>
         </is>
       </c>
       <c r="K21" s="2" t="n">
@@ -2511,11 +2511,11 @@
         </is>
       </c>
       <c r="I22" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J22" s="4" t="inlineStr">
         <is>
-          <t>CURRENT (2d ago)</t>
+          <t>CURRENT (3d ago)</t>
         </is>
       </c>
       <c r="K22" s="2" t="n">
@@ -2604,11 +2604,11 @@
         </is>
       </c>
       <c r="I23" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J23" s="4" t="inlineStr">
         <is>
-          <t>CURRENT (2d ago)</t>
+          <t>CURRENT (3d ago)</t>
         </is>
       </c>
       <c r="K23" s="2" t="n">
@@ -2697,11 +2697,11 @@
         </is>
       </c>
       <c r="I24" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J24" s="4" t="inlineStr">
         <is>
-          <t>CURRENT (0d ago)</t>
+          <t>CURRENT (1d ago)</t>
         </is>
       </c>
       <c r="K24" s="2" t="n">
@@ -2790,11 +2790,11 @@
         </is>
       </c>
       <c r="I25" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J25" s="4" t="inlineStr">
         <is>
-          <t>CURRENT (5d ago)</t>
+          <t>CURRENT (6d ago)</t>
         </is>
       </c>
       <c r="K25" s="2" t="n">
@@ -2883,11 +2883,11 @@
         </is>
       </c>
       <c r="I26" s="2" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="J26" s="5" t="inlineStr">
         <is>
-          <t>NORMAL INTERVAL (45d ago)</t>
+          <t>NORMAL INTERVAL (46d ago)</t>
         </is>
       </c>
       <c r="K26" s="2" t="n">
@@ -2976,11 +2976,11 @@
         </is>
       </c>
       <c r="I27" s="2" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="J27" s="5" t="inlineStr">
         <is>
-          <t>NORMAL INTERVAL (22d ago)</t>
+          <t>NORMAL INTERVAL (23d ago)</t>
         </is>
       </c>
       <c r="K27" s="2" t="n">
@@ -3069,11 +3069,11 @@
         </is>
       </c>
       <c r="I28" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J28" s="4" t="inlineStr">
         <is>
-          <t>CURRENT (1d ago)</t>
+          <t>CURRENT (2d ago)</t>
         </is>
       </c>
       <c r="K28" s="2" t="n">
@@ -3162,11 +3162,11 @@
         </is>
       </c>
       <c r="I29" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J29" s="4" t="inlineStr">
         <is>
-          <t>CURRENT (0d ago)</t>
+          <t>CURRENT (1d ago)</t>
         </is>
       </c>
       <c r="K29" s="2" t="n">
@@ -3255,11 +3255,11 @@
         </is>
       </c>
       <c r="I30" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J30" s="4" t="inlineStr">
         <is>
-          <t>CURRENT (0d ago)</t>
+          <t>CURRENT (1d ago)</t>
         </is>
       </c>
       <c r="K30" s="2" t="n">
@@ -3348,11 +3348,11 @@
         </is>
       </c>
       <c r="I31" s="2" t="n">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="J31" s="5" t="inlineStr">
         <is>
-          <t>NORMAL INTERVAL (80d ago)</t>
+          <t>NORMAL INTERVAL (81d ago)</t>
         </is>
       </c>
       <c r="K31" s="2" t="n">
@@ -3441,11 +3441,11 @@
         </is>
       </c>
       <c r="I32" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="J32" s="4" t="inlineStr">
         <is>
-          <t>CURRENT (7d ago)</t>
+          <t>CURRENT (8d ago)</t>
         </is>
       </c>
       <c r="K32" s="2" t="n">
@@ -3534,11 +3534,11 @@
         </is>
       </c>
       <c r="I33" s="2" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="J33" s="4" t="inlineStr">
         <is>
-          <t>CURRENT (12d ago)</t>
+          <t>CURRENT (13d ago)</t>
         </is>
       </c>
       <c r="K33" s="2" t="n">
@@ -5470,7 +5470,7 @@
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>6,106 rows</t>
+          <t>6,133 rows</t>
         </is>
       </c>
       <c r="H33" s="3" t="inlineStr">

--- a/data/extracted/series/corpus_publication_cadence_and_audit.xlsx
+++ b/data/extracted/series/corpus_publication_cadence_and_audit.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Corpus Cadence &amp; Inventory" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Graphic &amp; Chart Extraction" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Sub-Sector &amp; Fleet Breakdown" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Corpus Cadence &amp; Inventory" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Graphic &amp; Chart Extraction" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sub-Sector &amp; Fleet Breakdown" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -476,30 +476,36 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U33"/>
+  <dimension ref="A1:AA33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="29" customWidth="1" min="1" max="1"/>
     <col width="48" customWidth="1" min="2" max="2"/>
     <col width="39" customWidth="1" min="3" max="3"/>
-    <col width="48" customWidth="1" min="4" max="4"/>
+    <col width="47" customWidth="1" min="4" max="4"/>
     <col width="48" customWidth="1" min="5" max="5"/>
     <col width="18" customWidth="1" min="6" max="6"/>
     <col width="16" customWidth="1" min="7" max="7"/>
     <col width="14" customWidth="1" min="8" max="8"/>
     <col width="12" customWidth="1" min="9" max="9"/>
-    <col width="28" customWidth="1" min="10" max="10"/>
-    <col width="16" customWidth="1" min="11" max="11"/>
-    <col width="16" customWidth="1" min="12" max="12"/>
-    <col width="18" customWidth="1" min="13" max="13"/>
-    <col width="21" customWidth="1" min="14" max="14"/>
-    <col width="32" customWidth="1" min="15" max="15"/>
-    <col width="21" customWidth="1" min="16" max="16"/>
-    <col width="48" customWidth="1" min="17" max="17"/>
-    <col width="48" customWidth="1" min="18" max="18"/>
-    <col width="48" customWidth="1" min="19" max="19"/>
-    <col width="48" customWidth="1" min="20" max="20"/>
-    <col width="48" customWidth="1" min="21" max="21"/>
+    <col width="48" customWidth="1" min="10" max="10"/>
+    <col width="21" customWidth="1" min="11" max="11"/>
+    <col width="19" customWidth="1" min="12" max="12"/>
+    <col width="23" customWidth="1" min="13" max="13"/>
+    <col width="20" customWidth="1" min="14" max="14"/>
+    <col width="12" customWidth="1" min="15" max="15"/>
+    <col width="15" customWidth="1" min="16" max="16"/>
+    <col width="16" customWidth="1" min="17" max="17"/>
+    <col width="16" customWidth="1" min="18" max="18"/>
+    <col width="18" customWidth="1" min="19" max="19"/>
+    <col width="21" customWidth="1" min="20" max="20"/>
+    <col width="32" customWidth="1" min="21" max="21"/>
+    <col width="21" customWidth="1" min="22" max="22"/>
+    <col width="48" customWidth="1" min="23" max="23"/>
+    <col width="48" customWidth="1" min="24" max="24"/>
+    <col width="48" customWidth="1" min="25" max="25"/>
+    <col width="48" customWidth="1" min="26" max="26"/>
+    <col width="48" customWidth="1" min="27" max="27"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -550,60 +556,90 @@
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>Status (2026-10-17)</t>
+          <t>Status (2026-10-19)</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
         <is>
+          <t>Latest Issue (raw)</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>Latest Parsed MD</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>Parse Backlog (120d)</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>Tables Sidecars %</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>Tiny MDs</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>Fallback MDs</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
           <t>PDFs (Corpus)</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>HTML (Corpus)</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>Images (Corpus)</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>Native MD (Corpus)</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="U1" s="1" t="inlineStr">
         <is>
           <t>Extracted MD (data/extracted)</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="V1" s="1" t="inlineStr">
         <is>
           <t>Total Corpus Files</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="W1" s="1" t="inlineStr">
         <is>
           <t>Charts Extracted</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="X1" s="1" t="inlineStr">
         <is>
           <t>Chart Engine</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="Y1" s="1" t="inlineStr">
         <is>
           <t>Master Series CSVs</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="Z1" s="1" t="inlineStr">
         <is>
           <t>Primary Script</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="AA1" s="1" t="inlineStr">
         <is>
           <t>Notes</t>
         </is>
@@ -642,7 +678,7 @@
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>2021-06-25</t>
+          <t>2021-07-02</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
@@ -651,52 +687,74 @@
         </is>
       </c>
       <c r="I2" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J2" s="4" t="inlineStr">
         <is>
-          <t>CURRENT (0d ago)</t>
-        </is>
-      </c>
-      <c r="K2" s="2" t="n">
+          <t>CURRENT (2d)</t>
+        </is>
+      </c>
+      <c r="K2" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-17</t>
+        </is>
+      </c>
+      <c r="L2" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="M2" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N2" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="O2" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P2" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q2" s="2" t="n">
         <v>258</v>
       </c>
-      <c r="L2" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M2" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="N2" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="O2" s="2" t="n">
-        <v>254</v>
-      </c>
-      <c r="P2" s="3" t="n">
+      <c r="R2" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S2" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="T2" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="U2" s="2" t="n">
+        <v>253</v>
+      </c>
+      <c r="V2" s="2" t="n">
         <v>258</v>
       </c>
-      <c r="Q2" s="3" t="inlineStr">
+      <c r="W2" s="3" t="inlineStr">
         <is>
           <t>Yes (Secondhand valuation matrices &amp; demo trends)</t>
         </is>
       </c>
-      <c r="R2" s="3" t="inlineStr">
+      <c r="X2" s="3" t="inlineStr">
         <is>
           <t>Native coordinate grid &amp; affine scale parser</t>
         </is>
       </c>
-      <c r="S2" s="3" t="inlineStr">
-        <is>
-          <t>advanced_shipping_sales_series.csv (6,133 rows), advanced_shipping_demolition_series.csv (2,000 rows), advanced_shipping_secondhand_matrix_series.csv (8,125 rows), advanced_shipping_newbuilding_series.csv (1,907 rows), advanced_shipping_demo_sales_series.csv (600 rows)</t>
-        </is>
-      </c>
-      <c r="T2" s="3" t="inlineStr">
+      <c r="Y2" s="3" t="inlineStr">
+        <is>
+          <t>advanced_shipping_sales_series.csv (6,123 rows), advanced_shipping_demolition_series.csv (2,016 rows), advanced_shipping_secondhand_matrix_series.csv (8,125 rows), advanced_shipping_newbuilding_series.csv (1,911 rows), advanced_shipping_demo_sales_series.csv (601 rows)</t>
+        </is>
+      </c>
+      <c r="Z2" s="3" t="inlineStr">
         <is>
           <t>run_advanced_shipping_tables.py</t>
         </is>
       </c>
-      <c r="U2" s="3" t="inlineStr">
+      <c r="AA2" s="3" t="inlineStr">
         <is>
           <t>Last 3 pages discarded per parsing rules (currencies/stocks). European comma/dot decimals normalized.</t>
         </is>
@@ -735,7 +793,7 @@
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>2021-10-01</t>
+          <t>2021-07-02</t>
         </is>
       </c>
       <c r="H3" s="2" t="inlineStr">
@@ -744,52 +802,74 @@
         </is>
       </c>
       <c r="I3" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J3" s="4" t="inlineStr">
         <is>
-          <t>CURRENT (0d ago)</t>
-        </is>
-      </c>
-      <c r="K3" s="2" t="n">
+          <t>CURRENT (2d)</t>
+        </is>
+      </c>
+      <c r="K3" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-17</t>
+        </is>
+      </c>
+      <c r="L3" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="M3" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N3" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="O3" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P3" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q3" s="2" t="n">
         <v>259</v>
       </c>
-      <c r="L3" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M3" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="N3" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="O3" s="2" t="n">
-        <v>255</v>
-      </c>
-      <c r="P3" s="3" t="n">
+      <c r="R3" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S3" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="T3" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="U3" s="2" t="n">
+        <v>250</v>
+      </c>
+      <c r="V3" s="2" t="n">
         <v>259</v>
       </c>
-      <c r="Q3" s="3" t="inlineStr">
+      <c r="W3" s="3" t="inlineStr">
         <is>
           <t>Yes (Baltic Dirty &amp; Clean TCE trajectory curves)</t>
         </is>
       </c>
-      <c r="R3" s="3" t="inlineStr">
+      <c r="X3" s="3" t="inlineStr">
         <is>
           <t>Native PyMuPDF card layout geometry</t>
         </is>
       </c>
-      <c r="S3" s="3" t="inlineStr">
+      <c r="Y3" s="3" t="inlineStr">
         <is>
           <t>affinity_tce_series.csv (4,077 rows), affinity_bda_series.csv (750 rows), affinity_indices_series.csv (496 rows)</t>
         </is>
       </c>
-      <c r="T3" s="3" t="inlineStr">
+      <c r="Z3" s="3" t="inlineStr">
         <is>
           <t>run_affinity_tables.py</t>
         </is>
       </c>
-      <c r="U3" s="3" t="inlineStr">
+      <c r="AA3" s="3" t="inlineStr">
         <is>
           <t>Handles negative TCE rates (e.g. TC2 -$4,273). Full tanker commentary preserved.</t>
         </is>
@@ -837,52 +917,74 @@
         </is>
       </c>
       <c r="I4" s="2" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="J4" s="4" t="inlineStr">
         <is>
-          <t>CURRENT (8d ago)</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="n">
+          <t>CURRENT (10d)</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N4" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="O4" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P4" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q4" s="2" t="n">
         <v>221</v>
       </c>
-      <c r="L4" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M4" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="N4" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="O4" s="2" t="n">
+      <c r="R4" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S4" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="T4" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="U4" s="2" t="n">
         <v>216</v>
       </c>
-      <c r="P4" s="3" t="n">
+      <c r="V4" s="2" t="n">
         <v>221</v>
       </c>
-      <c r="Q4" s="3" t="inlineStr">
+      <c r="W4" s="3" t="inlineStr">
         <is>
           <t>No (Dense indicator tables across 5 pages)</t>
         </is>
       </c>
-      <c r="R4" s="3" t="inlineStr">
+      <c r="X4" s="3" t="inlineStr">
         <is>
           <t>Native layout block parser</t>
         </is>
       </c>
-      <c r="S4" s="3" t="inlineStr">
+      <c r="Y4" s="3" t="inlineStr">
         <is>
           <t>agora_indicators_series.csv (10,002 rows)</t>
         </is>
       </c>
-      <c r="T4" s="3" t="inlineStr">
+      <c r="Z4" s="3" t="inlineStr">
         <is>
           <t>format_agora_properly.py</t>
         </is>
       </c>
-      <c r="U4" s="3" t="inlineStr">
+      <c r="AA4" s="3" t="inlineStr">
         <is>
           <t>Parsed live right now for Week 39 (24 Sep reference). European decimals normalized.</t>
         </is>
@@ -921,7 +1023,7 @@
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>2021-06-30</t>
+          <t>2021-07-02</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
@@ -930,52 +1032,74 @@
         </is>
       </c>
       <c r="I5" s="2" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="J5" s="4" t="inlineStr">
         <is>
-          <t>CURRENT (3d ago)</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="n">
+          <t>CURRENT (5d)</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N5" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="O5" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P5" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q5" s="2" t="n">
         <v>252</v>
       </c>
-      <c r="L5" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M5" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="N5" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="O5" s="2" t="n">
-        <v>250</v>
-      </c>
-      <c r="P5" s="3" t="n">
+      <c r="R5" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S5" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="T5" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="U5" s="2" t="n">
+        <v>249</v>
+      </c>
+      <c r="V5" s="2" t="n">
         <v>252</v>
       </c>
-      <c r="Q5" s="3" t="inlineStr">
+      <c r="W5" s="3" t="inlineStr">
         <is>
           <t>Yes (Freight rates, FFA forward curves, ConTex index)</t>
         </is>
       </c>
-      <c r="R5" s="3" t="inlineStr">
+      <c r="X5" s="3" t="inlineStr">
         <is>
           <t>LlamaParse cover-to-cover (ciphered/2026) + Native PyMuPDF table &amp; chart parser + clean_all_brokers_formatting.py</t>
         </is>
       </c>
-      <c r="S5" s="3" t="inlineStr">
+      <c r="Y5" s="3" t="inlineStr">
         <is>
           <t>bancosta_freight_rates_series.csv (20,587 rows), bancosta_ffa_series.csv (7,726 rows), bancosta_sales_series.csv (3,240 rows), bancosta_commodities_series.csv (8,546 rows), bancosta_newbuilding_series.csv (2,377 rows), bancosta_secondhand_matrix_series.csv (1,898 rows), bancosta_demolition_series.csv (959 rows)</t>
         </is>
       </c>
-      <c r="T5" s="3" t="inlineStr">
+      <c r="Z5" s="3" t="inlineStr">
         <is>
           <t>run_banchero_llamaparse.py &amp; run_banchero_costa_tables.py</t>
         </is>
       </c>
-      <c r="U5" s="3" t="inlineStr">
+      <c r="AA5" s="3" t="inlineStr">
         <is>
           <t>Cover-to-cover LlamaParse for ciphered/2026 reports with automated quality gate (verify_broker_md_quality_gate.py). Extracts exact 7-digit IMO numbers on secondhand vessel transactions. Pages 2 to N-1 parsed.</t>
         </is>
@@ -1023,52 +1147,74 @@
         </is>
       </c>
       <c r="I6" s="2" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="J6" s="4" t="inlineStr">
         <is>
-          <t>CURRENT (5d ago)</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="n">
+          <t>CURRENT (7d)</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N6" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="O6" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P6" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q6" s="2" t="n">
         <v>140</v>
       </c>
-      <c r="L6" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M6" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="N6" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="O6" s="2" t="n">
-        <v>137</v>
-      </c>
-      <c r="P6" s="3" t="n">
+      <c r="R6" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S6" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="T6" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="U6" s="2" t="n">
+        <v>134</v>
+      </c>
+      <c r="V6" s="2" t="n">
         <v>140</v>
       </c>
-      <c r="Q6" s="3" t="inlineStr">
+      <c r="W6" s="3" t="inlineStr">
         <is>
           <t>No (Tabular S&amp;P and Baltic BSPA/BDA indices)</t>
         </is>
       </c>
-      <c r="R6" s="3" t="inlineStr">
+      <c r="X6" s="3" t="inlineStr">
         <is>
           <t>Native word geometry and dynamic anchor parser</t>
         </is>
       </c>
-      <c r="S6" s="3" t="inlineStr">
+      <c r="Y6" s="3" t="inlineStr">
         <is>
           <t>carriers_sales_series.csv (3,081 rows), carriers_dry_tc_period_series.csv (3,096 rows), carriers_indices_series.csv (1,806 rows), carriers_tanker_tce_series.csv (774 rows), carriers_bspa_series.csv (785 rows), carriers_newbuilding_series.csv (302 rows), carriers_demolition_series.csv (170 rows)</t>
         </is>
       </c>
-      <c r="T6" s="3" t="inlineStr">
+      <c r="Z6" s="3" t="inlineStr">
         <is>
           <t>run_carriers_complete.py</t>
         </is>
       </c>
-      <c r="U6" s="3" t="inlineStr">
+      <c r="AA6" s="3" t="inlineStr">
         <is>
           <t>Greek public equities &amp; daily quote stripped per rules. En bloc sister-ship prices handled.</t>
         </is>
@@ -1107,7 +1253,7 @@
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>2021-07-02</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
@@ -1116,52 +1262,74 @@
         </is>
       </c>
       <c r="I7" s="2" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="J7" s="4" t="inlineStr">
         <is>
-          <t>CURRENT (8d ago)</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="n">
-        <v>181</v>
-      </c>
-      <c r="L7" s="2" t="n">
-        <v>0</v>
+          <t>CURRENT (10d)</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
       </c>
       <c r="M7" s="2" t="n">
         <v>0</v>
       </c>
       <c r="N7" s="2" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="O7" s="2" t="n">
-        <v>181</v>
-      </c>
-      <c r="P7" s="3" t="n">
-        <v>181</v>
-      </c>
-      <c r="Q7" s="3" t="inlineStr">
+        <v>0</v>
+      </c>
+      <c r="P7" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q7" s="2" t="n">
+        <v>13</v>
+      </c>
+      <c r="R7" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S7" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="T7" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="U7" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="V7" s="2" t="n">
+        <v>13</v>
+      </c>
+      <c r="W7" s="3" t="inlineStr">
         <is>
           <t>No (Bulker &amp; Tanker reported sales transaction tables)</t>
         </is>
       </c>
-      <c r="R7" s="3" t="inlineStr">
+      <c r="X7" s="3" t="inlineStr">
         <is>
           <t>Native PyMuPDF table coordinate extractor</t>
         </is>
       </c>
-      <c r="S7" s="3" t="inlineStr">
+      <c r="Y7" s="3" t="inlineStr">
         <is>
           <t>clarksons_sales_series.csv (1,375 rows)</t>
         </is>
       </c>
-      <c r="T7" s="3" t="inlineStr">
+      <c r="Z7" s="3" t="inlineStr">
         <is>
           <t>run_clarksons.py</t>
         </is>
       </c>
-      <c r="U7" s="3" t="inlineStr">
+      <c r="AA7" s="3" t="inlineStr">
         <is>
           <t>Clarksons Platou Hellas S&amp;P Bulletins extracted cover-to-cover. Desk Talk commentary properly segregated into distinct dry cargo and tanker sections with Panamax comments preserved. Reported sales, demolition deals, and macro tables stacked.</t>
         </is>
@@ -1200,7 +1368,7 @@
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>2021-07-07</t>
+          <t>2018-07-18</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
@@ -1209,52 +1377,74 @@
         </is>
       </c>
       <c r="I8" s="2" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="J8" s="4" t="inlineStr">
         <is>
-          <t>CURRENT (2d ago)</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="n">
+          <t>CURRENT (4d)</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N8" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="O8" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P8" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q8" s="2" t="n">
         <v>267</v>
       </c>
-      <c r="L8" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M8" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="N8" s="2" t="n">
-        <v>4764</v>
-      </c>
-      <c r="O8" s="2" t="n">
-        <v>5036</v>
-      </c>
-      <c r="P8" s="3" t="n">
-        <v>5031</v>
-      </c>
-      <c r="Q8" s="3" t="inlineStr">
+      <c r="R8" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S8" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="T8" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="U8" s="2" t="n">
+        <v>262</v>
+      </c>
+      <c r="V8" s="2" t="n">
+        <v>267</v>
+      </c>
+      <c r="W8" s="3" t="inlineStr">
         <is>
           <t>Yes (Tanker spot WS, Dry bulk BDI &amp; TC, LPG/LNG)</t>
         </is>
       </c>
-      <c r="R8" s="3" t="inlineStr">
+      <c r="X8" s="3" t="inlineStr">
         <is>
           <t>Specialized 6-pillar normalized parser (run_fearnleys_normalized.py)</t>
         </is>
       </c>
-      <c r="S8" s="3" t="inlineStr">
+      <c r="Y8" s="3" t="inlineStr">
         <is>
           <t>fearnleys_rates_series.csv (17,153 rows)</t>
         </is>
       </c>
-      <c r="T8" s="3" t="inlineStr">
+      <c r="Z8" s="3" t="inlineStr">
         <is>
           <t>run_fearnleys_normalized.py</t>
         </is>
       </c>
-      <c r="U8" s="3" t="inlineStr">
+      <c r="AA8" s="3" t="inlineStr">
         <is>
           <t>Ingested live for Week 40. 419 weekly commentary reports generated across all 9 years (2018-2026) in reports/fearnleys/commentary/&lt;year&gt;/ and data/reports/fearnleys/commentary/&lt;year&gt;/. 182 bespoke research reports mirrored into reports/fearnleys/&lt;year&gt;/.</t>
         </is>
@@ -1293,7 +1483,7 @@
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>2018-09-05</t>
+          <t>2018-09-16</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
@@ -1302,52 +1492,70 @@
         </is>
       </c>
       <c r="I9" s="2" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="J9" s="4" t="inlineStr">
         <is>
-          <t>CURRENT (3d ago)</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="L9" s="2" t="n">
-        <v>0</v>
+          <t>CURRENT (5d)</t>
+        </is>
+      </c>
+      <c r="K9" s="2" t="inlineStr"/>
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
       </c>
       <c r="M9" s="2" t="n">
         <v>0</v>
       </c>
       <c r="N9" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O9" s="2" t="n">
+        <v>35</v>
+      </c>
+      <c r="P9" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q9" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R9" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S9" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="T9" s="2" t="n">
         <v>4764</v>
       </c>
-      <c r="O9" s="2" t="n">
+      <c r="U9" s="2" t="n">
         <v>4774</v>
       </c>
-      <c r="P9" s="3" t="n">
-        <v>4765</v>
-      </c>
-      <c r="Q9" s="3" t="inlineStr">
+      <c r="V9" s="2" t="n">
+        <v>4764</v>
+      </c>
+      <c r="W9" s="3" t="inlineStr">
         <is>
           <t>No (Dense narrative intelligence across 35 desks &amp; routes)</t>
         </is>
       </c>
-      <c r="R9" s="3" t="inlineStr">
+      <c r="X9" s="3" t="inlineStr">
         <is>
           <t>Direct Hasura GraphQL feed parser with clean Markdown reformatting</t>
         </is>
       </c>
-      <c r="S9" s="3" t="inlineStr">
+      <c r="Y9" s="3" t="inlineStr">
         <is>
           <t>fearnleys_broker_comments.csv (11,759 comments), corpus/01-brokers/fearnleys/voice/ (4,748 files), data/extracted/md/fearnleys/voice/ (4,765 comment files)</t>
         </is>
       </c>
-      <c r="T9" s="3" t="inlineStr">
+      <c r="Z9" s="3" t="inlineStr">
         <is>
           <t>export_broker_voice_to_corpus.py</t>
         </is>
       </c>
-      <c r="U9" s="3" t="inlineStr">
+      <c r="AA9" s="3" t="inlineStr">
         <is>
           <t>4,765 weekly desk comments segregated by sector, desk, and year across Tankers (1,795), Dry Bulk (1,154), Gas (1,097), Chartering (393), and S&amp;P (326). The 6,994 one-word tanker route-trend labels ("Steady", "Softer") stay as rows in the CSV and get no MD. Standardized YAML frontmatter.</t>
         </is>
@@ -1395,52 +1603,74 @@
         </is>
       </c>
       <c r="I10" s="2" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="J10" s="4" t="inlineStr">
         <is>
-          <t>CURRENT (3d ago)</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="n">
+          <t>CURRENT (5d)</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N10" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="O10" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="P10" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q10" s="2" t="n">
         <v>183</v>
       </c>
-      <c r="L10" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M10" s="2" t="n">
+      <c r="R10" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S10" s="2" t="n">
         <v>2858</v>
       </c>
-      <c r="N10" s="2" t="n">
+      <c r="T10" s="2" t="n">
         <v>186</v>
       </c>
-      <c r="O10" s="2" t="n">
+      <c r="U10" s="2" t="n">
         <v>185</v>
       </c>
-      <c r="P10" s="3" t="n">
+      <c r="V10" s="2" t="n">
         <v>3228</v>
       </c>
-      <c r="Q10" s="3" t="inlineStr">
+      <c r="W10" s="3" t="inlineStr">
         <is>
           <t>No (raster PNG charts carry no data; chart titles and printed tables only)</t>
         </is>
       </c>
-      <c r="R10" s="3" t="inlineStr">
+      <c r="X10" s="3" t="inlineStr">
         <is>
           <t>API content-block renderer (fearnleys_md_rebuild.py); chart values are not read</t>
         </is>
       </c>
-      <c r="S10" s="3" t="inlineStr">
+      <c r="Y10" s="3" t="inlineStr">
         <is>
           <t>fearnleys-md .tables.json sidecars (56 exact API tables, 14 printed Cape composite-model tables, chart titles); earlier chart-calibrated series deleted</t>
         </is>
       </c>
-      <c r="T10" s="3" t="inlineStr">
+      <c r="Z10" s="3" t="inlineStr">
         <is>
           <t>run_fearnleys_md_full_power.py</t>
         </is>
       </c>
-      <c r="U10" s="3" t="inlineStr">
+      <c r="AA10" s="3" t="inlineStr">
         <is>
           <t>Charts are raster PNGs kept as images with their titles; the earlier calibrated chart series were wrong and have been deleted.</t>
         </is>
@@ -1488,52 +1718,74 @@
         </is>
       </c>
       <c r="I11" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J11" s="4" t="inlineStr">
         <is>
-          <t>CURRENT (1d ago)</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="n">
+          <t>CURRENT (3d)</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N11" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="O11" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P11" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q11" s="2" t="n">
         <v>109</v>
       </c>
-      <c r="L11" s="2" t="n">
+      <c r="R11" s="2" t="n">
         <v>166</v>
       </c>
-      <c r="M11" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="N11" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="O11" s="2" t="n">
-        <v>264</v>
-      </c>
-      <c r="P11" s="3" t="n">
+      <c r="S11" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="T11" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="U11" s="2" t="n">
+        <v>263</v>
+      </c>
+      <c r="V11" s="2" t="n">
         <v>275</v>
       </c>
-      <c r="Q11" s="3" t="inlineStr">
+      <c r="W11" s="3" t="inlineStr">
         <is>
           <t>Yes (wpDataCharts daily vector curves for all 155 HTML reports in .charts.json)</t>
         </is>
       </c>
-      <c r="R11" s="3" t="inlineStr">
+      <c r="X11" s="3" t="inlineStr">
         <is>
           <t>Native PyMuPDF table parser (PDFs) + BeautifulSoup DOM &amp; wpDataCharts JSON extractor (HTML)</t>
         </is>
       </c>
-      <c r="S11" s="3" t="inlineStr">
+      <c r="Y11" s="3" t="inlineStr">
         <is>
           <t>gibson_tanker_spot_series.csv (3,612 rows), gibson_bunker_prices_series.csv (1,032 rows), gibson_master_tanker_series.xlsx</t>
         </is>
       </c>
-      <c r="T11" s="3" t="inlineStr">
+      <c r="Z11" s="3" t="inlineStr">
         <is>
           <t>run_gibson_pdf.py &amp; run_gibson_html.py</t>
         </is>
       </c>
-      <c r="U11" s="3" t="inlineStr">
+      <c r="AA11" s="3" t="inlineStr">
         <is>
           <t>100% complete coverage: 109 historical PDFs (2021-2023) + 155 live online HTML reports (2023-2026). Tabular assessments (Spot WS &amp; TCE, FFA, bunkers) and full editorial/sector commentary extracted.</t>
         </is>
@@ -1572,7 +1824,7 @@
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>2021-06-29</t>
+          <t>2021-07-06</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
@@ -1581,52 +1833,74 @@
         </is>
       </c>
       <c r="I12" s="2" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="J12" s="4" t="inlineStr">
         <is>
-          <t>CURRENT (3d ago)</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="n">
+          <t>CURRENT (5d)</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N12" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="O12" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P12" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q12" s="2" t="n">
         <v>261</v>
       </c>
-      <c r="L12" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M12" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="N12" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="O12" s="2" t="n">
+      <c r="R12" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S12" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="T12" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="U12" s="2" t="n">
         <v>257</v>
       </c>
-      <c r="P12" s="3" t="n">
+      <c r="V12" s="2" t="n">
         <v>261</v>
       </c>
-      <c r="Q12" s="3" t="inlineStr">
+      <c r="W12" s="3" t="inlineStr">
         <is>
           <t>Yes (Baltic &amp; Time Charter vector curves, Page 3)</t>
         </is>
       </c>
-      <c r="R12" s="3" t="inlineStr">
+      <c r="X12" s="3" t="inlineStr">
         <is>
           <t>LlamaParse cover-to-cover + PyMuPDF chart vector curves</t>
         </is>
       </c>
-      <c r="S12" s="3" t="inlineStr">
-        <is>
-          <t>intermodal_baltic_tc_series.csv (20,348 rows), intermodal_tc_rates_series.csv (5,233 rows), intermodal_newbuilding_series.csv (5,084 rows), intermodal_tanker_spot_series.csv (3,885 rows), intermodal_sales_series.csv (3,479 rows), intermodal_demolition_series.csv (2,620 rows)</t>
-        </is>
-      </c>
-      <c r="T12" s="3" t="inlineStr">
+      <c r="Y12" s="3" t="inlineStr">
+        <is>
+          <t>intermodal_tc_rates_series.csv (5,273 rows), intermodal_newbuilding_series.csv (5,130 rows), intermodal_tanker_spot_series.csv (3,915 rows), intermodal_sales_series.csv (3,502 rows), intermodal_demolition_series.csv (2,637 rows)</t>
+        </is>
+      </c>
+      <c r="Z12" s="3" t="inlineStr">
         <is>
           <t>run_intermodal_full.py</t>
         </is>
       </c>
-      <c r="U12" s="3" t="inlineStr">
+      <c r="AA12" s="3" t="inlineStr">
         <is>
           <t>100% cover-to-cover extraction (all 8 pages). Editorial essay, Tanker spot, Dry bulk TC, S&amp;P, NB, Demo.</t>
         </is>
@@ -1665,7 +1939,7 @@
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>2021-07-05</t>
+          <t>2023-01-01</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
@@ -1674,52 +1948,74 @@
         </is>
       </c>
       <c r="I13" s="2" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="J13" s="4" t="inlineStr">
         <is>
-          <t>CURRENT (5d ago)</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="n">
+          <t>CURRENT (7d)</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N13" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O13" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P13" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q13" s="2" t="n">
         <v>117</v>
       </c>
-      <c r="L13" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M13" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="N13" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="O13" s="2" t="n">
-        <v>230</v>
-      </c>
-      <c r="P13" s="3" t="n">
+      <c r="R13" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S13" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="T13" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="U13" s="2" t="n">
+        <v>113</v>
+      </c>
+      <c r="V13" s="2" t="n">
         <v>117</v>
       </c>
-      <c r="Q13" s="3" t="inlineStr">
+      <c r="W13" s="3" t="inlineStr">
         <is>
           <t>Yes (4 weekly freight indicator vector charts)</t>
         </is>
       </c>
-      <c r="R13" s="3" t="inlineStr">
+      <c r="X13" s="3" t="inlineStr">
         <is>
           <t>PyMuPDF drawing path &amp; polyline axis scale calibration</t>
         </is>
       </c>
-      <c r="S13" s="3" t="inlineStr">
-        <is>
-          <t>ism_handy_freight_series.csv (17,968 rows), ism_coaster_freight_series.csv (12,599 rows)</t>
-        </is>
-      </c>
-      <c r="T13" s="3" t="inlineStr">
+      <c r="Y13" s="3" t="inlineStr">
+        <is>
+          <t>ism_handy_freight_series.csv (17,851 rows), ism_coaster_freight_series.csv (12,491 rows)</t>
+        </is>
+      </c>
+      <c r="Z13" s="3" t="inlineStr">
         <is>
           <t>run_ism.py</t>
         </is>
       </c>
-      <c r="U13" s="3" t="inlineStr">
+      <c r="AA13" s="3" t="inlineStr">
         <is>
           <t>Overhauled to eliminate vertical axis tick number chains. Clean commentary under thematic subheaders.</t>
         </is>
@@ -1758,7 +2054,7 @@
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>2021-07-09</t>
+          <t>2025-10-03</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
@@ -1767,52 +2063,74 @@
         </is>
       </c>
       <c r="I14" s="2" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="J14" s="4" t="inlineStr">
         <is>
-          <t>CURRENT (8d ago)</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="n">
+          <t>CURRENT (10d)</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N14" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="O14" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P14" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q14" s="2" t="n">
         <v>50</v>
       </c>
-      <c r="L14" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M14" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="N14" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="O14" s="2" t="n">
+      <c r="R14" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S14" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="T14" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="U14" s="2" t="n">
         <v>48</v>
       </c>
-      <c r="P14" s="3" t="n">
+      <c r="V14" s="2" t="n">
         <v>50</v>
       </c>
-      <c r="Q14" s="3" t="inlineStr">
+      <c r="W14" s="3" t="inlineStr">
         <is>
           <t>No (S&amp;P deals, Demometer indicative ranges, Demo fixtures)</t>
         </is>
       </c>
-      <c r="R14" s="3" t="inlineStr">
+      <c r="X14" s="3" t="inlineStr">
         <is>
           <t>LiteParse in-process layout parser</t>
         </is>
       </c>
-      <c r="S14" s="3" t="inlineStr">
+      <c r="Y14" s="3" t="inlineStr">
         <is>
           <t>lion_deals_series.csv (1,312 rows), lion_sales_series.csv (1,203 rows), lion_demometer_series.csv (576 rows), lion_demolition_series.csv (516 rows), lion_demo_sales_series.csv (109 rows)</t>
         </is>
       </c>
-      <c r="T14" s="3" t="inlineStr">
+      <c r="Z14" s="3" t="inlineStr">
         <is>
           <t>run_lion_tables.py</t>
         </is>
       </c>
-      <c r="U14" s="3" t="inlineStr">
+      <c r="AA14" s="3" t="inlineStr">
         <is>
           <t>Joke of the week, author commentary preserved. Week 40 tables stacked cleanly.</t>
         </is>
@@ -1860,52 +2178,74 @@
         </is>
       </c>
       <c r="I15" s="2" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="J15" s="4" t="inlineStr">
         <is>
-          <t>CURRENT (5d ago)</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="n">
+          <t>CURRENT (7d)</t>
+        </is>
+      </c>
+      <c r="K15" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="L15" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="M15" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N15" s="2" t="n">
+        <v>99.40000000000001</v>
+      </c>
+      <c r="O15" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P15" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q15" s="2" t="n">
         <v>536</v>
       </c>
-      <c r="L15" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M15" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="N15" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="O15" s="2" t="n">
-        <v>531</v>
-      </c>
-      <c r="P15" s="3" t="n">
+      <c r="R15" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S15" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="T15" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="U15" s="2" t="n">
+        <v>520</v>
+      </c>
+      <c r="V15" s="2" t="n">
         <v>536</v>
       </c>
-      <c r="Q15" s="3" t="inlineStr">
+      <c r="W15" s="3" t="inlineStr">
         <is>
           <t>Yes (Atlantic &amp; Pacific Capesize index vector curves)</t>
         </is>
       </c>
-      <c r="R15" s="3" t="inlineStr">
+      <c r="X15" s="3" t="inlineStr">
         <is>
           <t>PyMuPDF span geometry + vector chart calibration</t>
         </is>
       </c>
-      <c r="S15" s="3" t="inlineStr">
+      <c r="Y15" s="3" t="inlineStr">
         <is>
           <t>ssy_capesize_index_series.csv (10,294 rows), ssy_capesize_series.csv (8,881 rows), ssy_route_rates_series.csv (5,190 rows), ssy_capesize_index_time_series.csv (519 rows)</t>
         </is>
       </c>
-      <c r="T15" s="3" t="inlineStr">
+      <c r="Z15" s="3" t="inlineStr">
         <is>
           <t>run_ssy_complete.py</t>
         </is>
       </c>
-      <c r="U15" s="3" t="inlineStr">
+      <c r="AA15" s="3" t="inlineStr">
         <is>
           <t>Covers both Atlantic Capesize Index (ACI) and Pacific Capesize Index (PCI).</t>
         </is>
@@ -1944,7 +2284,7 @@
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>2022-07-22</t>
+          <t>2022-07-24</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
@@ -1953,52 +2293,74 @@
         </is>
       </c>
       <c r="I16" s="2" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="J16" s="4" t="inlineStr">
         <is>
-          <t>CURRENT (5d ago)</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="n">
+          <t>CURRENT (7d)</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N16" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="O16" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P16" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q16" s="2" t="n">
         <v>203</v>
       </c>
-      <c r="L16" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M16" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="N16" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="O16" s="2" t="n">
-        <v>200</v>
-      </c>
-      <c r="P16" s="3" t="n">
+      <c r="R16" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S16" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="T16" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="U16" s="2" t="n">
+        <v>198</v>
+      </c>
+      <c r="V16" s="2" t="n">
         <v>203</v>
       </c>
-      <c r="Q16" s="3" t="inlineStr">
+      <c r="W16" s="3" t="inlineStr">
         <is>
           <t>Yes (Subcontinent scrap price trends $/LDT, metals/energy)</t>
         </is>
       </c>
-      <c r="R16" s="3" t="inlineStr">
+      <c r="X16" s="3" t="inlineStr">
         <is>
           <t>LlamaParse + World-Class Markdown Normalizer (run_star_asia_tables.py)</t>
         </is>
       </c>
-      <c r="S16" s="3" t="inlineStr">
+      <c r="Y16" s="3" t="inlineStr">
         <is>
           <t>star_asia_snp_sales_series.csv (3,575 rows), star_asia_deals_series.csv (3,362 rows), star_asia_valuation_matrix_series.csv (3,232 rows), star_asia_demolition_series.csv (3,152 rows), star_asia_metals_energy_series.csv (1,327 rows)</t>
         </is>
       </c>
-      <c r="T16" s="3" t="inlineStr">
+      <c r="Z16" s="3" t="inlineStr">
         <is>
           <t>run_star_asia_tables.py</t>
         </is>
       </c>
-      <c r="U16" s="3" t="inlineStr">
+      <c r="AA16" s="3" t="inlineStr">
         <is>
           <t>Gaddani / Turkey cell boundary merge defect resolved. Table headers and Baltic Dry Index / valuation matrices properly labeled. Disclaimers and contact footers removed. Explicit ISO issue dates stamped.</t>
         </is>
@@ -2046,52 +2408,74 @@
         </is>
       </c>
       <c r="I17" s="2" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="J17" s="4" t="inlineStr">
         <is>
-          <t>CURRENT (4d ago)</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="n">
+          <t>CURRENT (6d)</t>
+        </is>
+      </c>
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N17" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="O17" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P17" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q17" s="2" t="n">
         <v>275</v>
       </c>
-      <c r="L17" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M17" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="N17" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="O17" s="2" t="n">
-        <v>271</v>
-      </c>
-      <c r="P17" s="3" t="n">
+      <c r="R17" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S17" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="T17" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="U17" s="2" t="n">
+        <v>265</v>
+      </c>
+      <c r="V17" s="2" t="n">
         <v>275</v>
       </c>
-      <c r="Q17" s="3" t="inlineStr">
+      <c r="W17" s="3" t="inlineStr">
         <is>
           <t>Yes (Pages 2-3 freight curves, Pages 8-9 bunker spreads)</t>
         </is>
       </c>
-      <c r="R17" s="3" t="inlineStr">
+      <c r="X17" s="3" t="inlineStr">
         <is>
           <t>LiteParse cover-to-cover + vector chart parser</t>
         </is>
       </c>
-      <c r="S17" s="3" t="inlineStr">
+      <c r="Y17" s="3" t="inlineStr">
         <is>
           <t>xclusiv_secondhand_series.csv (8,593 rows), xclusiv_sales_series.csv (5,584 rows), xclusiv_demolition_series.csv (2,098 rows), xclusiv_newbuilding_prices_series.csv (1,379 rows), xclusiv_newbuilding_orders_series.csv (1,313 rows)</t>
         </is>
       </c>
-      <c r="T17" s="3" t="inlineStr">
+      <c r="Z17" s="3" t="inlineStr">
         <is>
           <t>run_xclusiv_tables.py</t>
         </is>
       </c>
-      <c r="U17" s="3" t="inlineStr">
+      <c r="AA17" s="3" t="inlineStr">
         <is>
           <t>100% cover-to-cover across all 9 pages. Full narrative commentary and S&amp;P tables extracted. Visually audited top pages to guarantee complete commentary and table fidelity without omissions.</t>
         </is>
@@ -2130,7 +2514,7 @@
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>2014-03-28</t>
+          <t>2021-07-02</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
@@ -2139,52 +2523,74 @@
         </is>
       </c>
       <c r="I18" s="2" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="J18" s="4" t="inlineStr">
         <is>
-          <t>CURRENT (7d ago)</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="n">
+          <t>CURRENT (9d)</t>
+        </is>
+      </c>
+      <c r="K18" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-10</t>
+        </is>
+      </c>
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-10</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N18" s="2" t="n">
+        <v>62.3</v>
+      </c>
+      <c r="O18" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P18" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q18" s="2" t="n">
         <v>2147</v>
       </c>
-      <c r="L18" s="2" t="n">
+      <c r="R18" s="2" t="n">
         <v>813</v>
       </c>
-      <c r="M18" s="2" t="n">
+      <c r="S18" s="2" t="n">
         <v>1212</v>
       </c>
-      <c r="N18" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="O18" s="2" t="n">
-        <v>1275</v>
-      </c>
-      <c r="P18" s="3" t="n">
+      <c r="T18" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="U18" s="2" t="n">
+        <v>753</v>
+      </c>
+      <c r="V18" s="2" t="n">
         <v>4172</v>
       </c>
-      <c r="Q18" s="3" t="inlineStr">
+      <c r="W18" s="3" t="inlineStr">
         <is>
           <t>Yes (Port position queue charts, cash buyer price matrices)</t>
         </is>
       </c>
-      <c r="R18" s="3" t="inlineStr">
+      <c r="X18" s="3" t="inlineStr">
         <is>
           <t>BeautifulSoup HTML + PyMuPDF spatial coordinate table parser</t>
         </is>
       </c>
-      <c r="S18" s="3" t="inlineStr">
+      <c r="Y18" s="3" t="inlineStr">
         <is>
           <t>athenian_indicative_demolition_series.csv (3,064 rows), hellenic_gms_port_positions_series.csv (3,014 rows), hellenic_gms_demolition_series.csv (1,104 rows), hellenic_best_oasis_deals_series.csv (905 rows), hellenic_best_oasis_demolition_series.csv (866 rows)</t>
         </is>
       </c>
-      <c r="T18" s="3" t="inlineStr">
+      <c r="Z18" s="3" t="inlineStr">
         <is>
           <t>run_hellenic_demolition.py &amp; run_best_oasis_demolition.py &amp; run_gms_demolition.py</t>
         </is>
       </c>
-      <c r="U18" s="3" t="inlineStr">
+      <c r="AA18" s="3" t="inlineStr">
         <is>
           <t>Distinguishes Athenian, Best Oasis, GMS cash buyer reports and port queue tables. Week 40 stacked.</t>
         </is>
@@ -2223,7 +2629,7 @@
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>2014-03-28</t>
+          <t>2021-07-07</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
@@ -2232,52 +2638,74 @@
         </is>
       </c>
       <c r="I19" s="2" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="J19" s="4" t="inlineStr">
         <is>
-          <t>CURRENT (3d ago)</t>
-        </is>
-      </c>
-      <c r="K19" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="L19" s="2" t="n">
+          <t>CURRENT (5d)</t>
+        </is>
+      </c>
+      <c r="K19" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="L19" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N19" s="2" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="O19" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P19" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q19" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R19" s="2" t="n">
         <v>281</v>
       </c>
-      <c r="M19" s="2" t="n">
+      <c r="S19" s="2" t="n">
         <v>763</v>
       </c>
-      <c r="N19" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="O19" s="2" t="n">
+      <c r="T19" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="U19" s="2" t="n">
         <v>267</v>
       </c>
-      <c r="P19" s="3" t="n">
+      <c r="V19" s="2" t="n">
         <v>1044</v>
       </c>
-      <c r="Q19" s="3" t="inlineStr">
+      <c r="W19" s="3" t="inlineStr">
         <is>
           <t>Yes (Alibra rate fixture comparison graphics)</t>
         </is>
       </c>
-      <c r="R19" s="3" t="inlineStr">
+      <c r="X19" s="3" t="inlineStr">
         <is>
           <t>HTML table &amp; image graphic OCR parsing</t>
         </is>
       </c>
-      <c r="S19" s="3" t="inlineStr">
-        <is>
-          <t>hellenic_alibra_dry_tc_series.csv (6,539 rows)</t>
-        </is>
-      </c>
-      <c r="T19" s="3" t="inlineStr">
+      <c r="Y19" s="3" t="inlineStr">
+        <is>
+          <t>hellenic_alibra_dry_tc_series.csv (6,563 rows)</t>
+        </is>
+      </c>
+      <c r="Z19" s="3" t="inlineStr">
         <is>
           <t>run_hellenic_alibra_tc.py</t>
         </is>
       </c>
-      <c r="U19" s="3" t="inlineStr">
+      <c r="AA19" s="3" t="inlineStr">
         <is>
           <t>Extracts 1Y, 2Y, 3Y, 5Y Dry Bulk period TC assessments across Capesize, Panamax, Supramax, Handy.</t>
         </is>
@@ -2316,7 +2744,7 @@
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>2014-03-28</t>
+          <t>2021-07-14</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
@@ -2325,52 +2753,74 @@
         </is>
       </c>
       <c r="I20" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J20" s="4" t="inlineStr">
         <is>
-          <t>CURRENT (1d ago)</t>
-        </is>
-      </c>
-      <c r="K20" s="2" t="n">
+          <t>CURRENT (3d)</t>
+        </is>
+      </c>
+      <c r="K20" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="L20" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N20" s="2" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="O20" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P20" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q20" s="2" t="n">
         <v>4542</v>
       </c>
-      <c r="L20" s="2" t="n">
-        <v>1202</v>
-      </c>
-      <c r="M20" s="2" t="n">
-        <v>3335</v>
-      </c>
-      <c r="N20" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="O20" s="2" t="n">
-        <v>1199</v>
-      </c>
-      <c r="P20" s="3" t="n">
-        <v>9057</v>
-      </c>
-      <c r="Q20" s="3" t="inlineStr">
+      <c r="R20" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S20" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="T20" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="U20" s="2" t="n">
+        <v>1190</v>
+      </c>
+      <c r="V20" s="2" t="n">
+        <v>4542</v>
+      </c>
+      <c r="W20" s="3" t="inlineStr">
         <is>
           <t>Yes (4 SMM driver vector charts + MMi inventory/margin curves)</t>
         </is>
       </c>
-      <c r="R20" s="3" t="inlineStr">
+      <c r="X20" s="3" t="inlineStr">
         <is>
           <t>PyMuPDF 2D spatial coordinate parser + SMM vector chart clipper</t>
         </is>
       </c>
-      <c r="S20" s="3" t="inlineStr">
-        <is>
-          <t>hellenic_iron_ore_pdf_brands_series.csv (31,516 rows)</t>
-        </is>
-      </c>
-      <c r="T20" s="3" t="inlineStr">
+      <c r="Y20" s="3" t="inlineStr">
+        <is>
+          <t>hellenic_iron_ore_pdf_brands_series.csv (31,527 rows)</t>
+        </is>
+      </c>
+      <c r="Z20" s="3" t="inlineStr">
         <is>
           <t>run_hellenic_iron_ore_pdf.py &amp; run_smm_iron_ore_daily.py</t>
         </is>
       </c>
-      <c r="U20" s="3" t="inlineStr">
+      <c r="AA20" s="3" t="inlineStr">
         <is>
           <t>Full dual-pipeline: 6-page MMi cover-to-cover + 1-page SMM Daily with 4 vector chart clips.</t>
         </is>
@@ -2394,7 +2844,7 @@
       </c>
       <c r="D21" s="3" t="inlineStr">
         <is>
-          <t>data/extracted/md/hellenic/shipbuilding/clarksons</t>
+          <t>data/extracted/md/clarksons</t>
         </is>
       </c>
       <c r="E21" s="3" t="inlineStr">
@@ -2409,61 +2859,83 @@
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>2014-03-28</t>
+          <t>2021-07-02</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="I21" s="2" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="J21" s="4" t="inlineStr">
         <is>
-          <t>CURRENT (11d ago)</t>
-        </is>
-      </c>
-      <c r="K21" s="2" t="n">
+          <t>SUPERSEDED (new issues arrive via corpus/01-brokers/clarksons (since 2026-08; last issue on this channel 2026-07-31))</t>
+        </is>
+      </c>
+      <c r="K21" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="L21" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="M21" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N21" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="O21" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P21" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q21" s="2" t="n">
         <v>1363</v>
       </c>
-      <c r="L21" s="2" t="n">
+      <c r="R21" s="2" t="n">
         <v>380</v>
       </c>
-      <c r="M21" s="2" t="n">
+      <c r="S21" s="2" t="n">
         <v>180</v>
       </c>
-      <c r="N21" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="O21" s="2" t="n">
-        <v>165</v>
-      </c>
-      <c r="P21" s="3" t="n">
+      <c r="T21" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="U21" s="2" t="n">
+        <v>170</v>
+      </c>
+      <c r="V21" s="2" t="n">
         <v>1923</v>
       </c>
-      <c r="Q21" s="3" t="inlineStr">
+      <c r="W21" s="3" t="inlineStr">
         <is>
           <t>No (Shipyard contracting and orderbook tables)</t>
         </is>
       </c>
-      <c r="R21" s="3" t="inlineStr">
+      <c r="X21" s="3" t="inlineStr">
         <is>
           <t>Native PyMuPDF table parser</t>
         </is>
       </c>
-      <c r="S21" s="3" t="inlineStr">
+      <c r="Y21" s="3" t="inlineStr">
         <is>
           <t>clarksons_snp_sales_series.csv (1,329 rows), clarksons_demolition_sales_series.csv (70 rows), clarksons_macro_series.csv (165 rows), clarksons_desk_talk_series.csv (352 rows)</t>
         </is>
       </c>
-      <c r="T21" s="3" t="inlineStr">
+      <c r="Z21" s="3" t="inlineStr">
         <is>
           <t>run_clarksons_hellas_world_class.py</t>
         </is>
       </c>
-      <c r="U21" s="3" t="inlineStr">
+      <c r="AA21" s="3" t="inlineStr">
         <is>
           <t>Clarksons Platou Hellas S&amp;P Bulletins extracted cover-to-cover with reported sales, demolition deals, and desk talk.</t>
         </is>
@@ -2502,7 +2974,7 @@
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>2014-03-28</t>
+          <t>2021-07-07</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
@@ -2511,52 +2983,74 @@
         </is>
       </c>
       <c r="I22" s="2" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="J22" s="4" t="inlineStr">
         <is>
-          <t>CURRENT (3d ago)</t>
-        </is>
-      </c>
-      <c r="K22" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="L22" s="2" t="n">
+          <t>CURRENT (5d)</t>
+        </is>
+      </c>
+      <c r="K22" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="L22" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N22" s="2" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="O22" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P22" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q22" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R22" s="2" t="n">
         <v>281</v>
       </c>
-      <c r="M22" s="2" t="n">
+      <c r="S22" s="2" t="n">
         <v>760</v>
       </c>
-      <c r="N22" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="O22" s="2" t="n">
+      <c r="T22" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="U22" s="2" t="n">
         <v>267</v>
       </c>
-      <c r="P22" s="3" t="n">
+      <c r="V22" s="2" t="n">
         <v>1041</v>
       </c>
-      <c r="Q22" s="3" t="inlineStr">
+      <c r="W22" s="3" t="inlineStr">
         <is>
           <t>Yes (Crude &amp; clean period earnings comparison graphics)</t>
         </is>
       </c>
-      <c r="R22" s="3" t="inlineStr">
+      <c r="X22" s="3" t="inlineStr">
         <is>
           <t>HTML table &amp; image graphic OCR parsing</t>
         </is>
       </c>
-      <c r="S22" s="3" t="inlineStr">
-        <is>
-          <t>hellenic_alibra_tanker_tc_series.csv (7,448 rows)</t>
-        </is>
-      </c>
-      <c r="T22" s="3" t="inlineStr">
+      <c r="Y22" s="3" t="inlineStr">
+        <is>
+          <t>hellenic_alibra_tanker_tc_series.csv (7,476 rows)</t>
+        </is>
+      </c>
+      <c r="Z22" s="3" t="inlineStr">
         <is>
           <t>run_hellenic_alibra_tc.py</t>
         </is>
       </c>
-      <c r="U22" s="3" t="inlineStr">
+      <c r="AA22" s="3" t="inlineStr">
         <is>
           <t>Extracts 1Y, 2Y, 3Y, 5Y Tanker period TC assessments across VLCC, Suezmax, Aframax, LR2, LR1, MR.</t>
         </is>
@@ -2595,7 +3089,7 @@
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>2014-03-28</t>
+          <t>2021-07-06</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
@@ -2604,52 +3098,74 @@
         </is>
       </c>
       <c r="I23" s="2" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="J23" s="4" t="inlineStr">
         <is>
-          <t>CURRENT (3d ago)</t>
-        </is>
-      </c>
-      <c r="K23" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="L23" s="2" t="n">
+          <t>CURRENT (5d)</t>
+        </is>
+      </c>
+      <c r="K23" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="L23" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="M23" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N23" s="2" t="n">
+        <v>99.59999999999999</v>
+      </c>
+      <c r="O23" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P23" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q23" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R23" s="2" t="n">
         <v>276</v>
       </c>
-      <c r="M23" s="2" t="n">
+      <c r="S23" s="2" t="n">
         <v>733</v>
       </c>
-      <c r="N23" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="O23" s="2" t="n">
-        <v>261</v>
-      </c>
-      <c r="P23" s="3" t="n">
+      <c r="T23" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="U23" s="2" t="n">
+        <v>257</v>
+      </c>
+      <c r="V23" s="2" t="n">
         <v>1009</v>
       </c>
-      <c r="Q23" s="3" t="inlineStr">
+      <c r="W23" s="3" t="inlineStr">
         <is>
           <t>Yes (VesselsValue fleet valuation index graphs)</t>
         </is>
       </c>
-      <c r="R23" s="3" t="inlineStr">
+      <c r="X23" s="3" t="inlineStr">
         <is>
           <t>HTML table parser + VV valuation matrix calculator</t>
         </is>
       </c>
-      <c r="S23" s="3" t="inlineStr">
+      <c r="Y23" s="3" t="inlineStr">
         <is>
           <t>hellenic_vv_matrix_series.csv (12,373 rows), hellenic_vv_sales_series.csv (2,077 rows)</t>
         </is>
       </c>
-      <c r="T23" s="3" t="inlineStr">
+      <c r="Z23" s="3" t="inlineStr">
         <is>
           <t>run_hellenic_vessel_valuations.py</t>
         </is>
       </c>
-      <c r="U23" s="3" t="inlineStr">
+      <c r="AA23" s="3" t="inlineStr">
         <is>
           <t>Full secondhand valuation matrix across Bulkers, Tankers, Containers for Newbuilding, 5Y, 10Y, 15Y, 20Y.</t>
         </is>
@@ -2697,52 +3213,74 @@
         </is>
       </c>
       <c r="I24" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J24" s="4" t="inlineStr">
         <is>
-          <t>CURRENT (1d ago)</t>
-        </is>
-      </c>
-      <c r="K24" s="2" t="n">
+          <t>CURRENT (3d)</t>
+        </is>
+      </c>
+      <c r="K24" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="L24" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="M24" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N24" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O24" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P24" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q24" s="2" t="n">
         <v>306</v>
       </c>
-      <c r="L24" s="2" t="n">
+      <c r="R24" s="2" t="n">
         <v>3254</v>
       </c>
-      <c r="M24" s="2" t="n">
+      <c r="S24" s="2" t="n">
         <v>15120</v>
       </c>
-      <c r="N24" s="2" t="n">
+      <c r="T24" s="2" t="n">
         <v>3225</v>
       </c>
-      <c r="O24" s="2" t="n">
+      <c r="U24" s="2" t="n">
         <v>3517</v>
       </c>
-      <c r="P24" s="3" t="n">
+      <c r="V24" s="2" t="n">
         <v>21905</v>
       </c>
-      <c r="Q24" s="3" t="inlineStr">
+      <c r="W24" s="3" t="inlineStr">
         <is>
           <t>Yes (Dry bulk freight fundamentals, ETF trajectories, &amp; localized Insights charts)</t>
         </is>
       </c>
-      <c r="R24" s="3" t="inlineStr">
+      <c r="X24" s="3" t="inlineStr">
         <is>
           <t>BeautifulSoup DOM + Asset Linker (run_breakwave_insights.py) &amp; PyMuPDF LiteParse (run_breakwave_clean_liteparse.py)</t>
         </is>
       </c>
-      <c r="S24" s="3" t="inlineStr">
+      <c r="Y24" s="3" t="inlineStr">
         <is>
           <t>breakwave_fundamentals_series.csv (2,759 rows), breakwave_insights_metadata.csv (3,225 rows)</t>
         </is>
       </c>
-      <c r="T24" s="3" t="inlineStr">
+      <c r="Z24" s="3" t="inlineStr">
         <is>
           <t>run_breakwave_insights.py &amp; run_breakwave_clean_liteparse.py</t>
         </is>
       </c>
-      <c r="U24" s="3" t="inlineStr">
+      <c r="AA24" s="3" t="inlineStr">
         <is>
           <t>100% 1:1 parity across 3,210 Insights articles (2020-2026) and 291 bi-weekly Dry Bulk/Tanker PDFs. Drybulk and Tankers partitioned by year (2018-2026 and 2023-2026). CI freshness comparison logic fixed to unblock automated workflow.</t>
         </is>
@@ -2786,56 +3324,78 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="I25" s="2" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="J25" s="4" t="inlineStr">
         <is>
-          <t>CURRENT (6d ago)</t>
-        </is>
-      </c>
-      <c r="K25" s="2" t="n">
+          <t>CURRENT (10d)</t>
+        </is>
+      </c>
+      <c r="K25" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="L25" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="M25" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N25" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="O25" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P25" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q25" s="2" t="n">
         <v>1095</v>
       </c>
-      <c r="L25" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M25" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="N25" s="2" t="n">
+      <c r="R25" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S25" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="T25" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="O25" s="2" t="n">
+      <c r="U25" s="2" t="n">
         <v>1091</v>
       </c>
-      <c r="P25" s="3" t="n">
-        <v>3270</v>
-      </c>
-      <c r="Q25" s="3" t="inlineStr">
+      <c r="V25" s="2" t="n">
+        <v>1100</v>
+      </c>
+      <c r="W25" s="3" t="inlineStr">
         <is>
           <t>Yes (Top Charterers annual/biannual volume rankings)</t>
         </is>
       </c>
-      <c r="R25" s="3" t="inlineStr">
+      <c r="X25" s="3" t="inlineStr">
         <is>
           <t>Local PyMuPDF geometry extraction (poten_clean_v2)</t>
         </is>
       </c>
-      <c r="S25" s="3" t="inlineStr">
+      <c r="Y25" s="3" t="inlineStr">
         <is>
           <t>poten_opinions_metadata.csv (1,095 rows), poten_top_charterers_series.csv (776 rows), poten_fixtures_series.csv (100 rows)</t>
         </is>
       </c>
-      <c r="T25" s="3" t="inlineStr">
+      <c r="Z25" s="3" t="inlineStr">
         <is>
           <t>run_poten.py</t>
         </is>
       </c>
-      <c r="U25" s="3" t="inlineStr">
+      <c r="AA25" s="3" t="inlineStr">
         <is>
           <t>Unbroken 22-year coverage (2004-2026). 1,087 reports cover-to-cover with 0 date exceptions.</t>
         </is>
@@ -2883,52 +3443,74 @@
         </is>
       </c>
       <c r="I26" s="2" t="n">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="J26" s="5" t="inlineStr">
         <is>
-          <t>NORMAL INTERVAL (46d ago)</t>
-        </is>
-      </c>
-      <c r="K26" s="2" t="n">
+          <t>DUE (48d, cadence monthly)</t>
+        </is>
+      </c>
+      <c r="K26" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="L26" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="M26" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N26" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="O26" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P26" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q26" s="2" t="n">
         <v>99</v>
       </c>
-      <c r="L26" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M26" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="N26" s="2" t="n">
+      <c r="R26" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S26" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="T26" s="2" t="n">
         <v>99</v>
       </c>
-      <c r="O26" s="2" t="n">
+      <c r="U26" s="2" t="n">
         <v>98</v>
       </c>
-      <c r="P26" s="3" t="n">
+      <c r="V26" s="2" t="n">
         <v>198</v>
       </c>
-      <c r="Q26" s="3" t="inlineStr">
+      <c r="W26" s="3" t="inlineStr">
         <is>
           <t>Yes (OSV utilisation curves, rig dayrates, offshore wind)</t>
         </is>
       </c>
-      <c r="R26" s="3" t="inlineStr">
+      <c r="X26" s="3" t="inlineStr">
         <is>
           <t>LlamaParse cover-to-cover + export_seabrokers_series.py</t>
         </is>
       </c>
-      <c r="S26" s="3" t="inlineStr">
+      <c r="Y26" s="3" t="inlineStr">
         <is>
           <t>seabrokers_osv_monthly_history_series.csv (6,376 rows), seabrokers_rigs_market_series.csv (4,482 rows), seabrokers_osv_utilisation_series.csv (2,328 rows), seabrokers_osv_spot_rates_series.csv (1,875 rows)</t>
         </is>
       </c>
-      <c r="T26" s="3" t="inlineStr">
+      <c r="Z26" s="3" t="inlineStr">
         <is>
           <t>run_seabrokers_llamaparse.py</t>
         </is>
       </c>
-      <c r="U26" s="3" t="inlineStr">
+      <c r="AA26" s="3" t="inlineStr">
         <is>
           <t>9 master series CSVs (15,430 rows total). Unbroken monthly offshore and subsea coverage.</t>
         </is>
@@ -2967,61 +3549,79 @@
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>2024-01-02</t>
+          <t>2024-01-09</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="I27" s="2" t="n">
-        <v>23</v>
-      </c>
-      <c r="J27" s="5" t="inlineStr">
-        <is>
-          <t>NORMAL INTERVAL (23d ago)</t>
-        </is>
-      </c>
-      <c r="K27" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="J27" s="4" t="inlineStr">
+        <is>
+          <t>CURRENT (6d)</t>
+        </is>
+      </c>
+      <c r="K27" s="2" t="inlineStr"/>
+      <c r="L27" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="M27" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N27" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="O27" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P27" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q27" s="2" t="n">
         <v>294</v>
       </c>
-      <c r="L27" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M27" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="N27" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="O27" s="2" t="n">
+      <c r="R27" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S27" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="T27" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="U27" s="2" t="n">
         <v>294</v>
       </c>
-      <c r="P27" s="3" t="n">
+      <c r="V27" s="2" t="n">
         <v>295</v>
       </c>
-      <c r="Q27" s="3" t="inlineStr">
+      <c r="W27" s="3" t="inlineStr">
         <is>
           <t>Yes (every left-axis chart line, read exactly from the vector paths; KPI tiles from the text layer)</t>
         </is>
       </c>
-      <c r="R27" s="3" t="inlineStr">
+      <c r="X27" s="3" t="inlineStr">
         <is>
           <t>Vector path reader calibrated to each chart's own tick and axis labels (run_drewry_ais_charts.py); KPI tiles, commentary and glossary from the text layer (run_drewry_ais.py)</t>
         </is>
       </c>
-      <c r="S27" s="3" t="inlineStr">
+      <c r="Y27" s="3" t="inlineStr">
         <is>
           <t>drewry_ais_chart_series.csv (83,090 rows)</t>
         </is>
       </c>
-      <c r="T27" s="3" t="inlineStr">
+      <c r="Z27" s="3" t="inlineStr">
         <is>
           <t>run_drewry_ais_charts.py</t>
         </is>
       </c>
-      <c r="U27" s="3" t="inlineStr">
+      <c r="AA27" s="3" t="inlineStr">
         <is>
           <t>82,793 chart points from 291 reports (the earlier four curve CSVs read Bezier control points as values and numbered weeks by position; they were deleted). Reports per class: Product LR1 (34), VLCC (32), LPG Carrier (32), Aframax (31), Product LR2 (31), Suezmax (30), Capesize (27), Handysize (25), Panamax (23), Supramax (23).</t>
         </is>
@@ -3069,52 +3669,70 @@
         </is>
       </c>
       <c r="I28" s="2" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="J28" s="4" t="inlineStr">
         <is>
-          <t>CURRENT (2d ago)</t>
-        </is>
-      </c>
-      <c r="K28" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="L28" s="2" t="n">
-        <v>0</v>
+          <t>CURRENT (4d)</t>
+        </is>
+      </c>
+      <c r="K28" s="2" t="inlineStr"/>
+      <c r="L28" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
       </c>
       <c r="M28" s="2" t="n">
         <v>0</v>
       </c>
       <c r="N28" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O28" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="P28" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q28" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R28" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S28" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="T28" s="2" t="n">
         <v>1096</v>
       </c>
-      <c r="O28" s="2" t="n">
+      <c r="U28" s="2" t="n">
         <v>555</v>
       </c>
-      <c r="P28" s="3" t="n">
-        <v>1108</v>
-      </c>
-      <c r="Q28" s="3" t="inlineStr">
+      <c r="V28" s="2" t="n">
+        <v>1102</v>
+      </c>
+      <c r="W28" s="3" t="inlineStr">
         <is>
           <t>Yes (Global container freight rate time series)</t>
         </is>
       </c>
-      <c r="R28" s="3" t="inlineStr">
+      <c r="X28" s="3" t="inlineStr">
         <is>
           <t>Wayback CDX &amp; live HTML parser with pv18 stability guard</t>
         </is>
       </c>
-      <c r="S28" s="3" t="inlineStr">
+      <c r="Y28" s="3" t="inlineStr">
         <is>
           <t>drewry_wci_historical.csv (138 rows), drewry_opinions_metadata.csv (555 rows), drewry_wci_series.csv (8 rows)</t>
         </is>
       </c>
-      <c r="T28" s="3" t="inlineStr">
+      <c r="Z28" s="3" t="inlineStr">
         <is>
           <t>run_drewry_opinions.py &amp; fetch_drewry_opinions_incremental.py &amp; fetch_drewry_wci.py</t>
         </is>
       </c>
-      <c r="U28" s="3" t="inlineStr">
+      <c r="AA28" s="3" t="inlineStr">
         <is>
           <t>556 opinion reports spanning 10 years (2017-2026) synchronized into reports/drewry/opinions/&lt;year&gt;/ and corpus/06-drewry/opinions/&lt;year&gt;/. Scraper updated with automatic ISO date prefixing (YYYY-MM-DD_&lt;slug&gt;.md) and dual-saving into both corpus/ and reports/ mirrors. Displayed directly on index.html.</t>
         </is>
@@ -3153,7 +3771,7 @@
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>2020-12-29</t>
+          <t>2018-06-06</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
@@ -3162,52 +3780,74 @@
         </is>
       </c>
       <c r="I29" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J29" s="4" t="inlineStr">
         <is>
-          <t>CURRENT (1d ago)</t>
-        </is>
-      </c>
-      <c r="K29" s="2" t="n">
+          <t>CURRENT (3d)</t>
+        </is>
+      </c>
+      <c r="K29" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="L29" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="M29" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N29" s="2" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="O29" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P29" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q29" s="2" t="n">
         <v>10</v>
       </c>
-      <c r="L29" s="2" t="n">
+      <c r="R29" s="2" t="n">
         <v>521</v>
       </c>
-      <c r="M29" s="2" t="n">
+      <c r="S29" s="2" t="n">
         <v>1564</v>
       </c>
-      <c r="N29" s="2" t="n">
+      <c r="T29" s="2" t="n">
         <v>456</v>
       </c>
-      <c r="O29" s="2" t="n">
+      <c r="U29" s="2" t="n">
         <v>452</v>
       </c>
-      <c r="P29" s="3" t="n">
+      <c r="V29" s="2" t="n">
         <v>2977</v>
       </c>
-      <c r="Q29" s="3" t="inlineStr">
+      <c r="W29" s="3" t="inlineStr">
         <is>
           <t>Yes (Bauxite/Coal/Crude flow monitors, trade flow heatmaps)</t>
         </is>
       </c>
-      <c r="R29" s="3" t="inlineStr">
+      <c r="X29" s="3" t="inlineStr">
         <is>
           <t>Playwright session scraper + static monitor markdown builder</t>
         </is>
       </c>
-      <c r="S29" s="3" t="inlineStr">
+      <c r="Y29" s="3" t="inlineStr">
         <is>
           <t>signal_reports_metadata.csv (452 rows), signal_vessel_counts_series.csv (120 rows), data/views/signal/live_fleet_positions.json (9,082 tracked hulls), data/views/signal/port_queues_active.json (1,932 ports)</t>
         </is>
       </c>
-      <c r="T29" s="3" t="inlineStr">
+      <c r="Z29" s="3" t="inlineStr">
         <is>
           <t>run_signal.py &amp; sync_live_fleet_pipeline.py</t>
         </is>
       </c>
-      <c r="U29" s="3" t="inlineStr">
+      <c r="AA29" s="3" t="inlineStr">
         <is>
           <t>Live automated telemetry syncs active tanker queues and fleet AIS positions. All 446 articles segregated by year across monitors, newsroom, and newsletters.</t>
         </is>
@@ -3246,7 +3886,7 @@
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>2015-01-02</t>
+          <t>2015-01-09</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
@@ -3255,52 +3895,74 @@
         </is>
       </c>
       <c r="I30" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J30" s="4" t="inlineStr">
         <is>
-          <t>CURRENT (1d ago)</t>
-        </is>
-      </c>
-      <c r="K30" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="L30" s="2" t="n">
+          <t>CURRENT (3d)</t>
+        </is>
+      </c>
+      <c r="K30" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="L30" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="M30" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N30" s="2" t="n">
+        <v>24.5</v>
+      </c>
+      <c r="O30" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P30" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q30" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R30" s="2" t="n">
         <v>3059</v>
       </c>
-      <c r="M30" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="N30" s="2" t="n">
+      <c r="S30" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="T30" s="2" t="n">
         <v>2239</v>
       </c>
-      <c r="O30" s="2" t="n">
+      <c r="U30" s="2" t="n">
         <v>2239</v>
       </c>
-      <c r="P30" s="3" t="n">
+      <c r="V30" s="2" t="n">
         <v>5298</v>
       </c>
-      <c r="Q30" s="3" t="inlineStr">
+      <c r="W30" s="3" t="inlineStr">
         <is>
           <t>No (Detailed fixture narratives and route earnings)</t>
         </is>
       </c>
-      <c r="R30" s="3" t="inlineStr">
+      <c r="X30" s="3" t="inlineStr">
         <is>
           <t>BeautifulSoup HTML layout parser</t>
         </is>
       </c>
-      <c r="S30" s="3" t="inlineStr">
+      <c r="Y30" s="3" t="inlineStr">
         <is>
           <t>baltic_reports_metadata.csv (2,239 rows), baltic_ncfi_series.csv (2,053 rows)</t>
         </is>
       </c>
-      <c r="T30" s="3" t="inlineStr">
+      <c r="Z30" s="3" t="inlineStr">
         <is>
           <t>run_baltic.py</t>
         </is>
       </c>
-      <c r="U30" s="3" t="inlineStr">
+      <c r="AA30" s="3" t="inlineStr">
         <is>
           <t>Covers Tanker, Dry Bulk, Container, Gas, and Ningbo Container Freight Index (NCFI). Week 40 (2026-10-02) extracted.</t>
         </is>
@@ -3348,52 +4010,70 @@
         </is>
       </c>
       <c r="I31" s="2" t="n">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="J31" s="5" t="inlineStr">
         <is>
-          <t>NORMAL INTERVAL (81d ago)</t>
-        </is>
-      </c>
-      <c r="K31" s="2" t="n">
+          <t>DUE (83d, cadence monthly)</t>
+        </is>
+      </c>
+      <c r="K31" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="L31" s="2" t="inlineStr"/>
+      <c r="M31" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N31" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O31" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P31" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q31" s="2" t="n">
         <v>518</v>
       </c>
-      <c r="L31" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M31" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="N31" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="O31" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="P31" s="3" t="n">
+      <c r="R31" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S31" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="T31" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="U31" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="V31" s="2" t="n">
         <v>518</v>
       </c>
-      <c r="Q31" s="3" t="inlineStr">
+      <c r="W31" s="3" t="inlineStr">
         <is>
           <t>No (Port Hedland &amp; Dampier iron ore export tonnage tables)</t>
         </is>
       </c>
-      <c r="R31" s="3" t="inlineStr">
+      <c r="X31" s="3" t="inlineStr">
         <is>
           <t>PDF tabular throughput parser + DuckDB</t>
         </is>
       </c>
-      <c r="S31" s="3" t="inlineStr">
+      <c r="Y31" s="3" t="inlineStr">
         <is>
           <t>australia_ppa_iron_ore.csv (423 rows)</t>
         </is>
       </c>
-      <c r="T31" s="3" t="inlineStr">
+      <c r="Z31" s="3" t="inlineStr">
         <is>
           <t>run_ppa.py</t>
         </is>
       </c>
-      <c r="U31" s="3" t="inlineStr">
+      <c r="AA31" s="3" t="inlineStr">
         <is>
           <t>All 110 loose PDFs consolidated into corpus/09-ppa/_root_pdfs/, leaving 0 unorganized root files. Directly feeds iron ore throughput charts on index.html. Stored in corpus.duckdb.</t>
         </is>
@@ -3417,7 +4097,7 @@
       </c>
       <c r="D32" s="3" t="inlineStr">
         <is>
-          <t>data/extracted/md/companies</t>
+          <t>corpus/10-companies</t>
         </is>
       </c>
       <c r="E32" s="3" t="inlineStr">
@@ -3432,61 +4112,83 @@
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>2014-01-01</t>
+          <t>2015-03-02</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="I32" s="2" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="J32" s="4" t="inlineStr">
         <is>
-          <t>CURRENT (8d ago)</t>
-        </is>
-      </c>
-      <c r="K32" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="L32" s="2" t="n">
-        <v>0</v>
+          <t>CURRENT (3d)</t>
+        </is>
+      </c>
+      <c r="K32" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="L32" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
       </c>
       <c r="M32" s="2" t="n">
         <v>0</v>
       </c>
       <c r="N32" s="2" t="n">
-        <v>1311</v>
+        <v>0</v>
       </c>
       <c r="O32" s="2" t="n">
-        <v>1310</v>
-      </c>
-      <c r="P32" s="3" t="n">
-        <v>1311</v>
-      </c>
-      <c r="Q32" s="3" t="inlineStr">
+        <v>0</v>
+      </c>
+      <c r="P32" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q32" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R32" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S32" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="T32" s="2" t="n">
+        <v>1333</v>
+      </c>
+      <c r="U32" s="2" t="n">
+        <v>1333</v>
+      </c>
+      <c r="V32" s="2" t="n">
+        <v>1333</v>
+      </c>
+      <c r="W32" s="3" t="inlineStr">
         <is>
           <t>No (Complete tabular statutory financials, fleet lists, debt notes)</t>
         </is>
       </c>
-      <c r="R32" s="3" t="inlineStr">
+      <c r="X32" s="3" t="inlineStr">
         <is>
           <t>sec2md HTML DOM parser + standardized YAML frontmatter normalizer</t>
         </is>
       </c>
-      <c r="S32" s="3" t="inlineStr">
+      <c r="Y32" s="3" t="inlineStr">
         <is>
           <t>Direct structured Markdown with standardized YAML frontmatter across 26 corporate subdirectories</t>
         </is>
       </c>
-      <c r="T32" s="3" t="inlineStr">
+      <c r="Z32" s="3" t="inlineStr">
         <is>
           <t>fetch_sec_filings.py &amp; audit_sec_corpus.py</t>
         </is>
       </c>
-      <c r="U32" s="3" t="inlineStr">
+      <c r="AA32" s="3" t="inlineStr">
         <is>
           <t>100% clean Markdown across 26 tickers (VALE, RIO, BHP, FSUGY, SBLK, GOGL, GNK, SB, DSX, SHIP, CTRM, GLBS, EDRY, FRO, INSW, STNG, DHT, TNK, TRMD, ECO, NAT, TNP, ASC, SFL, NVGS, LPG). Zero conversion artifacts. Standardized YAML frontmatter.</t>
         </is>
@@ -3510,7 +4212,7 @@
       </c>
       <c r="D33" s="3" t="inlineStr">
         <is>
-          <t>data/extracted/md/books</t>
+          <t>corpus/books</t>
         </is>
       </c>
       <c r="E33" s="3" t="inlineStr">
@@ -3530,58 +4232,72 @@
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>n/a</t>
         </is>
       </c>
       <c r="I33" s="2" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="J33" s="4" t="inlineStr">
         <is>
-          <t>CURRENT (13d ago)</t>
-        </is>
-      </c>
-      <c r="K33" s="2" t="n">
+          <t>REFERENCE</t>
+        </is>
+      </c>
+      <c r="K33" s="2" t="inlineStr"/>
+      <c r="L33" s="2" t="inlineStr"/>
+      <c r="M33" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N33" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O33" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P33" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q33" s="2" t="n">
         <v>12</v>
       </c>
-      <c r="L33" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M33" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="N33" s="2" t="n">
+      <c r="R33" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S33" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="T33" s="2" t="n">
         <v>12</v>
       </c>
-      <c r="O33" s="2" t="n">
+      <c r="U33" s="2" t="n">
         <v>12</v>
       </c>
-      <c r="P33" s="3" t="n">
+      <c r="V33" s="2" t="n">
         <v>24</v>
       </c>
-      <c r="Q33" s="3" t="inlineStr">
+      <c r="W33" s="3" t="inlineStr">
         <is>
           <t>Yes (LaTeX math formulas, figures, port facilities)</t>
         </is>
       </c>
-      <c r="R33" s="3" t="inlineStr">
+      <c r="X33" s="3" t="inlineStr">
         <is>
           <t>Native GFM normalizer + LaTeX math blocks ($$...$$)</t>
         </is>
       </c>
-      <c r="S33" s="3" t="inlineStr">
+      <c r="Y33" s="3" t="inlineStr">
         <is>
           <t>Clean Markdown in data/extracted/md/books/*.md and knowledge/docs/books/*.md</t>
         </is>
       </c>
-      <c r="T33" s="3" t="inlineStr">
+      <c r="Z33" s="3" t="inlineStr">
         <is>
           <t>normalize_maritime_books.py</t>
         </is>
       </c>
-      <c r="U33" s="3" t="inlineStr">
-        <is>
-          <t>12 foundational academic textbooks and handbooks fully normalized and audited with 100% byte parity in corpus/books/, data/extracted/md/books/, and knowledge/docs/books/.</t>
+      <c r="AA33" s="3" t="inlineStr">
+        <is>
+          <t>12 reference books; the normalized MDs live in corpus/books/ and are the GraphRAG input. knowledge/docs/books/ is the legacy RAG layer (built by process_knowledge.py from reports/*.pdf, older headings) and must not be ingested.</t>
         </is>
       </c>
     </row>
@@ -3596,7 +4312,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E12"/>
+  <dimension ref="A1:E11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="32" customWidth="1" min="1" max="1"/>
@@ -3686,7 +4402,7 @@
     <row r="4">
       <c r="A4" s="7" t="inlineStr">
         <is>
-          <t>01-brokers/intermodal</t>
+          <t>01-brokers/star_asia</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
@@ -3694,107 +4410,107 @@
       </c>
       <c r="C4" s="7" t="inlineStr">
         <is>
-          <t>PDF vector drawing strokes (Page 3)</t>
+          <t>PDF vector drawing strokes &amp; bar charts</t>
         </is>
       </c>
       <c r="D4" s="7" t="inlineStr">
         <is>
-          <t>Polyline vertex extraction matching Baltic dry &amp; TC curves</t>
+          <t>Subcontinent scrap price trend calibration ($/LDT)</t>
         </is>
       </c>
       <c r="E4" s="7" t="inlineStr">
         <is>
-          <t>intermodal_baltic_tc_series.csv (20,348 rows)</t>
+          <t>star_asia_scrap_price_trends_series.csv (347 rows)</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="7" t="inlineStr">
         <is>
-          <t>01-brokers/star_asia</t>
+          <t>02-hellenic/iron_ore</t>
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>0</v>
+        <v>3335</v>
       </c>
       <c r="C5" s="7" t="inlineStr">
         <is>
-          <t>PDF vector drawing strokes &amp; bar charts</t>
+          <t>JPG / PNG port inventory graphics</t>
         </is>
       </c>
       <c r="D5" s="7" t="inlineStr">
         <is>
-          <t>Subcontinent scrap price trend calibration ($/LDT)</t>
+          <t>OCR &amp; spatial coordinate table extraction</t>
         </is>
       </c>
       <c r="E5" s="7" t="inlineStr">
         <is>
-          <t>star_asia_scrap_price_trends_series.csv (347 rows)</t>
+          <t>hellenic_iron_ore_pdf_brands_series.csv (31,272 rows)</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="7" t="inlineStr">
         <is>
-          <t>02-hellenic/iron_ore</t>
+          <t>02-hellenic/demolition</t>
         </is>
       </c>
       <c r="B6" s="2" t="n">
-        <v>3335</v>
+        <v>1208</v>
       </c>
       <c r="C6" s="7" t="inlineStr">
         <is>
-          <t>JPG / PNG port inventory graphics</t>
+          <t>Cash buyer market insight graphics</t>
         </is>
       </c>
       <c r="D6" s="7" t="inlineStr">
         <is>
-          <t>OCR &amp; spatial coordinate table extraction</t>
+          <t>HTML table extraction + OCR fallback</t>
         </is>
       </c>
       <c r="E6" s="7" t="inlineStr">
         <is>
-          <t>hellenic_iron_ore_pdf_brands_series.csv (31,272 rows)</t>
+          <t>hellenic_gms_port_positions_series.csv (2,905 rows)</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="7" t="inlineStr">
         <is>
-          <t>02-hellenic/demolition</t>
+          <t>02-hellenic/dry_charter</t>
         </is>
       </c>
       <c r="B7" s="2" t="n">
-        <v>1208</v>
+        <v>759</v>
       </c>
       <c r="C7" s="7" t="inlineStr">
         <is>
-          <t>Cash buyer market insight graphics</t>
+          <t>Alibra Dry Bulk TC rate graphics</t>
         </is>
       </c>
       <c r="D7" s="7" t="inlineStr">
         <is>
-          <t>HTML table extraction + OCR fallback</t>
+          <t>Graphic OCR &amp; tabular parameter parsing</t>
         </is>
       </c>
       <c r="E7" s="7" t="inlineStr">
         <is>
-          <t>hellenic_gms_port_positions_series.csv (2,905 rows)</t>
+          <t>hellenic_alibra_dry_tc_series.csv (6,467 rows)</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="7" t="inlineStr">
         <is>
-          <t>02-hellenic/dry_charter</t>
+          <t>02-hellenic/tanker_charter</t>
         </is>
       </c>
       <c r="B8" s="2" t="n">
-        <v>759</v>
+        <v>757</v>
       </c>
       <c r="C8" s="7" t="inlineStr">
         <is>
-          <t>Alibra Dry Bulk TC rate graphics</t>
+          <t>Alibra Tanker TC rate graphics</t>
         </is>
       </c>
       <c r="D8" s="7" t="inlineStr">
@@ -3804,105 +4520,80 @@
       </c>
       <c r="E8" s="7" t="inlineStr">
         <is>
-          <t>hellenic_alibra_dry_tc_series.csv (6,467 rows)</t>
+          <t>hellenic_alibra_tanker_tc_series.csv (7,191 rows)</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="7" t="inlineStr">
         <is>
-          <t>02-hellenic/tanker_charter</t>
+          <t>02-hellenic/vessel_valuations</t>
         </is>
       </c>
       <c r="B9" s="2" t="n">
-        <v>757</v>
+        <v>726</v>
       </c>
       <c r="C9" s="7" t="inlineStr">
         <is>
-          <t>Alibra Tanker TC rate graphics</t>
+          <t>VesselsValue asset price charts</t>
         </is>
       </c>
       <c r="D9" s="7" t="inlineStr">
         <is>
-          <t>Graphic OCR &amp; tabular parameter parsing</t>
+          <t>Asset valuation curve digitizer &amp; matrix builder</t>
         </is>
       </c>
       <c r="E9" s="7" t="inlineStr">
         <is>
-          <t>hellenic_alibra_tanker_tc_series.csv (7,191 rows)</t>
+          <t>hellenic_vv_matrix_series.csv (12,340 rows)</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="7" t="inlineStr">
         <is>
-          <t>02-hellenic/vessel_valuations</t>
+          <t>03-breakwave</t>
         </is>
       </c>
       <c r="B10" s="2" t="n">
-        <v>726</v>
+        <v>15072</v>
       </c>
       <c r="C10" s="7" t="inlineStr">
         <is>
-          <t>VesselsValue asset price charts</t>
+          <t>Freight market fundamentals PNGs</t>
         </is>
       </c>
       <c r="D10" s="7" t="inlineStr">
         <is>
-          <t>Asset valuation curve digitizer &amp; matrix builder</t>
+          <t>BDRY/BWET index trajectory curves &amp; fundamental commentary</t>
         </is>
       </c>
       <c r="E10" s="7" t="inlineStr">
         <is>
-          <t>hellenic_vv_matrix_series.csv (12,340 rows)</t>
+          <t>breakwave_fundamentals_series.csv (2,746 rows)</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="7" t="inlineStr">
         <is>
-          <t>03-breakwave</t>
+          <t>07-signal</t>
         </is>
       </c>
       <c r="B11" s="2" t="n">
-        <v>15072</v>
+        <v>1885</v>
       </c>
       <c r="C11" s="7" t="inlineStr">
         <is>
-          <t>Freight market fundamentals PNGs</t>
+          <t>Flow heatmaps &amp; trade monitors</t>
         </is>
       </c>
       <c r="D11" s="7" t="inlineStr">
         <is>
-          <t>BDRY/BWET index trajectory curves &amp; fundamental commentary</t>
+          <t>Live telemetry pipeline &amp; monitor digest parser</t>
         </is>
       </c>
       <c r="E11" s="7" t="inlineStr">
-        <is>
-          <t>breakwave_fundamentals_series.csv (2,746 rows)</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="7" t="inlineStr">
-        <is>
-          <t>07-signal</t>
-        </is>
-      </c>
-      <c r="B12" s="2" t="n">
-        <v>1885</v>
-      </c>
-      <c r="C12" s="7" t="inlineStr">
-        <is>
-          <t>Flow heatmaps &amp; trade monitors</t>
-        </is>
-      </c>
-      <c r="D12" s="7" t="inlineStr">
-        <is>
-          <t>Live telemetry pipeline &amp; monitor digest parser</t>
-        </is>
-      </c>
-      <c r="E12" s="7" t="inlineStr">
         <is>
           <t>signal_reports_metadata.csv (446 rows)</t>
         </is>
@@ -4812,7 +5503,7 @@
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>6,539 rows</t>
+          <t>6,563 rows</t>
         </is>
       </c>
       <c r="H19" s="3" t="inlineStr">
@@ -4859,7 +5550,7 @@
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>7,448 rows</t>
+          <t>7,476 rows</t>
         </is>
       </c>
       <c r="H20" s="3" t="inlineStr">
@@ -4906,7 +5597,7 @@
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>31,516 rows</t>
+          <t>31,527 rows</t>
         </is>
       </c>
       <c r="H21" s="3" t="inlineStr">
@@ -5470,7 +6161,7 @@
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>6,133 rows</t>
+          <t>6,123 rows</t>
         </is>
       </c>
       <c r="H33" s="3" t="inlineStr">
@@ -5554,17 +6245,17 @@
       </c>
       <c r="E35" s="3" t="inlineStr">
         <is>
-          <t>Secondhand sales, newbuilding, scrap $/LDT, Page 3 Baltic curves</t>
+          <t>Secondhand sales, newbuilding, scrap $/LDT</t>
         </is>
       </c>
       <c r="F35" s="3" t="inlineStr">
         <is>
-          <t>intermodal_baltic_tc_series.csv</t>
+          <t>intermodal_sales_series.csv</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>20,348 rows</t>
+          <t>3,502 rows</t>
         </is>
       </c>
       <c r="H35" s="3" t="inlineStr">

--- a/data/extracted/series/corpus_publication_cadence_and_audit.xlsx
+++ b/data/extracted/series/corpus_publication_cadence_and_audit.xlsx
@@ -1488,21 +1488,21 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="I9" s="2" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="J9" s="4" t="inlineStr">
         <is>
-          <t>CURRENT (5d)</t>
+          <t>CURRENT (3d)</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr"/>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="M9" s="2" t="n">
@@ -1512,7 +1512,7 @@
         <v>0</v>
       </c>
       <c r="O9" s="2" t="n">
-        <v>35</v>
+        <v>41</v>
       </c>
       <c r="P9" s="2" t="n">
         <v>0</v>
@@ -1530,7 +1530,7 @@
         <v>4764</v>
       </c>
       <c r="U9" s="2" t="n">
-        <v>4774</v>
+        <v>4775</v>
       </c>
       <c r="V9" s="2" t="n">
         <v>4764</v>
@@ -2544,7 +2544,7 @@
         <v>0</v>
       </c>
       <c r="N18" s="2" t="n">
-        <v>62.3</v>
+        <v>0</v>
       </c>
       <c r="O18" s="2" t="n">
         <v>0</v>
@@ -2659,7 +2659,7 @@
         <v>0</v>
       </c>
       <c r="N19" s="2" t="n">
-        <v>0.4</v>
+        <v>0</v>
       </c>
       <c r="O19" s="2" t="n">
         <v>0</v>
@@ -2774,7 +2774,7 @@
         <v>0</v>
       </c>
       <c r="N20" s="2" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="O20" s="2" t="n">
         <v>0</v>
@@ -3004,7 +3004,7 @@
         <v>0</v>
       </c>
       <c r="N22" s="2" t="n">
-        <v>0.4</v>
+        <v>0</v>
       </c>
       <c r="O22" s="2" t="n">
         <v>0</v>
@@ -3119,7 +3119,7 @@
         <v>0</v>
       </c>
       <c r="N23" s="2" t="n">
-        <v>99.59999999999999</v>
+        <v>0</v>
       </c>
       <c r="O23" s="2" t="n">
         <v>0</v>

--- a/data/extracted/series/corpus_publication_cadence_and_audit.xlsx
+++ b/data/extracted/series/corpus_publication_cadence_and_audit.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Corpus Cadence &amp; Inventory" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Graphic &amp; Chart Extraction" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sub-Sector &amp; Fleet Breakdown" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Corpus Cadence &amp; Inventory" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Graphic &amp; Chart Extraction" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Sub-Sector &amp; Fleet Breakdown" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -38,7 +38,7 @@
       <sz val="10"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="6">
     <fill>
       <patternFill/>
     </fill>
@@ -55,6 +55,12 @@
       <patternFill patternType="solid">
         <fgColor rgb="00E2EFDA"/>
         <bgColor rgb="00E2EFDA"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F8CBAD"/>
+        <bgColor rgb="00F8CBAD"/>
       </patternFill>
     </fill>
     <fill>
@@ -90,7 +96,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -105,6 +111,9 @@
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -1258,20 +1267,20 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="I7" s="2" t="n">
-        <v>10</v>
-      </c>
-      <c r="J7" s="4" t="inlineStr">
-        <is>
-          <t>CURRENT (10d)</t>
+        <v>3</v>
+      </c>
+      <c r="J7" s="5" t="inlineStr">
+        <is>
+          <t>PARSE BEHIND (latest MD 7d older than latest issue)</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
@@ -1292,7 +1301,7 @@
         <v>0</v>
       </c>
       <c r="Q7" s="2" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="R7" s="2" t="n">
         <v>0</v>
@@ -1307,7 +1316,7 @@
         <v>10</v>
       </c>
       <c r="V7" s="2" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="W7" s="3" t="inlineStr">
         <is>
@@ -2059,25 +2068,25 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="I14" s="2" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="J14" s="4" t="inlineStr">
         <is>
-          <t>CURRENT (10d)</t>
+          <t>CURRENT (3d)</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="M14" s="2" t="n">
@@ -2093,7 +2102,7 @@
         <v>0</v>
       </c>
       <c r="Q14" s="2" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="R14" s="2" t="n">
         <v>0</v>
@@ -2105,10 +2114,10 @@
         <v>0</v>
       </c>
       <c r="U14" s="2" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="V14" s="2" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="W14" s="3" t="inlineStr">
         <is>
@@ -2122,7 +2131,7 @@
       </c>
       <c r="Y14" s="3" t="inlineStr">
         <is>
-          <t>lion_deals_series.csv (1,312 rows), lion_sales_series.csv (1,203 rows), lion_demometer_series.csv (576 rows), lion_demolition_series.csv (516 rows), lion_demo_sales_series.csv (109 rows)</t>
+          <t>lion_deals_series.csv (1,342 rows), lion_sales_series.csv (1,232 rows), lion_demometer_series.csv (588 rows), lion_demolition_series.csv (516 rows), lion_demo_sales_series.csv (110 rows)</t>
         </is>
       </c>
       <c r="Z14" s="3" t="inlineStr">
@@ -2174,25 +2183,25 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="I15" s="2" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="J15" s="4" t="inlineStr">
         <is>
-          <t>CURRENT (7d)</t>
+          <t>CURRENT (0d)</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="M15" s="2" t="n">
@@ -2208,7 +2217,7 @@
         <v>0</v>
       </c>
       <c r="Q15" s="2" t="n">
-        <v>536</v>
+        <v>538</v>
       </c>
       <c r="R15" s="2" t="n">
         <v>0</v>
@@ -2220,10 +2229,10 @@
         <v>0</v>
       </c>
       <c r="U15" s="2" t="n">
-        <v>520</v>
+        <v>522</v>
       </c>
       <c r="V15" s="2" t="n">
-        <v>536</v>
+        <v>538</v>
       </c>
       <c r="W15" s="3" t="inlineStr">
         <is>
@@ -2237,7 +2246,7 @@
       </c>
       <c r="Y15" s="3" t="inlineStr">
         <is>
-          <t>ssy_capesize_index_series.csv (10,294 rows), ssy_capesize_series.csv (8,881 rows), ssy_route_rates_series.csv (5,190 rows), ssy_capesize_index_time_series.csv (519 rows)</t>
+          <t>ssy_capesize_index_series.csv (10,438 rows), ssy_capesize_series.csv (8,881 rows), ssy_route_rates_series.csv (5,210 rows), ssy_capesize_index_time_series.csv (521 rows)</t>
         </is>
       </c>
       <c r="Z15" s="3" t="inlineStr">
@@ -2289,25 +2298,25 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="I16" s="2" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="J16" s="4" t="inlineStr">
         <is>
-          <t>CURRENT (7d)</t>
+          <t>CURRENT (0d)</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="M16" s="2" t="n">
@@ -2323,7 +2332,7 @@
         <v>0</v>
       </c>
       <c r="Q16" s="2" t="n">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="R16" s="2" t="n">
         <v>0</v>
@@ -2335,10 +2344,10 @@
         <v>0</v>
       </c>
       <c r="U16" s="2" t="n">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="V16" s="2" t="n">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="W16" s="3" t="inlineStr">
         <is>
@@ -2352,7 +2361,7 @@
       </c>
       <c r="Y16" s="3" t="inlineStr">
         <is>
-          <t>star_asia_snp_sales_series.csv (3,575 rows), star_asia_deals_series.csv (3,362 rows), star_asia_valuation_matrix_series.csv (3,232 rows), star_asia_demolition_series.csv (3,152 rows), star_asia_metals_energy_series.csv (1,327 rows)</t>
+          <t>star_asia_snp_sales_series.csv (3,575 rows), star_asia_deals_series.csv (3,386 rows), star_asia_valuation_matrix_series.csv (3,232 rows), star_asia_demolition_series.csv (3,168 rows), star_asia_metals_energy_series.csv (1,327 rows)</t>
         </is>
       </c>
       <c r="Z16" s="3" t="inlineStr">
@@ -3445,7 +3454,7 @@
       <c r="I26" s="2" t="n">
         <v>48</v>
       </c>
-      <c r="J26" s="5" t="inlineStr">
+      <c r="J26" s="6" t="inlineStr">
         <is>
           <t>DUE (48d, cadence monthly)</t>
         </is>
@@ -4012,7 +4021,7 @@
       <c r="I31" s="2" t="n">
         <v>83</v>
       </c>
-      <c r="J31" s="5" t="inlineStr">
+      <c r="J31" s="6" t="inlineStr">
         <is>
           <t>DUE (83d, cadence monthly)</t>
         </is>
@@ -4323,34 +4332,34 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="6" t="inlineStr">
+      <c r="A1" s="7" t="inlineStr">
         <is>
           <t>Source Category</t>
         </is>
       </c>
-      <c r="B1" s="6" t="inlineStr">
+      <c r="B1" s="7" t="inlineStr">
         <is>
           <t>Images in Corpus</t>
         </is>
       </c>
-      <c r="C1" s="6" t="inlineStr">
+      <c r="C1" s="7" t="inlineStr">
         <is>
           <t>Graphic Formats</t>
         </is>
       </c>
-      <c r="D1" s="6" t="inlineStr">
+      <c r="D1" s="7" t="inlineStr">
         <is>
           <t>Extraction Pipeline Applied</t>
         </is>
       </c>
-      <c r="E1" s="6" t="inlineStr">
+      <c r="E1" s="7" t="inlineStr">
         <is>
           <t>Extracted Series Output</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="7" t="inlineStr">
+      <c r="A2" s="8" t="inlineStr">
         <is>
           <t>01-brokers/fearnleys-md</t>
         </is>
@@ -4358,24 +4367,24 @@
       <c r="B2" s="2" t="n">
         <v>2786</v>
       </c>
-      <c r="C2" s="7" t="inlineStr">
+      <c r="C2" s="8" t="inlineStr">
         <is>
           <t>Raster PNG charts (no embedded data), JPG</t>
         </is>
       </c>
-      <c r="D2" s="7" t="inlineStr">
+      <c r="D2" s="8" t="inlineStr">
         <is>
           <t>Not read; titles kept, printed tables transcribed and verified</t>
         </is>
       </c>
-      <c r="E2" s="7" t="inlineStr">
+      <c r="E2" s="8" t="inlineStr">
         <is>
           <t>Chart titles in MDs and .tables.json sidecars; calibrated series deleted</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="7" t="inlineStr">
+      <c r="A3" s="8" t="inlineStr">
         <is>
           <t>01-brokers/ism</t>
         </is>
@@ -4383,24 +4392,24 @@
       <c r="B3" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="C3" s="7" t="inlineStr">
+      <c r="C3" s="8" t="inlineStr">
         <is>
           <t>PDF vector drawing strokes</t>
         </is>
       </c>
-      <c r="D3" s="7" t="inlineStr">
+      <c r="D3" s="8" t="inlineStr">
         <is>
           <t>Least-squares dual-axis scale calibration &amp; tick filtering</t>
         </is>
       </c>
-      <c r="E3" s="7" t="inlineStr">
+      <c r="E3" s="8" t="inlineStr">
         <is>
           <t>ism_handy_freight_series.csv, ism_coaster_freight_series.csv</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="7" t="inlineStr">
+      <c r="A4" s="8" t="inlineStr">
         <is>
           <t>01-brokers/star_asia</t>
         </is>
@@ -4408,24 +4417,24 @@
       <c r="B4" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="C4" s="7" t="inlineStr">
+      <c r="C4" s="8" t="inlineStr">
         <is>
           <t>PDF vector drawing strokes &amp; bar charts</t>
         </is>
       </c>
-      <c r="D4" s="7" t="inlineStr">
+      <c r="D4" s="8" t="inlineStr">
         <is>
           <t>Subcontinent scrap price trend calibration ($/LDT)</t>
         </is>
       </c>
-      <c r="E4" s="7" t="inlineStr">
+      <c r="E4" s="8" t="inlineStr">
         <is>
           <t>star_asia_scrap_price_trends_series.csv (347 rows)</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="7" t="inlineStr">
+      <c r="A5" s="8" t="inlineStr">
         <is>
           <t>02-hellenic/iron_ore</t>
         </is>
@@ -4433,24 +4442,24 @@
       <c r="B5" s="2" t="n">
         <v>3335</v>
       </c>
-      <c r="C5" s="7" t="inlineStr">
+      <c r="C5" s="8" t="inlineStr">
         <is>
           <t>JPG / PNG port inventory graphics</t>
         </is>
       </c>
-      <c r="D5" s="7" t="inlineStr">
+      <c r="D5" s="8" t="inlineStr">
         <is>
           <t>OCR &amp; spatial coordinate table extraction</t>
         </is>
       </c>
-      <c r="E5" s="7" t="inlineStr">
+      <c r="E5" s="8" t="inlineStr">
         <is>
           <t>hellenic_iron_ore_pdf_brands_series.csv (31,272 rows)</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="7" t="inlineStr">
+      <c r="A6" s="8" t="inlineStr">
         <is>
           <t>02-hellenic/demolition</t>
         </is>
@@ -4458,24 +4467,24 @@
       <c r="B6" s="2" t="n">
         <v>1208</v>
       </c>
-      <c r="C6" s="7" t="inlineStr">
+      <c r="C6" s="8" t="inlineStr">
         <is>
           <t>Cash buyer market insight graphics</t>
         </is>
       </c>
-      <c r="D6" s="7" t="inlineStr">
+      <c r="D6" s="8" t="inlineStr">
         <is>
           <t>HTML table extraction + OCR fallback</t>
         </is>
       </c>
-      <c r="E6" s="7" t="inlineStr">
+      <c r="E6" s="8" t="inlineStr">
         <is>
           <t>hellenic_gms_port_positions_series.csv (2,905 rows)</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="7" t="inlineStr">
+      <c r="A7" s="8" t="inlineStr">
         <is>
           <t>02-hellenic/dry_charter</t>
         </is>
@@ -4483,24 +4492,24 @@
       <c r="B7" s="2" t="n">
         <v>759</v>
       </c>
-      <c r="C7" s="7" t="inlineStr">
+      <c r="C7" s="8" t="inlineStr">
         <is>
           <t>Alibra Dry Bulk TC rate graphics</t>
         </is>
       </c>
-      <c r="D7" s="7" t="inlineStr">
+      <c r="D7" s="8" t="inlineStr">
         <is>
           <t>Graphic OCR &amp; tabular parameter parsing</t>
         </is>
       </c>
-      <c r="E7" s="7" t="inlineStr">
+      <c r="E7" s="8" t="inlineStr">
         <is>
           <t>hellenic_alibra_dry_tc_series.csv (6,467 rows)</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="7" t="inlineStr">
+      <c r="A8" s="8" t="inlineStr">
         <is>
           <t>02-hellenic/tanker_charter</t>
         </is>
@@ -4508,24 +4517,24 @@
       <c r="B8" s="2" t="n">
         <v>757</v>
       </c>
-      <c r="C8" s="7" t="inlineStr">
+      <c r="C8" s="8" t="inlineStr">
         <is>
           <t>Alibra Tanker TC rate graphics</t>
         </is>
       </c>
-      <c r="D8" s="7" t="inlineStr">
+      <c r="D8" s="8" t="inlineStr">
         <is>
           <t>Graphic OCR &amp; tabular parameter parsing</t>
         </is>
       </c>
-      <c r="E8" s="7" t="inlineStr">
+      <c r="E8" s="8" t="inlineStr">
         <is>
           <t>hellenic_alibra_tanker_tc_series.csv (7,191 rows)</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="7" t="inlineStr">
+      <c r="A9" s="8" t="inlineStr">
         <is>
           <t>02-hellenic/vessel_valuations</t>
         </is>
@@ -4533,24 +4542,24 @@
       <c r="B9" s="2" t="n">
         <v>726</v>
       </c>
-      <c r="C9" s="7" t="inlineStr">
+      <c r="C9" s="8" t="inlineStr">
         <is>
           <t>VesselsValue asset price charts</t>
         </is>
       </c>
-      <c r="D9" s="7" t="inlineStr">
+      <c r="D9" s="8" t="inlineStr">
         <is>
           <t>Asset valuation curve digitizer &amp; matrix builder</t>
         </is>
       </c>
-      <c r="E9" s="7" t="inlineStr">
+      <c r="E9" s="8" t="inlineStr">
         <is>
           <t>hellenic_vv_matrix_series.csv (12,340 rows)</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="7" t="inlineStr">
+      <c r="A10" s="8" t="inlineStr">
         <is>
           <t>03-breakwave</t>
         </is>
@@ -4558,24 +4567,24 @@
       <c r="B10" s="2" t="n">
         <v>15072</v>
       </c>
-      <c r="C10" s="7" t="inlineStr">
+      <c r="C10" s="8" t="inlineStr">
         <is>
           <t>Freight market fundamentals PNGs</t>
         </is>
       </c>
-      <c r="D10" s="7" t="inlineStr">
+      <c r="D10" s="8" t="inlineStr">
         <is>
           <t>BDRY/BWET index trajectory curves &amp; fundamental commentary</t>
         </is>
       </c>
-      <c r="E10" s="7" t="inlineStr">
+      <c r="E10" s="8" t="inlineStr">
         <is>
           <t>breakwave_fundamentals_series.csv (2,746 rows)</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="7" t="inlineStr">
+      <c r="A11" s="8" t="inlineStr">
         <is>
           <t>07-signal</t>
         </is>
@@ -4583,17 +4592,17 @@
       <c r="B11" s="2" t="n">
         <v>1885</v>
       </c>
-      <c r="C11" s="7" t="inlineStr">
+      <c r="C11" s="8" t="inlineStr">
         <is>
           <t>Flow heatmaps &amp; trade monitors</t>
         </is>
       </c>
-      <c r="D11" s="7" t="inlineStr">
+      <c r="D11" s="8" t="inlineStr">
         <is>
           <t>Live telemetry pipeline &amp; monitor digest parser</t>
         </is>
       </c>
-      <c r="E11" s="7" t="inlineStr">
+      <c r="E11" s="8" t="inlineStr">
         <is>
           <t>signal_reports_metadata.csv (446 rows)</t>
         </is>

--- a/data/extracted/series/corpus_publication_cadence_and_audit.xlsx
+++ b/data/extracted/series/corpus_publication_cadence_and_audit.xlsx
@@ -1488,21 +1488,21 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="I9" s="2" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="J9" s="4" t="inlineStr">
         <is>
-          <t>CURRENT (5d)</t>
+          <t>CURRENT (3d)</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr"/>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="M9" s="2" t="n">
@@ -1530,7 +1530,7 @@
         <v>4764</v>
       </c>
       <c r="U9" s="2" t="n">
-        <v>4774</v>
+        <v>4775</v>
       </c>
       <c r="V9" s="2" t="n">
         <v>4764</v>
@@ -3119,7 +3119,7 @@
         <v>0</v>
       </c>
       <c r="N23" s="2" t="n">
-        <v>99.59999999999999</v>
+        <v>100</v>
       </c>
       <c r="O23" s="2" t="n">
         <v>0</v>
@@ -4287,7 +4287,7 @@
       </c>
       <c r="Y33" s="3" t="inlineStr">
         <is>
-          <t>Clean Markdown in data/extracted/md/books/*.md and knowledge/docs/books/*.md</t>
+          <t>Normalized Markdown in corpus/books/*.md (no series; text corpus)</t>
         </is>
       </c>
       <c r="Z33" s="3" t="inlineStr">

--- a/data/extracted/series/corpus_publication_cadence_and_audit.xlsx
+++ b/data/extracted/series/corpus_publication_cadence_and_audit.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Corpus Cadence &amp; Inventory" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Graphic &amp; Chart Extraction" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Sub-Sector &amp; Fleet Breakdown" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Corpus Cadence &amp; Inventory" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Graphic &amp; Chart Extraction" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sub-Sector &amp; Fleet Breakdown" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -726,7 +726,7 @@
         <v>0</v>
       </c>
       <c r="Q2" s="2" t="n">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="R2" s="2" t="n">
         <v>0</v>
@@ -741,7 +741,7 @@
         <v>253</v>
       </c>
       <c r="V2" s="2" t="n">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="W2" s="3" t="inlineStr">
         <is>
@@ -841,7 +841,7 @@
         <v>0</v>
       </c>
       <c r="Q3" s="2" t="n">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="R3" s="2" t="n">
         <v>0</v>
@@ -856,7 +856,7 @@
         <v>250</v>
       </c>
       <c r="V3" s="2" t="n">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="W3" s="3" t="inlineStr">
         <is>
@@ -1301,7 +1301,7 @@
         <v>0</v>
       </c>
       <c r="Q7" s="2" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="R7" s="2" t="n">
         <v>0</v>
@@ -1316,7 +1316,7 @@
         <v>10</v>
       </c>
       <c r="V7" s="2" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="W7" s="3" t="inlineStr">
         <is>
@@ -2102,7 +2102,7 @@
         <v>0</v>
       </c>
       <c r="Q14" s="2" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="R14" s="2" t="n">
         <v>0</v>
@@ -2117,7 +2117,7 @@
         <v>49</v>
       </c>
       <c r="V14" s="2" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="W14" s="3" t="inlineStr">
         <is>
@@ -2217,7 +2217,7 @@
         <v>0</v>
       </c>
       <c r="Q15" s="2" t="n">
-        <v>538</v>
+        <v>540</v>
       </c>
       <c r="R15" s="2" t="n">
         <v>0</v>
@@ -2232,7 +2232,7 @@
         <v>522</v>
       </c>
       <c r="V15" s="2" t="n">
-        <v>538</v>
+        <v>540</v>
       </c>
       <c r="W15" s="3" t="inlineStr">
         <is>
@@ -2332,7 +2332,7 @@
         <v>0</v>
       </c>
       <c r="Q16" s="2" t="n">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="R16" s="2" t="n">
         <v>0</v>
@@ -2347,7 +2347,7 @@
         <v>199</v>
       </c>
       <c r="V16" s="2" t="n">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="W16" s="3" t="inlineStr">
         <is>
@@ -2528,32 +2528,32 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="I18" s="2" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="J18" s="4" t="inlineStr">
         <is>
-          <t>CURRENT (9d)</t>
+          <t>CURRENT (2d)</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="M18" s="2" t="n">
         <v>0</v>
       </c>
       <c r="N18" s="2" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="O18" s="2" t="n">
         <v>0</v>
@@ -2562,22 +2562,22 @@
         <v>0</v>
       </c>
       <c r="Q18" s="2" t="n">
-        <v>2147</v>
+        <v>2151</v>
       </c>
       <c r="R18" s="2" t="n">
-        <v>813</v>
+        <v>815</v>
       </c>
       <c r="S18" s="2" t="n">
-        <v>1212</v>
+        <v>1213</v>
       </c>
       <c r="T18" s="2" t="n">
         <v>0</v>
       </c>
       <c r="U18" s="2" t="n">
-        <v>753</v>
+        <v>754</v>
       </c>
       <c r="V18" s="2" t="n">
-        <v>4172</v>
+        <v>4179</v>
       </c>
       <c r="W18" s="3" t="inlineStr">
         <is>
@@ -2591,7 +2591,7 @@
       </c>
       <c r="Y18" s="3" t="inlineStr">
         <is>
-          <t>athenian_indicative_demolition_series.csv (3,064 rows), hellenic_gms_port_positions_series.csv (3,014 rows), hellenic_gms_demolition_series.csv (1,104 rows), hellenic_best_oasis_deals_series.csv (905 rows), hellenic_best_oasis_demolition_series.csv (866 rows)</t>
+          <t>athenian_indicative_demolition_series.csv (3,064 rows), hellenic_gms_port_positions_series.csv (3,029 rows), hellenic_gms_demolition_series.csv (1,108 rows), hellenic_best_oasis_deals_series.csv (905 rows), hellenic_best_oasis_demolition_series.csv (866 rows)</t>
         </is>
       </c>
       <c r="Z18" s="3" t="inlineStr">
@@ -2758,32 +2758,32 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="I20" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J20" s="4" t="inlineStr">
         <is>
-          <t>CURRENT (3d)</t>
+          <t>CURRENT (0d)</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="M20" s="2" t="n">
         <v>0</v>
       </c>
       <c r="N20" s="2" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="O20" s="2" t="n">
         <v>0</v>
@@ -2792,7 +2792,7 @@
         <v>0</v>
       </c>
       <c r="Q20" s="2" t="n">
-        <v>4542</v>
+        <v>4544</v>
       </c>
       <c r="R20" s="2" t="n">
         <v>0</v>
@@ -2804,10 +2804,10 @@
         <v>0</v>
       </c>
       <c r="U20" s="2" t="n">
-        <v>1190</v>
+        <v>1201</v>
       </c>
       <c r="V20" s="2" t="n">
-        <v>4542</v>
+        <v>4544</v>
       </c>
       <c r="W20" s="3" t="inlineStr">
         <is>
@@ -3218,25 +3218,25 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="I24" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J24" s="4" t="inlineStr">
         <is>
-          <t>CURRENT (3d)</t>
+          <t>CURRENT (0d)</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="M24" s="2" t="n">
@@ -3255,19 +3255,19 @@
         <v>306</v>
       </c>
       <c r="R24" s="2" t="n">
-        <v>3254</v>
+        <v>3256</v>
       </c>
       <c r="S24" s="2" t="n">
-        <v>15120</v>
+        <v>15122</v>
       </c>
       <c r="T24" s="2" t="n">
-        <v>3225</v>
+        <v>3227</v>
       </c>
       <c r="U24" s="2" t="n">
-        <v>3517</v>
+        <v>3519</v>
       </c>
       <c r="V24" s="2" t="n">
-        <v>21905</v>
+        <v>21911</v>
       </c>
       <c r="W24" s="3" t="inlineStr">
         <is>
@@ -3281,7 +3281,7 @@
       </c>
       <c r="Y24" s="3" t="inlineStr">
         <is>
-          <t>breakwave_fundamentals_series.csv (2,759 rows), breakwave_insights_metadata.csv (3,225 rows)</t>
+          <t>breakwave_fundamentals_series.csv (2,759 rows), breakwave_insights_metadata.csv (3,227 rows)</t>
         </is>
       </c>
       <c r="Z24" s="3" t="inlineStr">
@@ -5371,7 +5371,7 @@
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>1,104 rows</t>
+          <t>1,108 rows</t>
         </is>
       </c>
       <c r="H16" s="3" t="inlineStr">
@@ -5418,7 +5418,7 @@
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>3,014 rows</t>
+          <t>3,029 rows</t>
         </is>
       </c>
       <c r="H17" s="3" t="inlineStr">

--- a/data/extracted/series/corpus_publication_cadence_and_audit.xlsx
+++ b/data/extracted/series/corpus_publication_cadence_and_audit.xlsx
@@ -2553,7 +2553,7 @@
         <v>0</v>
       </c>
       <c r="N18" s="2" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="O18" s="2" t="n">
         <v>0</v>

--- a/data/extracted/series/corpus_publication_cadence_and_audit.xlsx
+++ b/data/extracted/series/corpus_publication_cadence_and_audit.xlsx
@@ -1521,7 +1521,7 @@
         <v>0</v>
       </c>
       <c r="O9" s="2" t="n">
-        <v>35</v>
+        <v>41</v>
       </c>
       <c r="P9" s="2" t="n">
         <v>0</v>
@@ -2361,7 +2361,7 @@
       </c>
       <c r="Y16" s="3" t="inlineStr">
         <is>
-          <t>star_asia_snp_sales_series.csv (3,575 rows), star_asia_deals_series.csv (3,386 rows), star_asia_valuation_matrix_series.csv (3,232 rows), star_asia_demolition_series.csv (3,168 rows), star_asia_metals_energy_series.csv (1,327 rows)</t>
+          <t>star_asia_snp_sales_series.csv (3,575 rows), star_asia_deals_series.csv (3,393 rows), star_asia_valuation_matrix_series.csv (3,232 rows), star_asia_demolition_series.csv (3,168 rows), star_asia_metals_energy_series.csv (1,327 rows)</t>
         </is>
       </c>
       <c r="Z16" s="3" t="inlineStr">
@@ -2413,25 +2413,25 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="I17" s="2" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="J17" s="4" t="inlineStr">
         <is>
-          <t>CURRENT (6d)</t>
+          <t>CURRENT (0d)</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="M17" s="2" t="n">
@@ -2447,7 +2447,7 @@
         <v>0</v>
       </c>
       <c r="Q17" s="2" t="n">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="R17" s="2" t="n">
         <v>0</v>
@@ -2459,10 +2459,10 @@
         <v>0</v>
       </c>
       <c r="U17" s="2" t="n">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="V17" s="2" t="n">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="W17" s="3" t="inlineStr">
         <is>
@@ -2476,7 +2476,7 @@
       </c>
       <c r="Y17" s="3" t="inlineStr">
         <is>
-          <t>xclusiv_secondhand_series.csv (8,593 rows), xclusiv_sales_series.csv (5,584 rows), xclusiv_demolition_series.csv (2,098 rows), xclusiv_newbuilding_prices_series.csv (1,379 rows), xclusiv_newbuilding_orders_series.csv (1,313 rows)</t>
+          <t>xclusiv_secondhand_series.csv (8,625 rows), xclusiv_sales_series.csv (5,593 rows), xclusiv_demolition_series.csv (2,106 rows), xclusiv_newbuilding_prices_series.csv (1,379 rows), xclusiv_newbuilding_orders_series.csv (1,313 rows)</t>
         </is>
       </c>
       <c r="Z17" s="3" t="inlineStr">
@@ -2553,7 +2553,7 @@
         <v>0</v>
       </c>
       <c r="N18" s="2" t="n">
-        <v>62.2</v>
+        <v>0</v>
       </c>
       <c r="O18" s="2" t="n">
         <v>0</v>
@@ -2668,7 +2668,7 @@
         <v>0</v>
       </c>
       <c r="N19" s="2" t="n">
-        <v>0.4</v>
+        <v>0</v>
       </c>
       <c r="O19" s="2" t="n">
         <v>0</v>
@@ -2783,7 +2783,7 @@
         <v>0</v>
       </c>
       <c r="N20" s="2" t="n">
-        <v>1.9</v>
+        <v>2.6</v>
       </c>
       <c r="O20" s="2" t="n">
         <v>0</v>
@@ -3013,7 +3013,7 @@
         <v>0</v>
       </c>
       <c r="N22" s="2" t="n">
-        <v>0.4</v>
+        <v>0</v>
       </c>
       <c r="O22" s="2" t="n">
         <v>0</v>
@@ -3128,7 +3128,7 @@
         <v>0</v>
       </c>
       <c r="N23" s="2" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="O23" s="2" t="n">
         <v>0</v>
@@ -3218,7 +3218,7 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="I24" s="2" t="n">
@@ -3231,12 +3231,12 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="M24" s="2" t="n">
@@ -3252,7 +3252,7 @@
         <v>0</v>
       </c>
       <c r="Q24" s="2" t="n">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="R24" s="2" t="n">
         <v>3256</v>
@@ -3264,10 +3264,10 @@
         <v>3227</v>
       </c>
       <c r="U24" s="2" t="n">
-        <v>3519</v>
+        <v>3520</v>
       </c>
       <c r="V24" s="2" t="n">
-        <v>21911</v>
+        <v>21912</v>
       </c>
       <c r="W24" s="3" t="inlineStr">
         <is>
@@ -3281,7 +3281,7 @@
       </c>
       <c r="Y24" s="3" t="inlineStr">
         <is>
-          <t>breakwave_fundamentals_series.csv (2,759 rows), breakwave_insights_metadata.csv (3,227 rows)</t>
+          <t>breakwave_fundamentals_series.csv (2,769 rows), breakwave_insights_metadata.csv (3,227 rows)</t>
         </is>
       </c>
       <c r="Z24" s="3" t="inlineStr">
@@ -6123,7 +6123,7 @@
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>5,584 rows</t>
+          <t>5,593 rows</t>
         </is>
       </c>
       <c r="H32" s="3" t="inlineStr">

--- a/data/extracted/series/corpus_publication_cadence_and_audit.xlsx
+++ b/data/extracted/series/corpus_publication_cadence_and_audit.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Corpus Cadence &amp; Inventory" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Graphic &amp; Chart Extraction" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sub-Sector &amp; Fleet Breakdown" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Corpus Cadence &amp; Inventory" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Graphic &amp; Chart Extraction" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Sub-Sector &amp; Fleet Breakdown" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -59,14 +59,14 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00F8CBAD"/>
-        <bgColor rgb="00F8CBAD"/>
+        <fgColor rgb="00FFF2CC"/>
+        <bgColor rgb="00FFF2CC"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFF2CC"/>
-        <bgColor rgb="00FFF2CC"/>
+        <fgColor rgb="00F8CBAD"/>
+        <bgColor rgb="00F8CBAD"/>
       </patternFill>
     </fill>
   </fills>
@@ -922,20 +922,20 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="I4" s="2" t="n">
-        <v>10</v>
-      </c>
-      <c r="J4" s="4" t="inlineStr">
-        <is>
-          <t>CURRENT (10d)</t>
+        <v>11</v>
+      </c>
+      <c r="J4" s="5" t="inlineStr">
+        <is>
+          <t>DUE (11d, cadence weekly)</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
@@ -956,7 +956,7 @@
         <v>0</v>
       </c>
       <c r="Q4" s="2" t="n">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="R4" s="2" t="n">
         <v>0</v>
@@ -968,10 +968,10 @@
         <v>0</v>
       </c>
       <c r="U4" s="2" t="n">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="V4" s="2" t="n">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="W4" s="3" t="inlineStr">
         <is>
@@ -1273,7 +1273,7 @@
       <c r="I7" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="J7" s="5" t="inlineStr">
+      <c r="J7" s="6" t="inlineStr">
         <is>
           <t>PARSE BEHIND (latest MD 7d older than latest issue)</t>
         </is>
@@ -2246,7 +2246,7 @@
       </c>
       <c r="Y15" s="3" t="inlineStr">
         <is>
-          <t>ssy_capesize_index_series.csv (10,438 rows), ssy_capesize_series.csv (8,881 rows), ssy_route_rates_series.csv (5,210 rows), ssy_capesize_index_time_series.csv (521 rows)</t>
+          <t>ssy_capesize_index_series.csv (8,737 rows), ssy_route_rates_series.csv (5,210 rows), ssy_capesize_index_time_series.csv (521 rows)</t>
         </is>
       </c>
       <c r="Z15" s="3" t="inlineStr">
@@ -2332,7 +2332,7 @@
         <v>0</v>
       </c>
       <c r="Q16" s="2" t="n">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="R16" s="2" t="n">
         <v>0</v>
@@ -2347,7 +2347,7 @@
         <v>199</v>
       </c>
       <c r="V16" s="2" t="n">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="W16" s="3" t="inlineStr">
         <is>
@@ -2361,7 +2361,7 @@
       </c>
       <c r="Y16" s="3" t="inlineStr">
         <is>
-          <t>star_asia_snp_sales_series.csv (3,575 rows), star_asia_deals_series.csv (3,393 rows), star_asia_valuation_matrix_series.csv (3,232 rows), star_asia_demolition_series.csv (3,168 rows), star_asia_metals_energy_series.csv (1,327 rows)</t>
+          <t>star_asia_snp_sales_series.csv (3,696 rows), star_asia_deals_series.csv (3,548 rows), star_asia_valuation_matrix_series.csv (3,346 rows), star_asia_demolition_series.csv (3,168 rows), star_asia_metals_energy_series.csv (1,382 rows)</t>
         </is>
       </c>
       <c r="Z16" s="3" t="inlineStr">
@@ -2783,7 +2783,7 @@
         <v>0</v>
       </c>
       <c r="N20" s="2" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="O20" s="2" t="n">
         <v>0</v>
@@ -2804,7 +2804,7 @@
         <v>0</v>
       </c>
       <c r="U20" s="2" t="n">
-        <v>1201</v>
+        <v>1191</v>
       </c>
       <c r="V20" s="2" t="n">
         <v>4544</v>
@@ -3454,7 +3454,7 @@
       <c r="I26" s="2" t="n">
         <v>48</v>
       </c>
-      <c r="J26" s="6" t="inlineStr">
+      <c r="J26" s="5" t="inlineStr">
         <is>
           <t>DUE (48d, cadence monthly)</t>
         </is>
@@ -4021,7 +4021,7 @@
       <c r="I31" s="2" t="n">
         <v>83</v>
       </c>
-      <c r="J31" s="6" t="inlineStr">
+      <c r="J31" s="5" t="inlineStr">
         <is>
           <t>DUE (83d, cadence monthly)</t>
         </is>
@@ -4419,17 +4419,17 @@
       </c>
       <c r="C4" s="8" t="inlineStr">
         <is>
-          <t>PDF vector drawing strokes &amp; bar charts</t>
+          <t>Image bar chart with printed data labels</t>
         </is>
       </c>
       <c r="D4" s="8" t="inlineStr">
         <is>
-          <t>Subcontinent scrap price trend calibration ($/LDT)</t>
+          <t>Annual LDT sold at Alang / Chattogram / Pakistan (printed labels only)</t>
         </is>
       </c>
       <c r="E4" s="8" t="inlineStr">
         <is>
-          <t>star_asia_scrap_price_trends_series.csv (347 rows)</t>
+          <t>star_asia_ldt_comparison_series.csv (1,320 rows)</t>
         </is>
       </c>
     </row>

--- a/data/extracted/series/corpus_publication_cadence_and_audit.xlsx
+++ b/data/extracted/series/corpus_publication_cadence_and_audit.xlsx
@@ -565,7 +565,7 @@
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>Status (2026-10-19)</t>
+          <t>Status (2026-10-20)</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
@@ -696,11 +696,11 @@
         </is>
       </c>
       <c r="I2" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J2" s="4" t="inlineStr">
         <is>
-          <t>CURRENT (2d)</t>
+          <t>CURRENT (3d)</t>
         </is>
       </c>
       <c r="K2" s="2" t="inlineStr">
@@ -811,11 +811,11 @@
         </is>
       </c>
       <c r="I3" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J3" s="4" t="inlineStr">
         <is>
-          <t>CURRENT (2d)</t>
+          <t>CURRENT (3d)</t>
         </is>
       </c>
       <c r="K3" s="2" t="inlineStr">
@@ -926,11 +926,11 @@
         </is>
       </c>
       <c r="I4" s="2" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="J4" s="5" t="inlineStr">
         <is>
-          <t>DUE (11d, cadence weekly)</t>
+          <t>DUE (12d, cadence weekly)</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -1041,11 +1041,11 @@
         </is>
       </c>
       <c r="I5" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J5" s="4" t="inlineStr">
         <is>
-          <t>CURRENT (5d)</t>
+          <t>CURRENT (6d)</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -1156,11 +1156,11 @@
         </is>
       </c>
       <c r="I6" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="J6" s="4" t="inlineStr">
         <is>
-          <t>CURRENT (7d)</t>
+          <t>CURRENT (8d)</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -1271,7 +1271,7 @@
         </is>
       </c>
       <c r="I7" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J7" s="6" t="inlineStr">
         <is>
@@ -1386,11 +1386,11 @@
         </is>
       </c>
       <c r="I8" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J8" s="4" t="inlineStr">
         <is>
-          <t>CURRENT (4d)</t>
+          <t>CURRENT (5d)</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -1501,11 +1501,11 @@
         </is>
       </c>
       <c r="I9" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J9" s="4" t="inlineStr">
         <is>
-          <t>CURRENT (3d)</t>
+          <t>CURRENT (4d)</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr"/>
@@ -1612,11 +1612,11 @@
         </is>
       </c>
       <c r="I10" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J10" s="4" t="inlineStr">
         <is>
-          <t>CURRENT (5d)</t>
+          <t>CURRENT (6d)</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1727,11 +1727,11 @@
         </is>
       </c>
       <c r="I11" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J11" s="4" t="inlineStr">
         <is>
-          <t>CURRENT (3d)</t>
+          <t>CURRENT (4d)</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -1842,11 +1842,11 @@
         </is>
       </c>
       <c r="I12" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J12" s="4" t="inlineStr">
         <is>
-          <t>CURRENT (5d)</t>
+          <t>CURRENT (6d)</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1957,11 +1957,11 @@
         </is>
       </c>
       <c r="I13" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="J13" s="4" t="inlineStr">
         <is>
-          <t>CURRENT (7d)</t>
+          <t>CURRENT (8d)</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
@@ -2072,11 +2072,11 @@
         </is>
       </c>
       <c r="I14" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J14" s="4" t="inlineStr">
         <is>
-          <t>CURRENT (3d)</t>
+          <t>CURRENT (4d)</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2187,11 +2187,11 @@
         </is>
       </c>
       <c r="I15" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J15" s="4" t="inlineStr">
         <is>
-          <t>CURRENT (0d)</t>
+          <t>CURRENT (1d)</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
@@ -2302,11 +2302,11 @@
         </is>
       </c>
       <c r="I16" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J16" s="4" t="inlineStr">
         <is>
-          <t>CURRENT (0d)</t>
+          <t>CURRENT (1d)</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -2417,11 +2417,11 @@
         </is>
       </c>
       <c r="I17" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J17" s="4" t="inlineStr">
         <is>
-          <t>CURRENT (0d)</t>
+          <t>CURRENT (1d)</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -2532,11 +2532,11 @@
         </is>
       </c>
       <c r="I18" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J18" s="4" t="inlineStr">
         <is>
-          <t>CURRENT (2d)</t>
+          <t>CURRENT (3d)</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
@@ -2647,11 +2647,11 @@
         </is>
       </c>
       <c r="I19" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J19" s="4" t="inlineStr">
         <is>
-          <t>CURRENT (5d)</t>
+          <t>CURRENT (6d)</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
@@ -2762,11 +2762,11 @@
         </is>
       </c>
       <c r="I20" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J20" s="4" t="inlineStr">
         <is>
-          <t>CURRENT (0d)</t>
+          <t>CURRENT (1d)</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -2992,11 +2992,11 @@
         </is>
       </c>
       <c r="I22" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J22" s="4" t="inlineStr">
         <is>
-          <t>CURRENT (5d)</t>
+          <t>CURRENT (6d)</t>
         </is>
       </c>
       <c r="K22" s="2" t="inlineStr">
@@ -3107,11 +3107,11 @@
         </is>
       </c>
       <c r="I23" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J23" s="4" t="inlineStr">
         <is>
-          <t>CURRENT (5d)</t>
+          <t>CURRENT (6d)</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
@@ -3337,11 +3337,11 @@
         </is>
       </c>
       <c r="I25" s="2" t="n">
-        <v>10</v>
-      </c>
-      <c r="J25" s="4" t="inlineStr">
-        <is>
-          <t>CURRENT (10d)</t>
+        <v>11</v>
+      </c>
+      <c r="J25" s="5" t="inlineStr">
+        <is>
+          <t>DUE (11d, cadence weekly)</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
@@ -3452,11 +3452,11 @@
         </is>
       </c>
       <c r="I26" s="2" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="J26" s="5" t="inlineStr">
         <is>
-          <t>DUE (48d, cadence monthly)</t>
+          <t>DUE (49d, cadence monthly)</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
@@ -3567,11 +3567,11 @@
         </is>
       </c>
       <c r="I27" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J27" s="4" t="inlineStr">
         <is>
-          <t>CURRENT (6d)</t>
+          <t>CURRENT (7d)</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr"/>
@@ -3678,11 +3678,11 @@
         </is>
       </c>
       <c r="I28" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J28" s="4" t="inlineStr">
         <is>
-          <t>CURRENT (4d)</t>
+          <t>CURRENT (5d)</t>
         </is>
       </c>
       <c r="K28" s="2" t="inlineStr"/>
@@ -3789,11 +3789,11 @@
         </is>
       </c>
       <c r="I29" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J29" s="4" t="inlineStr">
         <is>
-          <t>CURRENT (3d)</t>
+          <t>CURRENT (4d)</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
@@ -3904,11 +3904,11 @@
         </is>
       </c>
       <c r="I30" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J30" s="4" t="inlineStr">
         <is>
-          <t>CURRENT (3d)</t>
+          <t>CURRENT (4d)</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
@@ -4019,11 +4019,11 @@
         </is>
       </c>
       <c r="I31" s="2" t="n">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="J31" s="5" t="inlineStr">
         <is>
-          <t>DUE (83d, cadence monthly)</t>
+          <t>DUE (84d, cadence monthly)</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
@@ -4130,11 +4130,11 @@
         </is>
       </c>
       <c r="I32" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J32" s="4" t="inlineStr">
         <is>
-          <t>CURRENT (3d)</t>
+          <t>CURRENT (4d)</t>
         </is>
       </c>
       <c r="K32" s="2" t="inlineStr">

--- a/data/extracted/series/corpus_publication_cadence_and_audit.xlsx
+++ b/data/extracted/series/corpus_publication_cadence_and_audit.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Corpus Cadence &amp; Inventory" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Graphic &amp; Chart Extraction" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Sub-Sector &amp; Fleet Breakdown" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Corpus Cadence &amp; Inventory" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Graphic &amp; Chart Extraction" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sub-Sector &amp; Fleet Breakdown" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -2758,32 +2758,32 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="I20" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J20" s="4" t="inlineStr">
         <is>
-          <t>CURRENT (1d)</t>
+          <t>CURRENT (0d)</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="M20" s="2" t="n">
         <v>0</v>
       </c>
       <c r="N20" s="2" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="O20" s="2" t="n">
         <v>0</v>
@@ -2792,7 +2792,7 @@
         <v>0</v>
       </c>
       <c r="Q20" s="2" t="n">
-        <v>4544</v>
+        <v>4546</v>
       </c>
       <c r="R20" s="2" t="n">
         <v>0</v>
@@ -2804,10 +2804,10 @@
         <v>0</v>
       </c>
       <c r="U20" s="2" t="n">
-        <v>1191</v>
+        <v>1192</v>
       </c>
       <c r="V20" s="2" t="n">
-        <v>4544</v>
+        <v>4546</v>
       </c>
       <c r="W20" s="3" t="inlineStr">
         <is>
@@ -3255,19 +3255,19 @@
         <v>307</v>
       </c>
       <c r="R24" s="2" t="n">
-        <v>3256</v>
+        <v>3258</v>
       </c>
       <c r="S24" s="2" t="n">
-        <v>15122</v>
+        <v>15128</v>
       </c>
       <c r="T24" s="2" t="n">
-        <v>3227</v>
+        <v>3229</v>
       </c>
       <c r="U24" s="2" t="n">
-        <v>3520</v>
+        <v>3522</v>
       </c>
       <c r="V24" s="2" t="n">
-        <v>21912</v>
+        <v>21922</v>
       </c>
       <c r="W24" s="3" t="inlineStr">
         <is>
@@ -3281,7 +3281,7 @@
       </c>
       <c r="Y24" s="3" t="inlineStr">
         <is>
-          <t>breakwave_fundamentals_series.csv (2,769 rows), breakwave_insights_metadata.csv (3,227 rows)</t>
+          <t>breakwave_fundamentals_series.csv (2,769 rows), breakwave_insights_metadata.csv (3,229 rows)</t>
         </is>
       </c>
       <c r="Z24" s="3" t="inlineStr">

--- a/data/extracted/series/corpus_publication_cadence_and_audit.xlsx
+++ b/data/extracted/series/corpus_publication_cadence_and_audit.xlsx
@@ -755,7 +755,7 @@
       </c>
       <c r="Y2" s="3" t="inlineStr">
         <is>
-          <t>advanced_shipping_sales_series.csv (6,853 rows), advanced_shipping_demolition_series.csv (2,024 rows), advanced_shipping_secondhand_matrix_series.csv (8,157 rows), advanced_shipping_newbuilding_series.csv (1,922 rows), advanced_shipping_demo_sales_series.csv (606 rows)</t>
+          <t>advanced_shipping_sales_series.csv (6,857 rows), advanced_shipping_demolition_series.csv (2,024 rows), advanced_shipping_secondhand_matrix_series.csv (8,157 rows), advanced_shipping_newbuilding_series.csv (1,922 rows), advanced_shipping_demo_sales_series.csv (606 rows)</t>
         </is>
       </c>
       <c r="Z2" s="3" t="inlineStr">
@@ -1901,7 +1901,7 @@
       </c>
       <c r="Y12" s="3" t="inlineStr">
         <is>
-          <t>intermodal_tc_rates_series.csv (5,273 rows), intermodal_newbuilding_series.csv (5,130 rows), intermodal_tanker_spot_series.csv (3,915 rows), intermodal_sales_series.csv (3,848 rows), intermodal_demolition_series.csv (2,637 rows)</t>
+          <t>intermodal_tc_rates_series.csv (5,273 rows), intermodal_newbuilding_series.csv (5,130 rows), intermodal_tanker_spot_series.csv (3,915 rows), intermodal_sales_series.csv (3,846 rows), intermodal_demolition_series.csv (2,637 rows)</t>
         </is>
       </c>
       <c r="Z12" s="3" t="inlineStr">
@@ -2208,7 +2208,7 @@
         <v>0</v>
       </c>
       <c r="N15" s="2" t="n">
-        <v>99.40000000000001</v>
+        <v>99.59999999999999</v>
       </c>
       <c r="O15" s="2" t="n">
         <v>0</v>
@@ -2229,7 +2229,7 @@
         <v>0</v>
       </c>
       <c r="U15" s="2" t="n">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="V15" s="2" t="n">
         <v>540</v>
@@ -2246,7 +2246,7 @@
       </c>
       <c r="Y15" s="3" t="inlineStr">
         <is>
-          <t>ssy_capesize_index_series.csv (8,737 rows), ssy_route_rates_series.csv (5,210 rows), ssy_capesize_index_time_series.csv (521 rows)</t>
+          <t>ssy_capesize_index_series.csv (916 rows), ssy_route_rates_series.csv (5,230 rows), ssy_capesize_index_time_series.csv (523 rows)</t>
         </is>
       </c>
       <c r="Z15" s="3" t="inlineStr">
@@ -2476,7 +2476,7 @@
       </c>
       <c r="Y17" s="3" t="inlineStr">
         <is>
-          <t>xclusiv_secondhand_series.csv (8,625 rows), xclusiv_sales_series.csv (5,593 rows), xclusiv_demolition_series.csv (2,106 rows), xclusiv_newbuilding_prices_series.csv (1,379 rows), xclusiv_newbuilding_orders_series.csv (1,313 rows)</t>
+          <t>xclusiv_secondhand_series.csv (8,625 rows), xclusiv_sales_series.csv (5,593 rows), xclusiv_demolition_series.csv (2,106 rows), xclusiv_newbuilding_prices_series.csv (1,397 rows), xclusiv_newbuilding_orders_series.csv (1,328 rows)</t>
         </is>
       </c>
       <c r="Z17" s="3" t="inlineStr">
@@ -2562,7 +2562,7 @@
         <v>0</v>
       </c>
       <c r="Q18" s="2" t="n">
-        <v>2151</v>
+        <v>1947</v>
       </c>
       <c r="R18" s="2" t="n">
         <v>815</v>
@@ -2577,7 +2577,7 @@
         <v>754</v>
       </c>
       <c r="V18" s="2" t="n">
-        <v>4179</v>
+        <v>3975</v>
       </c>
       <c r="W18" s="3" t="inlineStr">
         <is>
@@ -2792,7 +2792,7 @@
         <v>0</v>
       </c>
       <c r="Q20" s="2" t="n">
-        <v>4546</v>
+        <v>3545</v>
       </c>
       <c r="R20" s="2" t="n">
         <v>0</v>
@@ -2807,7 +2807,7 @@
         <v>1192</v>
       </c>
       <c r="V20" s="2" t="n">
-        <v>4546</v>
+        <v>3545</v>
       </c>
       <c r="W20" s="3" t="inlineStr">
         <is>
@@ -2907,7 +2907,7 @@
         <v>0</v>
       </c>
       <c r="Q21" s="2" t="n">
-        <v>1363</v>
+        <v>1041</v>
       </c>
       <c r="R21" s="2" t="n">
         <v>380</v>
@@ -2922,7 +2922,7 @@
         <v>170</v>
       </c>
       <c r="V21" s="2" t="n">
-        <v>1923</v>
+        <v>1601</v>
       </c>
       <c r="W21" s="3" t="inlineStr">
         <is>
@@ -6170,7 +6170,7 @@
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>6,853 rows</t>
+          <t>6,857 rows</t>
         </is>
       </c>
       <c r="H33" s="3" t="inlineStr">
@@ -6264,7 +6264,7 @@
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>3,848 rows</t>
+          <t>3,846 rows</t>
         </is>
       </c>
       <c r="H35" s="3" t="inlineStr">

--- a/data/extracted/series/corpus_publication_cadence_and_audit.xlsx
+++ b/data/extracted/series/corpus_publication_cadence_and_audit.xlsx
@@ -2476,7 +2476,7 @@
       </c>
       <c r="Y17" s="3" t="inlineStr">
         <is>
-          <t>xclusiv_secondhand_series.csv (8,625 rows), xclusiv_sales_series.csv (5,593 rows), xclusiv_demolition_series.csv (2,106 rows), xclusiv_newbuilding_prices_series.csv (1,397 rows), xclusiv_newbuilding_orders_series.csv (1,328 rows)</t>
+          <t>xclusiv_secondhand_series.csv (8,625 rows), xclusiv_sales_series.csv (5,593 rows), xclusiv_demolition_series.csv (2,106 rows), xclusiv_newbuilding_prices_series.csv (1,406 rows), xclusiv_newbuilding_orders_series.csv (1,336 rows)</t>
         </is>
       </c>
       <c r="Z17" s="3" t="inlineStr">
@@ -2528,32 +2528,32 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="I18" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J18" s="4" t="inlineStr">
         <is>
-          <t>CURRENT (3d)</t>
+          <t>CURRENT (0d)</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-18</t>
         </is>
       </c>
       <c r="M18" s="2" t="n">
         <v>0</v>
       </c>
       <c r="N18" s="2" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="O18" s="2" t="n">
         <v>0</v>
@@ -2562,10 +2562,10 @@
         <v>0</v>
       </c>
       <c r="Q18" s="2" t="n">
-        <v>1947</v>
+        <v>1949</v>
       </c>
       <c r="R18" s="2" t="n">
-        <v>815</v>
+        <v>816</v>
       </c>
       <c r="S18" s="2" t="n">
         <v>1213</v>
@@ -2574,10 +2574,10 @@
         <v>0</v>
       </c>
       <c r="U18" s="2" t="n">
-        <v>754</v>
+        <v>755</v>
       </c>
       <c r="V18" s="2" t="n">
-        <v>3975</v>
+        <v>3978</v>
       </c>
       <c r="W18" s="3" t="inlineStr">
         <is>
@@ -2591,7 +2591,7 @@
       </c>
       <c r="Y18" s="3" t="inlineStr">
         <is>
-          <t>athenian_indicative_demolition_series.csv (3,064 rows), hellenic_gms_port_positions_series.csv (3,029 rows), hellenic_gms_demolition_series.csv (1,108 rows), hellenic_best_oasis_deals_series.csv (905 rows), hellenic_best_oasis_demolition_series.csv (866 rows)</t>
+          <t>athenian_indicative_demolition_series.csv (3,076 rows), hellenic_gms_port_positions_series.csv (3,029 rows), hellenic_gms_demolition_series.csv (1,108 rows), hellenic_best_oasis_deals_series.csv (905 rows), hellenic_best_oasis_demolition_series.csv (866 rows)</t>
         </is>
       </c>
       <c r="Z18" s="3" t="inlineStr">
@@ -2910,7 +2910,7 @@
         <v>1041</v>
       </c>
       <c r="R21" s="2" t="n">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="S21" s="2" t="n">
         <v>180</v>
@@ -2922,7 +2922,7 @@
         <v>170</v>
       </c>
       <c r="V21" s="2" t="n">
-        <v>1601</v>
+        <v>1602</v>
       </c>
       <c r="W21" s="3" t="inlineStr">
         <is>
@@ -3103,32 +3103,32 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="I23" s="2" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="J23" s="4" t="inlineStr">
         <is>
-          <t>CURRENT (6d)</t>
+          <t>CURRENT (0d)</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="M23" s="2" t="n">
         <v>0</v>
       </c>
       <c r="N23" s="2" t="n">
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="O23" s="2" t="n">
         <v>0</v>
@@ -3140,7 +3140,7 @@
         <v>0</v>
       </c>
       <c r="R23" s="2" t="n">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="S23" s="2" t="n">
         <v>733</v>
@@ -3149,10 +3149,10 @@
         <v>0</v>
       </c>
       <c r="U23" s="2" t="n">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="V23" s="2" t="n">
-        <v>1009</v>
+        <v>1010</v>
       </c>
       <c r="W23" s="3" t="inlineStr">
         <is>
@@ -3166,7 +3166,7 @@
       </c>
       <c r="Y23" s="3" t="inlineStr">
         <is>
-          <t>hellenic_vv_matrix_series.csv (12,373 rows), hellenic_vv_sales_series.csv (2,077 rows)</t>
+          <t>hellenic_vv_matrix_series.csv (12,373 rows), hellenic_vv_sales_series.csv (2,091 rows)</t>
         </is>
       </c>
       <c r="Z23" s="3" t="inlineStr">
@@ -5324,7 +5324,7 @@
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>3,064 rows</t>
+          <t>3,076 rows</t>
         </is>
       </c>
       <c r="H15" s="3" t="inlineStr">
@@ -5794,7 +5794,7 @@
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>2,077 rows</t>
+          <t>2,091 rows</t>
         </is>
       </c>
       <c r="H25" s="3" t="inlineStr">

--- a/data/extracted/series/corpus_publication_cadence_and_audit.xlsx
+++ b/data/extracted/series/corpus_publication_cadence_and_audit.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Corpus Cadence &amp; Inventory" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Graphic &amp; Chart Extraction" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sub-Sector &amp; Fleet Breakdown" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Corpus Cadence &amp; Inventory" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Graphic &amp; Chart Extraction" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Sub-Sector &amp; Fleet Breakdown" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1037,25 +1037,25 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="I5" s="2" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="J5" s="4" t="inlineStr">
         <is>
-          <t>CURRENT (6d)</t>
+          <t>CURRENT (0d)</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="M5" s="2" t="n">
@@ -1071,7 +1071,7 @@
         <v>0</v>
       </c>
       <c r="Q5" s="2" t="n">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="R5" s="2" t="n">
         <v>0</v>
@@ -1083,10 +1083,10 @@
         <v>0</v>
       </c>
       <c r="U5" s="2" t="n">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="V5" s="2" t="n">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="W5" s="3" t="inlineStr">
         <is>
@@ -1100,7 +1100,7 @@
       </c>
       <c r="Y5" s="3" t="inlineStr">
         <is>
-          <t>bancosta_freight_rates_series.csv (20,587 rows), bancosta_ffa_series.csv (7,726 rows), bancosta_sales_series.csv (3,240 rows), bancosta_commodities_series.csv (8,546 rows), bancosta_newbuilding_series.csv (2,377 rows), bancosta_secondhand_matrix_series.csv (1,898 rows), bancosta_demolition_series.csv (959 rows)</t>
+          <t>bancosta_freight_rates_series.csv (20,677 rows), bancosta_ffa_series.csv (7,762 rows), bancosta_sales_series.csv (3,261 rows), bancosta_commodities_series.csv (8,573 rows), bancosta_newbuilding_series.csv (2,377 rows), bancosta_secondhand_matrix_series.csv (1,898 rows), bancosta_demolition_series.csv (959 rows)</t>
         </is>
       </c>
       <c r="Z5" s="3" t="inlineStr">
@@ -1838,25 +1838,25 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="I12" s="2" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="J12" s="4" t="inlineStr">
         <is>
-          <t>CURRENT (6d)</t>
+          <t>CURRENT (0d)</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="M12" s="2" t="n">
@@ -1872,7 +1872,7 @@
         <v>0</v>
       </c>
       <c r="Q12" s="2" t="n">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="R12" s="2" t="n">
         <v>0</v>
@@ -1884,10 +1884,10 @@
         <v>0</v>
       </c>
       <c r="U12" s="2" t="n">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="V12" s="2" t="n">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="W12" s="3" t="inlineStr">
         <is>
@@ -2246,7 +2246,7 @@
       </c>
       <c r="Y15" s="3" t="inlineStr">
         <is>
-          <t>ssy_capesize_index_series.csv (916 rows), ssy_route_rates_series.csv (5,230 rows), ssy_capesize_index_time_series.csv (523 rows)</t>
+          <t>ssy_capesize_index_series.csv (922 rows), ssy_route_rates_series.csv (5,230 rows), ssy_capesize_index_time_series.csv (523 rows)</t>
         </is>
       </c>
       <c r="Z15" s="3" t="inlineStr">
@@ -2553,7 +2553,7 @@
         <v>0</v>
       </c>
       <c r="N18" s="2" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="O18" s="2" t="n">
         <v>0</v>
@@ -2783,7 +2783,7 @@
         <v>0</v>
       </c>
       <c r="N20" s="2" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="O20" s="2" t="n">
         <v>0</v>
@@ -3128,7 +3128,7 @@
         <v>0</v>
       </c>
       <c r="N23" s="2" t="n">
-        <v>0.4</v>
+        <v>0</v>
       </c>
       <c r="O23" s="2" t="n">
         <v>0</v>
@@ -6217,7 +6217,7 @@
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>3,240 rows</t>
+          <t>3,261 rows</t>
         </is>
       </c>
       <c r="H34" s="3" t="inlineStr">

--- a/data/extracted/series/corpus_publication_cadence_and_audit.xlsx
+++ b/data/extracted/series/corpus_publication_cadence_and_audit.xlsx
@@ -565,7 +565,7 @@
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>Status (2026-10-20)</t>
+          <t>Status (2026-10-21)</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
@@ -696,11 +696,11 @@
         </is>
       </c>
       <c r="I2" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J2" s="4" t="inlineStr">
         <is>
-          <t>CURRENT (3d)</t>
+          <t>CURRENT (4d)</t>
         </is>
       </c>
       <c r="K2" s="2" t="inlineStr">
@@ -811,11 +811,11 @@
         </is>
       </c>
       <c r="I3" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J3" s="4" t="inlineStr">
         <is>
-          <t>CURRENT (3d)</t>
+          <t>CURRENT (4d)</t>
         </is>
       </c>
       <c r="K3" s="2" t="inlineStr">
@@ -926,11 +926,11 @@
         </is>
       </c>
       <c r="I4" s="2" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="J4" s="5" t="inlineStr">
         <is>
-          <t>DUE (12d, cadence weekly)</t>
+          <t>DUE (13d, cadence weekly)</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -1156,11 +1156,11 @@
         </is>
       </c>
       <c r="I6" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J6" s="4" t="inlineStr">
         <is>
-          <t>CURRENT (8d)</t>
+          <t>CURRENT (9d)</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -1271,7 +1271,7 @@
         </is>
       </c>
       <c r="I7" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J7" s="6" t="inlineStr">
         <is>
@@ -1386,11 +1386,11 @@
         </is>
       </c>
       <c r="I8" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J8" s="4" t="inlineStr">
         <is>
-          <t>CURRENT (5d)</t>
+          <t>CURRENT (6d)</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -1497,21 +1497,21 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="I9" s="2" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="J9" s="4" t="inlineStr">
         <is>
-          <t>CURRENT (4d)</t>
+          <t>CURRENT (0d)</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr"/>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="M9" s="2" t="n">
@@ -1539,7 +1539,7 @@
         <v>4764</v>
       </c>
       <c r="U9" s="2" t="n">
-        <v>4775</v>
+        <v>4778</v>
       </c>
       <c r="V9" s="2" t="n">
         <v>4764</v>
@@ -1612,11 +1612,11 @@
         </is>
       </c>
       <c r="I10" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J10" s="4" t="inlineStr">
         <is>
-          <t>CURRENT (6d)</t>
+          <t>CURRENT (7d)</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1727,11 +1727,11 @@
         </is>
       </c>
       <c r="I11" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J11" s="4" t="inlineStr">
         <is>
-          <t>CURRENT (4d)</t>
+          <t>CURRENT (5d)</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -1957,11 +1957,11 @@
         </is>
       </c>
       <c r="I13" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J13" s="4" t="inlineStr">
         <is>
-          <t>CURRENT (8d)</t>
+          <t>CURRENT (9d)</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
@@ -2072,11 +2072,11 @@
         </is>
       </c>
       <c r="I14" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J14" s="4" t="inlineStr">
         <is>
-          <t>CURRENT (4d)</t>
+          <t>CURRENT (5d)</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2187,11 +2187,11 @@
         </is>
       </c>
       <c r="I15" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J15" s="4" t="inlineStr">
         <is>
-          <t>CURRENT (1d)</t>
+          <t>CURRENT (2d)</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
@@ -2302,11 +2302,11 @@
         </is>
       </c>
       <c r="I16" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J16" s="4" t="inlineStr">
         <is>
-          <t>CURRENT (1d)</t>
+          <t>CURRENT (2d)</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -2417,11 +2417,11 @@
         </is>
       </c>
       <c r="I17" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J17" s="4" t="inlineStr">
         <is>
-          <t>CURRENT (1d)</t>
+          <t>CURRENT (2d)</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -2532,11 +2532,11 @@
         </is>
       </c>
       <c r="I18" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J18" s="4" t="inlineStr">
         <is>
-          <t>CURRENT (0d)</t>
+          <t>CURRENT (1d)</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
@@ -2647,11 +2647,11 @@
         </is>
       </c>
       <c r="I19" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J19" s="4" t="inlineStr">
         <is>
-          <t>CURRENT (6d)</t>
+          <t>CURRENT (7d)</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
@@ -2762,11 +2762,11 @@
         </is>
       </c>
       <c r="I20" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J20" s="4" t="inlineStr">
         <is>
-          <t>CURRENT (0d)</t>
+          <t>CURRENT (1d)</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -2992,11 +2992,11 @@
         </is>
       </c>
       <c r="I22" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J22" s="4" t="inlineStr">
         <is>
-          <t>CURRENT (6d)</t>
+          <t>CURRENT (7d)</t>
         </is>
       </c>
       <c r="K22" s="2" t="inlineStr">
@@ -3107,11 +3107,11 @@
         </is>
       </c>
       <c r="I23" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J23" s="4" t="inlineStr">
         <is>
-          <t>CURRENT (0d)</t>
+          <t>CURRENT (1d)</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
@@ -3222,11 +3222,11 @@
         </is>
       </c>
       <c r="I24" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J24" s="4" t="inlineStr">
         <is>
-          <t>CURRENT (0d)</t>
+          <t>CURRENT (1d)</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
@@ -3337,11 +3337,11 @@
         </is>
       </c>
       <c r="I25" s="2" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="J25" s="5" t="inlineStr">
         <is>
-          <t>DUE (11d, cadence weekly)</t>
+          <t>DUE (12d, cadence weekly)</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
@@ -3452,11 +3452,11 @@
         </is>
       </c>
       <c r="I26" s="2" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="J26" s="5" t="inlineStr">
         <is>
-          <t>DUE (49d, cadence monthly)</t>
+          <t>DUE (50d, cadence monthly)</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
@@ -3567,11 +3567,11 @@
         </is>
       </c>
       <c r="I27" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="J27" s="4" t="inlineStr">
         <is>
-          <t>CURRENT (7d)</t>
+          <t>CURRENT (8d)</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr"/>
@@ -3678,11 +3678,11 @@
         </is>
       </c>
       <c r="I28" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J28" s="4" t="inlineStr">
         <is>
-          <t>CURRENT (5d)</t>
+          <t>CURRENT (6d)</t>
         </is>
       </c>
       <c r="K28" s="2" t="inlineStr"/>
@@ -3789,11 +3789,11 @@
         </is>
       </c>
       <c r="I29" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J29" s="4" t="inlineStr">
         <is>
-          <t>CURRENT (4d)</t>
+          <t>CURRENT (5d)</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
@@ -3904,11 +3904,11 @@
         </is>
       </c>
       <c r="I30" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J30" s="4" t="inlineStr">
         <is>
-          <t>CURRENT (4d)</t>
+          <t>CURRENT (5d)</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
@@ -4019,11 +4019,11 @@
         </is>
       </c>
       <c r="I31" s="2" t="n">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="J31" s="5" t="inlineStr">
         <is>
-          <t>DUE (84d, cadence monthly)</t>
+          <t>DUE (85d, cadence monthly)</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
@@ -4130,11 +4130,11 @@
         </is>
       </c>
       <c r="I32" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J32" s="4" t="inlineStr">
         <is>
-          <t>CURRENT (4d)</t>
+          <t>CURRENT (5d)</t>
         </is>
       </c>
       <c r="K32" s="2" t="inlineStr">

--- a/data/extracted/series/corpus_publication_cadence_and_audit.xlsx
+++ b/data/extracted/series/corpus_publication_cadence_and_audit.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Corpus Cadence &amp; Inventory" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Graphic &amp; Chart Extraction" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Sub-Sector &amp; Fleet Breakdown" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Corpus Cadence &amp; Inventory" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Graphic &amp; Chart Extraction" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sub-Sector &amp; Fleet Breakdown" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -2758,32 +2758,32 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="I20" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J20" s="4" t="inlineStr">
         <is>
-          <t>CURRENT (1d)</t>
+          <t>CURRENT (0d)</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="M20" s="2" t="n">
         <v>0</v>
       </c>
       <c r="N20" s="2" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="O20" s="2" t="n">
         <v>0</v>
@@ -2792,7 +2792,7 @@
         <v>0</v>
       </c>
       <c r="Q20" s="2" t="n">
-        <v>3545</v>
+        <v>3547</v>
       </c>
       <c r="R20" s="2" t="n">
         <v>0</v>
@@ -2804,10 +2804,10 @@
         <v>0</v>
       </c>
       <c r="U20" s="2" t="n">
-        <v>1192</v>
+        <v>1193</v>
       </c>
       <c r="V20" s="2" t="n">
-        <v>3545</v>
+        <v>3547</v>
       </c>
       <c r="W20" s="3" t="inlineStr">
         <is>
@@ -3218,25 +3218,25 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="I24" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J24" s="4" t="inlineStr">
         <is>
-          <t>CURRENT (1d)</t>
+          <t>CURRENT (0d)</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="M24" s="2" t="n">
@@ -3255,19 +3255,19 @@
         <v>307</v>
       </c>
       <c r="R24" s="2" t="n">
-        <v>3258</v>
+        <v>3260</v>
       </c>
       <c r="S24" s="2" t="n">
-        <v>15128</v>
+        <v>15129</v>
       </c>
       <c r="T24" s="2" t="n">
-        <v>3229</v>
+        <v>3231</v>
       </c>
       <c r="U24" s="2" t="n">
-        <v>3522</v>
+        <v>3524</v>
       </c>
       <c r="V24" s="2" t="n">
-        <v>21922</v>
+        <v>21927</v>
       </c>
       <c r="W24" s="3" t="inlineStr">
         <is>
@@ -3281,7 +3281,7 @@
       </c>
       <c r="Y24" s="3" t="inlineStr">
         <is>
-          <t>breakwave_fundamentals_series.csv (2,769 rows), breakwave_insights_metadata.csv (3,229 rows)</t>
+          <t>breakwave_fundamentals_series.csv (2,769 rows), breakwave_insights_metadata.csv (3,231 rows)</t>
         </is>
       </c>
       <c r="Z24" s="3" t="inlineStr">

--- a/data/extracted/series/corpus_publication_cadence_and_audit.xlsx
+++ b/data/extracted/series/corpus_publication_cadence_and_audit.xlsx
@@ -1536,13 +1536,13 @@
         <v>0</v>
       </c>
       <c r="T9" s="2" t="n">
-        <v>4764</v>
+        <v>4773</v>
       </c>
       <c r="U9" s="2" t="n">
-        <v>4778</v>
+        <v>4783</v>
       </c>
       <c r="V9" s="2" t="n">
-        <v>4764</v>
+        <v>4773</v>
       </c>
       <c r="W9" s="3" t="inlineStr">
         <is>
@@ -2783,7 +2783,7 @@
         <v>0</v>
       </c>
       <c r="N20" s="2" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="O20" s="2" t="n">
         <v>0</v>

--- a/data/extracted/series/corpus_publication_cadence_and_audit.xlsx
+++ b/data/extracted/series/corpus_publication_cadence_and_audit.xlsx
@@ -1539,7 +1539,7 @@
         <v>4773</v>
       </c>
       <c r="U9" s="2" t="n">
-        <v>4783</v>
+        <v>4778</v>
       </c>
       <c r="V9" s="2" t="n">
         <v>4773</v>
@@ -2643,32 +2643,32 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="I19" s="2" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="J19" s="4" t="inlineStr">
         <is>
-          <t>CURRENT (7d)</t>
+          <t>CURRENT (0d)</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="M19" s="2" t="n">
         <v>0</v>
       </c>
       <c r="N19" s="2" t="n">
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="O19" s="2" t="n">
         <v>0</v>
@@ -2680,19 +2680,19 @@
         <v>0</v>
       </c>
       <c r="R19" s="2" t="n">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="S19" s="2" t="n">
-        <v>763</v>
+        <v>764</v>
       </c>
       <c r="T19" s="2" t="n">
         <v>0</v>
       </c>
       <c r="U19" s="2" t="n">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="V19" s="2" t="n">
-        <v>1044</v>
+        <v>1046</v>
       </c>
       <c r="W19" s="3" t="inlineStr">
         <is>
@@ -2706,7 +2706,7 @@
       </c>
       <c r="Y19" s="3" t="inlineStr">
         <is>
-          <t>hellenic_alibra_dry_tc_series.csv (6,563 rows)</t>
+          <t>hellenic_alibra_dry_tc_series.csv (6,587 rows)</t>
         </is>
       </c>
       <c r="Z19" s="3" t="inlineStr">
@@ -2783,7 +2783,7 @@
         <v>0</v>
       </c>
       <c r="N20" s="2" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="O20" s="2" t="n">
         <v>0</v>
@@ -2988,32 +2988,32 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="I22" s="2" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="J22" s="4" t="inlineStr">
         <is>
-          <t>CURRENT (7d)</t>
+          <t>CURRENT (0d)</t>
         </is>
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="M22" s="2" t="n">
         <v>0</v>
       </c>
       <c r="N22" s="2" t="n">
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="O22" s="2" t="n">
         <v>0</v>
@@ -3025,19 +3025,19 @@
         <v>0</v>
       </c>
       <c r="R22" s="2" t="n">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="S22" s="2" t="n">
-        <v>760</v>
+        <v>761</v>
       </c>
       <c r="T22" s="2" t="n">
         <v>0</v>
       </c>
       <c r="U22" s="2" t="n">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="V22" s="2" t="n">
-        <v>1041</v>
+        <v>1043</v>
       </c>
       <c r="W22" s="3" t="inlineStr">
         <is>
@@ -3051,7 +3051,7 @@
       </c>
       <c r="Y22" s="3" t="inlineStr">
         <is>
-          <t>hellenic_alibra_tanker_tc_series.csv (7,476 rows)</t>
+          <t>hellenic_alibra_tanker_tc_series.csv (7,504 rows)</t>
         </is>
       </c>
       <c r="Z22" s="3" t="inlineStr">
@@ -5512,7 +5512,7 @@
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>6,563 rows</t>
+          <t>6,587 rows</t>
         </is>
       </c>
       <c r="H19" s="3" t="inlineStr">
@@ -5559,7 +5559,7 @@
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>7,476 rows</t>
+          <t>7,504 rows</t>
         </is>
       </c>
       <c r="H20" s="3" t="inlineStr">

--- a/data/extracted/series/corpus_publication_cadence_and_audit.xlsx
+++ b/data/extracted/series/corpus_publication_cadence_and_audit.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Corpus Cadence &amp; Inventory" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Graphic &amp; Chart Extraction" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sub-Sector &amp; Fleet Breakdown" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Corpus Cadence &amp; Inventory" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Graphic &amp; Chart Extraction" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Sub-Sector &amp; Fleet Breakdown" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1382,25 +1382,25 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="I8" s="2" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="J8" s="4" t="inlineStr">
         <is>
-          <t>CURRENT (6d)</t>
+          <t>CURRENT (0d)</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="M8" s="2" t="n">
@@ -1416,7 +1416,7 @@
         <v>0</v>
       </c>
       <c r="Q8" s="2" t="n">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="R8" s="2" t="n">
         <v>0</v>
@@ -1428,10 +1428,10 @@
         <v>0</v>
       </c>
       <c r="U8" s="2" t="n">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="V8" s="2" t="n">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="W8" s="3" t="inlineStr">
         <is>
@@ -1445,7 +1445,7 @@
       </c>
       <c r="Y8" s="3" t="inlineStr">
         <is>
-          <t>fearnleys_rates_series.csv (17,153 rows)</t>
+          <t>fearnleys_rates_series.csv (17,193 rows)</t>
         </is>
       </c>
       <c r="Z8" s="3" t="inlineStr">
@@ -2668,7 +2668,7 @@
         <v>0</v>
       </c>
       <c r="N19" s="2" t="n">
-        <v>0.4</v>
+        <v>0</v>
       </c>
       <c r="O19" s="2" t="n">
         <v>0</v>
@@ -2783,7 +2783,7 @@
         <v>0</v>
       </c>
       <c r="N20" s="2" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="O20" s="2" t="n">
         <v>0</v>
@@ -3013,7 +3013,7 @@
         <v>0</v>
       </c>
       <c r="N22" s="2" t="n">
-        <v>0.4</v>
+        <v>0</v>
       </c>
       <c r="O22" s="2" t="n">
         <v>0</v>

--- a/data/extracted/series/corpus_publication_cadence_and_audit.xlsx
+++ b/data/extracted/series/corpus_publication_cadence_and_audit.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Corpus Cadence &amp; Inventory" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Graphic &amp; Chart Extraction" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Sub-Sector &amp; Fleet Breakdown" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Corpus Cadence &amp; Inventory" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Graphic &amp; Chart Extraction" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sub-Sector &amp; Fleet Breakdown" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -565,7 +565,7 @@
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>Status (2026-10-21)</t>
+          <t>Status (2026-10-22)</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
@@ -696,11 +696,11 @@
         </is>
       </c>
       <c r="I2" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J2" s="4" t="inlineStr">
         <is>
-          <t>CURRENT (4d)</t>
+          <t>CURRENT (5d)</t>
         </is>
       </c>
       <c r="K2" s="2" t="inlineStr">
@@ -811,11 +811,11 @@
         </is>
       </c>
       <c r="I3" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J3" s="4" t="inlineStr">
         <is>
-          <t>CURRENT (4d)</t>
+          <t>CURRENT (5d)</t>
         </is>
       </c>
       <c r="K3" s="2" t="inlineStr">
@@ -926,11 +926,11 @@
         </is>
       </c>
       <c r="I4" s="2" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="J4" s="5" t="inlineStr">
         <is>
-          <t>DUE (13d, cadence weekly)</t>
+          <t>DUE (14d, cadence weekly)</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -1041,11 +1041,11 @@
         </is>
       </c>
       <c r="I5" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J5" s="4" t="inlineStr">
         <is>
-          <t>CURRENT (0d)</t>
+          <t>CURRENT (1d)</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -1156,11 +1156,11 @@
         </is>
       </c>
       <c r="I6" s="2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J6" s="4" t="inlineStr">
         <is>
-          <t>CURRENT (9d)</t>
+          <t>CURRENT (10d)</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -1271,7 +1271,7 @@
         </is>
       </c>
       <c r="I7" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J7" s="6" t="inlineStr">
         <is>
@@ -1501,11 +1501,11 @@
         </is>
       </c>
       <c r="I9" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J9" s="4" t="inlineStr">
         <is>
-          <t>CURRENT (0d)</t>
+          <t>CURRENT (1d)</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr"/>
@@ -1539,7 +1539,7 @@
         <v>4773</v>
       </c>
       <c r="U9" s="2" t="n">
-        <v>4778</v>
+        <v>4783</v>
       </c>
       <c r="V9" s="2" t="n">
         <v>4773</v>
@@ -1612,11 +1612,11 @@
         </is>
       </c>
       <c r="I10" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="J10" s="4" t="inlineStr">
         <is>
-          <t>CURRENT (7d)</t>
+          <t>CURRENT (8d)</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1727,11 +1727,11 @@
         </is>
       </c>
       <c r="I11" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J11" s="4" t="inlineStr">
         <is>
-          <t>CURRENT (5d)</t>
+          <t>CURRENT (6d)</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -1842,11 +1842,11 @@
         </is>
       </c>
       <c r="I12" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J12" s="4" t="inlineStr">
         <is>
-          <t>CURRENT (0d)</t>
+          <t>CURRENT (1d)</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1957,11 +1957,11 @@
         </is>
       </c>
       <c r="I13" s="2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J13" s="4" t="inlineStr">
         <is>
-          <t>CURRENT (9d)</t>
+          <t>CURRENT (10d)</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
@@ -2072,11 +2072,11 @@
         </is>
       </c>
       <c r="I14" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J14" s="4" t="inlineStr">
         <is>
-          <t>CURRENT (5d)</t>
+          <t>CURRENT (6d)</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2187,11 +2187,11 @@
         </is>
       </c>
       <c r="I15" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J15" s="4" t="inlineStr">
         <is>
-          <t>CURRENT (2d)</t>
+          <t>CURRENT (3d)</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
@@ -2302,11 +2302,11 @@
         </is>
       </c>
       <c r="I16" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J16" s="4" t="inlineStr">
         <is>
-          <t>CURRENT (2d)</t>
+          <t>CURRENT (3d)</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -2417,11 +2417,11 @@
         </is>
       </c>
       <c r="I17" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J17" s="4" t="inlineStr">
         <is>
-          <t>CURRENT (2d)</t>
+          <t>CURRENT (3d)</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -2532,11 +2532,11 @@
         </is>
       </c>
       <c r="I18" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J18" s="4" t="inlineStr">
         <is>
-          <t>CURRENT (1d)</t>
+          <t>CURRENT (2d)</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
@@ -2647,11 +2647,11 @@
         </is>
       </c>
       <c r="I19" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J19" s="4" t="inlineStr">
         <is>
-          <t>CURRENT (0d)</t>
+          <t>CURRENT (1d)</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
@@ -2762,11 +2762,11 @@
         </is>
       </c>
       <c r="I20" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J20" s="4" t="inlineStr">
         <is>
-          <t>CURRENT (0d)</t>
+          <t>CURRENT (1d)</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -2992,11 +2992,11 @@
         </is>
       </c>
       <c r="I22" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J22" s="4" t="inlineStr">
         <is>
-          <t>CURRENT (0d)</t>
+          <t>CURRENT (1d)</t>
         </is>
       </c>
       <c r="K22" s="2" t="inlineStr">
@@ -3107,11 +3107,11 @@
         </is>
       </c>
       <c r="I23" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J23" s="4" t="inlineStr">
         <is>
-          <t>CURRENT (1d)</t>
+          <t>CURRENT (2d)</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
@@ -3222,11 +3222,11 @@
         </is>
       </c>
       <c r="I24" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J24" s="4" t="inlineStr">
         <is>
-          <t>CURRENT (0d)</t>
+          <t>CURRENT (1d)</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
@@ -3337,11 +3337,11 @@
         </is>
       </c>
       <c r="I25" s="2" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="J25" s="5" t="inlineStr">
         <is>
-          <t>DUE (12d, cadence weekly)</t>
+          <t>DUE (13d, cadence weekly)</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
@@ -3452,11 +3452,11 @@
         </is>
       </c>
       <c r="I26" s="2" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="J26" s="5" t="inlineStr">
         <is>
-          <t>DUE (50d, cadence monthly)</t>
+          <t>DUE (51d, cadence monthly)</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
@@ -3567,11 +3567,11 @@
         </is>
       </c>
       <c r="I27" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J27" s="4" t="inlineStr">
         <is>
-          <t>CURRENT (8d)</t>
+          <t>CURRENT (9d)</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr"/>
@@ -3678,11 +3678,11 @@
         </is>
       </c>
       <c r="I28" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J28" s="4" t="inlineStr">
         <is>
-          <t>CURRENT (6d)</t>
+          <t>CURRENT (7d)</t>
         </is>
       </c>
       <c r="K28" s="2" t="inlineStr"/>
@@ -3789,11 +3789,11 @@
         </is>
       </c>
       <c r="I29" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J29" s="4" t="inlineStr">
         <is>
-          <t>CURRENT (5d)</t>
+          <t>CURRENT (6d)</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
@@ -3904,11 +3904,11 @@
         </is>
       </c>
       <c r="I30" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J30" s="4" t="inlineStr">
         <is>
-          <t>CURRENT (5d)</t>
+          <t>CURRENT (6d)</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
@@ -4019,11 +4019,11 @@
         </is>
       </c>
       <c r="I31" s="2" t="n">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="J31" s="5" t="inlineStr">
         <is>
-          <t>DUE (85d, cadence monthly)</t>
+          <t>DUE (86d, cadence monthly)</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
@@ -4130,11 +4130,11 @@
         </is>
       </c>
       <c r="I32" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J32" s="4" t="inlineStr">
         <is>
-          <t>CURRENT (5d)</t>
+          <t>CURRENT (6d)</t>
         </is>
       </c>
       <c r="K32" s="2" t="inlineStr">

--- a/data/extracted/series/corpus_publication_cadence_and_audit.xlsx
+++ b/data/extracted/series/corpus_publication_cadence_and_audit.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Corpus Cadence &amp; Inventory" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Graphic &amp; Chart Extraction" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Sub-Sector &amp; Fleet Breakdown" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Corpus Cadence &amp; Inventory" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Graphic &amp; Chart Extraction" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sub-Sector &amp; Fleet Breakdown" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1608,25 +1608,25 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="I10" s="2" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="J10" s="4" t="inlineStr">
         <is>
-          <t>CURRENT (8d)</t>
+          <t>CURRENT (0d)</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="M10" s="2" t="n">
@@ -1642,22 +1642,22 @@
         <v>0</v>
       </c>
       <c r="Q10" s="2" t="n">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="R10" s="2" t="n">
         <v>0</v>
       </c>
       <c r="S10" s="2" t="n">
-        <v>2858</v>
+        <v>2869</v>
       </c>
       <c r="T10" s="2" t="n">
+        <v>187</v>
+      </c>
+      <c r="U10" s="2" t="n">
         <v>186</v>
       </c>
-      <c r="U10" s="2" t="n">
-        <v>185</v>
-      </c>
       <c r="V10" s="2" t="n">
-        <v>3228</v>
+        <v>3241</v>
       </c>
       <c r="W10" s="3" t="inlineStr">
         <is>

--- a/data/extracted/series/corpus_publication_cadence_and_audit.xlsx
+++ b/data/extracted/series/corpus_publication_cadence_and_audit.xlsx
@@ -2758,32 +2758,32 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="I20" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J20" s="4" t="inlineStr">
         <is>
-          <t>CURRENT (1d)</t>
+          <t>CURRENT (0d)</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="M20" s="2" t="n">
         <v>0</v>
       </c>
       <c r="N20" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O20" s="2" t="n">
         <v>0</v>
@@ -2792,7 +2792,7 @@
         <v>0</v>
       </c>
       <c r="Q20" s="2" t="n">
-        <v>3547</v>
+        <v>3549</v>
       </c>
       <c r="R20" s="2" t="n">
         <v>0</v>
@@ -2804,10 +2804,10 @@
         <v>0</v>
       </c>
       <c r="U20" s="2" t="n">
-        <v>1193</v>
+        <v>1194</v>
       </c>
       <c r="V20" s="2" t="n">
-        <v>3547</v>
+        <v>3549</v>
       </c>
       <c r="W20" s="3" t="inlineStr">
         <is>
@@ -3218,25 +3218,25 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="I24" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J24" s="4" t="inlineStr">
         <is>
-          <t>CURRENT (1d)</t>
+          <t>CURRENT (0d)</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="M24" s="2" t="n">
@@ -3255,19 +3255,19 @@
         <v>307</v>
       </c>
       <c r="R24" s="2" t="n">
-        <v>3260</v>
+        <v>3262</v>
       </c>
       <c r="S24" s="2" t="n">
-        <v>15129</v>
+        <v>15132</v>
       </c>
       <c r="T24" s="2" t="n">
-        <v>3231</v>
+        <v>3233</v>
       </c>
       <c r="U24" s="2" t="n">
-        <v>3524</v>
+        <v>3526</v>
       </c>
       <c r="V24" s="2" t="n">
-        <v>21927</v>
+        <v>21934</v>
       </c>
       <c r="W24" s="3" t="inlineStr">
         <is>
@@ -3281,7 +3281,7 @@
       </c>
       <c r="Y24" s="3" t="inlineStr">
         <is>
-          <t>breakwave_fundamentals_series.csv (2,769 rows), breakwave_insights_metadata.csv (3,231 rows)</t>
+          <t>breakwave_fundamentals_series.csv (2,769 rows), breakwave_insights_metadata.csv (3,233 rows)</t>
         </is>
       </c>
       <c r="Z24" s="3" t="inlineStr">

--- a/data/extracted/series/corpus_publication_cadence_and_audit.xlsx
+++ b/data/extracted/series/corpus_publication_cadence_and_audit.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Corpus Cadence &amp; Inventory" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Graphic &amp; Chart Extraction" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sub-Sector &amp; Fleet Breakdown" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Corpus Cadence &amp; Inventory" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Graphic &amp; Chart Extraction" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Sub-Sector &amp; Fleet Breakdown" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -2783,7 +2783,7 @@
         <v>0</v>
       </c>
       <c r="N20" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O20" s="2" t="n">
         <v>0</v>

--- a/data/extracted/series/corpus_publication_cadence_and_audit.xlsx
+++ b/data/extracted/series/corpus_publication_cadence_and_audit.xlsx
@@ -565,7 +565,7 @@
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>Status (2026-10-22)</t>
+          <t>Status (2026-10-23)</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
@@ -696,11 +696,11 @@
         </is>
       </c>
       <c r="I2" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J2" s="4" t="inlineStr">
         <is>
-          <t>CURRENT (5d)</t>
+          <t>CURRENT (6d)</t>
         </is>
       </c>
       <c r="K2" s="2" t="inlineStr">
@@ -811,11 +811,11 @@
         </is>
       </c>
       <c r="I3" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J3" s="4" t="inlineStr">
         <is>
-          <t>CURRENT (5d)</t>
+          <t>CURRENT (6d)</t>
         </is>
       </c>
       <c r="K3" s="2" t="inlineStr">
@@ -926,11 +926,11 @@
         </is>
       </c>
       <c r="I4" s="2" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="J4" s="5" t="inlineStr">
         <is>
-          <t>DUE (14d, cadence weekly)</t>
+          <t>DUE (15d, cadence weekly)</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -1041,11 +1041,11 @@
         </is>
       </c>
       <c r="I5" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J5" s="4" t="inlineStr">
         <is>
-          <t>CURRENT (1d)</t>
+          <t>CURRENT (2d)</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -1156,11 +1156,11 @@
         </is>
       </c>
       <c r="I6" s="2" t="n">
-        <v>10</v>
-      </c>
-      <c r="J6" s="4" t="inlineStr">
-        <is>
-          <t>CURRENT (10d)</t>
+        <v>11</v>
+      </c>
+      <c r="J6" s="5" t="inlineStr">
+        <is>
+          <t>DUE (11d, cadence weekly)</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -1271,7 +1271,7 @@
         </is>
       </c>
       <c r="I7" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J7" s="6" t="inlineStr">
         <is>
@@ -1386,11 +1386,11 @@
         </is>
       </c>
       <c r="I8" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J8" s="4" t="inlineStr">
         <is>
-          <t>CURRENT (0d)</t>
+          <t>CURRENT (1d)</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -1501,11 +1501,11 @@
         </is>
       </c>
       <c r="I9" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J9" s="4" t="inlineStr">
         <is>
-          <t>CURRENT (1d)</t>
+          <t>CURRENT (2d)</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr"/>
@@ -1612,11 +1612,11 @@
         </is>
       </c>
       <c r="I10" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J10" s="4" t="inlineStr">
         <is>
-          <t>CURRENT (0d)</t>
+          <t>CURRENT (1d)</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1727,11 +1727,11 @@
         </is>
       </c>
       <c r="I11" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J11" s="4" t="inlineStr">
         <is>
-          <t>CURRENT (6d)</t>
+          <t>CURRENT (7d)</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -1842,11 +1842,11 @@
         </is>
       </c>
       <c r="I12" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J12" s="4" t="inlineStr">
         <is>
-          <t>CURRENT (1d)</t>
+          <t>CURRENT (2d)</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1957,11 +1957,11 @@
         </is>
       </c>
       <c r="I13" s="2" t="n">
-        <v>10</v>
-      </c>
-      <c r="J13" s="4" t="inlineStr">
-        <is>
-          <t>CURRENT (10d)</t>
+        <v>11</v>
+      </c>
+      <c r="J13" s="5" t="inlineStr">
+        <is>
+          <t>DUE (11d, cadence weekly)</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
@@ -2072,11 +2072,11 @@
         </is>
       </c>
       <c r="I14" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J14" s="4" t="inlineStr">
         <is>
-          <t>CURRENT (6d)</t>
+          <t>CURRENT (7d)</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2187,11 +2187,11 @@
         </is>
       </c>
       <c r="I15" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J15" s="4" t="inlineStr">
         <is>
-          <t>CURRENT (3d)</t>
+          <t>CURRENT (4d)</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
@@ -2302,11 +2302,11 @@
         </is>
       </c>
       <c r="I16" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J16" s="4" t="inlineStr">
         <is>
-          <t>CURRENT (3d)</t>
+          <t>CURRENT (4d)</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -2417,11 +2417,11 @@
         </is>
       </c>
       <c r="I17" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J17" s="4" t="inlineStr">
         <is>
-          <t>CURRENT (3d)</t>
+          <t>CURRENT (4d)</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -2532,11 +2532,11 @@
         </is>
       </c>
       <c r="I18" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J18" s="4" t="inlineStr">
         <is>
-          <t>CURRENT (2d)</t>
+          <t>CURRENT (3d)</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
@@ -2647,11 +2647,11 @@
         </is>
       </c>
       <c r="I19" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J19" s="4" t="inlineStr">
         <is>
-          <t>CURRENT (1d)</t>
+          <t>CURRENT (2d)</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
@@ -2762,11 +2762,11 @@
         </is>
       </c>
       <c r="I20" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J20" s="4" t="inlineStr">
         <is>
-          <t>CURRENT (0d)</t>
+          <t>CURRENT (1d)</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -2992,11 +2992,11 @@
         </is>
       </c>
       <c r="I22" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J22" s="4" t="inlineStr">
         <is>
-          <t>CURRENT (1d)</t>
+          <t>CURRENT (2d)</t>
         </is>
       </c>
       <c r="K22" s="2" t="inlineStr">
@@ -3107,11 +3107,11 @@
         </is>
       </c>
       <c r="I23" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J23" s="4" t="inlineStr">
         <is>
-          <t>CURRENT (2d)</t>
+          <t>CURRENT (3d)</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
@@ -3222,11 +3222,11 @@
         </is>
       </c>
       <c r="I24" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J24" s="4" t="inlineStr">
         <is>
-          <t>CURRENT (0d)</t>
+          <t>CURRENT (1d)</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
@@ -3337,11 +3337,11 @@
         </is>
       </c>
       <c r="I25" s="2" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="J25" s="5" t="inlineStr">
         <is>
-          <t>DUE (13d, cadence weekly)</t>
+          <t>DUE (14d, cadence weekly)</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
@@ -3452,11 +3452,11 @@
         </is>
       </c>
       <c r="I26" s="2" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="J26" s="5" t="inlineStr">
         <is>
-          <t>DUE (51d, cadence monthly)</t>
+          <t>DUE (52d, cadence monthly)</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
@@ -3567,11 +3567,11 @@
         </is>
       </c>
       <c r="I27" s="2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J27" s="4" t="inlineStr">
         <is>
-          <t>CURRENT (9d)</t>
+          <t>CURRENT (10d)</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr"/>
@@ -3678,11 +3678,11 @@
         </is>
       </c>
       <c r="I28" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="J28" s="4" t="inlineStr">
         <is>
-          <t>CURRENT (7d)</t>
+          <t>CURRENT (8d)</t>
         </is>
       </c>
       <c r="K28" s="2" t="inlineStr"/>
@@ -3789,11 +3789,11 @@
         </is>
       </c>
       <c r="I29" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J29" s="4" t="inlineStr">
         <is>
-          <t>CURRENT (6d)</t>
+          <t>CURRENT (7d)</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
@@ -3904,11 +3904,11 @@
         </is>
       </c>
       <c r="I30" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J30" s="4" t="inlineStr">
         <is>
-          <t>CURRENT (6d)</t>
+          <t>CURRENT (7d)</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
@@ -4019,11 +4019,11 @@
         </is>
       </c>
       <c r="I31" s="2" t="n">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="J31" s="5" t="inlineStr">
         <is>
-          <t>DUE (86d, cadence monthly)</t>
+          <t>DUE (87d, cadence monthly)</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
@@ -4130,11 +4130,11 @@
         </is>
       </c>
       <c r="I32" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J32" s="4" t="inlineStr">
         <is>
-          <t>CURRENT (6d)</t>
+          <t>CURRENT (7d)</t>
         </is>
       </c>
       <c r="K32" s="2" t="inlineStr">

--- a/data/extracted/series/corpus_publication_cadence_and_audit.xlsx
+++ b/data/extracted/series/corpus_publication_cadence_and_audit.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Corpus Cadence &amp; Inventory" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Graphic &amp; Chart Extraction" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Sub-Sector &amp; Fleet Breakdown" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Corpus Cadence &amp; Inventory" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Graphic &amp; Chart Extraction" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sub-Sector &amp; Fleet Breakdown" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -2758,32 +2758,32 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="I20" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J20" s="4" t="inlineStr">
         <is>
-          <t>CURRENT (1d)</t>
+          <t>CURRENT (0d)</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="M20" s="2" t="n">
         <v>0</v>
       </c>
       <c r="N20" s="2" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="O20" s="2" t="n">
         <v>0</v>
@@ -2792,7 +2792,7 @@
         <v>0</v>
       </c>
       <c r="Q20" s="2" t="n">
-        <v>3549</v>
+        <v>3551</v>
       </c>
       <c r="R20" s="2" t="n">
         <v>0</v>
@@ -2804,10 +2804,10 @@
         <v>0</v>
       </c>
       <c r="U20" s="2" t="n">
-        <v>1194</v>
+        <v>1195</v>
       </c>
       <c r="V20" s="2" t="n">
-        <v>3549</v>
+        <v>3551</v>
       </c>
       <c r="W20" s="3" t="inlineStr">
         <is>
@@ -3140,7 +3140,7 @@
         <v>0</v>
       </c>
       <c r="R23" s="2" t="n">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="S23" s="2" t="n">
         <v>733</v>
@@ -3152,7 +3152,7 @@
         <v>258</v>
       </c>
       <c r="V23" s="2" t="n">
-        <v>1010</v>
+        <v>1011</v>
       </c>
       <c r="W23" s="3" t="inlineStr">
         <is>
@@ -3218,25 +3218,25 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="I24" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J24" s="4" t="inlineStr">
         <is>
-          <t>CURRENT (1d)</t>
+          <t>CURRENT (0d)</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="M24" s="2" t="n">
@@ -3255,19 +3255,19 @@
         <v>307</v>
       </c>
       <c r="R24" s="2" t="n">
-        <v>3262</v>
+        <v>3264</v>
       </c>
       <c r="S24" s="2" t="n">
-        <v>15132</v>
+        <v>15135</v>
       </c>
       <c r="T24" s="2" t="n">
-        <v>3233</v>
+        <v>3235</v>
       </c>
       <c r="U24" s="2" t="n">
-        <v>3526</v>
+        <v>3528</v>
       </c>
       <c r="V24" s="2" t="n">
-        <v>21934</v>
+        <v>21941</v>
       </c>
       <c r="W24" s="3" t="inlineStr">
         <is>
@@ -3281,7 +3281,7 @@
       </c>
       <c r="Y24" s="3" t="inlineStr">
         <is>
-          <t>breakwave_fundamentals_series.csv (2,769 rows), breakwave_insights_metadata.csv (3,233 rows)</t>
+          <t>breakwave_fundamentals_series.csv (2,769 rows), breakwave_insights_metadata.csv (3,235 rows)</t>
         </is>
       </c>
       <c r="Z24" s="3" t="inlineStr">
@@ -3900,32 +3900,32 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="I30" s="2" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="J30" s="4" t="inlineStr">
         <is>
-          <t>CURRENT (7d)</t>
+          <t>CURRENT (0d)</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="M30" s="2" t="n">
         <v>0</v>
       </c>
       <c r="N30" s="2" t="n">
-        <v>24.5</v>
+        <v>24.6</v>
       </c>
       <c r="O30" s="2" t="n">
         <v>0</v>
@@ -3937,19 +3937,19 @@
         <v>0</v>
       </c>
       <c r="R30" s="2" t="n">
-        <v>3059</v>
+        <v>3060</v>
       </c>
       <c r="S30" s="2" t="n">
         <v>0</v>
       </c>
       <c r="T30" s="2" t="n">
-        <v>2239</v>
+        <v>2240</v>
       </c>
       <c r="U30" s="2" t="n">
-        <v>2239</v>
+        <v>2240</v>
       </c>
       <c r="V30" s="2" t="n">
-        <v>5298</v>
+        <v>5300</v>
       </c>
       <c r="W30" s="3" t="inlineStr">
         <is>
@@ -3963,7 +3963,7 @@
       </c>
       <c r="Y30" s="3" t="inlineStr">
         <is>
-          <t>baltic_reports_metadata.csv (2,239 rows), baltic_ncfi_series.csv (2,053 rows)</t>
+          <t>baltic_reports_metadata.csv (2,240 rows), baltic_ncfi_series.csv (2,057 rows)</t>
         </is>
       </c>
       <c r="Z30" s="3" t="inlineStr">

--- a/data/extracted/series/corpus_publication_cadence_and_audit.xlsx
+++ b/data/extracted/series/corpus_publication_cadence_and_audit.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Corpus Cadence &amp; Inventory" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Graphic &amp; Chart Extraction" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sub-Sector &amp; Fleet Breakdown" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Corpus Cadence &amp; Inventory" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Graphic &amp; Chart Extraction" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Sub-Sector &amp; Fleet Breakdown" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -2783,7 +2783,7 @@
         <v>0</v>
       </c>
       <c r="N20" s="2" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="O20" s="2" t="n">
         <v>0</v>
@@ -3333,25 +3333,25 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="I25" s="2" t="n">
-        <v>14</v>
-      </c>
-      <c r="J25" s="5" t="inlineStr">
-        <is>
-          <t>DUE (14d, cadence weekly)</t>
+        <v>7</v>
+      </c>
+      <c r="J25" s="4" t="inlineStr">
+        <is>
+          <t>CURRENT (7d)</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="M25" s="2" t="n">
@@ -3367,7 +3367,7 @@
         <v>0</v>
       </c>
       <c r="Q25" s="2" t="n">
-        <v>1095</v>
+        <v>1096</v>
       </c>
       <c r="R25" s="2" t="n">
         <v>0</v>
@@ -3376,13 +3376,13 @@
         <v>0</v>
       </c>
       <c r="T25" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="U25" s="2" t="n">
-        <v>1091</v>
+        <v>1092</v>
       </c>
       <c r="V25" s="2" t="n">
-        <v>1100</v>
+        <v>1102</v>
       </c>
       <c r="W25" s="3" t="inlineStr">
         <is>
@@ -3396,7 +3396,7 @@
       </c>
       <c r="Y25" s="3" t="inlineStr">
         <is>
-          <t>poten_opinions_metadata.csv (1,095 rows), poten_top_charterers_series.csv (776 rows), poten_fixtures_series.csv (100 rows)</t>
+          <t>poten_opinions_metadata.csv (1,096 rows), poten_top_charterers_series.csv (776 rows), poten_fixtures_series.csv (100 rows)</t>
         </is>
       </c>
       <c r="Z25" s="3" t="inlineStr">
@@ -3563,21 +3563,21 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="I27" s="2" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="J27" s="4" t="inlineStr">
         <is>
-          <t>CURRENT (10d)</t>
+          <t>CURRENT (2d)</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr"/>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="M27" s="2" t="n">
@@ -3593,7 +3593,7 @@
         <v>0</v>
       </c>
       <c r="Q27" s="2" t="n">
-        <v>294</v>
+        <v>297</v>
       </c>
       <c r="R27" s="2" t="n">
         <v>0</v>
@@ -3605,10 +3605,10 @@
         <v>0</v>
       </c>
       <c r="U27" s="2" t="n">
-        <v>294</v>
+        <v>297</v>
       </c>
       <c r="V27" s="2" t="n">
-        <v>295</v>
+        <v>298</v>
       </c>
       <c r="W27" s="3" t="inlineStr">
         <is>
@@ -3622,7 +3622,7 @@
       </c>
       <c r="Y27" s="3" t="inlineStr">
         <is>
-          <t>drewry_ais_chart_series.csv (83,090 rows)</t>
+          <t>drewry_ais_chart_series.csv (83,396 rows)</t>
         </is>
       </c>
       <c r="Z27" s="3" t="inlineStr">
@@ -3674,21 +3674,21 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="I28" s="2" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="J28" s="4" t="inlineStr">
         <is>
-          <t>CURRENT (8d)</t>
+          <t>CURRENT (1d)</t>
         </is>
       </c>
       <c r="K28" s="2" t="inlineStr"/>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="M28" s="2" t="n">
@@ -3713,13 +3713,13 @@
         <v>0</v>
       </c>
       <c r="T28" s="2" t="n">
-        <v>1096</v>
+        <v>1099</v>
       </c>
       <c r="U28" s="2" t="n">
-        <v>555</v>
+        <v>558</v>
       </c>
       <c r="V28" s="2" t="n">
-        <v>1102</v>
+        <v>1105</v>
       </c>
       <c r="W28" s="3" t="inlineStr">
         <is>
@@ -3733,7 +3733,7 @@
       </c>
       <c r="Y28" s="3" t="inlineStr">
         <is>
-          <t>drewry_wci_historical.csv (138 rows), drewry_opinions_metadata.csv (555 rows), drewry_wci_series.csv (8 rows)</t>
+          <t>drewry_wci_historical.csv (139 rows), drewry_opinions_metadata.csv (558 rows), drewry_wci_series.csv (9 rows)</t>
         </is>
       </c>
       <c r="Z28" s="3" t="inlineStr">
@@ -4713,7 +4713,7 @@
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>83,090 rows</t>
+          <t>83,396 rows</t>
         </is>
       </c>
       <c r="H2" s="3" t="inlineStr">
@@ -4760,7 +4760,7 @@
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>83,090 rows</t>
+          <t>83,396 rows</t>
         </is>
       </c>
       <c r="H3" s="3" t="inlineStr">
@@ -4807,7 +4807,7 @@
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>83,090 rows</t>
+          <t>83,396 rows</t>
         </is>
       </c>
       <c r="H4" s="3" t="inlineStr">
@@ -4854,7 +4854,7 @@
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>83,090 rows</t>
+          <t>83,396 rows</t>
         </is>
       </c>
       <c r="H5" s="3" t="inlineStr">
@@ -4901,7 +4901,7 @@
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>83,090 rows</t>
+          <t>83,396 rows</t>
         </is>
       </c>
       <c r="H6" s="3" t="inlineStr">
@@ -4948,7 +4948,7 @@
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>83,090 rows</t>
+          <t>83,396 rows</t>
         </is>
       </c>
       <c r="H7" s="3" t="inlineStr">
@@ -4995,7 +4995,7 @@
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>83,090 rows</t>
+          <t>83,396 rows</t>
         </is>
       </c>
       <c r="H8" s="3" t="inlineStr">
@@ -5042,7 +5042,7 @@
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>83,090 rows</t>
+          <t>83,396 rows</t>
         </is>
       </c>
       <c r="H9" s="3" t="inlineStr">
@@ -5089,7 +5089,7 @@
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>83,090 rows</t>
+          <t>83,396 rows</t>
         </is>
       </c>
       <c r="H10" s="3" t="inlineStr">
@@ -5136,7 +5136,7 @@
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>83,090 rows</t>
+          <t>83,396 rows</t>
         </is>
       </c>
       <c r="H11" s="3" t="inlineStr">
@@ -5183,7 +5183,7 @@
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>83,090 rows</t>
+          <t>83,396 rows</t>
         </is>
       </c>
       <c r="H12" s="3" t="inlineStr">
@@ -5230,7 +5230,7 @@
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>83,090 rows</t>
+          <t>83,396 rows</t>
         </is>
       </c>
       <c r="H13" s="3" t="inlineStr">
@@ -5277,7 +5277,7 @@
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>83,090 rows</t>
+          <t>83,396 rows</t>
         </is>
       </c>
       <c r="H14" s="3" t="inlineStr">
@@ -6311,7 +6311,7 @@
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>138 rows</t>
+          <t>139 rows</t>
         </is>
       </c>
       <c r="H36" s="3" t="inlineStr">

--- a/data/extracted/series/corpus_publication_cadence_and_audit.xlsx
+++ b/data/extracted/series/corpus_publication_cadence_and_audit.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Corpus Cadence &amp; Inventory" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Graphic &amp; Chart Extraction" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Sub-Sector &amp; Fleet Breakdown" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Corpus Cadence &amp; Inventory" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Graphic &amp; Chart Extraction" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sub-Sector &amp; Fleet Breakdown" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -2783,7 +2783,7 @@
         <v>0</v>
       </c>
       <c r="N20" s="2" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="O20" s="2" t="n">
         <v>0</v>
@@ -3333,25 +3333,25 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="I25" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="J25" s="4" t="inlineStr">
-        <is>
-          <t>CURRENT (7d)</t>
+        <v>14</v>
+      </c>
+      <c r="J25" s="5" t="inlineStr">
+        <is>
+          <t>DUE (14d, cadence weekly)</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="M25" s="2" t="n">
@@ -3367,7 +3367,7 @@
         <v>0</v>
       </c>
       <c r="Q25" s="2" t="n">
-        <v>1096</v>
+        <v>1095</v>
       </c>
       <c r="R25" s="2" t="n">
         <v>0</v>
@@ -3376,13 +3376,13 @@
         <v>0</v>
       </c>
       <c r="T25" s="2" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="U25" s="2" t="n">
-        <v>1092</v>
+        <v>1091</v>
       </c>
       <c r="V25" s="2" t="n">
-        <v>1102</v>
+        <v>1100</v>
       </c>
       <c r="W25" s="3" t="inlineStr">
         <is>
@@ -3396,7 +3396,7 @@
       </c>
       <c r="Y25" s="3" t="inlineStr">
         <is>
-          <t>poten_opinions_metadata.csv (1,096 rows), poten_top_charterers_series.csv (776 rows), poten_fixtures_series.csv (100 rows)</t>
+          <t>poten_opinions_metadata.csv (1,095 rows), poten_top_charterers_series.csv (776 rows), poten_fixtures_series.csv (100 rows)</t>
         </is>
       </c>
       <c r="Z25" s="3" t="inlineStr">
@@ -3563,21 +3563,21 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="I27" s="2" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="J27" s="4" t="inlineStr">
         <is>
-          <t>CURRENT (2d)</t>
+          <t>CURRENT (10d)</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr"/>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="M27" s="2" t="n">
@@ -3593,7 +3593,7 @@
         <v>0</v>
       </c>
       <c r="Q27" s="2" t="n">
-        <v>297</v>
+        <v>294</v>
       </c>
       <c r="R27" s="2" t="n">
         <v>0</v>
@@ -3605,10 +3605,10 @@
         <v>0</v>
       </c>
       <c r="U27" s="2" t="n">
-        <v>297</v>
+        <v>294</v>
       </c>
       <c r="V27" s="2" t="n">
-        <v>298</v>
+        <v>295</v>
       </c>
       <c r="W27" s="3" t="inlineStr">
         <is>
@@ -3622,7 +3622,7 @@
       </c>
       <c r="Y27" s="3" t="inlineStr">
         <is>
-          <t>drewry_ais_chart_series.csv (83,396 rows)</t>
+          <t>drewry_ais_chart_series.csv (83,090 rows)</t>
         </is>
       </c>
       <c r="Z27" s="3" t="inlineStr">
@@ -3674,21 +3674,21 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="I28" s="2" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="J28" s="4" t="inlineStr">
         <is>
-          <t>CURRENT (1d)</t>
+          <t>CURRENT (8d)</t>
         </is>
       </c>
       <c r="K28" s="2" t="inlineStr"/>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="M28" s="2" t="n">
@@ -3713,13 +3713,13 @@
         <v>0</v>
       </c>
       <c r="T28" s="2" t="n">
-        <v>1099</v>
+        <v>1096</v>
       </c>
       <c r="U28" s="2" t="n">
-        <v>558</v>
+        <v>555</v>
       </c>
       <c r="V28" s="2" t="n">
-        <v>1105</v>
+        <v>1102</v>
       </c>
       <c r="W28" s="3" t="inlineStr">
         <is>
@@ -3733,7 +3733,7 @@
       </c>
       <c r="Y28" s="3" t="inlineStr">
         <is>
-          <t>drewry_wci_historical.csv (139 rows), drewry_opinions_metadata.csv (558 rows), drewry_wci_series.csv (9 rows)</t>
+          <t>drewry_wci_historical.csv (138 rows), drewry_opinions_metadata.csv (555 rows), drewry_wci_series.csv (8 rows)</t>
         </is>
       </c>
       <c r="Z28" s="3" t="inlineStr">
@@ -3925,7 +3925,7 @@
         <v>0</v>
       </c>
       <c r="N30" s="2" t="n">
-        <v>24.6</v>
+        <v>24.5</v>
       </c>
       <c r="O30" s="2" t="n">
         <v>0</v>
@@ -3937,19 +3937,19 @@
         <v>0</v>
       </c>
       <c r="R30" s="2" t="n">
-        <v>3060</v>
+        <v>3064</v>
       </c>
       <c r="S30" s="2" t="n">
         <v>0</v>
       </c>
       <c r="T30" s="2" t="n">
-        <v>2240</v>
+        <v>2244</v>
       </c>
       <c r="U30" s="2" t="n">
-        <v>2240</v>
+        <v>2244</v>
       </c>
       <c r="V30" s="2" t="n">
-        <v>5300</v>
+        <v>5308</v>
       </c>
       <c r="W30" s="3" t="inlineStr">
         <is>
@@ -3963,7 +3963,7 @@
       </c>
       <c r="Y30" s="3" t="inlineStr">
         <is>
-          <t>baltic_reports_metadata.csv (2,240 rows), baltic_ncfi_series.csv (2,057 rows)</t>
+          <t>baltic_reports_metadata.csv (2,244 rows), baltic_ncfi_series.csv (2,057 rows)</t>
         </is>
       </c>
       <c r="Z30" s="3" t="inlineStr">
@@ -4713,7 +4713,7 @@
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>83,396 rows</t>
+          <t>83,090 rows</t>
         </is>
       </c>
       <c r="H2" s="3" t="inlineStr">
@@ -4760,7 +4760,7 @@
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>83,396 rows</t>
+          <t>83,090 rows</t>
         </is>
       </c>
       <c r="H3" s="3" t="inlineStr">
@@ -4807,7 +4807,7 @@
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>83,396 rows</t>
+          <t>83,090 rows</t>
         </is>
       </c>
       <c r="H4" s="3" t="inlineStr">
@@ -4854,7 +4854,7 @@
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>83,396 rows</t>
+          <t>83,090 rows</t>
         </is>
       </c>
       <c r="H5" s="3" t="inlineStr">
@@ -4901,7 +4901,7 @@
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>83,396 rows</t>
+          <t>83,090 rows</t>
         </is>
       </c>
       <c r="H6" s="3" t="inlineStr">
@@ -4948,7 +4948,7 @@
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>83,396 rows</t>
+          <t>83,090 rows</t>
         </is>
       </c>
       <c r="H7" s="3" t="inlineStr">
@@ -4995,7 +4995,7 @@
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>83,396 rows</t>
+          <t>83,090 rows</t>
         </is>
       </c>
       <c r="H8" s="3" t="inlineStr">
@@ -5042,7 +5042,7 @@
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>83,396 rows</t>
+          <t>83,090 rows</t>
         </is>
       </c>
       <c r="H9" s="3" t="inlineStr">
@@ -5089,7 +5089,7 @@
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>83,396 rows</t>
+          <t>83,090 rows</t>
         </is>
       </c>
       <c r="H10" s="3" t="inlineStr">
@@ -5136,7 +5136,7 @@
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>83,396 rows</t>
+          <t>83,090 rows</t>
         </is>
       </c>
       <c r="H11" s="3" t="inlineStr">
@@ -5183,7 +5183,7 @@
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>83,396 rows</t>
+          <t>83,090 rows</t>
         </is>
       </c>
       <c r="H12" s="3" t="inlineStr">
@@ -5230,7 +5230,7 @@
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>83,396 rows</t>
+          <t>83,090 rows</t>
         </is>
       </c>
       <c r="H13" s="3" t="inlineStr">
@@ -5277,7 +5277,7 @@
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>83,396 rows</t>
+          <t>83,090 rows</t>
         </is>
       </c>
       <c r="H14" s="3" t="inlineStr">
@@ -6311,7 +6311,7 @@
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>139 rows</t>
+          <t>138 rows</t>
         </is>
       </c>
       <c r="H36" s="3" t="inlineStr">

--- a/data/extracted/series/corpus_publication_cadence_and_audit.xlsx
+++ b/data/extracted/series/corpus_publication_cadence_and_audit.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Corpus Cadence &amp; Inventory" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Graphic &amp; Chart Extraction" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sub-Sector &amp; Fleet Breakdown" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Corpus Cadence &amp; Inventory" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Graphic &amp; Chart Extraction" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Sub-Sector &amp; Fleet Breakdown" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1723,25 +1723,25 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="I11" s="2" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="J11" s="4" t="inlineStr">
         <is>
-          <t>CURRENT (7d)</t>
+          <t>CURRENT (0d)</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="M11" s="2" t="n">
@@ -1760,7 +1760,7 @@
         <v>109</v>
       </c>
       <c r="R11" s="2" t="n">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="S11" s="2" t="n">
         <v>0</v>
@@ -1769,10 +1769,10 @@
         <v>0</v>
       </c>
       <c r="U11" s="2" t="n">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="V11" s="2" t="n">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="W11" s="3" t="inlineStr">
         <is>
@@ -1786,7 +1786,7 @@
       </c>
       <c r="Y11" s="3" t="inlineStr">
         <is>
-          <t>gibson_tanker_spot_series.csv (3,612 rows), gibson_bunker_prices_series.csv (1,032 rows), gibson_master_tanker_series.xlsx</t>
+          <t>gibson_tanker_spot_series.csv (3,626 rows), gibson_bunker_prices_series.csv (1,036 rows), gibson_master_tanker_series.xlsx</t>
         </is>
       </c>
       <c r="Z11" s="3" t="inlineStr">
@@ -2783,7 +2783,7 @@
         <v>0</v>
       </c>
       <c r="N20" s="2" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="O20" s="2" t="n">
         <v>0</v>
@@ -3333,25 +3333,25 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="I25" s="2" t="n">
-        <v>14</v>
-      </c>
-      <c r="J25" s="5" t="inlineStr">
-        <is>
-          <t>DUE (14d, cadence weekly)</t>
+        <v>7</v>
+      </c>
+      <c r="J25" s="4" t="inlineStr">
+        <is>
+          <t>CURRENT (7d)</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="M25" s="2" t="n">
@@ -3367,7 +3367,7 @@
         <v>0</v>
       </c>
       <c r="Q25" s="2" t="n">
-        <v>1095</v>
+        <v>1096</v>
       </c>
       <c r="R25" s="2" t="n">
         <v>0</v>
@@ -3376,13 +3376,13 @@
         <v>0</v>
       </c>
       <c r="T25" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="U25" s="2" t="n">
-        <v>1091</v>
+        <v>1092</v>
       </c>
       <c r="V25" s="2" t="n">
-        <v>1100</v>
+        <v>1102</v>
       </c>
       <c r="W25" s="3" t="inlineStr">
         <is>
@@ -3396,7 +3396,7 @@
       </c>
       <c r="Y25" s="3" t="inlineStr">
         <is>
-          <t>poten_opinions_metadata.csv (1,095 rows), poten_top_charterers_series.csv (776 rows), poten_fixtures_series.csv (100 rows)</t>
+          <t>poten_opinions_metadata.csv (1,096 rows), poten_top_charterers_series.csv (776 rows), poten_fixtures_series.csv (100 rows)</t>
         </is>
       </c>
       <c r="Z25" s="3" t="inlineStr">
@@ -3563,21 +3563,21 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="I27" s="2" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="J27" s="4" t="inlineStr">
         <is>
-          <t>CURRENT (10d)</t>
+          <t>CURRENT (2d)</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr"/>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="M27" s="2" t="n">
@@ -3593,7 +3593,7 @@
         <v>0</v>
       </c>
       <c r="Q27" s="2" t="n">
-        <v>294</v>
+        <v>297</v>
       </c>
       <c r="R27" s="2" t="n">
         <v>0</v>
@@ -3605,10 +3605,10 @@
         <v>0</v>
       </c>
       <c r="U27" s="2" t="n">
-        <v>294</v>
+        <v>297</v>
       </c>
       <c r="V27" s="2" t="n">
-        <v>295</v>
+        <v>298</v>
       </c>
       <c r="W27" s="3" t="inlineStr">
         <is>
@@ -3622,7 +3622,7 @@
       </c>
       <c r="Y27" s="3" t="inlineStr">
         <is>
-          <t>drewry_ais_chart_series.csv (83,090 rows)</t>
+          <t>drewry_ais_chart_series.csv (83,396 rows)</t>
         </is>
       </c>
       <c r="Z27" s="3" t="inlineStr">
@@ -3674,21 +3674,21 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="I28" s="2" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="J28" s="4" t="inlineStr">
         <is>
-          <t>CURRENT (8d)</t>
+          <t>CURRENT (1d)</t>
         </is>
       </c>
       <c r="K28" s="2" t="inlineStr"/>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="M28" s="2" t="n">
@@ -3713,13 +3713,13 @@
         <v>0</v>
       </c>
       <c r="T28" s="2" t="n">
-        <v>1096</v>
+        <v>1099</v>
       </c>
       <c r="U28" s="2" t="n">
-        <v>555</v>
+        <v>558</v>
       </c>
       <c r="V28" s="2" t="n">
-        <v>1102</v>
+        <v>1105</v>
       </c>
       <c r="W28" s="3" t="inlineStr">
         <is>
@@ -3733,7 +3733,7 @@
       </c>
       <c r="Y28" s="3" t="inlineStr">
         <is>
-          <t>drewry_wci_historical.csv (138 rows), drewry_opinions_metadata.csv (555 rows), drewry_wci_series.csv (8 rows)</t>
+          <t>drewry_wci_historical.csv (139 rows), drewry_opinions_metadata.csv (558 rows), drewry_wci_series.csv (9 rows)</t>
         </is>
       </c>
       <c r="Z28" s="3" t="inlineStr">
@@ -4713,7 +4713,7 @@
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>83,090 rows</t>
+          <t>83,396 rows</t>
         </is>
       </c>
       <c r="H2" s="3" t="inlineStr">
@@ -4760,7 +4760,7 @@
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>83,090 rows</t>
+          <t>83,396 rows</t>
         </is>
       </c>
       <c r="H3" s="3" t="inlineStr">
@@ -4807,7 +4807,7 @@
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>83,090 rows</t>
+          <t>83,396 rows</t>
         </is>
       </c>
       <c r="H4" s="3" t="inlineStr">
@@ -4854,7 +4854,7 @@
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>83,090 rows</t>
+          <t>83,396 rows</t>
         </is>
       </c>
       <c r="H5" s="3" t="inlineStr">
@@ -4901,7 +4901,7 @@
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>83,090 rows</t>
+          <t>83,396 rows</t>
         </is>
       </c>
       <c r="H6" s="3" t="inlineStr">
@@ -4948,7 +4948,7 @@
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>83,090 rows</t>
+          <t>83,396 rows</t>
         </is>
       </c>
       <c r="H7" s="3" t="inlineStr">
@@ -4995,7 +4995,7 @@
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>83,090 rows</t>
+          <t>83,396 rows</t>
         </is>
       </c>
       <c r="H8" s="3" t="inlineStr">
@@ -5042,7 +5042,7 @@
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>83,090 rows</t>
+          <t>83,396 rows</t>
         </is>
       </c>
       <c r="H9" s="3" t="inlineStr">
@@ -5089,7 +5089,7 @@
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>83,090 rows</t>
+          <t>83,396 rows</t>
         </is>
       </c>
       <c r="H10" s="3" t="inlineStr">
@@ -5136,7 +5136,7 @@
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>83,090 rows</t>
+          <t>83,396 rows</t>
         </is>
       </c>
       <c r="H11" s="3" t="inlineStr">
@@ -5183,7 +5183,7 @@
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>83,090 rows</t>
+          <t>83,396 rows</t>
         </is>
       </c>
       <c r="H12" s="3" t="inlineStr">
@@ -5230,7 +5230,7 @@
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>83,090 rows</t>
+          <t>83,396 rows</t>
         </is>
       </c>
       <c r="H13" s="3" t="inlineStr">
@@ -5277,7 +5277,7 @@
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>83,090 rows</t>
+          <t>83,396 rows</t>
         </is>
       </c>
       <c r="H14" s="3" t="inlineStr">
@@ -6311,7 +6311,7 @@
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>138 rows</t>
+          <t>139 rows</t>
         </is>
       </c>
       <c r="H36" s="3" t="inlineStr">

--- a/data/extracted/series/corpus_publication_cadence_and_audit.xlsx
+++ b/data/extracted/series/corpus_publication_cadence_and_audit.xlsx
@@ -3785,15 +3785,15 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="I29" s="2" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="J29" s="4" t="inlineStr">
         <is>
-          <t>CURRENT (7d)</t>
+          <t>CURRENT (0d)</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
@@ -3803,7 +3803,7 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="M29" s="2" t="n">
@@ -3822,19 +3822,19 @@
         <v>10</v>
       </c>
       <c r="R29" s="2" t="n">
-        <v>521</v>
+        <v>523</v>
       </c>
       <c r="S29" s="2" t="n">
-        <v>1564</v>
+        <v>1570</v>
       </c>
       <c r="T29" s="2" t="n">
-        <v>456</v>
+        <v>458</v>
       </c>
       <c r="U29" s="2" t="n">
-        <v>452</v>
+        <v>454</v>
       </c>
       <c r="V29" s="2" t="n">
-        <v>2977</v>
+        <v>2987</v>
       </c>
       <c r="W29" s="3" t="inlineStr">
         <is>
@@ -3848,7 +3848,7 @@
       </c>
       <c r="Y29" s="3" t="inlineStr">
         <is>
-          <t>signal_reports_metadata.csv (452 rows), signal_vessel_counts_series.csv (120 rows), data/views/signal/live_fleet_positions.json (9,082 tracked hulls), data/views/signal/port_queues_active.json (1,932 ports)</t>
+          <t>signal_reports_metadata.csv (454 rows), signal_vessel_counts_series.csv (120 rows), data/views/signal/live_fleet_positions.json (9,082 tracked hulls), data/views/signal/port_queues_active.json (1,932 ports)</t>
         </is>
       </c>
       <c r="Z29" s="3" t="inlineStr">
@@ -6076,7 +6076,7 @@
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>452 rows</t>
+          <t>454 rows</t>
         </is>
       </c>
       <c r="H31" s="3" t="inlineStr">

--- a/data/extracted/series/corpus_publication_cadence_and_audit.xlsx
+++ b/data/extracted/series/corpus_publication_cadence_and_audit.xlsx
@@ -565,7 +565,7 @@
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>Status (2026-10-23)</t>
+          <t>Status (2026-10-24)</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
@@ -696,11 +696,11 @@
         </is>
       </c>
       <c r="I2" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J2" s="4" t="inlineStr">
         <is>
-          <t>CURRENT (6d)</t>
+          <t>CURRENT (7d)</t>
         </is>
       </c>
       <c r="K2" s="2" t="inlineStr">
@@ -807,25 +807,25 @@
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="I3" s="2" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="J3" s="4" t="inlineStr">
         <is>
-          <t>CURRENT (6d)</t>
+          <t>CURRENT (0d)</t>
         </is>
       </c>
       <c r="K3" s="2" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="L3" s="2" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="M3" s="2" t="n">
@@ -841,7 +841,7 @@
         <v>0</v>
       </c>
       <c r="Q3" s="2" t="n">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="R3" s="2" t="n">
         <v>0</v>
@@ -853,10 +853,10 @@
         <v>0</v>
       </c>
       <c r="U3" s="2" t="n">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="V3" s="2" t="n">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="W3" s="3" t="inlineStr">
         <is>
@@ -870,7 +870,7 @@
       </c>
       <c r="Y3" s="3" t="inlineStr">
         <is>
-          <t>affinity_tce_series.csv (4,077 rows), affinity_bda_series.csv (750 rows), affinity_indices_series.csv (496 rows)</t>
+          <t>affinity_tce_series.csv (4,096 rows), affinity_bda_series.csv (753 rows), affinity_indices_series.csv (496 rows)</t>
         </is>
       </c>
       <c r="Z3" s="3" t="inlineStr">
@@ -922,25 +922,25 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="I4" s="2" t="n">
-        <v>15</v>
-      </c>
-      <c r="J4" s="5" t="inlineStr">
-        <is>
-          <t>DUE (15d, cadence weekly)</t>
+        <v>1</v>
+      </c>
+      <c r="J4" s="4" t="inlineStr">
+        <is>
+          <t>CURRENT (1d)</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="M4" s="2" t="n">
@@ -956,7 +956,7 @@
         <v>0</v>
       </c>
       <c r="Q4" s="2" t="n">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="R4" s="2" t="n">
         <v>0</v>
@@ -968,10 +968,10 @@
         <v>0</v>
       </c>
       <c r="U4" s="2" t="n">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="V4" s="2" t="n">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="W4" s="3" t="inlineStr">
         <is>
@@ -1041,11 +1041,11 @@
         </is>
       </c>
       <c r="I5" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J5" s="4" t="inlineStr">
         <is>
-          <t>CURRENT (2d)</t>
+          <t>CURRENT (3d)</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -1156,11 +1156,11 @@
         </is>
       </c>
       <c r="I6" s="2" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="J6" s="5" t="inlineStr">
         <is>
-          <t>DUE (11d, cadence weekly)</t>
+          <t>DUE (12d, cadence weekly)</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -1267,20 +1267,20 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="I7" s="2" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="J7" s="6" t="inlineStr">
         <is>
-          <t>PARSE BEHIND (latest MD 7d older than latest issue)</t>
+          <t>PARSE BEHIND (1 recent issue(s) without MD)</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
@@ -1289,7 +1289,7 @@
         </is>
       </c>
       <c r="M7" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N7" s="2" t="n">
         <v>100</v>
@@ -1301,7 +1301,7 @@
         <v>0</v>
       </c>
       <c r="Q7" s="2" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="R7" s="2" t="n">
         <v>0</v>
@@ -1316,7 +1316,7 @@
         <v>10</v>
       </c>
       <c r="V7" s="2" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="W7" s="3" t="inlineStr">
         <is>
@@ -1386,11 +1386,11 @@
         </is>
       </c>
       <c r="I8" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J8" s="4" t="inlineStr">
         <is>
-          <t>CURRENT (1d)</t>
+          <t>CURRENT (2d)</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -1501,11 +1501,11 @@
         </is>
       </c>
       <c r="I9" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J9" s="4" t="inlineStr">
         <is>
-          <t>CURRENT (2d)</t>
+          <t>CURRENT (3d)</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr"/>
@@ -1612,11 +1612,11 @@
         </is>
       </c>
       <c r="I10" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J10" s="4" t="inlineStr">
         <is>
-          <t>CURRENT (1d)</t>
+          <t>CURRENT (2d)</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1727,11 +1727,11 @@
         </is>
       </c>
       <c r="I11" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J11" s="4" t="inlineStr">
         <is>
-          <t>CURRENT (0d)</t>
+          <t>CURRENT (1d)</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -1842,11 +1842,11 @@
         </is>
       </c>
       <c r="I12" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J12" s="4" t="inlineStr">
         <is>
-          <t>CURRENT (2d)</t>
+          <t>CURRENT (3d)</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1957,11 +1957,11 @@
         </is>
       </c>
       <c r="I13" s="2" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="J13" s="5" t="inlineStr">
         <is>
-          <t>DUE (11d, cadence weekly)</t>
+          <t>DUE (12d, cadence weekly)</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
@@ -2068,25 +2068,25 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="I14" s="2" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="J14" s="4" t="inlineStr">
         <is>
-          <t>CURRENT (7d)</t>
+          <t>CURRENT (1d)</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="M14" s="2" t="n">
@@ -2102,7 +2102,7 @@
         <v>0</v>
       </c>
       <c r="Q14" s="2" t="n">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="R14" s="2" t="n">
         <v>0</v>
@@ -2114,10 +2114,10 @@
         <v>0</v>
       </c>
       <c r="U14" s="2" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="V14" s="2" t="n">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="W14" s="3" t="inlineStr">
         <is>
@@ -2131,7 +2131,7 @@
       </c>
       <c r="Y14" s="3" t="inlineStr">
         <is>
-          <t>lion_deals_series.csv (1,342 rows), lion_sales_series.csv (1,232 rows), lion_demometer_series.csv (588 rows), lion_demolition_series.csv (516 rows), lion_demo_sales_series.csv (110 rows)</t>
+          <t>lion_deals_series.csv (1,369 rows), lion_sales_series.csv (1,255 rows), lion_demometer_series.csv (600 rows), lion_demolition_series.csv (516 rows), lion_demo_sales_series.csv (114 rows)</t>
         </is>
       </c>
       <c r="Z14" s="3" t="inlineStr">
@@ -2187,11 +2187,11 @@
         </is>
       </c>
       <c r="I15" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J15" s="4" t="inlineStr">
         <is>
-          <t>CURRENT (4d)</t>
+          <t>CURRENT (5d)</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
@@ -2302,11 +2302,11 @@
         </is>
       </c>
       <c r="I16" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J16" s="4" t="inlineStr">
         <is>
-          <t>CURRENT (4d)</t>
+          <t>CURRENT (5d)</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -2417,11 +2417,11 @@
         </is>
       </c>
       <c r="I17" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J17" s="4" t="inlineStr">
         <is>
-          <t>CURRENT (4d)</t>
+          <t>CURRENT (5d)</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -2532,11 +2532,11 @@
         </is>
       </c>
       <c r="I18" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J18" s="4" t="inlineStr">
         <is>
-          <t>CURRENT (3d)</t>
+          <t>CURRENT (4d)</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
@@ -2647,11 +2647,11 @@
         </is>
       </c>
       <c r="I19" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J19" s="4" t="inlineStr">
         <is>
-          <t>CURRENT (2d)</t>
+          <t>CURRENT (3d)</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
@@ -2762,11 +2762,11 @@
         </is>
       </c>
       <c r="I20" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J20" s="4" t="inlineStr">
         <is>
-          <t>CURRENT (0d)</t>
+          <t>CURRENT (1d)</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -2992,11 +2992,11 @@
         </is>
       </c>
       <c r="I22" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J22" s="4" t="inlineStr">
         <is>
-          <t>CURRENT (2d)</t>
+          <t>CURRENT (3d)</t>
         </is>
       </c>
       <c r="K22" s="2" t="inlineStr">
@@ -3107,11 +3107,11 @@
         </is>
       </c>
       <c r="I23" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J23" s="4" t="inlineStr">
         <is>
-          <t>CURRENT (3d)</t>
+          <t>CURRENT (4d)</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
@@ -3222,11 +3222,11 @@
         </is>
       </c>
       <c r="I24" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J24" s="4" t="inlineStr">
         <is>
-          <t>CURRENT (0d)</t>
+          <t>CURRENT (1d)</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
@@ -3337,11 +3337,11 @@
         </is>
       </c>
       <c r="I25" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="J25" s="4" t="inlineStr">
         <is>
-          <t>CURRENT (7d)</t>
+          <t>CURRENT (8d)</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
@@ -3452,11 +3452,11 @@
         </is>
       </c>
       <c r="I26" s="2" t="n">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="J26" s="5" t="inlineStr">
         <is>
-          <t>DUE (52d, cadence monthly)</t>
+          <t>DUE (53d, cadence monthly)</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
@@ -3567,11 +3567,11 @@
         </is>
       </c>
       <c r="I27" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J27" s="4" t="inlineStr">
         <is>
-          <t>CURRENT (2d)</t>
+          <t>CURRENT (3d)</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr"/>
@@ -3678,11 +3678,11 @@
         </is>
       </c>
       <c r="I28" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J28" s="4" t="inlineStr">
         <is>
-          <t>CURRENT (1d)</t>
+          <t>CURRENT (2d)</t>
         </is>
       </c>
       <c r="K28" s="2" t="inlineStr"/>
@@ -3789,11 +3789,11 @@
         </is>
       </c>
       <c r="I29" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J29" s="4" t="inlineStr">
         <is>
-          <t>CURRENT (0d)</t>
+          <t>CURRENT (1d)</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
@@ -3904,11 +3904,11 @@
         </is>
       </c>
       <c r="I30" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J30" s="4" t="inlineStr">
         <is>
-          <t>CURRENT (0d)</t>
+          <t>CURRENT (1d)</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
@@ -4019,11 +4019,11 @@
         </is>
       </c>
       <c r="I31" s="2" t="n">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="J31" s="5" t="inlineStr">
         <is>
-          <t>DUE (87d, cadence monthly)</t>
+          <t>DUE (88d, cadence monthly)</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
@@ -4130,11 +4130,11 @@
         </is>
       </c>
       <c r="I32" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="J32" s="4" t="inlineStr">
         <is>
-          <t>CURRENT (7d)</t>
+          <t>CURRENT (8d)</t>
         </is>
       </c>
       <c r="K32" s="2" t="inlineStr">

--- a/data/extracted/series/corpus_publication_cadence_and_audit.xlsx
+++ b/data/extracted/series/corpus_publication_cadence_and_audit.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Corpus Cadence &amp; Inventory" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Graphic &amp; Chart Extraction" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Sub-Sector &amp; Fleet Breakdown" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Corpus Cadence &amp; Inventory" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Graphic &amp; Chart Extraction" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sub-Sector &amp; Fleet Breakdown" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -38,7 +38,7 @@
       <sz val="10"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="5">
     <fill>
       <patternFill/>
     </fill>
@@ -61,12 +61,6 @@
       <patternFill patternType="solid">
         <fgColor rgb="00FFF2CC"/>
         <bgColor rgb="00FFF2CC"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00F8CBAD"/>
-        <bgColor rgb="00F8CBAD"/>
       </patternFill>
     </fill>
   </fills>
@@ -96,7 +90,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -111,9 +105,6 @@
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -565,7 +556,7 @@
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>Status (2026-10-24)</t>
+          <t>Status (2026-10-26)</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
@@ -696,11 +687,11 @@
         </is>
       </c>
       <c r="I2" s="2" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="J2" s="4" t="inlineStr">
         <is>
-          <t>CURRENT (7d)</t>
+          <t>CURRENT (9d)</t>
         </is>
       </c>
       <c r="K2" s="2" t="inlineStr">
@@ -811,11 +802,11 @@
         </is>
       </c>
       <c r="I3" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J3" s="4" t="inlineStr">
         <is>
-          <t>CURRENT (0d)</t>
+          <t>CURRENT (2d)</t>
         </is>
       </c>
       <c r="K3" s="2" t="inlineStr">
@@ -870,7 +861,7 @@
       </c>
       <c r="Y3" s="3" t="inlineStr">
         <is>
-          <t>affinity_tce_series.csv (4,096 rows), affinity_bda_series.csv (753 rows), affinity_indices_series.csv (496 rows)</t>
+          <t>affinity_tce_series.csv (4,096 rows), affinity_bda_series.csv (753 rows), affinity_indices_series.csv (502 rows)</t>
         </is>
       </c>
       <c r="Z3" s="3" t="inlineStr">
@@ -926,11 +917,11 @@
         </is>
       </c>
       <c r="I4" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J4" s="4" t="inlineStr">
         <is>
-          <t>CURRENT (1d)</t>
+          <t>CURRENT (3d)</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -985,7 +976,7 @@
       </c>
       <c r="Y4" s="3" t="inlineStr">
         <is>
-          <t>agora_indicators_series.csv (10,002 rows)</t>
+          <t>agora_indicators_series.csv (10,143 rows)</t>
         </is>
       </c>
       <c r="Z4" s="3" t="inlineStr">
@@ -1041,11 +1032,11 @@
         </is>
       </c>
       <c r="I5" s="2" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="J5" s="4" t="inlineStr">
         <is>
-          <t>CURRENT (3d)</t>
+          <t>CURRENT (5d)</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -1100,7 +1091,7 @@
       </c>
       <c r="Y5" s="3" t="inlineStr">
         <is>
-          <t>bancosta_freight_rates_series.csv (20,677 rows), bancosta_ffa_series.csv (7,762 rows), bancosta_sales_series.csv (3,261 rows), bancosta_commodities_series.csv (8,573 rows), bancosta_newbuilding_series.csv (2,377 rows), bancosta_secondhand_matrix_series.csv (1,898 rows), bancosta_demolition_series.csv (959 rows)</t>
+          <t>bancosta_freight_rates_series.csv (20,677 rows), bancosta_ffa_series.csv (7,762 rows), bancosta_sales_series.csv (3,261 rows), bancosta_commodities_series.csv (8,573 rows), bancosta_newbuilding_series.csv (2,544 rows), bancosta_secondhand_matrix_series.csv (1,945 rows), bancosta_demolition_series.csv (1,053 rows)</t>
         </is>
       </c>
       <c r="Z5" s="3" t="inlineStr">
@@ -1156,11 +1147,11 @@
         </is>
       </c>
       <c r="I6" s="2" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="J6" s="5" t="inlineStr">
         <is>
-          <t>DUE (12d, cadence weekly)</t>
+          <t>DUE (14d, cadence weekly)</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -1215,7 +1206,7 @@
       </c>
       <c r="Y6" s="3" t="inlineStr">
         <is>
-          <t>carriers_sales_series.csv (3,081 rows), carriers_dry_tc_period_series.csv (3,096 rows), carriers_indices_series.csv (1,806 rows), carriers_tanker_tce_series.csv (774 rows), carriers_bspa_series.csv (785 rows), carriers_newbuilding_series.csv (302 rows), carriers_demolition_series.csv (170 rows)</t>
+          <t>carriers_sales_series.csv (3,146 rows), carriers_dry_tc_period_series.csv (3,168 rows), carriers_indices_series.csv (1,848 rows), carriers_tanker_tce_series.csv (807 rows), carriers_bspa_series.csv (792 rows), carriers_newbuilding_series.csv (304 rows), carriers_demolition_series.csv (172 rows)</t>
         </is>
       </c>
       <c r="Z6" s="3" t="inlineStr">
@@ -1271,11 +1262,11 @@
         </is>
       </c>
       <c r="I7" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J7" s="6" t="inlineStr">
-        <is>
-          <t>PARSE BEHIND (1 recent issue(s) without MD)</t>
+        <v>3</v>
+      </c>
+      <c r="J7" s="4" t="inlineStr">
+        <is>
+          <t>CURRENT (3d)</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
@@ -1285,11 +1276,11 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="M7" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N7" s="2" t="n">
         <v>100</v>
@@ -1313,7 +1304,7 @@
         <v>0</v>
       </c>
       <c r="U7" s="2" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="V7" s="2" t="n">
         <v>16</v>
@@ -1330,7 +1321,7 @@
       </c>
       <c r="Y7" s="3" t="inlineStr">
         <is>
-          <t>clarksons_sales_series.csv (1,375 rows)</t>
+          <t>clarksons_sales_series.csv (1,388 rows)</t>
         </is>
       </c>
       <c r="Z7" s="3" t="inlineStr">
@@ -1386,11 +1377,11 @@
         </is>
       </c>
       <c r="I8" s="2" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="J8" s="4" t="inlineStr">
         <is>
-          <t>CURRENT (2d)</t>
+          <t>CURRENT (4d)</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -1497,7 +1488,7 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="I9" s="2" t="n">
@@ -1511,7 +1502,7 @@
       <c r="K9" s="2" t="inlineStr"/>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="M9" s="2" t="n">
@@ -1539,7 +1530,7 @@
         <v>4773</v>
       </c>
       <c r="U9" s="2" t="n">
-        <v>4783</v>
+        <v>4784</v>
       </c>
       <c r="V9" s="2" t="n">
         <v>4773</v>
@@ -1612,11 +1603,11 @@
         </is>
       </c>
       <c r="I10" s="2" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="J10" s="4" t="inlineStr">
         <is>
-          <t>CURRENT (2d)</t>
+          <t>CURRENT (4d)</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1727,11 +1718,11 @@
         </is>
       </c>
       <c r="I11" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J11" s="4" t="inlineStr">
         <is>
-          <t>CURRENT (1d)</t>
+          <t>CURRENT (3d)</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -1842,11 +1833,11 @@
         </is>
       </c>
       <c r="I12" s="2" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="J12" s="4" t="inlineStr">
         <is>
-          <t>CURRENT (3d)</t>
+          <t>CURRENT (5d)</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1901,7 +1892,7 @@
       </c>
       <c r="Y12" s="3" t="inlineStr">
         <is>
-          <t>intermodal_tc_rates_series.csv (5,273 rows), intermodal_newbuilding_series.csv (5,130 rows), intermodal_tanker_spot_series.csv (3,915 rows), intermodal_sales_series.csv (3,846 rows), intermodal_demolition_series.csv (2,637 rows)</t>
+          <t>intermodal_tc_rates_series.csv (5,293 rows), intermodal_newbuilding_series.csv (5,155 rows), intermodal_tanker_spot_series.csv (3,930 rows), intermodal_sales_series.csv (3,858 rows), intermodal_demolition_series.csv (2,647 rows)</t>
         </is>
       </c>
       <c r="Z12" s="3" t="inlineStr">
@@ -1957,11 +1948,11 @@
         </is>
       </c>
       <c r="I13" s="2" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="J13" s="5" t="inlineStr">
         <is>
-          <t>DUE (12d, cadence weekly)</t>
+          <t>DUE (14d, cadence weekly)</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
@@ -2072,11 +2063,11 @@
         </is>
       </c>
       <c r="I14" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J14" s="4" t="inlineStr">
         <is>
-          <t>CURRENT (1d)</t>
+          <t>CURRENT (3d)</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2131,7 +2122,7 @@
       </c>
       <c r="Y14" s="3" t="inlineStr">
         <is>
-          <t>lion_deals_series.csv (1,369 rows), lion_sales_series.csv (1,255 rows), lion_demometer_series.csv (600 rows), lion_demolition_series.csv (516 rows), lion_demo_sales_series.csv (114 rows)</t>
+          <t>lion_deals_series.csv (1,369 rows), lion_sales_series.csv (1,255 rows), lion_demometer_series.csv (600 rows), lion_demolition_series.csv (600 rows), lion_demo_sales_series.csv (114 rows)</t>
         </is>
       </c>
       <c r="Z14" s="3" t="inlineStr">
@@ -2187,11 +2178,11 @@
         </is>
       </c>
       <c r="I15" s="2" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="J15" s="4" t="inlineStr">
         <is>
-          <t>CURRENT (5d)</t>
+          <t>CURRENT (7d)</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
@@ -2302,11 +2293,11 @@
         </is>
       </c>
       <c r="I16" s="2" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="J16" s="4" t="inlineStr">
         <is>
-          <t>CURRENT (5d)</t>
+          <t>CURRENT (7d)</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -2361,7 +2352,7 @@
       </c>
       <c r="Y16" s="3" t="inlineStr">
         <is>
-          <t>star_asia_snp_sales_series.csv (3,696 rows), star_asia_deals_series.csv (3,548 rows), star_asia_valuation_matrix_series.csv (3,346 rows), star_asia_demolition_series.csv (3,168 rows), star_asia_metals_energy_series.csv (1,382 rows)</t>
+          <t>star_asia_snp_sales_series.csv (3,703 rows), star_asia_deals_series.csv (3,548 rows), star_asia_valuation_matrix_series.csv (3,346 rows), star_asia_demolition_series.csv (3,168 rows), star_asia_metals_energy_series.csv (1,382 rows)</t>
         </is>
       </c>
       <c r="Z16" s="3" t="inlineStr">
@@ -2417,11 +2408,11 @@
         </is>
       </c>
       <c r="I17" s="2" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="J17" s="4" t="inlineStr">
         <is>
-          <t>CURRENT (5d)</t>
+          <t>CURRENT (7d)</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -2532,11 +2523,11 @@
         </is>
       </c>
       <c r="I18" s="2" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="J18" s="4" t="inlineStr">
         <is>
-          <t>CURRENT (4d)</t>
+          <t>CURRENT (6d)</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
@@ -2647,11 +2638,11 @@
         </is>
       </c>
       <c r="I19" s="2" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="J19" s="4" t="inlineStr">
         <is>
-          <t>CURRENT (3d)</t>
+          <t>CURRENT (5d)</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
@@ -2762,11 +2753,11 @@
         </is>
       </c>
       <c r="I20" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J20" s="4" t="inlineStr">
         <is>
-          <t>CURRENT (1d)</t>
+          <t>CURRENT (3d)</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -2821,7 +2812,7 @@
       </c>
       <c r="Y20" s="3" t="inlineStr">
         <is>
-          <t>hellenic_iron_ore_pdf_brands_series.csv (31,527 rows)</t>
+          <t>hellenic_iron_ore_pdf_brands_series.csv (32,482 rows)</t>
         </is>
       </c>
       <c r="Z20" s="3" t="inlineStr">
@@ -2992,11 +2983,11 @@
         </is>
       </c>
       <c r="I22" s="2" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="J22" s="4" t="inlineStr">
         <is>
-          <t>CURRENT (3d)</t>
+          <t>CURRENT (5d)</t>
         </is>
       </c>
       <c r="K22" s="2" t="inlineStr">
@@ -3107,11 +3098,11 @@
         </is>
       </c>
       <c r="I23" s="2" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="J23" s="4" t="inlineStr">
         <is>
-          <t>CURRENT (4d)</t>
+          <t>CURRENT (6d)</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
@@ -3143,7 +3134,7 @@
         <v>278</v>
       </c>
       <c r="S23" s="2" t="n">
-        <v>733</v>
+        <v>736</v>
       </c>
       <c r="T23" s="2" t="n">
         <v>0</v>
@@ -3152,7 +3143,7 @@
         <v>258</v>
       </c>
       <c r="V23" s="2" t="n">
-        <v>1011</v>
+        <v>1014</v>
       </c>
       <c r="W23" s="3" t="inlineStr">
         <is>
@@ -3166,7 +3157,7 @@
       </c>
       <c r="Y23" s="3" t="inlineStr">
         <is>
-          <t>hellenic_vv_matrix_series.csv (12,373 rows), hellenic_vv_sales_series.csv (2,091 rows)</t>
+          <t>hellenic_vv_matrix_series.csv (19,946 rows), hellenic_vv_sales_series.csv (2,091 rows)</t>
         </is>
       </c>
       <c r="Z23" s="3" t="inlineStr">
@@ -3222,11 +3213,11 @@
         </is>
       </c>
       <c r="I24" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J24" s="4" t="inlineStr">
         <is>
-          <t>CURRENT (1d)</t>
+          <t>CURRENT (3d)</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
@@ -3337,11 +3328,11 @@
         </is>
       </c>
       <c r="I25" s="2" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="J25" s="4" t="inlineStr">
         <is>
-          <t>CURRENT (8d)</t>
+          <t>CURRENT (10d)</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
@@ -3452,11 +3443,11 @@
         </is>
       </c>
       <c r="I26" s="2" t="n">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="J26" s="5" t="inlineStr">
         <is>
-          <t>DUE (53d, cadence monthly)</t>
+          <t>DUE (55d, cadence monthly)</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
@@ -3511,7 +3502,7 @@
       </c>
       <c r="Y26" s="3" t="inlineStr">
         <is>
-          <t>seabrokers_osv_monthly_history_series.csv (6,376 rows), seabrokers_rigs_market_series.csv (4,482 rows), seabrokers_osv_utilisation_series.csv (2,328 rows), seabrokers_osv_spot_rates_series.csv (1,895 rows)</t>
+          <t>seabrokers_osv_monthly_history_series.csv (6,900 rows), seabrokers_rigs_market_series.csv (3,139 rows), seabrokers_osv_utilisation_series.csv (2,352 rows), seabrokers_osv_spot_rates_series.csv (1,920 rows)</t>
         </is>
       </c>
       <c r="Z26" s="3" t="inlineStr">
@@ -3567,11 +3558,11 @@
         </is>
       </c>
       <c r="I27" s="2" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="J27" s="4" t="inlineStr">
         <is>
-          <t>CURRENT (3d)</t>
+          <t>CURRENT (5d)</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr"/>
@@ -3678,11 +3669,11 @@
         </is>
       </c>
       <c r="I28" s="2" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="J28" s="4" t="inlineStr">
         <is>
-          <t>CURRENT (2d)</t>
+          <t>CURRENT (4d)</t>
         </is>
       </c>
       <c r="K28" s="2" t="inlineStr"/>
@@ -3789,11 +3780,11 @@
         </is>
       </c>
       <c r="I29" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J29" s="4" t="inlineStr">
         <is>
-          <t>CURRENT (1d)</t>
+          <t>CURRENT (3d)</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
@@ -3904,11 +3895,11 @@
         </is>
       </c>
       <c r="I30" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J30" s="4" t="inlineStr">
         <is>
-          <t>CURRENT (1d)</t>
+          <t>CURRENT (3d)</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
@@ -4019,11 +4010,11 @@
         </is>
       </c>
       <c r="I31" s="2" t="n">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="J31" s="5" t="inlineStr">
         <is>
-          <t>DUE (88d, cadence monthly)</t>
+          <t>DUE (90d, cadence monthly)</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
@@ -4126,25 +4117,25 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="I32" s="2" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="J32" s="4" t="inlineStr">
         <is>
-          <t>CURRENT (8d)</t>
+          <t>CURRENT (3d)</t>
         </is>
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="M32" s="2" t="n">
@@ -4169,13 +4160,13 @@
         <v>0</v>
       </c>
       <c r="T32" s="2" t="n">
-        <v>1333</v>
+        <v>1339</v>
       </c>
       <c r="U32" s="2" t="n">
-        <v>1333</v>
+        <v>1339</v>
       </c>
       <c r="V32" s="2" t="n">
-        <v>1333</v>
+        <v>1339</v>
       </c>
       <c r="W32" s="3" t="inlineStr">
         <is>
@@ -4332,34 +4323,34 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="7" t="inlineStr">
+      <c r="A1" s="6" t="inlineStr">
         <is>
           <t>Source Category</t>
         </is>
       </c>
-      <c r="B1" s="7" t="inlineStr">
+      <c r="B1" s="6" t="inlineStr">
         <is>
           <t>Images in Corpus</t>
         </is>
       </c>
-      <c r="C1" s="7" t="inlineStr">
+      <c r="C1" s="6" t="inlineStr">
         <is>
           <t>Graphic Formats</t>
         </is>
       </c>
-      <c r="D1" s="7" t="inlineStr">
+      <c r="D1" s="6" t="inlineStr">
         <is>
           <t>Extraction Pipeline Applied</t>
         </is>
       </c>
-      <c r="E1" s="7" t="inlineStr">
+      <c r="E1" s="6" t="inlineStr">
         <is>
           <t>Extracted Series Output</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="8" t="inlineStr">
+      <c r="A2" s="7" t="inlineStr">
         <is>
           <t>01-brokers/fearnleys-md</t>
         </is>
@@ -4367,24 +4358,24 @@
       <c r="B2" s="2" t="n">
         <v>2786</v>
       </c>
-      <c r="C2" s="8" t="inlineStr">
+      <c r="C2" s="7" t="inlineStr">
         <is>
           <t>Raster PNG charts (no embedded data), JPG</t>
         </is>
       </c>
-      <c r="D2" s="8" t="inlineStr">
+      <c r="D2" s="7" t="inlineStr">
         <is>
           <t>Not read; titles kept, printed tables transcribed and verified</t>
         </is>
       </c>
-      <c r="E2" s="8" t="inlineStr">
+      <c r="E2" s="7" t="inlineStr">
         <is>
           <t>Chart titles in MDs and .tables.json sidecars; calibrated series deleted</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="8" t="inlineStr">
+      <c r="A3" s="7" t="inlineStr">
         <is>
           <t>01-brokers/ism</t>
         </is>
@@ -4392,24 +4383,24 @@
       <c r="B3" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="C3" s="8" t="inlineStr">
+      <c r="C3" s="7" t="inlineStr">
         <is>
           <t>PDF vector drawing strokes</t>
         </is>
       </c>
-      <c r="D3" s="8" t="inlineStr">
+      <c r="D3" s="7" t="inlineStr">
         <is>
           <t>Least-squares dual-axis scale calibration &amp; tick filtering</t>
         </is>
       </c>
-      <c r="E3" s="8" t="inlineStr">
+      <c r="E3" s="7" t="inlineStr">
         <is>
           <t>ism_handy_freight_series.csv, ism_coaster_freight_series.csv</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="8" t="inlineStr">
+      <c r="A4" s="7" t="inlineStr">
         <is>
           <t>01-brokers/star_asia</t>
         </is>
@@ -4417,24 +4408,24 @@
       <c r="B4" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="C4" s="8" t="inlineStr">
+      <c r="C4" s="7" t="inlineStr">
         <is>
           <t>Image bar chart with printed data labels</t>
         </is>
       </c>
-      <c r="D4" s="8" t="inlineStr">
+      <c r="D4" s="7" t="inlineStr">
         <is>
           <t>Annual LDT sold at Alang / Chattogram / Pakistan (printed labels only)</t>
         </is>
       </c>
-      <c r="E4" s="8" t="inlineStr">
+      <c r="E4" s="7" t="inlineStr">
         <is>
           <t>star_asia_ldt_comparison_series.csv (1,320 rows)</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="8" t="inlineStr">
+      <c r="A5" s="7" t="inlineStr">
         <is>
           <t>02-hellenic/iron_ore</t>
         </is>
@@ -4442,24 +4433,24 @@
       <c r="B5" s="2" t="n">
         <v>3335</v>
       </c>
-      <c r="C5" s="8" t="inlineStr">
+      <c r="C5" s="7" t="inlineStr">
         <is>
           <t>JPG / PNG port inventory graphics</t>
         </is>
       </c>
-      <c r="D5" s="8" t="inlineStr">
+      <c r="D5" s="7" t="inlineStr">
         <is>
           <t>OCR &amp; spatial coordinate table extraction</t>
         </is>
       </c>
-      <c r="E5" s="8" t="inlineStr">
+      <c r="E5" s="7" t="inlineStr">
         <is>
           <t>hellenic_iron_ore_pdf_brands_series.csv (31,272 rows)</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="8" t="inlineStr">
+      <c r="A6" s="7" t="inlineStr">
         <is>
           <t>02-hellenic/demolition</t>
         </is>
@@ -4467,24 +4458,24 @@
       <c r="B6" s="2" t="n">
         <v>1208</v>
       </c>
-      <c r="C6" s="8" t="inlineStr">
+      <c r="C6" s="7" t="inlineStr">
         <is>
           <t>Cash buyer market insight graphics</t>
         </is>
       </c>
-      <c r="D6" s="8" t="inlineStr">
+      <c r="D6" s="7" t="inlineStr">
         <is>
           <t>HTML table extraction + OCR fallback</t>
         </is>
       </c>
-      <c r="E6" s="8" t="inlineStr">
+      <c r="E6" s="7" t="inlineStr">
         <is>
           <t>hellenic_gms_port_positions_series.csv (2,905 rows)</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="8" t="inlineStr">
+      <c r="A7" s="7" t="inlineStr">
         <is>
           <t>02-hellenic/dry_charter</t>
         </is>
@@ -4492,24 +4483,24 @@
       <c r="B7" s="2" t="n">
         <v>759</v>
       </c>
-      <c r="C7" s="8" t="inlineStr">
+      <c r="C7" s="7" t="inlineStr">
         <is>
           <t>Alibra Dry Bulk TC rate graphics</t>
         </is>
       </c>
-      <c r="D7" s="8" t="inlineStr">
+      <c r="D7" s="7" t="inlineStr">
         <is>
           <t>Graphic OCR &amp; tabular parameter parsing</t>
         </is>
       </c>
-      <c r="E7" s="8" t="inlineStr">
+      <c r="E7" s="7" t="inlineStr">
         <is>
           <t>hellenic_alibra_dry_tc_series.csv (6,467 rows)</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="8" t="inlineStr">
+      <c r="A8" s="7" t="inlineStr">
         <is>
           <t>02-hellenic/tanker_charter</t>
         </is>
@@ -4517,24 +4508,24 @@
       <c r="B8" s="2" t="n">
         <v>757</v>
       </c>
-      <c r="C8" s="8" t="inlineStr">
+      <c r="C8" s="7" t="inlineStr">
         <is>
           <t>Alibra Tanker TC rate graphics</t>
         </is>
       </c>
-      <c r="D8" s="8" t="inlineStr">
+      <c r="D8" s="7" t="inlineStr">
         <is>
           <t>Graphic OCR &amp; tabular parameter parsing</t>
         </is>
       </c>
-      <c r="E8" s="8" t="inlineStr">
+      <c r="E8" s="7" t="inlineStr">
         <is>
           <t>hellenic_alibra_tanker_tc_series.csv (7,191 rows)</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="8" t="inlineStr">
+      <c r="A9" s="7" t="inlineStr">
         <is>
           <t>02-hellenic/vessel_valuations</t>
         </is>
@@ -4542,24 +4533,24 @@
       <c r="B9" s="2" t="n">
         <v>726</v>
       </c>
-      <c r="C9" s="8" t="inlineStr">
+      <c r="C9" s="7" t="inlineStr">
         <is>
           <t>VesselsValue asset price charts</t>
         </is>
       </c>
-      <c r="D9" s="8" t="inlineStr">
+      <c r="D9" s="7" t="inlineStr">
         <is>
           <t>Asset valuation curve digitizer &amp; matrix builder</t>
         </is>
       </c>
-      <c r="E9" s="8" t="inlineStr">
+      <c r="E9" s="7" t="inlineStr">
         <is>
           <t>hellenic_vv_matrix_series.csv (12,340 rows)</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="8" t="inlineStr">
+      <c r="A10" s="7" t="inlineStr">
         <is>
           <t>03-breakwave</t>
         </is>
@@ -4567,24 +4558,24 @@
       <c r="B10" s="2" t="n">
         <v>15072</v>
       </c>
-      <c r="C10" s="8" t="inlineStr">
+      <c r="C10" s="7" t="inlineStr">
         <is>
           <t>Freight market fundamentals PNGs</t>
         </is>
       </c>
-      <c r="D10" s="8" t="inlineStr">
+      <c r="D10" s="7" t="inlineStr">
         <is>
           <t>BDRY/BWET index trajectory curves &amp; fundamental commentary</t>
         </is>
       </c>
-      <c r="E10" s="8" t="inlineStr">
+      <c r="E10" s="7" t="inlineStr">
         <is>
           <t>breakwave_fundamentals_series.csv (2,746 rows)</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="8" t="inlineStr">
+      <c r="A11" s="7" t="inlineStr">
         <is>
           <t>07-signal</t>
         </is>
@@ -4592,17 +4583,17 @@
       <c r="B11" s="2" t="n">
         <v>1885</v>
       </c>
-      <c r="C11" s="8" t="inlineStr">
+      <c r="C11" s="7" t="inlineStr">
         <is>
           <t>Flow heatmaps &amp; trade monitors</t>
         </is>
       </c>
-      <c r="D11" s="8" t="inlineStr">
+      <c r="D11" s="7" t="inlineStr">
         <is>
           <t>Live telemetry pipeline &amp; monitor digest parser</t>
         </is>
       </c>
-      <c r="E11" s="8" t="inlineStr">
+      <c r="E11" s="7" t="inlineStr">
         <is>
           <t>signal_reports_metadata.csv (446 rows)</t>
         </is>
@@ -5606,7 +5597,7 @@
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>31,527 rows</t>
+          <t>32,482 rows</t>
         </is>
       </c>
       <c r="H21" s="3" t="inlineStr">
@@ -5653,7 +5644,7 @@
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>1,175 rows</t>
+          <t>1,193 rows</t>
         </is>
       </c>
       <c r="H22" s="3" t="inlineStr">
@@ -5747,7 +5738,7 @@
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>12,373 rows</t>
+          <t>19,946 rows</t>
         </is>
       </c>
       <c r="H24" s="3" t="inlineStr">
@@ -6029,7 +6020,7 @@
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>6,376 rows</t>
+          <t>6,900 rows</t>
         </is>
       </c>
       <c r="H30" s="3" t="inlineStr">
@@ -6264,7 +6255,7 @@
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>3,846 rows</t>
+          <t>3,858 rows</t>
         </is>
       </c>
       <c r="H35" s="3" t="inlineStr">

--- a/data/extracted/series/corpus_publication_cadence_and_audit.xlsx
+++ b/data/extracted/series/corpus_publication_cadence_and_audit.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Corpus Cadence &amp; Inventory" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Graphic &amp; Chart Extraction" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sub-Sector &amp; Fleet Breakdown" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Corpus Cadence &amp; Inventory" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Graphic &amp; Chart Extraction" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Sub-Sector &amp; Fleet Breakdown" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -683,25 +683,25 @@
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="I2" s="2" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="J2" s="4" t="inlineStr">
         <is>
-          <t>CURRENT (9d)</t>
+          <t>CURRENT (2d)</t>
         </is>
       </c>
       <c r="K2" s="2" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="L2" s="2" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="M2" s="2" t="n">
@@ -717,7 +717,7 @@
         <v>0</v>
       </c>
       <c r="Q2" s="2" t="n">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="R2" s="2" t="n">
         <v>0</v>
@@ -729,10 +729,10 @@
         <v>0</v>
       </c>
       <c r="U2" s="2" t="n">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="V2" s="2" t="n">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="W2" s="3" t="inlineStr">
         <is>
@@ -746,7 +746,7 @@
       </c>
       <c r="Y2" s="3" t="inlineStr">
         <is>
-          <t>advanced_shipping_sales_series.csv (6,857 rows), advanced_shipping_demolition_series.csv (2,024 rows), advanced_shipping_secondhand_matrix_series.csv (8,157 rows), advanced_shipping_newbuilding_series.csv (1,922 rows), advanced_shipping_demo_sales_series.csv (606 rows)</t>
+          <t>advanced_shipping_sales_series.csv (6,877 rows), advanced_shipping_demolition_series.csv (2,032 rows), advanced_shipping_secondhand_matrix_series.csv (8,189 rows), advanced_shipping_newbuilding_series.csv (1,929 rows), advanced_shipping_demo_sales_series.csv (608 rows)</t>
         </is>
       </c>
       <c r="Z2" s="3" t="inlineStr">
@@ -2174,25 +2174,25 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="I15" s="2" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="J15" s="4" t="inlineStr">
         <is>
-          <t>CURRENT (7d)</t>
+          <t>CURRENT (0d)</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="M15" s="2" t="n">
@@ -2208,7 +2208,7 @@
         <v>0</v>
       </c>
       <c r="Q15" s="2" t="n">
-        <v>540</v>
+        <v>542</v>
       </c>
       <c r="R15" s="2" t="n">
         <v>0</v>
@@ -2220,10 +2220,10 @@
         <v>0</v>
       </c>
       <c r="U15" s="2" t="n">
-        <v>523</v>
+        <v>525</v>
       </c>
       <c r="V15" s="2" t="n">
-        <v>540</v>
+        <v>542</v>
       </c>
       <c r="W15" s="3" t="inlineStr">
         <is>
@@ -2237,7 +2237,7 @@
       </c>
       <c r="Y15" s="3" t="inlineStr">
         <is>
-          <t>ssy_capesize_index_series.csv (922 rows), ssy_route_rates_series.csv (5,230 rows), ssy_capesize_index_time_series.csv (523 rows)</t>
+          <t>ssy_capesize_index_series.csv (924 rows), ssy_route_rates_series.csv (5,250 rows), ssy_capesize_index_time_series.csv (525 rows)</t>
         </is>
       </c>
       <c r="Z15" s="3" t="inlineStr">
@@ -2289,25 +2289,25 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="I16" s="2" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="J16" s="4" t="inlineStr">
         <is>
-          <t>CURRENT (7d)</t>
+          <t>CURRENT (0d)</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="M16" s="2" t="n">
@@ -2323,7 +2323,7 @@
         <v>0</v>
       </c>
       <c r="Q16" s="2" t="n">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="R16" s="2" t="n">
         <v>0</v>
@@ -2335,10 +2335,10 @@
         <v>0</v>
       </c>
       <c r="U16" s="2" t="n">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="V16" s="2" t="n">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="W16" s="3" t="inlineStr">
         <is>
@@ -2352,7 +2352,7 @@
       </c>
       <c r="Y16" s="3" t="inlineStr">
         <is>
-          <t>star_asia_snp_sales_series.csv (3,703 rows), star_asia_deals_series.csv (3,548 rows), star_asia_valuation_matrix_series.csv (3,346 rows), star_asia_demolition_series.csv (3,168 rows), star_asia_metals_energy_series.csv (1,382 rows)</t>
+          <t>star_asia_snp_sales_series.csv (3,719 rows), star_asia_deals_series.csv (3,575 rows), star_asia_valuation_matrix_series.csv (3,359 rows), star_asia_demolition_series.csv (3,184 rows), star_asia_metals_energy_series.csv (1,391 rows)</t>
         </is>
       </c>
       <c r="Z16" s="3" t="inlineStr">
@@ -6161,7 +6161,7 @@
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>6,857 rows</t>
+          <t>6,877 rows</t>
         </is>
       </c>
       <c r="H33" s="3" t="inlineStr">

--- a/data/extracted/series/corpus_publication_cadence_and_audit.xlsx
+++ b/data/extracted/series/corpus_publication_cadence_and_audit.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Corpus Cadence &amp; Inventory" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Graphic &amp; Chart Extraction" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Sub-Sector &amp; Fleet Breakdown" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Corpus Cadence &amp; Inventory" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Graphic &amp; Chart Extraction" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sub-Sector &amp; Fleet Breakdown" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -2519,32 +2519,32 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="I18" s="2" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="J18" s="4" t="inlineStr">
         <is>
-          <t>CURRENT (6d)</t>
+          <t>CURRENT (2d)</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="M18" s="2" t="n">
         <v>0</v>
       </c>
       <c r="N18" s="2" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="O18" s="2" t="n">
         <v>0</v>
@@ -2553,22 +2553,22 @@
         <v>0</v>
       </c>
       <c r="Q18" s="2" t="n">
-        <v>1949</v>
+        <v>1953</v>
       </c>
       <c r="R18" s="2" t="n">
-        <v>816</v>
+        <v>818</v>
       </c>
       <c r="S18" s="2" t="n">
-        <v>1213</v>
+        <v>1214</v>
       </c>
       <c r="T18" s="2" t="n">
         <v>0</v>
       </c>
       <c r="U18" s="2" t="n">
-        <v>755</v>
+        <v>756</v>
       </c>
       <c r="V18" s="2" t="n">
-        <v>3978</v>
+        <v>3985</v>
       </c>
       <c r="W18" s="3" t="inlineStr">
         <is>
@@ -2582,7 +2582,7 @@
       </c>
       <c r="Y18" s="3" t="inlineStr">
         <is>
-          <t>athenian_indicative_demolition_series.csv (3,076 rows), hellenic_gms_port_positions_series.csv (3,029 rows), hellenic_gms_demolition_series.csv (1,108 rows), hellenic_best_oasis_deals_series.csv (905 rows), hellenic_best_oasis_demolition_series.csv (866 rows)</t>
+          <t>athenian_indicative_demolition_series.csv (3,076 rows), hellenic_gms_port_positions_series.csv (3,041 rows), hellenic_gms_demolition_series.csv (1,112 rows), hellenic_best_oasis_deals_series.csv (905 rows), hellenic_best_oasis_demolition_series.csv (866 rows)</t>
         </is>
       </c>
       <c r="Z18" s="3" t="inlineStr">
@@ -2749,32 +2749,32 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="I20" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J20" s="4" t="inlineStr">
         <is>
-          <t>CURRENT (3d)</t>
+          <t>CURRENT (0d)</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="M20" s="2" t="n">
         <v>0</v>
       </c>
       <c r="N20" s="2" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="O20" s="2" t="n">
         <v>0</v>
@@ -2783,7 +2783,7 @@
         <v>0</v>
       </c>
       <c r="Q20" s="2" t="n">
-        <v>3551</v>
+        <v>3553</v>
       </c>
       <c r="R20" s="2" t="n">
         <v>0</v>
@@ -2795,10 +2795,10 @@
         <v>0</v>
       </c>
       <c r="U20" s="2" t="n">
-        <v>1195</v>
+        <v>1196</v>
       </c>
       <c r="V20" s="2" t="n">
-        <v>3551</v>
+        <v>3553</v>
       </c>
       <c r="W20" s="3" t="inlineStr">
         <is>
@@ -2812,7 +2812,7 @@
       </c>
       <c r="Y20" s="3" t="inlineStr">
         <is>
-          <t>hellenic_iron_ore_pdf_brands_series.csv (32,482 rows)</t>
+          <t>hellenic_iron_ore_pdf_brands_series.csv (32,502 rows)</t>
         </is>
       </c>
       <c r="Z20" s="3" t="inlineStr">
@@ -3019,7 +3019,7 @@
         <v>282</v>
       </c>
       <c r="S22" s="2" t="n">
-        <v>761</v>
+        <v>762</v>
       </c>
       <c r="T22" s="2" t="n">
         <v>0</v>
@@ -3028,7 +3028,7 @@
         <v>268</v>
       </c>
       <c r="V22" s="2" t="n">
-        <v>1043</v>
+        <v>1044</v>
       </c>
       <c r="W22" s="3" t="inlineStr">
         <is>
@@ -3209,25 +3209,25 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="I24" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J24" s="4" t="inlineStr">
         <is>
-          <t>CURRENT (3d)</t>
+          <t>CURRENT (0d)</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="M24" s="2" t="n">
@@ -3246,19 +3246,19 @@
         <v>307</v>
       </c>
       <c r="R24" s="2" t="n">
-        <v>3264</v>
+        <v>3266</v>
       </c>
       <c r="S24" s="2" t="n">
-        <v>15135</v>
+        <v>15137</v>
       </c>
       <c r="T24" s="2" t="n">
-        <v>3235</v>
+        <v>3237</v>
       </c>
       <c r="U24" s="2" t="n">
-        <v>3528</v>
+        <v>3530</v>
       </c>
       <c r="V24" s="2" t="n">
-        <v>21941</v>
+        <v>21947</v>
       </c>
       <c r="W24" s="3" t="inlineStr">
         <is>
@@ -3272,7 +3272,7 @@
       </c>
       <c r="Y24" s="3" t="inlineStr">
         <is>
-          <t>breakwave_fundamentals_series.csv (2,769 rows), breakwave_insights_metadata.csv (3,235 rows)</t>
+          <t>breakwave_fundamentals_series.csv (2,769 rows), breakwave_insights_metadata.csv (3,237 rows)</t>
         </is>
       </c>
       <c r="Z24" s="3" t="inlineStr">
@@ -5362,7 +5362,7 @@
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>1,108 rows</t>
+          <t>1,112 rows</t>
         </is>
       </c>
       <c r="H16" s="3" t="inlineStr">
@@ -5409,7 +5409,7 @@
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>3,029 rows</t>
+          <t>3,041 rows</t>
         </is>
       </c>
       <c r="H17" s="3" t="inlineStr">
@@ -5597,7 +5597,7 @@
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>32,482 rows</t>
+          <t>32,502 rows</t>
         </is>
       </c>
       <c r="H21" s="3" t="inlineStr">
@@ -5644,7 +5644,7 @@
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>1,193 rows</t>
+          <t>1,194 rows</t>
         </is>
       </c>
       <c r="H22" s="3" t="inlineStr">

--- a/data/extracted/series/corpus_publication_cadence_and_audit.xlsx
+++ b/data/extracted/series/corpus_publication_cadence_and_audit.xlsx
@@ -2544,7 +2544,7 @@
         <v>0</v>
       </c>
       <c r="N18" s="2" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="O18" s="2" t="n">
         <v>0</v>

--- a/data/extracted/series/corpus_publication_cadence_and_audit.xlsx
+++ b/data/extracted/series/corpus_publication_cadence_and_audit.xlsx
@@ -1143,25 +1143,25 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J6" s="4" t="inlineStr">
+        <is>
+          <t>CURRENT (0d)</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
           <t>2026-10-12</t>
         </is>
       </c>
-      <c r="I6" s="2" t="n">
-        <v>14</v>
-      </c>
-      <c r="J6" s="5" t="inlineStr">
-        <is>
-          <t>DUE (14d, cadence weekly)</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-12</t>
-        </is>
-      </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="M6" s="2" t="n">
@@ -1177,7 +1177,7 @@
         <v>0</v>
       </c>
       <c r="Q6" s="2" t="n">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="R6" s="2" t="n">
         <v>0</v>
@@ -1189,10 +1189,10 @@
         <v>0</v>
       </c>
       <c r="U6" s="2" t="n">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="V6" s="2" t="n">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="W6" s="3" t="inlineStr">
         <is>
@@ -1206,7 +1206,7 @@
       </c>
       <c r="Y6" s="3" t="inlineStr">
         <is>
-          <t>carriers_sales_series.csv (3,146 rows), carriers_dry_tc_period_series.csv (3,168 rows), carriers_indices_series.csv (1,848 rows), carriers_tanker_tce_series.csv (807 rows), carriers_bspa_series.csv (792 rows), carriers_newbuilding_series.csv (304 rows), carriers_demolition_series.csv (172 rows)</t>
+          <t>carriers_sales_series.csv (3,192 rows), carriers_dry_tc_period_series.csv (3,216 rows), carriers_indices_series.csv (1,876 rows), carriers_tanker_tce_series.csv (819 rows), carriers_bspa_series.csv (804 rows), carriers_newbuilding_series.csv (308 rows), carriers_demolition_series.csv (174 rows)</t>
         </is>
       </c>
       <c r="Z6" s="3" t="inlineStr">
@@ -3209,7 +3209,7 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="I24" s="2" t="n">
@@ -3222,12 +3222,12 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="M24" s="2" t="n">
@@ -3243,7 +3243,7 @@
         <v>0</v>
       </c>
       <c r="Q24" s="2" t="n">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="R24" s="2" t="n">
         <v>3266</v>
@@ -3255,10 +3255,10 @@
         <v>3237</v>
       </c>
       <c r="U24" s="2" t="n">
-        <v>3530</v>
+        <v>3531</v>
       </c>
       <c r="V24" s="2" t="n">
-        <v>21947</v>
+        <v>21948</v>
       </c>
       <c r="W24" s="3" t="inlineStr">
         <is>
@@ -3272,7 +3272,7 @@
       </c>
       <c r="Y24" s="3" t="inlineStr">
         <is>
-          <t>breakwave_fundamentals_series.csv (2,769 rows), breakwave_insights_metadata.csv (3,237 rows)</t>
+          <t>breakwave_fundamentals_series.csv (2,781 rows), breakwave_insights_metadata.csv (3,237 rows)</t>
         </is>
       </c>
       <c r="Z24" s="3" t="inlineStr">

--- a/data/extracted/series/corpus_publication_cadence_and_audit.xlsx
+++ b/data/extracted/series/corpus_publication_cadence_and_audit.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Corpus Cadence &amp; Inventory" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Graphic &amp; Chart Extraction" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sub-Sector &amp; Fleet Breakdown" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Corpus Cadence &amp; Inventory" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Graphic &amp; Chart Extraction" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Sub-Sector &amp; Fleet Breakdown" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -2404,25 +2404,25 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="I17" s="2" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="J17" s="4" t="inlineStr">
         <is>
-          <t>CURRENT (7d)</t>
+          <t>CURRENT (0d)</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="M17" s="2" t="n">
@@ -2438,7 +2438,7 @@
         <v>0</v>
       </c>
       <c r="Q17" s="2" t="n">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="R17" s="2" t="n">
         <v>0</v>
@@ -2450,10 +2450,10 @@
         <v>0</v>
       </c>
       <c r="U17" s="2" t="n">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="V17" s="2" t="n">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="W17" s="3" t="inlineStr">
         <is>
@@ -2467,7 +2467,7 @@
       </c>
       <c r="Y17" s="3" t="inlineStr">
         <is>
-          <t>xclusiv_secondhand_series.csv (8,625 rows), xclusiv_sales_series.csv (5,593 rows), xclusiv_demolition_series.csv (2,106 rows), xclusiv_newbuilding_prices_series.csv (1,406 rows), xclusiv_newbuilding_orders_series.csv (1,336 rows)</t>
+          <t>xclusiv_secondhand_series.csv (8,657 rows), xclusiv_sales_series.csv (5,607 rows), xclusiv_demolition_series.csv (2,114 rows), xclusiv_newbuilding_prices_series.csv (1,415 rows), xclusiv_newbuilding_orders_series.csv (1,347 rows)</t>
         </is>
       </c>
       <c r="Z17" s="3" t="inlineStr">
@@ -2774,7 +2774,7 @@
         <v>0</v>
       </c>
       <c r="N20" s="2" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="O20" s="2" t="n">
         <v>0</v>
@@ -6114,7 +6114,7 @@
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>5,593 rows</t>
+          <t>5,607 rows</t>
         </is>
       </c>
       <c r="H32" s="3" t="inlineStr">

--- a/data/extracted/series/corpus_publication_cadence_and_audit.xlsx
+++ b/data/extracted/series/corpus_publication_cadence_and_audit.xlsx
@@ -38,7 +38,7 @@
       <sz val="10"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="6">
     <fill>
       <patternFill/>
     </fill>
@@ -61,6 +61,12 @@
       <patternFill patternType="solid">
         <fgColor rgb="00FFF2CC"/>
         <bgColor rgb="00FFF2CC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F8CBAD"/>
+        <bgColor rgb="00F8CBAD"/>
       </patternFill>
     </fill>
   </fills>
@@ -90,7 +96,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -105,6 +111,9 @@
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -556,7 +565,7 @@
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>Status (2026-10-26)</t>
+          <t>Status (2026-10-27)</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
@@ -687,11 +696,11 @@
         </is>
       </c>
       <c r="I2" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J2" s="4" t="inlineStr">
         <is>
-          <t>CURRENT (2d)</t>
+          <t>CURRENT (3d)</t>
         </is>
       </c>
       <c r="K2" s="2" t="inlineStr">
@@ -802,11 +811,11 @@
         </is>
       </c>
       <c r="I3" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J3" s="4" t="inlineStr">
         <is>
-          <t>CURRENT (2d)</t>
+          <t>CURRENT (3d)</t>
         </is>
       </c>
       <c r="K3" s="2" t="inlineStr">
@@ -917,11 +926,11 @@
         </is>
       </c>
       <c r="I4" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J4" s="4" t="inlineStr">
         <is>
-          <t>CURRENT (3d)</t>
+          <t>CURRENT (4d)</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -1032,11 +1041,11 @@
         </is>
       </c>
       <c r="I5" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J5" s="4" t="inlineStr">
         <is>
-          <t>CURRENT (5d)</t>
+          <t>CURRENT (6d)</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -1147,11 +1156,11 @@
         </is>
       </c>
       <c r="I6" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J6" s="4" t="inlineStr">
         <is>
-          <t>CURRENT (0d)</t>
+          <t>CURRENT (1d)</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -1262,11 +1271,11 @@
         </is>
       </c>
       <c r="I7" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J7" s="4" t="inlineStr">
         <is>
-          <t>CURRENT (3d)</t>
+          <t>CURRENT (4d)</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
@@ -1377,11 +1386,11 @@
         </is>
       </c>
       <c r="I8" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J8" s="4" t="inlineStr">
         <is>
-          <t>CURRENT (4d)</t>
+          <t>CURRENT (5d)</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -1492,11 +1501,11 @@
         </is>
       </c>
       <c r="I9" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J9" s="4" t="inlineStr">
         <is>
-          <t>CURRENT (3d)</t>
+          <t>CURRENT (4d)</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr"/>
@@ -1603,11 +1612,11 @@
         </is>
       </c>
       <c r="I10" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J10" s="4" t="inlineStr">
         <is>
-          <t>CURRENT (4d)</t>
+          <t>CURRENT (5d)</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1718,11 +1727,11 @@
         </is>
       </c>
       <c r="I11" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J11" s="4" t="inlineStr">
         <is>
-          <t>CURRENT (3d)</t>
+          <t>CURRENT (4d)</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -1833,11 +1842,11 @@
         </is>
       </c>
       <c r="I12" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J12" s="4" t="inlineStr">
         <is>
-          <t>CURRENT (5d)</t>
+          <t>CURRENT (6d)</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1948,11 +1957,11 @@
         </is>
       </c>
       <c r="I13" s="2" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="J13" s="5" t="inlineStr">
         <is>
-          <t>DUE (14d, cadence weekly)</t>
+          <t>DUE (15d, cadence weekly)</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
@@ -2063,11 +2072,11 @@
         </is>
       </c>
       <c r="I14" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J14" s="4" t="inlineStr">
         <is>
-          <t>CURRENT (3d)</t>
+          <t>CURRENT (4d)</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2178,11 +2187,11 @@
         </is>
       </c>
       <c r="I15" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J15" s="4" t="inlineStr">
         <is>
-          <t>CURRENT (0d)</t>
+          <t>CURRENT (1d)</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
@@ -2293,11 +2302,11 @@
         </is>
       </c>
       <c r="I16" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J16" s="4" t="inlineStr">
         <is>
-          <t>CURRENT (0d)</t>
+          <t>CURRENT (1d)</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -2523,11 +2532,11 @@
         </is>
       </c>
       <c r="I18" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J18" s="4" t="inlineStr">
         <is>
-          <t>CURRENT (2d)</t>
+          <t>CURRENT (3d)</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
@@ -2638,11 +2647,11 @@
         </is>
       </c>
       <c r="I19" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J19" s="4" t="inlineStr">
         <is>
-          <t>CURRENT (5d)</t>
+          <t>CURRENT (6d)</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
@@ -2753,11 +2762,11 @@
         </is>
       </c>
       <c r="I20" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J20" s="4" t="inlineStr">
         <is>
-          <t>CURRENT (0d)</t>
+          <t>CURRENT (1d)</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -2983,11 +2992,11 @@
         </is>
       </c>
       <c r="I22" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J22" s="4" t="inlineStr">
         <is>
-          <t>CURRENT (5d)</t>
+          <t>CURRENT (6d)</t>
         </is>
       </c>
       <c r="K22" s="2" t="inlineStr">
@@ -3098,11 +3107,11 @@
         </is>
       </c>
       <c r="I23" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J23" s="4" t="inlineStr">
         <is>
-          <t>CURRENT (6d)</t>
+          <t>CURRENT (7d)</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
@@ -3328,11 +3337,11 @@
         </is>
       </c>
       <c r="I25" s="2" t="n">
-        <v>10</v>
-      </c>
-      <c r="J25" s="4" t="inlineStr">
-        <is>
-          <t>CURRENT (10d)</t>
+        <v>11</v>
+      </c>
+      <c r="J25" s="5" t="inlineStr">
+        <is>
+          <t>DUE (11d, cadence weekly)</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
@@ -3443,11 +3452,11 @@
         </is>
       </c>
       <c r="I26" s="2" t="n">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="J26" s="5" t="inlineStr">
         <is>
-          <t>DUE (55d, cadence monthly)</t>
+          <t>DUE (56d, cadence monthly)</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
@@ -3558,11 +3567,11 @@
         </is>
       </c>
       <c r="I27" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J27" s="4" t="inlineStr">
         <is>
-          <t>CURRENT (5d)</t>
+          <t>CURRENT (6d)</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr"/>
@@ -3669,11 +3678,11 @@
         </is>
       </c>
       <c r="I28" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J28" s="4" t="inlineStr">
         <is>
-          <t>CURRENT (4d)</t>
+          <t>CURRENT (5d)</t>
         </is>
       </c>
       <c r="K28" s="2" t="inlineStr"/>
@@ -3780,11 +3789,11 @@
         </is>
       </c>
       <c r="I29" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J29" s="4" t="inlineStr">
         <is>
-          <t>CURRENT (3d)</t>
+          <t>CURRENT (4d)</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
@@ -3895,11 +3904,11 @@
         </is>
       </c>
       <c r="I30" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J30" s="4" t="inlineStr">
         <is>
-          <t>CURRENT (3d)</t>
+          <t>CURRENT (4d)</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
@@ -4010,11 +4019,11 @@
         </is>
       </c>
       <c r="I31" s="2" t="n">
-        <v>90</v>
-      </c>
-      <c r="J31" s="5" t="inlineStr">
-        <is>
-          <t>DUE (90d, cadence monthly)</t>
+        <v>91</v>
+      </c>
+      <c r="J31" s="6" t="inlineStr">
+        <is>
+          <t>STALE (91d, cadence monthly)</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
@@ -4121,11 +4130,11 @@
         </is>
       </c>
       <c r="I32" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J32" s="4" t="inlineStr">
         <is>
-          <t>CURRENT (3d)</t>
+          <t>CURRENT (4d)</t>
         </is>
       </c>
       <c r="K32" s="2" t="inlineStr">
@@ -4323,34 +4332,34 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="6" t="inlineStr">
+      <c r="A1" s="7" t="inlineStr">
         <is>
           <t>Source Category</t>
         </is>
       </c>
-      <c r="B1" s="6" t="inlineStr">
+      <c r="B1" s="7" t="inlineStr">
         <is>
           <t>Images in Corpus</t>
         </is>
       </c>
-      <c r="C1" s="6" t="inlineStr">
+      <c r="C1" s="7" t="inlineStr">
         <is>
           <t>Graphic Formats</t>
         </is>
       </c>
-      <c r="D1" s="6" t="inlineStr">
+      <c r="D1" s="7" t="inlineStr">
         <is>
           <t>Extraction Pipeline Applied</t>
         </is>
       </c>
-      <c r="E1" s="6" t="inlineStr">
+      <c r="E1" s="7" t="inlineStr">
         <is>
           <t>Extracted Series Output</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="7" t="inlineStr">
+      <c r="A2" s="8" t="inlineStr">
         <is>
           <t>01-brokers/fearnleys-md</t>
         </is>
@@ -4358,24 +4367,24 @@
       <c r="B2" s="2" t="n">
         <v>2786</v>
       </c>
-      <c r="C2" s="7" t="inlineStr">
+      <c r="C2" s="8" t="inlineStr">
         <is>
           <t>Raster PNG charts (no embedded data), JPG</t>
         </is>
       </c>
-      <c r="D2" s="7" t="inlineStr">
+      <c r="D2" s="8" t="inlineStr">
         <is>
           <t>Not read; titles kept, printed tables transcribed and verified</t>
         </is>
       </c>
-      <c r="E2" s="7" t="inlineStr">
+      <c r="E2" s="8" t="inlineStr">
         <is>
           <t>Chart titles in MDs and .tables.json sidecars; calibrated series deleted</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="7" t="inlineStr">
+      <c r="A3" s="8" t="inlineStr">
         <is>
           <t>01-brokers/ism</t>
         </is>
@@ -4383,24 +4392,24 @@
       <c r="B3" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="C3" s="7" t="inlineStr">
+      <c r="C3" s="8" t="inlineStr">
         <is>
           <t>PDF vector drawing strokes</t>
         </is>
       </c>
-      <c r="D3" s="7" t="inlineStr">
+      <c r="D3" s="8" t="inlineStr">
         <is>
           <t>Least-squares dual-axis scale calibration &amp; tick filtering</t>
         </is>
       </c>
-      <c r="E3" s="7" t="inlineStr">
+      <c r="E3" s="8" t="inlineStr">
         <is>
           <t>ism_handy_freight_series.csv, ism_coaster_freight_series.csv</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="7" t="inlineStr">
+      <c r="A4" s="8" t="inlineStr">
         <is>
           <t>01-brokers/star_asia</t>
         </is>
@@ -4408,24 +4417,24 @@
       <c r="B4" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="C4" s="7" t="inlineStr">
+      <c r="C4" s="8" t="inlineStr">
         <is>
           <t>Image bar chart with printed data labels</t>
         </is>
       </c>
-      <c r="D4" s="7" t="inlineStr">
+      <c r="D4" s="8" t="inlineStr">
         <is>
           <t>Annual LDT sold at Alang / Chattogram / Pakistan (printed labels only)</t>
         </is>
       </c>
-      <c r="E4" s="7" t="inlineStr">
+      <c r="E4" s="8" t="inlineStr">
         <is>
           <t>star_asia_ldt_comparison_series.csv (1,320 rows)</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="7" t="inlineStr">
+      <c r="A5" s="8" t="inlineStr">
         <is>
           <t>02-hellenic/iron_ore</t>
         </is>
@@ -4433,24 +4442,24 @@
       <c r="B5" s="2" t="n">
         <v>3335</v>
       </c>
-      <c r="C5" s="7" t="inlineStr">
+      <c r="C5" s="8" t="inlineStr">
         <is>
           <t>JPG / PNG port inventory graphics</t>
         </is>
       </c>
-      <c r="D5" s="7" t="inlineStr">
+      <c r="D5" s="8" t="inlineStr">
         <is>
           <t>OCR &amp; spatial coordinate table extraction</t>
         </is>
       </c>
-      <c r="E5" s="7" t="inlineStr">
+      <c r="E5" s="8" t="inlineStr">
         <is>
           <t>hellenic_iron_ore_pdf_brands_series.csv (31,272 rows)</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="7" t="inlineStr">
+      <c r="A6" s="8" t="inlineStr">
         <is>
           <t>02-hellenic/demolition</t>
         </is>
@@ -4458,24 +4467,24 @@
       <c r="B6" s="2" t="n">
         <v>1208</v>
       </c>
-      <c r="C6" s="7" t="inlineStr">
+      <c r="C6" s="8" t="inlineStr">
         <is>
           <t>Cash buyer market insight graphics</t>
         </is>
       </c>
-      <c r="D6" s="7" t="inlineStr">
+      <c r="D6" s="8" t="inlineStr">
         <is>
           <t>HTML table extraction + OCR fallback</t>
         </is>
       </c>
-      <c r="E6" s="7" t="inlineStr">
+      <c r="E6" s="8" t="inlineStr">
         <is>
           <t>hellenic_gms_port_positions_series.csv (2,905 rows)</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="7" t="inlineStr">
+      <c r="A7" s="8" t="inlineStr">
         <is>
           <t>02-hellenic/dry_charter</t>
         </is>
@@ -4483,24 +4492,24 @@
       <c r="B7" s="2" t="n">
         <v>759</v>
       </c>
-      <c r="C7" s="7" t="inlineStr">
+      <c r="C7" s="8" t="inlineStr">
         <is>
           <t>Alibra Dry Bulk TC rate graphics</t>
         </is>
       </c>
-      <c r="D7" s="7" t="inlineStr">
+      <c r="D7" s="8" t="inlineStr">
         <is>
           <t>Graphic OCR &amp; tabular parameter parsing</t>
         </is>
       </c>
-      <c r="E7" s="7" t="inlineStr">
+      <c r="E7" s="8" t="inlineStr">
         <is>
           <t>hellenic_alibra_dry_tc_series.csv (6,467 rows)</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="7" t="inlineStr">
+      <c r="A8" s="8" t="inlineStr">
         <is>
           <t>02-hellenic/tanker_charter</t>
         </is>
@@ -4508,24 +4517,24 @@
       <c r="B8" s="2" t="n">
         <v>757</v>
       </c>
-      <c r="C8" s="7" t="inlineStr">
+      <c r="C8" s="8" t="inlineStr">
         <is>
           <t>Alibra Tanker TC rate graphics</t>
         </is>
       </c>
-      <c r="D8" s="7" t="inlineStr">
+      <c r="D8" s="8" t="inlineStr">
         <is>
           <t>Graphic OCR &amp; tabular parameter parsing</t>
         </is>
       </c>
-      <c r="E8" s="7" t="inlineStr">
+      <c r="E8" s="8" t="inlineStr">
         <is>
           <t>hellenic_alibra_tanker_tc_series.csv (7,191 rows)</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="7" t="inlineStr">
+      <c r="A9" s="8" t="inlineStr">
         <is>
           <t>02-hellenic/vessel_valuations</t>
         </is>
@@ -4533,24 +4542,24 @@
       <c r="B9" s="2" t="n">
         <v>726</v>
       </c>
-      <c r="C9" s="7" t="inlineStr">
+      <c r="C9" s="8" t="inlineStr">
         <is>
           <t>VesselsValue asset price charts</t>
         </is>
       </c>
-      <c r="D9" s="7" t="inlineStr">
+      <c r="D9" s="8" t="inlineStr">
         <is>
           <t>Asset valuation curve digitizer &amp; matrix builder</t>
         </is>
       </c>
-      <c r="E9" s="7" t="inlineStr">
+      <c r="E9" s="8" t="inlineStr">
         <is>
           <t>hellenic_vv_matrix_series.csv (12,340 rows)</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="7" t="inlineStr">
+      <c r="A10" s="8" t="inlineStr">
         <is>
           <t>03-breakwave</t>
         </is>
@@ -4558,24 +4567,24 @@
       <c r="B10" s="2" t="n">
         <v>15072</v>
       </c>
-      <c r="C10" s="7" t="inlineStr">
+      <c r="C10" s="8" t="inlineStr">
         <is>
           <t>Freight market fundamentals PNGs</t>
         </is>
       </c>
-      <c r="D10" s="7" t="inlineStr">
+      <c r="D10" s="8" t="inlineStr">
         <is>
           <t>BDRY/BWET index trajectory curves &amp; fundamental commentary</t>
         </is>
       </c>
-      <c r="E10" s="7" t="inlineStr">
+      <c r="E10" s="8" t="inlineStr">
         <is>
           <t>breakwave_fundamentals_series.csv (2,746 rows)</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="7" t="inlineStr">
+      <c r="A11" s="8" t="inlineStr">
         <is>
           <t>07-signal</t>
         </is>
@@ -4583,17 +4592,17 @@
       <c r="B11" s="2" t="n">
         <v>1885</v>
       </c>
-      <c r="C11" s="7" t="inlineStr">
+      <c r="C11" s="8" t="inlineStr">
         <is>
           <t>Flow heatmaps &amp; trade monitors</t>
         </is>
       </c>
-      <c r="D11" s="7" t="inlineStr">
+      <c r="D11" s="8" t="inlineStr">
         <is>
           <t>Live telemetry pipeline &amp; monitor digest parser</t>
         </is>
       </c>
-      <c r="E11" s="7" t="inlineStr">
+      <c r="E11" s="8" t="inlineStr">
         <is>
           <t>signal_reports_metadata.csv (446 rows)</t>
         </is>

--- a/data/extracted/series/corpus_publication_cadence_and_audit.xlsx
+++ b/data/extracted/series/corpus_publication_cadence_and_audit.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Corpus Cadence &amp; Inventory" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Graphic &amp; Chart Extraction" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Sub-Sector &amp; Fleet Breakdown" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Corpus Cadence &amp; Inventory" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Graphic &amp; Chart Extraction" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sub-Sector &amp; Fleet Breakdown" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -2758,32 +2758,32 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="I20" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J20" s="4" t="inlineStr">
         <is>
-          <t>CURRENT (1d)</t>
+          <t>CURRENT (0d)</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="M20" s="2" t="n">
         <v>0</v>
       </c>
       <c r="N20" s="2" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="O20" s="2" t="n">
         <v>0</v>
@@ -2792,7 +2792,7 @@
         <v>0</v>
       </c>
       <c r="Q20" s="2" t="n">
-        <v>3553</v>
+        <v>3555</v>
       </c>
       <c r="R20" s="2" t="n">
         <v>0</v>
@@ -2804,10 +2804,10 @@
         <v>0</v>
       </c>
       <c r="U20" s="2" t="n">
-        <v>1196</v>
+        <v>1197</v>
       </c>
       <c r="V20" s="2" t="n">
-        <v>3553</v>
+        <v>3555</v>
       </c>
       <c r="W20" s="3" t="inlineStr">
         <is>
@@ -2821,7 +2821,7 @@
       </c>
       <c r="Y20" s="3" t="inlineStr">
         <is>
-          <t>hellenic_iron_ore_pdf_brands_series.csv (32,502 rows)</t>
+          <t>hellenic_iron_ore_pdf_brands_series.csv (32,522 rows)</t>
         </is>
       </c>
       <c r="Z20" s="3" t="inlineStr">
@@ -3255,19 +3255,19 @@
         <v>308</v>
       </c>
       <c r="R24" s="2" t="n">
-        <v>3266</v>
+        <v>3267</v>
       </c>
       <c r="S24" s="2" t="n">
-        <v>15137</v>
+        <v>15140</v>
       </c>
       <c r="T24" s="2" t="n">
-        <v>3237</v>
+        <v>3238</v>
       </c>
       <c r="U24" s="2" t="n">
-        <v>3531</v>
+        <v>3532</v>
       </c>
       <c r="V24" s="2" t="n">
-        <v>21948</v>
+        <v>21953</v>
       </c>
       <c r="W24" s="3" t="inlineStr">
         <is>
@@ -3281,7 +3281,7 @@
       </c>
       <c r="Y24" s="3" t="inlineStr">
         <is>
-          <t>breakwave_fundamentals_series.csv (2,781 rows), breakwave_insights_metadata.csv (3,237 rows)</t>
+          <t>breakwave_fundamentals_series.csv (2,781 rows), breakwave_insights_metadata.csv (3,238 rows)</t>
         </is>
       </c>
       <c r="Z24" s="3" t="inlineStr">
@@ -5606,7 +5606,7 @@
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>32,502 rows</t>
+          <t>32,522 rows</t>
         </is>
       </c>
       <c r="H21" s="3" t="inlineStr">
@@ -5653,7 +5653,7 @@
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>1,194 rows</t>
+          <t>1,195 rows</t>
         </is>
       </c>
       <c r="H22" s="3" t="inlineStr">

--- a/data/extracted/series/corpus_publication_cadence_and_audit.xlsx
+++ b/data/extracted/series/corpus_publication_cadence_and_audit.xlsx
@@ -2528,32 +2528,32 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="I18" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J18" s="4" t="inlineStr">
         <is>
-          <t>CURRENT (3d)</t>
+          <t>CURRENT (0d)</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-25</t>
         </is>
       </c>
       <c r="M18" s="2" t="n">
         <v>0</v>
       </c>
       <c r="N18" s="2" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="O18" s="2" t="n">
         <v>0</v>
@@ -2562,10 +2562,10 @@
         <v>0</v>
       </c>
       <c r="Q18" s="2" t="n">
-        <v>1953</v>
+        <v>1955</v>
       </c>
       <c r="R18" s="2" t="n">
-        <v>818</v>
+        <v>819</v>
       </c>
       <c r="S18" s="2" t="n">
         <v>1214</v>
@@ -2574,10 +2574,10 @@
         <v>0</v>
       </c>
       <c r="U18" s="2" t="n">
-        <v>756</v>
+        <v>757</v>
       </c>
       <c r="V18" s="2" t="n">
-        <v>3985</v>
+        <v>3988</v>
       </c>
       <c r="W18" s="3" t="inlineStr">
         <is>
@@ -2591,7 +2591,7 @@
       </c>
       <c r="Y18" s="3" t="inlineStr">
         <is>
-          <t>athenian_indicative_demolition_series.csv (3,076 rows), hellenic_gms_port_positions_series.csv (3,041 rows), hellenic_gms_demolition_series.csv (1,112 rows), hellenic_best_oasis_deals_series.csv (905 rows), hellenic_best_oasis_demolition_series.csv (866 rows)</t>
+          <t>athenian_indicative_demolition_series.csv (3,088 rows), hellenic_gms_port_positions_series.csv (3,041 rows), hellenic_gms_demolition_series.csv (1,112 rows), hellenic_best_oasis_deals_series.csv (905 rows), hellenic_best_oasis_demolition_series.csv (866 rows)</t>
         </is>
       </c>
       <c r="Z18" s="3" t="inlineStr">
@@ -2910,7 +2910,7 @@
         <v>1041</v>
       </c>
       <c r="R21" s="2" t="n">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="S21" s="2" t="n">
         <v>180</v>
@@ -2922,7 +2922,7 @@
         <v>170</v>
       </c>
       <c r="V21" s="2" t="n">
-        <v>1602</v>
+        <v>1603</v>
       </c>
       <c r="W21" s="3" t="inlineStr">
         <is>
@@ -3103,32 +3103,32 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="I23" s="2" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="J23" s="4" t="inlineStr">
         <is>
-          <t>CURRENT (7d)</t>
+          <t>CURRENT (0d)</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="M23" s="2" t="n">
         <v>0</v>
       </c>
       <c r="N23" s="2" t="n">
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="O23" s="2" t="n">
         <v>0</v>
@@ -3140,19 +3140,19 @@
         <v>0</v>
       </c>
       <c r="R23" s="2" t="n">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="S23" s="2" t="n">
-        <v>736</v>
+        <v>737</v>
       </c>
       <c r="T23" s="2" t="n">
         <v>0</v>
       </c>
       <c r="U23" s="2" t="n">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="V23" s="2" t="n">
-        <v>1014</v>
+        <v>1016</v>
       </c>
       <c r="W23" s="3" t="inlineStr">
         <is>
@@ -3166,7 +3166,7 @@
       </c>
       <c r="Y23" s="3" t="inlineStr">
         <is>
-          <t>hellenic_vv_matrix_series.csv (19,946 rows), hellenic_vv_sales_series.csv (2,091 rows)</t>
+          <t>hellenic_vv_matrix_series.csv (20,024 rows), hellenic_vv_sales_series.csv (2,102 rows)</t>
         </is>
       </c>
       <c r="Z23" s="3" t="inlineStr">
@@ -5324,7 +5324,7 @@
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>3,076 rows</t>
+          <t>3,088 rows</t>
         </is>
       </c>
       <c r="H15" s="3" t="inlineStr">
@@ -5747,7 +5747,7 @@
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>19,946 rows</t>
+          <t>20,024 rows</t>
         </is>
       </c>
       <c r="H24" s="3" t="inlineStr">
@@ -5794,7 +5794,7 @@
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>2,091 rows</t>
+          <t>2,102 rows</t>
         </is>
       </c>
       <c r="H25" s="3" t="inlineStr">

--- a/data/extracted/series/corpus_publication_cadence_and_audit.xlsx
+++ b/data/extracted/series/corpus_publication_cadence_and_audit.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Corpus Cadence &amp; Inventory" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Graphic &amp; Chart Extraction" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sub-Sector &amp; Fleet Breakdown" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Corpus Cadence &amp; Inventory" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Graphic &amp; Chart Extraction" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Sub-Sector &amp; Fleet Breakdown" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -2553,7 +2553,7 @@
         <v>0</v>
       </c>
       <c r="N18" s="2" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="O18" s="2" t="n">
         <v>0</v>
@@ -2783,7 +2783,7 @@
         <v>0</v>
       </c>
       <c r="N20" s="2" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="O20" s="2" t="n">
         <v>0</v>
@@ -3128,7 +3128,7 @@
         <v>0</v>
       </c>
       <c r="N23" s="2" t="n">
-        <v>0.4</v>
+        <v>0</v>
       </c>
       <c r="O23" s="2" t="n">
         <v>0</v>

--- a/data/extracted/series/corpus_publication_cadence_and_audit.xlsx
+++ b/data/extracted/series/corpus_publication_cadence_and_audit.xlsx
@@ -565,7 +565,7 @@
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>Status (2026-10-27)</t>
+          <t>Status (2026-10-28)</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
@@ -696,11 +696,11 @@
         </is>
       </c>
       <c r="I2" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J2" s="4" t="inlineStr">
         <is>
-          <t>CURRENT (3d)</t>
+          <t>CURRENT (4d)</t>
         </is>
       </c>
       <c r="K2" s="2" t="inlineStr">
@@ -811,11 +811,11 @@
         </is>
       </c>
       <c r="I3" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J3" s="4" t="inlineStr">
         <is>
-          <t>CURRENT (3d)</t>
+          <t>CURRENT (4d)</t>
         </is>
       </c>
       <c r="K3" s="2" t="inlineStr">
@@ -926,11 +926,11 @@
         </is>
       </c>
       <c r="I4" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J4" s="4" t="inlineStr">
         <is>
-          <t>CURRENT (4d)</t>
+          <t>CURRENT (5d)</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -1041,11 +1041,11 @@
         </is>
       </c>
       <c r="I5" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J5" s="4" t="inlineStr">
         <is>
-          <t>CURRENT (6d)</t>
+          <t>CURRENT (7d)</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -1156,11 +1156,11 @@
         </is>
       </c>
       <c r="I6" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J6" s="4" t="inlineStr">
         <is>
-          <t>CURRENT (1d)</t>
+          <t>CURRENT (2d)</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -1271,11 +1271,11 @@
         </is>
       </c>
       <c r="I7" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J7" s="4" t="inlineStr">
         <is>
-          <t>CURRENT (4d)</t>
+          <t>CURRENT (5d)</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
@@ -1386,11 +1386,11 @@
         </is>
       </c>
       <c r="I8" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J8" s="4" t="inlineStr">
         <is>
-          <t>CURRENT (5d)</t>
+          <t>CURRENT (6d)</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -1497,21 +1497,21 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="I9" s="2" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="J9" s="4" t="inlineStr">
         <is>
-          <t>CURRENT (4d)</t>
+          <t>CURRENT (0d)</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr"/>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="M9" s="2" t="n">
@@ -1539,7 +1539,7 @@
         <v>4773</v>
       </c>
       <c r="U9" s="2" t="n">
-        <v>4784</v>
+        <v>4786</v>
       </c>
       <c r="V9" s="2" t="n">
         <v>4773</v>
@@ -1612,11 +1612,11 @@
         </is>
       </c>
       <c r="I10" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J10" s="4" t="inlineStr">
         <is>
-          <t>CURRENT (5d)</t>
+          <t>CURRENT (6d)</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1727,11 +1727,11 @@
         </is>
       </c>
       <c r="I11" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J11" s="4" t="inlineStr">
         <is>
-          <t>CURRENT (4d)</t>
+          <t>CURRENT (5d)</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -1842,11 +1842,11 @@
         </is>
       </c>
       <c r="I12" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J12" s="4" t="inlineStr">
         <is>
-          <t>CURRENT (6d)</t>
+          <t>CURRENT (7d)</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1957,11 +1957,11 @@
         </is>
       </c>
       <c r="I13" s="2" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="J13" s="5" t="inlineStr">
         <is>
-          <t>DUE (15d, cadence weekly)</t>
+          <t>DUE (16d, cadence weekly)</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
@@ -2072,11 +2072,11 @@
         </is>
       </c>
       <c r="I14" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J14" s="4" t="inlineStr">
         <is>
-          <t>CURRENT (4d)</t>
+          <t>CURRENT (5d)</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2187,11 +2187,11 @@
         </is>
       </c>
       <c r="I15" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J15" s="4" t="inlineStr">
         <is>
-          <t>CURRENT (1d)</t>
+          <t>CURRENT (2d)</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
@@ -2302,11 +2302,11 @@
         </is>
       </c>
       <c r="I16" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J16" s="4" t="inlineStr">
         <is>
-          <t>CURRENT (1d)</t>
+          <t>CURRENT (2d)</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -2417,11 +2417,11 @@
         </is>
       </c>
       <c r="I17" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J17" s="4" t="inlineStr">
         <is>
-          <t>CURRENT (0d)</t>
+          <t>CURRENT (1d)</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -2532,11 +2532,11 @@
         </is>
       </c>
       <c r="I18" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J18" s="4" t="inlineStr">
         <is>
-          <t>CURRENT (0d)</t>
+          <t>CURRENT (1d)</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
@@ -2647,11 +2647,11 @@
         </is>
       </c>
       <c r="I19" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J19" s="4" t="inlineStr">
         <is>
-          <t>CURRENT (6d)</t>
+          <t>CURRENT (7d)</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
@@ -2762,11 +2762,11 @@
         </is>
       </c>
       <c r="I20" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J20" s="4" t="inlineStr">
         <is>
-          <t>CURRENT (0d)</t>
+          <t>CURRENT (1d)</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -2992,11 +2992,11 @@
         </is>
       </c>
       <c r="I22" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J22" s="4" t="inlineStr">
         <is>
-          <t>CURRENT (6d)</t>
+          <t>CURRENT (7d)</t>
         </is>
       </c>
       <c r="K22" s="2" t="inlineStr">
@@ -3107,11 +3107,11 @@
         </is>
       </c>
       <c r="I23" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J23" s="4" t="inlineStr">
         <is>
-          <t>CURRENT (0d)</t>
+          <t>CURRENT (1d)</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
@@ -3222,11 +3222,11 @@
         </is>
       </c>
       <c r="I24" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J24" s="4" t="inlineStr">
         <is>
-          <t>CURRENT (0d)</t>
+          <t>CURRENT (1d)</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
@@ -3337,11 +3337,11 @@
         </is>
       </c>
       <c r="I25" s="2" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="J25" s="5" t="inlineStr">
         <is>
-          <t>DUE (11d, cadence weekly)</t>
+          <t>DUE (12d, cadence weekly)</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
@@ -3452,11 +3452,11 @@
         </is>
       </c>
       <c r="I26" s="2" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="J26" s="5" t="inlineStr">
         <is>
-          <t>DUE (56d, cadence monthly)</t>
+          <t>DUE (57d, cadence monthly)</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
@@ -3567,11 +3567,11 @@
         </is>
       </c>
       <c r="I27" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J27" s="4" t="inlineStr">
         <is>
-          <t>CURRENT (6d)</t>
+          <t>CURRENT (7d)</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr"/>
@@ -3678,11 +3678,11 @@
         </is>
       </c>
       <c r="I28" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J28" s="4" t="inlineStr">
         <is>
-          <t>CURRENT (5d)</t>
+          <t>CURRENT (6d)</t>
         </is>
       </c>
       <c r="K28" s="2" t="inlineStr"/>
@@ -3789,11 +3789,11 @@
         </is>
       </c>
       <c r="I29" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J29" s="4" t="inlineStr">
         <is>
-          <t>CURRENT (4d)</t>
+          <t>CURRENT (5d)</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
@@ -3904,11 +3904,11 @@
         </is>
       </c>
       <c r="I30" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J30" s="4" t="inlineStr">
         <is>
-          <t>CURRENT (4d)</t>
+          <t>CURRENT (5d)</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
@@ -4019,11 +4019,11 @@
         </is>
       </c>
       <c r="I31" s="2" t="n">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="J31" s="6" t="inlineStr">
         <is>
-          <t>STALE (91d, cadence monthly)</t>
+          <t>STALE (92d, cadence monthly)</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
@@ -4130,11 +4130,11 @@
         </is>
       </c>
       <c r="I32" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J32" s="4" t="inlineStr">
         <is>
-          <t>CURRENT (4d)</t>
+          <t>CURRENT (5d)</t>
         </is>
       </c>
       <c r="K32" s="2" t="inlineStr">

--- a/data/extracted/series/corpus_publication_cadence_and_audit.xlsx
+++ b/data/extracted/series/corpus_publication_cadence_and_audit.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Corpus Cadence &amp; Inventory" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Graphic &amp; Chart Extraction" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Sub-Sector &amp; Fleet Breakdown" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Corpus Cadence &amp; Inventory" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Graphic &amp; Chart Extraction" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sub-Sector &amp; Fleet Breakdown" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1651,13 +1651,13 @@
         <v>2869</v>
       </c>
       <c r="T10" s="2" t="n">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="U10" s="2" t="n">
         <v>186</v>
       </c>
       <c r="V10" s="2" t="n">
-        <v>3241</v>
+        <v>3242</v>
       </c>
       <c r="W10" s="3" t="inlineStr">
         <is>
@@ -2783,7 +2783,7 @@
         <v>0</v>
       </c>
       <c r="N20" s="2" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="O20" s="2" t="n">
         <v>0</v>
@@ -3218,25 +3218,25 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="I24" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J24" s="4" t="inlineStr">
         <is>
-          <t>CURRENT (1d)</t>
+          <t>CURRENT (0d)</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="M24" s="2" t="n">
@@ -3255,19 +3255,19 @@
         <v>308</v>
       </c>
       <c r="R24" s="2" t="n">
-        <v>3267</v>
+        <v>3269</v>
       </c>
       <c r="S24" s="2" t="n">
-        <v>15140</v>
+        <v>15146</v>
       </c>
       <c r="T24" s="2" t="n">
-        <v>3238</v>
+        <v>3240</v>
       </c>
       <c r="U24" s="2" t="n">
-        <v>3532</v>
+        <v>3534</v>
       </c>
       <c r="V24" s="2" t="n">
-        <v>21953</v>
+        <v>21963</v>
       </c>
       <c r="W24" s="3" t="inlineStr">
         <is>
@@ -3281,7 +3281,7 @@
       </c>
       <c r="Y24" s="3" t="inlineStr">
         <is>
-          <t>breakwave_fundamentals_series.csv (2,781 rows), breakwave_insights_metadata.csv (3,238 rows)</t>
+          <t>breakwave_fundamentals_series.csv (2,781 rows), breakwave_insights_metadata.csv (3,240 rows)</t>
         </is>
       </c>
       <c r="Z24" s="3" t="inlineStr">

--- a/data/extracted/series/corpus_publication_cadence_and_audit.xlsx
+++ b/data/extracted/series/corpus_publication_cadence_and_audit.xlsx
@@ -1536,13 +1536,13 @@
         <v>0</v>
       </c>
       <c r="T9" s="2" t="n">
-        <v>4773</v>
+        <v>4781</v>
       </c>
       <c r="U9" s="2" t="n">
-        <v>4786</v>
+        <v>4791</v>
       </c>
       <c r="V9" s="2" t="n">
-        <v>4773</v>
+        <v>4781</v>
       </c>
       <c r="W9" s="3" t="inlineStr">
         <is>
@@ -1608,25 +1608,25 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="I10" s="2" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="J10" s="4" t="inlineStr">
         <is>
-          <t>CURRENT (6d)</t>
+          <t>CURRENT (0d)</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="M10" s="2" t="n">
@@ -1642,22 +1642,22 @@
         <v>0</v>
       </c>
       <c r="Q10" s="2" t="n">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="R10" s="2" t="n">
         <v>0</v>
       </c>
       <c r="S10" s="2" t="n">
-        <v>2869</v>
+        <v>2893</v>
       </c>
       <c r="T10" s="2" t="n">
+        <v>189</v>
+      </c>
+      <c r="U10" s="2" t="n">
         <v>188</v>
       </c>
-      <c r="U10" s="2" t="n">
-        <v>186</v>
-      </c>
       <c r="V10" s="2" t="n">
-        <v>3242</v>
+        <v>3269</v>
       </c>
       <c r="W10" s="3" t="inlineStr">
         <is>
@@ -2783,7 +2783,7 @@
         <v>0</v>
       </c>
       <c r="N20" s="2" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="O20" s="2" t="n">
         <v>0</v>

--- a/data/extracted/series/corpus_publication_cadence_and_audit.xlsx
+++ b/data/extracted/series/corpus_publication_cadence_and_audit.xlsx
@@ -1539,7 +1539,7 @@
         <v>4781</v>
       </c>
       <c r="U9" s="2" t="n">
-        <v>4791</v>
+        <v>4786</v>
       </c>
       <c r="V9" s="2" t="n">
         <v>4781</v>
@@ -2783,7 +2783,7 @@
         <v>0</v>
       </c>
       <c r="N20" s="2" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="O20" s="2" t="n">
         <v>0</v>

--- a/data/extracted/series/corpus_publication_cadence_and_audit.xlsx
+++ b/data/extracted/series/corpus_publication_cadence_and_audit.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Corpus Cadence &amp; Inventory" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Graphic &amp; Chart Extraction" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sub-Sector &amp; Fleet Breakdown" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Corpus Cadence &amp; Inventory" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Graphic &amp; Chart Extraction" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Sub-Sector &amp; Fleet Breakdown" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -2783,7 +2783,7 @@
         <v>0</v>
       </c>
       <c r="N20" s="2" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="O20" s="2" t="n">
         <v>0</v>

--- a/data/extracted/series/corpus_publication_cadence_and_audit.xlsx
+++ b/data/extracted/series/corpus_publication_cadence_and_audit.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Corpus Cadence &amp; Inventory" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Graphic &amp; Chart Extraction" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Sub-Sector &amp; Fleet Breakdown" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Corpus Cadence &amp; Inventory" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Graphic &amp; Chart Extraction" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sub-Sector &amp; Fleet Breakdown" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -565,7 +565,7 @@
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>Status (2026-10-28)</t>
+          <t>Status (2026-10-29)</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
@@ -696,11 +696,11 @@
         </is>
       </c>
       <c r="I2" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J2" s="4" t="inlineStr">
         <is>
-          <t>CURRENT (4d)</t>
+          <t>CURRENT (5d)</t>
         </is>
       </c>
       <c r="K2" s="2" t="inlineStr">
@@ -811,11 +811,11 @@
         </is>
       </c>
       <c r="I3" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J3" s="4" t="inlineStr">
         <is>
-          <t>CURRENT (4d)</t>
+          <t>CURRENT (5d)</t>
         </is>
       </c>
       <c r="K3" s="2" t="inlineStr">
@@ -926,11 +926,11 @@
         </is>
       </c>
       <c r="I4" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J4" s="4" t="inlineStr">
         <is>
-          <t>CURRENT (5d)</t>
+          <t>CURRENT (6d)</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -1041,11 +1041,11 @@
         </is>
       </c>
       <c r="I5" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="J5" s="4" t="inlineStr">
         <is>
-          <t>CURRENT (7d)</t>
+          <t>CURRENT (8d)</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -1156,11 +1156,11 @@
         </is>
       </c>
       <c r="I6" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J6" s="4" t="inlineStr">
         <is>
-          <t>CURRENT (2d)</t>
+          <t>CURRENT (3d)</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -1271,11 +1271,11 @@
         </is>
       </c>
       <c r="I7" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J7" s="4" t="inlineStr">
         <is>
-          <t>CURRENT (5d)</t>
+          <t>CURRENT (6d)</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
@@ -1386,11 +1386,11 @@
         </is>
       </c>
       <c r="I8" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J8" s="4" t="inlineStr">
         <is>
-          <t>CURRENT (6d)</t>
+          <t>CURRENT (7d)</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -1501,11 +1501,11 @@
         </is>
       </c>
       <c r="I9" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J9" s="4" t="inlineStr">
         <is>
-          <t>CURRENT (0d)</t>
+          <t>CURRENT (1d)</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr"/>
@@ -1539,7 +1539,7 @@
         <v>4781</v>
       </c>
       <c r="U9" s="2" t="n">
-        <v>4786</v>
+        <v>4792</v>
       </c>
       <c r="V9" s="2" t="n">
         <v>4781</v>
@@ -1654,7 +1654,7 @@
         <v>189</v>
       </c>
       <c r="U10" s="2" t="n">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="V10" s="2" t="n">
         <v>3269</v>
@@ -1727,11 +1727,11 @@
         </is>
       </c>
       <c r="I11" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J11" s="4" t="inlineStr">
         <is>
-          <t>CURRENT (5d)</t>
+          <t>CURRENT (6d)</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -1842,11 +1842,11 @@
         </is>
       </c>
       <c r="I12" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="J12" s="4" t="inlineStr">
         <is>
-          <t>CURRENT (7d)</t>
+          <t>CURRENT (8d)</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1957,11 +1957,11 @@
         </is>
       </c>
       <c r="I13" s="2" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="J13" s="5" t="inlineStr">
         <is>
-          <t>DUE (16d, cadence weekly)</t>
+          <t>DUE (17d, cadence weekly)</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
@@ -2072,11 +2072,11 @@
         </is>
       </c>
       <c r="I14" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J14" s="4" t="inlineStr">
         <is>
-          <t>CURRENT (5d)</t>
+          <t>CURRENT (6d)</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2187,11 +2187,11 @@
         </is>
       </c>
       <c r="I15" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J15" s="4" t="inlineStr">
         <is>
-          <t>CURRENT (2d)</t>
+          <t>CURRENT (3d)</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
@@ -2302,11 +2302,11 @@
         </is>
       </c>
       <c r="I16" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J16" s="4" t="inlineStr">
         <is>
-          <t>CURRENT (2d)</t>
+          <t>CURRENT (3d)</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -2417,11 +2417,11 @@
         </is>
       </c>
       <c r="I17" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J17" s="4" t="inlineStr">
         <is>
-          <t>CURRENT (1d)</t>
+          <t>CURRENT (2d)</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -2532,11 +2532,11 @@
         </is>
       </c>
       <c r="I18" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J18" s="4" t="inlineStr">
         <is>
-          <t>CURRENT (1d)</t>
+          <t>CURRENT (2d)</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
@@ -2647,11 +2647,11 @@
         </is>
       </c>
       <c r="I19" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="J19" s="4" t="inlineStr">
         <is>
-          <t>CURRENT (7d)</t>
+          <t>CURRENT (8d)</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
@@ -2762,11 +2762,11 @@
         </is>
       </c>
       <c r="I20" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J20" s="4" t="inlineStr">
         <is>
-          <t>CURRENT (1d)</t>
+          <t>CURRENT (2d)</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -2992,11 +2992,11 @@
         </is>
       </c>
       <c r="I22" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="J22" s="4" t="inlineStr">
         <is>
-          <t>CURRENT (7d)</t>
+          <t>CURRENT (8d)</t>
         </is>
       </c>
       <c r="K22" s="2" t="inlineStr">
@@ -3107,11 +3107,11 @@
         </is>
       </c>
       <c r="I23" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J23" s="4" t="inlineStr">
         <is>
-          <t>CURRENT (1d)</t>
+          <t>CURRENT (2d)</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
@@ -3222,11 +3222,11 @@
         </is>
       </c>
       <c r="I24" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J24" s="4" t="inlineStr">
         <is>
-          <t>CURRENT (0d)</t>
+          <t>CURRENT (1d)</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
@@ -3337,11 +3337,11 @@
         </is>
       </c>
       <c r="I25" s="2" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="J25" s="5" t="inlineStr">
         <is>
-          <t>DUE (12d, cadence weekly)</t>
+          <t>DUE (13d, cadence weekly)</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
@@ -3452,11 +3452,11 @@
         </is>
       </c>
       <c r="I26" s="2" t="n">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="J26" s="5" t="inlineStr">
         <is>
-          <t>DUE (57d, cadence monthly)</t>
+          <t>DUE (58d, cadence monthly)</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
@@ -3567,11 +3567,11 @@
         </is>
       </c>
       <c r="I27" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="J27" s="4" t="inlineStr">
         <is>
-          <t>CURRENT (7d)</t>
+          <t>CURRENT (8d)</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr"/>
@@ -3678,11 +3678,11 @@
         </is>
       </c>
       <c r="I28" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J28" s="4" t="inlineStr">
         <is>
-          <t>CURRENT (6d)</t>
+          <t>CURRENT (7d)</t>
         </is>
       </c>
       <c r="K28" s="2" t="inlineStr"/>
@@ -3789,11 +3789,11 @@
         </is>
       </c>
       <c r="I29" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J29" s="4" t="inlineStr">
         <is>
-          <t>CURRENT (5d)</t>
+          <t>CURRENT (6d)</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
@@ -3904,11 +3904,11 @@
         </is>
       </c>
       <c r="I30" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J30" s="4" t="inlineStr">
         <is>
-          <t>CURRENT (5d)</t>
+          <t>CURRENT (6d)</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
@@ -4019,11 +4019,11 @@
         </is>
       </c>
       <c r="I31" s="2" t="n">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="J31" s="6" t="inlineStr">
         <is>
-          <t>STALE (92d, cadence monthly)</t>
+          <t>STALE (93d, cadence monthly)</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
@@ -4130,11 +4130,11 @@
         </is>
       </c>
       <c r="I32" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J32" s="4" t="inlineStr">
         <is>
-          <t>CURRENT (5d)</t>
+          <t>CURRENT (6d)</t>
         </is>
       </c>
       <c r="K32" s="2" t="inlineStr">

--- a/data/extracted/series/corpus_publication_cadence_and_audit.xlsx
+++ b/data/extracted/series/corpus_publication_cadence_and_audit.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Corpus Cadence &amp; Inventory" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Graphic &amp; Chart Extraction" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sub-Sector &amp; Fleet Breakdown" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Corpus Cadence &amp; Inventory" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Graphic &amp; Chart Extraction" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Sub-Sector &amp; Fleet Breakdown" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1037,25 +1037,25 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="I5" s="2" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="J5" s="4" t="inlineStr">
         <is>
-          <t>CURRENT (8d)</t>
+          <t>CURRENT (1d)</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="M5" s="2" t="n">
@@ -1071,7 +1071,7 @@
         <v>0</v>
       </c>
       <c r="Q5" s="2" t="n">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="R5" s="2" t="n">
         <v>0</v>
@@ -1083,10 +1083,10 @@
         <v>0</v>
       </c>
       <c r="U5" s="2" t="n">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="V5" s="2" t="n">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="W5" s="3" t="inlineStr">
         <is>
@@ -1100,7 +1100,7 @@
       </c>
       <c r="Y5" s="3" t="inlineStr">
         <is>
-          <t>bancosta_freight_rates_series.csv (20,677 rows), bancosta_ffa_series.csv (7,762 rows), bancosta_sales_series.csv (3,261 rows), bancosta_commodities_series.csv (8,573 rows), bancosta_newbuilding_series.csv (2,544 rows), bancosta_secondhand_matrix_series.csv (1,945 rows), bancosta_demolition_series.csv (1,053 rows)</t>
+          <t>bancosta_freight_rates_series.csv (20,767 rows), bancosta_ffa_series.csv (7,798 rows), bancosta_sales_series.csv (3,272 rows), bancosta_commodities_series.csv (8,600 rows), bancosta_newbuilding_series.csv (2,557 rows), bancosta_secondhand_matrix_series.csv (1,952 rows), bancosta_demolition_series.csv (1,059 rows)</t>
         </is>
       </c>
       <c r="Z5" s="3" t="inlineStr">
@@ -1382,25 +1382,25 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="I8" s="2" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="J8" s="4" t="inlineStr">
         <is>
-          <t>CURRENT (7d)</t>
+          <t>CURRENT (0d)</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="M8" s="2" t="n">
@@ -1416,7 +1416,7 @@
         <v>0</v>
       </c>
       <c r="Q8" s="2" t="n">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="R8" s="2" t="n">
         <v>0</v>
@@ -1428,10 +1428,10 @@
         <v>0</v>
       </c>
       <c r="U8" s="2" t="n">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="V8" s="2" t="n">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="W8" s="3" t="inlineStr">
         <is>
@@ -1445,7 +1445,7 @@
       </c>
       <c r="Y8" s="3" t="inlineStr">
         <is>
-          <t>fearnleys_rates_series.csv (17,193 rows)</t>
+          <t>fearnleys_rates_series.csv (17,228 rows)</t>
         </is>
       </c>
       <c r="Z8" s="3" t="inlineStr">
@@ -1838,25 +1838,25 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="I12" s="2" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="J12" s="4" t="inlineStr">
         <is>
-          <t>CURRENT (8d)</t>
+          <t>CURRENT (1d)</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="M12" s="2" t="n">
@@ -1872,7 +1872,7 @@
         <v>0</v>
       </c>
       <c r="Q12" s="2" t="n">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="R12" s="2" t="n">
         <v>0</v>
@@ -1884,10 +1884,10 @@
         <v>0</v>
       </c>
       <c r="U12" s="2" t="n">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="V12" s="2" t="n">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="W12" s="3" t="inlineStr">
         <is>
@@ -1901,7 +1901,7 @@
       </c>
       <c r="Y12" s="3" t="inlineStr">
         <is>
-          <t>intermodal_tc_rates_series.csv (5,293 rows), intermodal_newbuilding_series.csv (5,155 rows), intermodal_tanker_spot_series.csv (3,930 rows), intermodal_sales_series.csv (3,858 rows), intermodal_demolition_series.csv (2,647 rows)</t>
+          <t>intermodal_tc_rates_series.csv (5,313 rows), intermodal_newbuilding_series.csv (5,176 rows), intermodal_tanker_spot_series.csv (3,945 rows), intermodal_sales_series.csv (3,870 rows), intermodal_demolition_series.csv (2,656 rows)</t>
         </is>
       </c>
       <c r="Z12" s="3" t="inlineStr">
@@ -6217,7 +6217,7 @@
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>3,261 rows</t>
+          <t>3,272 rows</t>
         </is>
       </c>
       <c r="H34" s="3" t="inlineStr">
@@ -6264,7 +6264,7 @@
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>3,858 rows</t>
+          <t>3,870 rows</t>
         </is>
       </c>
       <c r="H35" s="3" t="inlineStr">

--- a/data/extracted/series/corpus_publication_cadence_and_audit.xlsx
+++ b/data/extracted/series/corpus_publication_cadence_and_audit.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Corpus Cadence &amp; Inventory" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Graphic &amp; Chart Extraction" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Sub-Sector &amp; Fleet Breakdown" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Corpus Cadence &amp; Inventory" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Graphic &amp; Chart Extraction" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sub-Sector &amp; Fleet Breakdown" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1536,13 +1536,13 @@
         <v>0</v>
       </c>
       <c r="T9" s="2" t="n">
-        <v>4781</v>
+        <v>4782</v>
       </c>
       <c r="U9" s="2" t="n">
         <v>4792</v>
       </c>
       <c r="V9" s="2" t="n">
-        <v>4781</v>
+        <v>4782</v>
       </c>
       <c r="W9" s="3" t="inlineStr">
         <is>
@@ -1642,22 +1642,22 @@
         <v>0</v>
       </c>
       <c r="Q10" s="2" t="n">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="R10" s="2" t="n">
         <v>0</v>
       </c>
       <c r="S10" s="2" t="n">
-        <v>2893</v>
+        <v>2904</v>
       </c>
       <c r="T10" s="2" t="n">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="U10" s="2" t="n">
         <v>189</v>
       </c>
       <c r="V10" s="2" t="n">
-        <v>3269</v>
+        <v>3282</v>
       </c>
       <c r="W10" s="3" t="inlineStr">
         <is>

--- a/data/extracted/series/corpus_publication_cadence_and_audit.xlsx
+++ b/data/extracted/series/corpus_publication_cadence_and_audit.xlsx
@@ -2643,32 +2643,32 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="I19" s="2" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="J19" s="4" t="inlineStr">
         <is>
-          <t>CURRENT (8d)</t>
+          <t>CURRENT (1d)</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="M19" s="2" t="n">
         <v>0</v>
       </c>
       <c r="N19" s="2" t="n">
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="O19" s="2" t="n">
         <v>0</v>
@@ -2680,19 +2680,19 @@
         <v>0</v>
       </c>
       <c r="R19" s="2" t="n">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="S19" s="2" t="n">
-        <v>764</v>
+        <v>766</v>
       </c>
       <c r="T19" s="2" t="n">
         <v>0</v>
       </c>
       <c r="U19" s="2" t="n">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="V19" s="2" t="n">
-        <v>1046</v>
+        <v>1049</v>
       </c>
       <c r="W19" s="3" t="inlineStr">
         <is>
@@ -2706,7 +2706,7 @@
       </c>
       <c r="Y19" s="3" t="inlineStr">
         <is>
-          <t>hellenic_alibra_dry_tc_series.csv (6,587 rows)</t>
+          <t>hellenic_alibra_dry_tc_series.csv (6,611 rows)</t>
         </is>
       </c>
       <c r="Z19" s="3" t="inlineStr">
@@ -2758,32 +2758,32 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="I20" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J20" s="4" t="inlineStr">
         <is>
-          <t>CURRENT (2d)</t>
+          <t>CURRENT (0d)</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="M20" s="2" t="n">
         <v>0</v>
       </c>
       <c r="N20" s="2" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="O20" s="2" t="n">
         <v>0</v>
@@ -2792,7 +2792,7 @@
         <v>0</v>
       </c>
       <c r="Q20" s="2" t="n">
-        <v>3555</v>
+        <v>3559</v>
       </c>
       <c r="R20" s="2" t="n">
         <v>0</v>
@@ -2804,10 +2804,10 @@
         <v>0</v>
       </c>
       <c r="U20" s="2" t="n">
-        <v>1197</v>
+        <v>1199</v>
       </c>
       <c r="V20" s="2" t="n">
-        <v>3555</v>
+        <v>3559</v>
       </c>
       <c r="W20" s="3" t="inlineStr">
         <is>
@@ -2821,7 +2821,7 @@
       </c>
       <c r="Y20" s="3" t="inlineStr">
         <is>
-          <t>hellenic_iron_ore_pdf_brands_series.csv (32,522 rows)</t>
+          <t>hellenic_iron_ore_pdf_brands_series.csv (32,562 rows)</t>
         </is>
       </c>
       <c r="Z20" s="3" t="inlineStr">
@@ -2988,32 +2988,32 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="I22" s="2" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="J22" s="4" t="inlineStr">
         <is>
-          <t>CURRENT (8d)</t>
+          <t>CURRENT (1d)</t>
         </is>
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="M22" s="2" t="n">
         <v>0</v>
       </c>
       <c r="N22" s="2" t="n">
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="O22" s="2" t="n">
         <v>0</v>
@@ -3025,19 +3025,19 @@
         <v>0</v>
       </c>
       <c r="R22" s="2" t="n">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="S22" s="2" t="n">
-        <v>762</v>
+        <v>764</v>
       </c>
       <c r="T22" s="2" t="n">
         <v>0</v>
       </c>
       <c r="U22" s="2" t="n">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="V22" s="2" t="n">
-        <v>1044</v>
+        <v>1047</v>
       </c>
       <c r="W22" s="3" t="inlineStr">
         <is>
@@ -3051,7 +3051,7 @@
       </c>
       <c r="Y22" s="3" t="inlineStr">
         <is>
-          <t>hellenic_alibra_tanker_tc_series.csv (7,504 rows)</t>
+          <t>hellenic_alibra_tanker_tc_series.csv (7,532 rows)</t>
         </is>
       </c>
       <c r="Z22" s="3" t="inlineStr">
@@ -3218,25 +3218,25 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="I24" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J24" s="4" t="inlineStr">
         <is>
-          <t>CURRENT (1d)</t>
+          <t>CURRENT (0d)</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="M24" s="2" t="n">
@@ -3255,19 +3255,19 @@
         <v>308</v>
       </c>
       <c r="R24" s="2" t="n">
-        <v>3269</v>
+        <v>3271</v>
       </c>
       <c r="S24" s="2" t="n">
-        <v>15146</v>
+        <v>15153</v>
       </c>
       <c r="T24" s="2" t="n">
-        <v>3240</v>
+        <v>3242</v>
       </c>
       <c r="U24" s="2" t="n">
-        <v>3534</v>
+        <v>3536</v>
       </c>
       <c r="V24" s="2" t="n">
-        <v>21963</v>
+        <v>21974</v>
       </c>
       <c r="W24" s="3" t="inlineStr">
         <is>
@@ -3281,7 +3281,7 @@
       </c>
       <c r="Y24" s="3" t="inlineStr">
         <is>
-          <t>breakwave_fundamentals_series.csv (2,781 rows), breakwave_insights_metadata.csv (3,240 rows)</t>
+          <t>breakwave_fundamentals_series.csv (2,781 rows), breakwave_insights_metadata.csv (3,242 rows)</t>
         </is>
       </c>
       <c r="Z24" s="3" t="inlineStr">
@@ -5512,7 +5512,7 @@
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>6,587 rows</t>
+          <t>6,611 rows</t>
         </is>
       </c>
       <c r="H19" s="3" t="inlineStr">
@@ -5559,7 +5559,7 @@
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>7,504 rows</t>
+          <t>7,532 rows</t>
         </is>
       </c>
       <c r="H20" s="3" t="inlineStr">
@@ -5606,7 +5606,7 @@
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>32,522 rows</t>
+          <t>32,562 rows</t>
         </is>
       </c>
       <c r="H21" s="3" t="inlineStr">
@@ -5653,7 +5653,7 @@
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>1,195 rows</t>
+          <t>1,197 rows</t>
         </is>
       </c>
       <c r="H22" s="3" t="inlineStr">

--- a/data/extracted/series/corpus_publication_cadence_and_audit.xlsx
+++ b/data/extracted/series/corpus_publication_cadence_and_audit.xlsx
@@ -2668,7 +2668,7 @@
         <v>0</v>
       </c>
       <c r="N19" s="2" t="n">
-        <v>0.4</v>
+        <v>0</v>
       </c>
       <c r="O19" s="2" t="n">
         <v>0</v>
@@ -3013,7 +3013,7 @@
         <v>0</v>
       </c>
       <c r="N22" s="2" t="n">
-        <v>0.4</v>
+        <v>0</v>
       </c>
       <c r="O22" s="2" t="n">
         <v>0</v>

--- a/data/extracted/series/corpus_publication_cadence_and_audit.xlsx
+++ b/data/extracted/series/corpus_publication_cadence_and_audit.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Corpus Cadence &amp; Inventory" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Graphic &amp; Chart Extraction" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sub-Sector &amp; Fleet Breakdown" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Corpus Cadence &amp; Inventory" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Graphic &amp; Chart Extraction" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Sub-Sector &amp; Fleet Breakdown" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -2783,7 +2783,7 @@
         <v>0</v>
       </c>
       <c r="N20" s="2" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="O20" s="2" t="n">
         <v>0</v>

--- a/data/extracted/series/corpus_publication_cadence_and_audit.xlsx
+++ b/data/extracted/series/corpus_publication_cadence_and_audit.xlsx
@@ -565,7 +565,7 @@
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>Status (2026-10-29)</t>
+          <t>Status (2026-10-30)</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
@@ -696,11 +696,11 @@
         </is>
       </c>
       <c r="I2" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J2" s="4" t="inlineStr">
         <is>
-          <t>CURRENT (5d)</t>
+          <t>CURRENT (6d)</t>
         </is>
       </c>
       <c r="K2" s="2" t="inlineStr">
@@ -811,11 +811,11 @@
         </is>
       </c>
       <c r="I3" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J3" s="4" t="inlineStr">
         <is>
-          <t>CURRENT (5d)</t>
+          <t>CURRENT (6d)</t>
         </is>
       </c>
       <c r="K3" s="2" t="inlineStr">
@@ -926,11 +926,11 @@
         </is>
       </c>
       <c r="I4" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J4" s="4" t="inlineStr">
         <is>
-          <t>CURRENT (6d)</t>
+          <t>CURRENT (7d)</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -1041,11 +1041,11 @@
         </is>
       </c>
       <c r="I5" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J5" s="4" t="inlineStr">
         <is>
-          <t>CURRENT (1d)</t>
+          <t>CURRENT (2d)</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -1156,11 +1156,11 @@
         </is>
       </c>
       <c r="I6" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J6" s="4" t="inlineStr">
         <is>
-          <t>CURRENT (3d)</t>
+          <t>CURRENT (4d)</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -1271,11 +1271,11 @@
         </is>
       </c>
       <c r="I7" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J7" s="4" t="inlineStr">
         <is>
-          <t>CURRENT (6d)</t>
+          <t>CURRENT (7d)</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
@@ -1386,11 +1386,11 @@
         </is>
       </c>
       <c r="I8" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J8" s="4" t="inlineStr">
         <is>
-          <t>CURRENT (0d)</t>
+          <t>CURRENT (1d)</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -1501,11 +1501,11 @@
         </is>
       </c>
       <c r="I9" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J9" s="4" t="inlineStr">
         <is>
-          <t>CURRENT (1d)</t>
+          <t>CURRENT (2d)</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr"/>
@@ -1727,11 +1727,11 @@
         </is>
       </c>
       <c r="I11" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J11" s="4" t="inlineStr">
         <is>
-          <t>CURRENT (6d)</t>
+          <t>CURRENT (7d)</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -1842,11 +1842,11 @@
         </is>
       </c>
       <c r="I12" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J12" s="4" t="inlineStr">
         <is>
-          <t>CURRENT (1d)</t>
+          <t>CURRENT (2d)</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1957,11 +1957,11 @@
         </is>
       </c>
       <c r="I13" s="2" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="J13" s="5" t="inlineStr">
         <is>
-          <t>DUE (17d, cadence weekly)</t>
+          <t>DUE (18d, cadence weekly)</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
@@ -2072,11 +2072,11 @@
         </is>
       </c>
       <c r="I14" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J14" s="4" t="inlineStr">
         <is>
-          <t>CURRENT (6d)</t>
+          <t>CURRENT (7d)</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2187,11 +2187,11 @@
         </is>
       </c>
       <c r="I15" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J15" s="4" t="inlineStr">
         <is>
-          <t>CURRENT (3d)</t>
+          <t>CURRENT (4d)</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
@@ -2302,11 +2302,11 @@
         </is>
       </c>
       <c r="I16" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J16" s="4" t="inlineStr">
         <is>
-          <t>CURRENT (3d)</t>
+          <t>CURRENT (4d)</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -2417,11 +2417,11 @@
         </is>
       </c>
       <c r="I17" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J17" s="4" t="inlineStr">
         <is>
-          <t>CURRENT (2d)</t>
+          <t>CURRENT (3d)</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -2532,11 +2532,11 @@
         </is>
       </c>
       <c r="I18" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J18" s="4" t="inlineStr">
         <is>
-          <t>CURRENT (2d)</t>
+          <t>CURRENT (3d)</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
@@ -2647,11 +2647,11 @@
         </is>
       </c>
       <c r="I19" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J19" s="4" t="inlineStr">
         <is>
-          <t>CURRENT (1d)</t>
+          <t>CURRENT (2d)</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
@@ -2762,11 +2762,11 @@
         </is>
       </c>
       <c r="I20" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J20" s="4" t="inlineStr">
         <is>
-          <t>CURRENT (0d)</t>
+          <t>CURRENT (1d)</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -2992,11 +2992,11 @@
         </is>
       </c>
       <c r="I22" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J22" s="4" t="inlineStr">
         <is>
-          <t>CURRENT (1d)</t>
+          <t>CURRENT (2d)</t>
         </is>
       </c>
       <c r="K22" s="2" t="inlineStr">
@@ -3107,11 +3107,11 @@
         </is>
       </c>
       <c r="I23" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J23" s="4" t="inlineStr">
         <is>
-          <t>CURRENT (2d)</t>
+          <t>CURRENT (3d)</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
@@ -3222,11 +3222,11 @@
         </is>
       </c>
       <c r="I24" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J24" s="4" t="inlineStr">
         <is>
-          <t>CURRENT (0d)</t>
+          <t>CURRENT (1d)</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
@@ -3337,11 +3337,11 @@
         </is>
       </c>
       <c r="I25" s="2" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="J25" s="5" t="inlineStr">
         <is>
-          <t>DUE (13d, cadence weekly)</t>
+          <t>DUE (14d, cadence weekly)</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
@@ -3452,11 +3452,11 @@
         </is>
       </c>
       <c r="I26" s="2" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="J26" s="5" t="inlineStr">
         <is>
-          <t>DUE (58d, cadence monthly)</t>
+          <t>DUE (59d, cadence monthly)</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
@@ -3567,11 +3567,11 @@
         </is>
       </c>
       <c r="I27" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J27" s="4" t="inlineStr">
         <is>
-          <t>CURRENT (8d)</t>
+          <t>CURRENT (9d)</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr"/>
@@ -3678,11 +3678,11 @@
         </is>
       </c>
       <c r="I28" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="J28" s="4" t="inlineStr">
         <is>
-          <t>CURRENT (7d)</t>
+          <t>CURRENT (8d)</t>
         </is>
       </c>
       <c r="K28" s="2" t="inlineStr"/>
@@ -3789,11 +3789,11 @@
         </is>
       </c>
       <c r="I29" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J29" s="4" t="inlineStr">
         <is>
-          <t>CURRENT (6d)</t>
+          <t>CURRENT (7d)</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
@@ -3904,11 +3904,11 @@
         </is>
       </c>
       <c r="I30" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J30" s="4" t="inlineStr">
         <is>
-          <t>CURRENT (6d)</t>
+          <t>CURRENT (7d)</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
@@ -4019,11 +4019,11 @@
         </is>
       </c>
       <c r="I31" s="2" t="n">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="J31" s="6" t="inlineStr">
         <is>
-          <t>STALE (93d, cadence monthly)</t>
+          <t>STALE (94d, cadence monthly)</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
@@ -4130,11 +4130,11 @@
         </is>
       </c>
       <c r="I32" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J32" s="4" t="inlineStr">
         <is>
-          <t>CURRENT (6d)</t>
+          <t>CURRENT (7d)</t>
         </is>
       </c>
       <c r="K32" s="2" t="inlineStr">

--- a/data/extracted/series/corpus_publication_cadence_and_audit.xlsx
+++ b/data/extracted/series/corpus_publication_cadence_and_audit.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Corpus Cadence &amp; Inventory" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Graphic &amp; Chart Extraction" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Sub-Sector &amp; Fleet Breakdown" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Corpus Cadence &amp; Inventory" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Graphic &amp; Chart Extraction" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sub-Sector &amp; Fleet Breakdown" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1651,13 +1651,13 @@
         <v>2904</v>
       </c>
       <c r="T10" s="2" t="n">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="U10" s="2" t="n">
         <v>189</v>
       </c>
       <c r="V10" s="2" t="n">
-        <v>3282</v>
+        <v>3283</v>
       </c>
       <c r="W10" s="3" t="inlineStr">
         <is>
@@ -2758,32 +2758,32 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="I20" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J20" s="4" t="inlineStr">
         <is>
-          <t>CURRENT (1d)</t>
+          <t>CURRENT (0d)</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="M20" s="2" t="n">
         <v>0</v>
       </c>
       <c r="N20" s="2" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="O20" s="2" t="n">
         <v>0</v>
@@ -2792,7 +2792,7 @@
         <v>0</v>
       </c>
       <c r="Q20" s="2" t="n">
-        <v>3559</v>
+        <v>3561</v>
       </c>
       <c r="R20" s="2" t="n">
         <v>0</v>
@@ -2804,10 +2804,10 @@
         <v>0</v>
       </c>
       <c r="U20" s="2" t="n">
-        <v>1199</v>
+        <v>1200</v>
       </c>
       <c r="V20" s="2" t="n">
-        <v>3559</v>
+        <v>3561</v>
       </c>
       <c r="W20" s="3" t="inlineStr">
         <is>
@@ -2821,7 +2821,7 @@
       </c>
       <c r="Y20" s="3" t="inlineStr">
         <is>
-          <t>hellenic_iron_ore_pdf_brands_series.csv (32,562 rows)</t>
+          <t>hellenic_iron_ore_pdf_brands_series.csv (32,582 rows)</t>
         </is>
       </c>
       <c r="Z20" s="3" t="inlineStr">
@@ -3218,25 +3218,25 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="I24" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J24" s="4" t="inlineStr">
         <is>
-          <t>CURRENT (1d)</t>
+          <t>CURRENT (0d)</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="M24" s="2" t="n">
@@ -3255,19 +3255,19 @@
         <v>308</v>
       </c>
       <c r="R24" s="2" t="n">
-        <v>3271</v>
+        <v>3273</v>
       </c>
       <c r="S24" s="2" t="n">
-        <v>15153</v>
+        <v>15156</v>
       </c>
       <c r="T24" s="2" t="n">
-        <v>3242</v>
+        <v>3244</v>
       </c>
       <c r="U24" s="2" t="n">
-        <v>3536</v>
+        <v>3538</v>
       </c>
       <c r="V24" s="2" t="n">
-        <v>21974</v>
+        <v>21981</v>
       </c>
       <c r="W24" s="3" t="inlineStr">
         <is>
@@ -3281,7 +3281,7 @@
       </c>
       <c r="Y24" s="3" t="inlineStr">
         <is>
-          <t>breakwave_fundamentals_series.csv (2,781 rows), breakwave_insights_metadata.csv (3,242 rows)</t>
+          <t>breakwave_fundamentals_series.csv (2,781 rows), breakwave_insights_metadata.csv (3,244 rows)</t>
         </is>
       </c>
       <c r="Z24" s="3" t="inlineStr">
@@ -3900,25 +3900,25 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="I30" s="2" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="J30" s="4" t="inlineStr">
         <is>
-          <t>CURRENT (7d)</t>
+          <t>CURRENT (0d)</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="M30" s="2" t="n">
@@ -3937,19 +3937,19 @@
         <v>0</v>
       </c>
       <c r="R30" s="2" t="n">
-        <v>3064</v>
+        <v>3069</v>
       </c>
       <c r="S30" s="2" t="n">
         <v>0</v>
       </c>
       <c r="T30" s="2" t="n">
-        <v>2244</v>
+        <v>2249</v>
       </c>
       <c r="U30" s="2" t="n">
-        <v>2244</v>
+        <v>2249</v>
       </c>
       <c r="V30" s="2" t="n">
-        <v>5308</v>
+        <v>5318</v>
       </c>
       <c r="W30" s="3" t="inlineStr">
         <is>
@@ -3963,7 +3963,7 @@
       </c>
       <c r="Y30" s="3" t="inlineStr">
         <is>
-          <t>baltic_reports_metadata.csv (2,244 rows), baltic_ncfi_series.csv (2,057 rows)</t>
+          <t>baltic_reports_metadata.csv (2,249 rows), baltic_ncfi_series.csv (2,061 rows)</t>
         </is>
       </c>
       <c r="Z30" s="3" t="inlineStr">
@@ -5606,7 +5606,7 @@
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>32,562 rows</t>
+          <t>32,582 rows</t>
         </is>
       </c>
       <c r="H21" s="3" t="inlineStr">
@@ -5653,7 +5653,7 @@
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>1,197 rows</t>
+          <t>1,198 rows</t>
         </is>
       </c>
       <c r="H22" s="3" t="inlineStr">

--- a/data/extracted/series/corpus_publication_cadence_and_audit.xlsx
+++ b/data/extracted/series/corpus_publication_cadence_and_audit.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Corpus Cadence &amp; Inventory" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Graphic &amp; Chart Extraction" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sub-Sector &amp; Fleet Breakdown" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Corpus Cadence &amp; Inventory" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Graphic &amp; Chart Extraction" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Sub-Sector &amp; Fleet Breakdown" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -2783,7 +2783,7 @@
         <v>0</v>
       </c>
       <c r="N20" s="2" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="O20" s="2" t="n">
         <v>0</v>
@@ -3563,21 +3563,21 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="I27" s="2" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="J27" s="4" t="inlineStr">
         <is>
-          <t>CURRENT (9d)</t>
+          <t>CURRENT (3d)</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr"/>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="M27" s="2" t="n">
@@ -3593,7 +3593,7 @@
         <v>0</v>
       </c>
       <c r="Q27" s="2" t="n">
-        <v>297</v>
+        <v>300</v>
       </c>
       <c r="R27" s="2" t="n">
         <v>0</v>
@@ -3605,10 +3605,10 @@
         <v>0</v>
       </c>
       <c r="U27" s="2" t="n">
-        <v>297</v>
+        <v>300</v>
       </c>
       <c r="V27" s="2" t="n">
-        <v>298</v>
+        <v>301</v>
       </c>
       <c r="W27" s="3" t="inlineStr">
         <is>
@@ -3622,7 +3622,7 @@
       </c>
       <c r="Y27" s="3" t="inlineStr">
         <is>
-          <t>drewry_ais_chart_series.csv (83,396 rows)</t>
+          <t>drewry_ais_chart_series.csv (83,699 rows)</t>
         </is>
       </c>
       <c r="Z27" s="3" t="inlineStr">
@@ -3674,21 +3674,21 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="I28" s="2" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="J28" s="4" t="inlineStr">
         <is>
-          <t>CURRENT (8d)</t>
+          <t>CURRENT (0d)</t>
         </is>
       </c>
       <c r="K28" s="2" t="inlineStr"/>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="M28" s="2" t="n">
@@ -3713,13 +3713,13 @@
         <v>0</v>
       </c>
       <c r="T28" s="2" t="n">
-        <v>1099</v>
+        <v>1103</v>
       </c>
       <c r="U28" s="2" t="n">
-        <v>558</v>
+        <v>562</v>
       </c>
       <c r="V28" s="2" t="n">
-        <v>1105</v>
+        <v>1109</v>
       </c>
       <c r="W28" s="3" t="inlineStr">
         <is>
@@ -3733,7 +3733,7 @@
       </c>
       <c r="Y28" s="3" t="inlineStr">
         <is>
-          <t>drewry_wci_historical.csv (139 rows), drewry_opinions_metadata.csv (558 rows), drewry_wci_series.csv (9 rows)</t>
+          <t>drewry_wci_historical.csv (140 rows), drewry_opinions_metadata.csv (562 rows), drewry_wci_series.csv (10 rows)</t>
         </is>
       </c>
       <c r="Z28" s="3" t="inlineStr">
@@ -4713,7 +4713,7 @@
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>83,396 rows</t>
+          <t>83,699 rows</t>
         </is>
       </c>
       <c r="H2" s="3" t="inlineStr">
@@ -4760,7 +4760,7 @@
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>83,396 rows</t>
+          <t>83,699 rows</t>
         </is>
       </c>
       <c r="H3" s="3" t="inlineStr">
@@ -4807,7 +4807,7 @@
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>83,396 rows</t>
+          <t>83,699 rows</t>
         </is>
       </c>
       <c r="H4" s="3" t="inlineStr">
@@ -4854,7 +4854,7 @@
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>83,396 rows</t>
+          <t>83,699 rows</t>
         </is>
       </c>
       <c r="H5" s="3" t="inlineStr">
@@ -4901,7 +4901,7 @@
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>83,396 rows</t>
+          <t>83,699 rows</t>
         </is>
       </c>
       <c r="H6" s="3" t="inlineStr">
@@ -4948,7 +4948,7 @@
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>83,396 rows</t>
+          <t>83,699 rows</t>
         </is>
       </c>
       <c r="H7" s="3" t="inlineStr">
@@ -4995,7 +4995,7 @@
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>83,396 rows</t>
+          <t>83,699 rows</t>
         </is>
       </c>
       <c r="H8" s="3" t="inlineStr">
@@ -5042,7 +5042,7 @@
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>83,396 rows</t>
+          <t>83,699 rows</t>
         </is>
       </c>
       <c r="H9" s="3" t="inlineStr">
@@ -5089,7 +5089,7 @@
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>83,396 rows</t>
+          <t>83,699 rows</t>
         </is>
       </c>
       <c r="H10" s="3" t="inlineStr">
@@ -5136,7 +5136,7 @@
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>83,396 rows</t>
+          <t>83,699 rows</t>
         </is>
       </c>
       <c r="H11" s="3" t="inlineStr">
@@ -5183,7 +5183,7 @@
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>83,396 rows</t>
+          <t>83,699 rows</t>
         </is>
       </c>
       <c r="H12" s="3" t="inlineStr">
@@ -5230,7 +5230,7 @@
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>83,396 rows</t>
+          <t>83,699 rows</t>
         </is>
       </c>
       <c r="H13" s="3" t="inlineStr">
@@ -5277,7 +5277,7 @@
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>83,396 rows</t>
+          <t>83,699 rows</t>
         </is>
       </c>
       <c r="H14" s="3" t="inlineStr">
@@ -6311,7 +6311,7 @@
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>139 rows</t>
+          <t>140 rows</t>
         </is>
       </c>
       <c r="H36" s="3" t="inlineStr">

--- a/data/extracted/series/corpus_publication_cadence_and_audit.xlsx
+++ b/data/extracted/series/corpus_publication_cadence_and_audit.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Corpus Cadence &amp; Inventory" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Graphic &amp; Chart Extraction" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Sub-Sector &amp; Fleet Breakdown" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Corpus Cadence &amp; Inventory" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Graphic &amp; Chart Extraction" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sub-Sector &amp; Fleet Breakdown" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1267,25 +1267,25 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J7" s="4" t="inlineStr">
+        <is>
+          <t>CURRENT (0d)</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
           <t>2026-10-23</t>
         </is>
       </c>
-      <c r="I7" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="J7" s="4" t="inlineStr">
-        <is>
-          <t>CURRENT (7d)</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-23</t>
-        </is>
-      </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="M7" s="2" t="n">
@@ -1301,7 +1301,7 @@
         <v>0</v>
       </c>
       <c r="Q7" s="2" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="R7" s="2" t="n">
         <v>0</v>
@@ -1313,10 +1313,10 @@
         <v>0</v>
       </c>
       <c r="U7" s="2" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="V7" s="2" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="W7" s="3" t="inlineStr">
         <is>
@@ -1330,7 +1330,7 @@
       </c>
       <c r="Y7" s="3" t="inlineStr">
         <is>
-          <t>clarksons_sales_series.csv (1,388 rows)</t>
+          <t>clarksons_sales_series.csv (1,393 rows)</t>
         </is>
       </c>
       <c r="Z7" s="3" t="inlineStr">
@@ -2068,25 +2068,25 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="I14" s="2" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="J14" s="4" t="inlineStr">
         <is>
-          <t>CURRENT (7d)</t>
+          <t>CURRENT (0d)</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="M14" s="2" t="n">
@@ -2102,7 +2102,7 @@
         <v>0</v>
       </c>
       <c r="Q14" s="2" t="n">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="R14" s="2" t="n">
         <v>0</v>
@@ -2114,10 +2114,10 @@
         <v>0</v>
       </c>
       <c r="U14" s="2" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="V14" s="2" t="n">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="W14" s="3" t="inlineStr">
         <is>
@@ -2131,7 +2131,7 @@
       </c>
       <c r="Y14" s="3" t="inlineStr">
         <is>
-          <t>lion_deals_series.csv (1,369 rows), lion_sales_series.csv (1,255 rows), lion_demometer_series.csv (600 rows), lion_demolition_series.csv (600 rows), lion_demo_sales_series.csv (114 rows)</t>
+          <t>lion_deals_series.csv (1,385 rows), lion_sales_series.csv (1,270 rows), lion_demometer_series.csv (612 rows), lion_demolition_series.csv (600 rows), lion_demo_sales_series.csv (115 rows)</t>
         </is>
       </c>
       <c r="Z14" s="3" t="inlineStr">
@@ -2783,7 +2783,7 @@
         <v>0</v>
       </c>
       <c r="N20" s="2" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="O20" s="2" t="n">
         <v>0</v>
@@ -3563,21 +3563,21 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="I27" s="2" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="J27" s="4" t="inlineStr">
         <is>
-          <t>CURRENT (3d)</t>
+          <t>CURRENT (9d)</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr"/>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="M27" s="2" t="n">
@@ -3593,7 +3593,7 @@
         <v>0</v>
       </c>
       <c r="Q27" s="2" t="n">
-        <v>300</v>
+        <v>297</v>
       </c>
       <c r="R27" s="2" t="n">
         <v>0</v>
@@ -3605,10 +3605,10 @@
         <v>0</v>
       </c>
       <c r="U27" s="2" t="n">
-        <v>300</v>
+        <v>297</v>
       </c>
       <c r="V27" s="2" t="n">
-        <v>301</v>
+        <v>298</v>
       </c>
       <c r="W27" s="3" t="inlineStr">
         <is>
@@ -3622,7 +3622,7 @@
       </c>
       <c r="Y27" s="3" t="inlineStr">
         <is>
-          <t>drewry_ais_chart_series.csv (83,699 rows)</t>
+          <t>drewry_ais_chart_series.csv (83,396 rows)</t>
         </is>
       </c>
       <c r="Z27" s="3" t="inlineStr">
@@ -3674,21 +3674,21 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="I28" s="2" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="J28" s="4" t="inlineStr">
         <is>
-          <t>CURRENT (0d)</t>
+          <t>CURRENT (8d)</t>
         </is>
       </c>
       <c r="K28" s="2" t="inlineStr"/>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="M28" s="2" t="n">
@@ -3713,13 +3713,13 @@
         <v>0</v>
       </c>
       <c r="T28" s="2" t="n">
-        <v>1103</v>
+        <v>1099</v>
       </c>
       <c r="U28" s="2" t="n">
-        <v>562</v>
+        <v>558</v>
       </c>
       <c r="V28" s="2" t="n">
-        <v>1109</v>
+        <v>1105</v>
       </c>
       <c r="W28" s="3" t="inlineStr">
         <is>
@@ -3733,7 +3733,7 @@
       </c>
       <c r="Y28" s="3" t="inlineStr">
         <is>
-          <t>drewry_wci_historical.csv (140 rows), drewry_opinions_metadata.csv (562 rows), drewry_wci_series.csv (10 rows)</t>
+          <t>drewry_wci_historical.csv (139 rows), drewry_opinions_metadata.csv (558 rows), drewry_wci_series.csv (9 rows)</t>
         </is>
       </c>
       <c r="Z28" s="3" t="inlineStr">
@@ -4713,7 +4713,7 @@
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>83,699 rows</t>
+          <t>83,396 rows</t>
         </is>
       </c>
       <c r="H2" s="3" t="inlineStr">
@@ -4760,7 +4760,7 @@
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>83,699 rows</t>
+          <t>83,396 rows</t>
         </is>
       </c>
       <c r="H3" s="3" t="inlineStr">
@@ -4807,7 +4807,7 @@
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>83,699 rows</t>
+          <t>83,396 rows</t>
         </is>
       </c>
       <c r="H4" s="3" t="inlineStr">
@@ -4854,7 +4854,7 @@
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>83,699 rows</t>
+          <t>83,396 rows</t>
         </is>
       </c>
       <c r="H5" s="3" t="inlineStr">
@@ -4901,7 +4901,7 @@
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>83,699 rows</t>
+          <t>83,396 rows</t>
         </is>
       </c>
       <c r="H6" s="3" t="inlineStr">
@@ -4948,7 +4948,7 @@
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>83,699 rows</t>
+          <t>83,396 rows</t>
         </is>
       </c>
       <c r="H7" s="3" t="inlineStr">
@@ -4995,7 +4995,7 @@
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>83,699 rows</t>
+          <t>83,396 rows</t>
         </is>
       </c>
       <c r="H8" s="3" t="inlineStr">
@@ -5042,7 +5042,7 @@
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>83,699 rows</t>
+          <t>83,396 rows</t>
         </is>
       </c>
       <c r="H9" s="3" t="inlineStr">
@@ -5089,7 +5089,7 @@
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>83,699 rows</t>
+          <t>83,396 rows</t>
         </is>
       </c>
       <c r="H10" s="3" t="inlineStr">
@@ -5136,7 +5136,7 @@
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>83,699 rows</t>
+          <t>83,396 rows</t>
         </is>
       </c>
       <c r="H11" s="3" t="inlineStr">
@@ -5183,7 +5183,7 @@
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>83,699 rows</t>
+          <t>83,396 rows</t>
         </is>
       </c>
       <c r="H12" s="3" t="inlineStr">
@@ -5230,7 +5230,7 @@
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>83,699 rows</t>
+          <t>83,396 rows</t>
         </is>
       </c>
       <c r="H13" s="3" t="inlineStr">
@@ -5277,7 +5277,7 @@
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>83,699 rows</t>
+          <t>83,396 rows</t>
         </is>
       </c>
       <c r="H14" s="3" t="inlineStr">
@@ -6311,7 +6311,7 @@
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>140 rows</t>
+          <t>139 rows</t>
         </is>
       </c>
       <c r="H36" s="3" t="inlineStr">

--- a/data/extracted/series/corpus_publication_cadence_and_audit.xlsx
+++ b/data/extracted/series/corpus_publication_cadence_and_audit.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Corpus Cadence &amp; Inventory" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Graphic &amp; Chart Extraction" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sub-Sector &amp; Fleet Breakdown" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Corpus Cadence &amp; Inventory" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Graphic &amp; Chart Extraction" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Sub-Sector &amp; Fleet Breakdown" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1723,25 +1723,25 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="I11" s="2" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="J11" s="4" t="inlineStr">
         <is>
-          <t>CURRENT (7d)</t>
+          <t>CURRENT (0d)</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="M11" s="2" t="n">
@@ -1760,7 +1760,7 @@
         <v>109</v>
       </c>
       <c r="R11" s="2" t="n">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="S11" s="2" t="n">
         <v>0</v>
@@ -1769,10 +1769,10 @@
         <v>0</v>
       </c>
       <c r="U11" s="2" t="n">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="V11" s="2" t="n">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="W11" s="3" t="inlineStr">
         <is>
@@ -1786,7 +1786,7 @@
       </c>
       <c r="Y11" s="3" t="inlineStr">
         <is>
-          <t>gibson_tanker_spot_series.csv (3,626 rows), gibson_bunker_prices_series.csv (1,036 rows), gibson_master_tanker_series.xlsx</t>
+          <t>gibson_tanker_spot_series.csv (3,640 rows), gibson_bunker_prices_series.csv (1,040 rows), gibson_master_tanker_series.xlsx</t>
         </is>
       </c>
       <c r="Z11" s="3" t="inlineStr">
@@ -2131,7 +2131,7 @@
       </c>
       <c r="Y14" s="3" t="inlineStr">
         <is>
-          <t>lion_deals_series.csv (1,385 rows), lion_sales_series.csv (1,270 rows), lion_demometer_series.csv (612 rows), lion_demolition_series.csv (600 rows), lion_demo_sales_series.csv (115 rows)</t>
+          <t>lion_deals_series.csv (1,385 rows), lion_sales_series.csv (1,270 rows), lion_demometer_series.csv (612 rows), lion_demolition_series.csv (612 rows), lion_demo_sales_series.csv (115 rows)</t>
         </is>
       </c>
       <c r="Z14" s="3" t="inlineStr">
@@ -2783,7 +2783,7 @@
         <v>0</v>
       </c>
       <c r="N20" s="2" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="O20" s="2" t="n">
         <v>0</v>
@@ -3563,21 +3563,21 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="I27" s="2" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="J27" s="4" t="inlineStr">
         <is>
-          <t>CURRENT (9d)</t>
+          <t>CURRENT (3d)</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr"/>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="M27" s="2" t="n">
@@ -3593,7 +3593,7 @@
         <v>0</v>
       </c>
       <c r="Q27" s="2" t="n">
-        <v>297</v>
+        <v>300</v>
       </c>
       <c r="R27" s="2" t="n">
         <v>0</v>
@@ -3605,10 +3605,10 @@
         <v>0</v>
       </c>
       <c r="U27" s="2" t="n">
-        <v>297</v>
+        <v>300</v>
       </c>
       <c r="V27" s="2" t="n">
-        <v>298</v>
+        <v>301</v>
       </c>
       <c r="W27" s="3" t="inlineStr">
         <is>
@@ -3622,7 +3622,7 @@
       </c>
       <c r="Y27" s="3" t="inlineStr">
         <is>
-          <t>drewry_ais_chart_series.csv (83,396 rows)</t>
+          <t>drewry_ais_chart_series.csv (83,699 rows)</t>
         </is>
       </c>
       <c r="Z27" s="3" t="inlineStr">
@@ -3674,21 +3674,21 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="I28" s="2" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="J28" s="4" t="inlineStr">
         <is>
-          <t>CURRENT (8d)</t>
+          <t>CURRENT (0d)</t>
         </is>
       </c>
       <c r="K28" s="2" t="inlineStr"/>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="M28" s="2" t="n">
@@ -3713,13 +3713,13 @@
         <v>0</v>
       </c>
       <c r="T28" s="2" t="n">
-        <v>1099</v>
+        <v>1103</v>
       </c>
       <c r="U28" s="2" t="n">
-        <v>558</v>
+        <v>562</v>
       </c>
       <c r="V28" s="2" t="n">
-        <v>1105</v>
+        <v>1109</v>
       </c>
       <c r="W28" s="3" t="inlineStr">
         <is>
@@ -3733,7 +3733,7 @@
       </c>
       <c r="Y28" s="3" t="inlineStr">
         <is>
-          <t>drewry_wci_historical.csv (139 rows), drewry_opinions_metadata.csv (558 rows), drewry_wci_series.csv (9 rows)</t>
+          <t>drewry_wci_historical.csv (140 rows), drewry_opinions_metadata.csv (562 rows), drewry_wci_series.csv (10 rows)</t>
         </is>
       </c>
       <c r="Z28" s="3" t="inlineStr">
@@ -4713,7 +4713,7 @@
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>83,396 rows</t>
+          <t>83,699 rows</t>
         </is>
       </c>
       <c r="H2" s="3" t="inlineStr">
@@ -4760,7 +4760,7 @@
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>83,396 rows</t>
+          <t>83,699 rows</t>
         </is>
       </c>
       <c r="H3" s="3" t="inlineStr">
@@ -4807,7 +4807,7 @@
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>83,396 rows</t>
+          <t>83,699 rows</t>
         </is>
       </c>
       <c r="H4" s="3" t="inlineStr">
@@ -4854,7 +4854,7 @@
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>83,396 rows</t>
+          <t>83,699 rows</t>
         </is>
       </c>
       <c r="H5" s="3" t="inlineStr">
@@ -4901,7 +4901,7 @@
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>83,396 rows</t>
+          <t>83,699 rows</t>
         </is>
       </c>
       <c r="H6" s="3" t="inlineStr">
@@ -4948,7 +4948,7 @@
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>83,396 rows</t>
+          <t>83,699 rows</t>
         </is>
       </c>
       <c r="H7" s="3" t="inlineStr">
@@ -4995,7 +4995,7 @@
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>83,396 rows</t>
+          <t>83,699 rows</t>
         </is>
       </c>
       <c r="H8" s="3" t="inlineStr">
@@ -5042,7 +5042,7 @@
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>83,396 rows</t>
+          <t>83,699 rows</t>
         </is>
       </c>
       <c r="H9" s="3" t="inlineStr">
@@ -5089,7 +5089,7 @@
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>83,396 rows</t>
+          <t>83,699 rows</t>
         </is>
       </c>
       <c r="H10" s="3" t="inlineStr">
@@ -5136,7 +5136,7 @@
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>83,396 rows</t>
+          <t>83,699 rows</t>
         </is>
       </c>
       <c r="H11" s="3" t="inlineStr">
@@ -5183,7 +5183,7 @@
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>83,396 rows</t>
+          <t>83,699 rows</t>
         </is>
       </c>
       <c r="H12" s="3" t="inlineStr">
@@ -5230,7 +5230,7 @@
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>83,396 rows</t>
+          <t>83,699 rows</t>
         </is>
       </c>
       <c r="H13" s="3" t="inlineStr">
@@ -5277,7 +5277,7 @@
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>83,396 rows</t>
+          <t>83,699 rows</t>
         </is>
       </c>
       <c r="H14" s="3" t="inlineStr">
@@ -6311,7 +6311,7 @@
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>139 rows</t>
+          <t>140 rows</t>
         </is>
       </c>
       <c r="H36" s="3" t="inlineStr">

--- a/data/extracted/series/corpus_publication_cadence_and_audit.xlsx
+++ b/data/extracted/series/corpus_publication_cadence_and_audit.xlsx
@@ -3785,15 +3785,15 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="I29" s="2" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="J29" s="4" t="inlineStr">
         <is>
-          <t>CURRENT (7d)</t>
+          <t>CURRENT (1d)</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
@@ -3803,7 +3803,7 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="M29" s="2" t="n">
@@ -3822,19 +3822,19 @@
         <v>10</v>
       </c>
       <c r="R29" s="2" t="n">
-        <v>523</v>
+        <v>525</v>
       </c>
       <c r="S29" s="2" t="n">
-        <v>1570</v>
+        <v>1590</v>
       </c>
       <c r="T29" s="2" t="n">
-        <v>458</v>
+        <v>460</v>
       </c>
       <c r="U29" s="2" t="n">
-        <v>454</v>
+        <v>456</v>
       </c>
       <c r="V29" s="2" t="n">
-        <v>2987</v>
+        <v>3011</v>
       </c>
       <c r="W29" s="3" t="inlineStr">
         <is>
@@ -3848,7 +3848,7 @@
       </c>
       <c r="Y29" s="3" t="inlineStr">
         <is>
-          <t>signal_reports_metadata.csv (454 rows), signal_vessel_counts_series.csv (120 rows), data/views/signal/live_fleet_positions.json (9,082 tracked hulls), data/views/signal/port_queues_active.json (1,932 ports)</t>
+          <t>signal_reports_metadata.csv (456 rows), signal_vessel_counts_series.csv (120 rows), data/views/signal/live_fleet_positions.json (9,082 tracked hulls), data/views/signal/port_queues_active.json (1,932 ports)</t>
         </is>
       </c>
       <c r="Z29" s="3" t="inlineStr">
@@ -6076,7 +6076,7 @@
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>454 rows</t>
+          <t>456 rows</t>
         </is>
       </c>
       <c r="H31" s="3" t="inlineStr">

--- a/data/extracted/series/corpus_publication_cadence_and_audit.xlsx
+++ b/data/extracted/series/corpus_publication_cadence_and_audit.xlsx
@@ -565,7 +565,7 @@
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>Status (2026-10-30)</t>
+          <t>Status (2026-10-31)</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
@@ -696,11 +696,11 @@
         </is>
       </c>
       <c r="I2" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J2" s="4" t="inlineStr">
         <is>
-          <t>CURRENT (6d)</t>
+          <t>CURRENT (7d)</t>
         </is>
       </c>
       <c r="K2" s="2" t="inlineStr">
@@ -807,25 +807,25 @@
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="I3" s="2" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="J3" s="4" t="inlineStr">
         <is>
-          <t>CURRENT (6d)</t>
+          <t>CURRENT (0d)</t>
         </is>
       </c>
       <c r="K3" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="L3" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="M3" s="2" t="n">
@@ -841,7 +841,7 @@
         <v>0</v>
       </c>
       <c r="Q3" s="2" t="n">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="R3" s="2" t="n">
         <v>0</v>
@@ -853,10 +853,10 @@
         <v>0</v>
       </c>
       <c r="U3" s="2" t="n">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="V3" s="2" t="n">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="W3" s="3" t="inlineStr">
         <is>
@@ -870,7 +870,7 @@
       </c>
       <c r="Y3" s="3" t="inlineStr">
         <is>
-          <t>affinity_tce_series.csv (4,096 rows), affinity_bda_series.csv (753 rows), affinity_indices_series.csv (502 rows)</t>
+          <t>affinity_tce_series.csv (4,115 rows), affinity_bda_series.csv (756 rows), affinity_indices_series.csv (504 rows)</t>
         </is>
       </c>
       <c r="Z3" s="3" t="inlineStr">
@@ -926,11 +926,11 @@
         </is>
       </c>
       <c r="I4" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="J4" s="4" t="inlineStr">
         <is>
-          <t>CURRENT (7d)</t>
+          <t>CURRENT (8d)</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -1041,11 +1041,11 @@
         </is>
       </c>
       <c r="I5" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J5" s="4" t="inlineStr">
         <is>
-          <t>CURRENT (2d)</t>
+          <t>CURRENT (3d)</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -1156,11 +1156,11 @@
         </is>
       </c>
       <c r="I6" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J6" s="4" t="inlineStr">
         <is>
-          <t>CURRENT (4d)</t>
+          <t>CURRENT (5d)</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -1271,11 +1271,11 @@
         </is>
       </c>
       <c r="I7" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J7" s="4" t="inlineStr">
         <is>
-          <t>CURRENT (0d)</t>
+          <t>CURRENT (1d)</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
@@ -1386,11 +1386,11 @@
         </is>
       </c>
       <c r="I8" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J8" s="4" t="inlineStr">
         <is>
-          <t>CURRENT (1d)</t>
+          <t>CURRENT (2d)</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -1501,11 +1501,11 @@
         </is>
       </c>
       <c r="I9" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J9" s="4" t="inlineStr">
         <is>
-          <t>CURRENT (2d)</t>
+          <t>CURRENT (3d)</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr"/>
@@ -1612,11 +1612,11 @@
         </is>
       </c>
       <c r="I10" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J10" s="4" t="inlineStr">
         <is>
-          <t>CURRENT (0d)</t>
+          <t>CURRENT (1d)</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1727,11 +1727,11 @@
         </is>
       </c>
       <c r="I11" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J11" s="4" t="inlineStr">
         <is>
-          <t>CURRENT (0d)</t>
+          <t>CURRENT (1d)</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -1842,11 +1842,11 @@
         </is>
       </c>
       <c r="I12" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J12" s="4" t="inlineStr">
         <is>
-          <t>CURRENT (2d)</t>
+          <t>CURRENT (3d)</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1957,11 +1957,11 @@
         </is>
       </c>
       <c r="I13" s="2" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J13" s="5" t="inlineStr">
         <is>
-          <t>DUE (18d, cadence weekly)</t>
+          <t>DUE (19d, cadence weekly)</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
@@ -2072,11 +2072,11 @@
         </is>
       </c>
       <c r="I14" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J14" s="4" t="inlineStr">
         <is>
-          <t>CURRENT (0d)</t>
+          <t>CURRENT (1d)</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2187,11 +2187,11 @@
         </is>
       </c>
       <c r="I15" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J15" s="4" t="inlineStr">
         <is>
-          <t>CURRENT (4d)</t>
+          <t>CURRENT (5d)</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
@@ -2302,11 +2302,11 @@
         </is>
       </c>
       <c r="I16" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J16" s="4" t="inlineStr">
         <is>
-          <t>CURRENT (4d)</t>
+          <t>CURRENT (5d)</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -2417,11 +2417,11 @@
         </is>
       </c>
       <c r="I17" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J17" s="4" t="inlineStr">
         <is>
-          <t>CURRENT (3d)</t>
+          <t>CURRENT (4d)</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -2532,11 +2532,11 @@
         </is>
       </c>
       <c r="I18" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J18" s="4" t="inlineStr">
         <is>
-          <t>CURRENT (3d)</t>
+          <t>CURRENT (4d)</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
@@ -2647,11 +2647,11 @@
         </is>
       </c>
       <c r="I19" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J19" s="4" t="inlineStr">
         <is>
-          <t>CURRENT (2d)</t>
+          <t>CURRENT (3d)</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
@@ -2762,11 +2762,11 @@
         </is>
       </c>
       <c r="I20" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J20" s="4" t="inlineStr">
         <is>
-          <t>CURRENT (0d)</t>
+          <t>CURRENT (1d)</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -2992,11 +2992,11 @@
         </is>
       </c>
       <c r="I22" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J22" s="4" t="inlineStr">
         <is>
-          <t>CURRENT (2d)</t>
+          <t>CURRENT (3d)</t>
         </is>
       </c>
       <c r="K22" s="2" t="inlineStr">
@@ -3107,11 +3107,11 @@
         </is>
       </c>
       <c r="I23" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J23" s="4" t="inlineStr">
         <is>
-          <t>CURRENT (3d)</t>
+          <t>CURRENT (4d)</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
@@ -3222,11 +3222,11 @@
         </is>
       </c>
       <c r="I24" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J24" s="4" t="inlineStr">
         <is>
-          <t>CURRENT (0d)</t>
+          <t>CURRENT (1d)</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
@@ -3337,11 +3337,11 @@
         </is>
       </c>
       <c r="I25" s="2" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="J25" s="5" t="inlineStr">
         <is>
-          <t>DUE (14d, cadence weekly)</t>
+          <t>DUE (15d, cadence weekly)</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
@@ -3452,11 +3452,11 @@
         </is>
       </c>
       <c r="I26" s="2" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="J26" s="5" t="inlineStr">
         <is>
-          <t>DUE (59d, cadence monthly)</t>
+          <t>DUE (60d, cadence monthly)</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
@@ -3567,11 +3567,11 @@
         </is>
       </c>
       <c r="I27" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J27" s="4" t="inlineStr">
         <is>
-          <t>CURRENT (3d)</t>
+          <t>CURRENT (4d)</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr"/>
@@ -3678,11 +3678,11 @@
         </is>
       </c>
       <c r="I28" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J28" s="4" t="inlineStr">
         <is>
-          <t>CURRENT (0d)</t>
+          <t>CURRENT (1d)</t>
         </is>
       </c>
       <c r="K28" s="2" t="inlineStr"/>
@@ -3789,11 +3789,11 @@
         </is>
       </c>
       <c r="I29" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J29" s="4" t="inlineStr">
         <is>
-          <t>CURRENT (1d)</t>
+          <t>CURRENT (2d)</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
@@ -3904,11 +3904,11 @@
         </is>
       </c>
       <c r="I30" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J30" s="4" t="inlineStr">
         <is>
-          <t>CURRENT (0d)</t>
+          <t>CURRENT (1d)</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
@@ -4019,11 +4019,11 @@
         </is>
       </c>
       <c r="I31" s="2" t="n">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="J31" s="6" t="inlineStr">
         <is>
-          <t>STALE (94d, cadence monthly)</t>
+          <t>STALE (95d, cadence monthly)</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
@@ -4130,11 +4130,11 @@
         </is>
       </c>
       <c r="I32" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="J32" s="4" t="inlineStr">
         <is>
-          <t>CURRENT (7d)</t>
+          <t>CURRENT (8d)</t>
         </is>
       </c>
       <c r="K32" s="2" t="inlineStr">
